--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX140"/>
+  <dimension ref="A1:DW140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,11 +1079,6 @@
       </c>
       <c r="DW1" t="inlineStr">
         <is>
-          <t>Worcester</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
           <t>ROW_TOTAL</t>
         </is>
       </c>
@@ -1470,9 +1465,6 @@
         <v>105</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
         <v>3913</v>
       </c>
     </row>
@@ -1858,9 +1850,6 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX3" t="n">
         <v>3042</v>
       </c>
     </row>
@@ -2246,9 +2235,6 @@
         <v>90</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX4" t="n">
         <v>3428</v>
       </c>
     </row>
@@ -2634,9 +2620,6 @@
         <v>145</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX5" t="n">
         <v>6856</v>
       </c>
     </row>
@@ -3022,9 +3005,6 @@
         <v>80</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
         <v>4864</v>
       </c>
     </row>
@@ -3083,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1581</v>
+        <v>1606</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -3410,9 +3390,6 @@
         <v>120</v>
       </c>
       <c r="DW7" t="n">
-        <v>25</v>
-      </c>
-      <c r="DX7" t="n">
         <v>4418</v>
       </c>
     </row>
@@ -3798,9 +3775,6 @@
         <v>105</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
         <v>4482</v>
       </c>
     </row>
@@ -4186,9 +4160,6 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX9" t="n">
         <v>5047</v>
       </c>
     </row>
@@ -4574,9 +4545,6 @@
         <v>170</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
         <v>5877</v>
       </c>
     </row>
@@ -4962,9 +4930,6 @@
         <v>95</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX11" t="n">
         <v>4120</v>
       </c>
     </row>
@@ -5350,9 +5315,6 @@
         <v>112</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX12" t="n">
         <v>5336</v>
       </c>
     </row>
@@ -5411,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2077</v>
+        <v>2092</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -5738,9 +5700,6 @@
         <v>60</v>
       </c>
       <c r="DW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX13" t="n">
         <v>5301</v>
       </c>
     </row>
@@ -6126,9 +6085,6 @@
         <v>145</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX14" t="n">
         <v>4432</v>
       </c>
     </row>
@@ -6514,9 +6470,6 @@
         <v>80</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX15" t="n">
         <v>6308</v>
       </c>
     </row>
@@ -6902,9 +6855,6 @@
         <v>200</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
         <v>5676</v>
       </c>
     </row>
@@ -7290,9 +7240,6 @@
         <v>100</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX17" t="n">
         <v>6593</v>
       </c>
     </row>
@@ -7678,9 +7625,6 @@
         <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX18" t="n">
         <v>7082</v>
       </c>
     </row>
@@ -8066,9 +8010,6 @@
         <v>265</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX19" t="n">
         <v>10586</v>
       </c>
     </row>
@@ -8454,9 +8395,6 @@
         <v>80</v>
       </c>
       <c r="DW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX20" t="n">
         <v>13147</v>
       </c>
     </row>
@@ -8842,9 +8780,6 @@
         <v>110</v>
       </c>
       <c r="DW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX21" t="n">
         <v>7916</v>
       </c>
     </row>
@@ -9230,9 +9165,6 @@
         <v>265</v>
       </c>
       <c r="DW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX22" t="n">
         <v>8012</v>
       </c>
     </row>
@@ -9618,9 +9550,6 @@
         <v>175</v>
       </c>
       <c r="DW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX23" t="n">
         <v>8118</v>
       </c>
     </row>
@@ -10006,9 +9935,6 @@
         <v>155</v>
       </c>
       <c r="DW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX24" t="n">
         <v>6385</v>
       </c>
     </row>
@@ -10394,9 +10320,6 @@
         <v>100</v>
       </c>
       <c r="DW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX25" t="n">
         <v>6113</v>
       </c>
     </row>
@@ -10782,9 +10705,6 @@
         <v>275</v>
       </c>
       <c r="DW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX26" t="n">
         <v>9614</v>
       </c>
     </row>
@@ -11170,9 +11090,6 @@
         <v>135</v>
       </c>
       <c r="DW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX27" t="n">
         <v>7109</v>
       </c>
     </row>
@@ -11558,9 +11475,6 @@
         <v>120</v>
       </c>
       <c r="DW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX28" t="n">
         <v>8471</v>
       </c>
     </row>
@@ -11946,9 +11860,6 @@
         <v>255</v>
       </c>
       <c r="DW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX29" t="n">
         <v>7500</v>
       </c>
     </row>
@@ -12334,9 +12245,6 @@
         <v>115</v>
       </c>
       <c r="DW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX30" t="n">
         <v>9528</v>
       </c>
     </row>
@@ -12722,9 +12630,6 @@
         <v>125</v>
       </c>
       <c r="DW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX31" t="n">
         <v>10630</v>
       </c>
     </row>
@@ -13110,9 +13015,6 @@
         <v>245</v>
       </c>
       <c r="DW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX32" t="n">
         <v>10874</v>
       </c>
     </row>
@@ -13498,9 +13400,6 @@
         <v>150</v>
       </c>
       <c r="DW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX33" t="n">
         <v>10666</v>
       </c>
     </row>
@@ -13886,9 +13785,6 @@
         <v>250</v>
       </c>
       <c r="DW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX34" t="n">
         <v>12456</v>
       </c>
     </row>
@@ -14274,9 +14170,6 @@
         <v>130</v>
       </c>
       <c r="DW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX35" t="n">
         <v>13691</v>
       </c>
     </row>
@@ -14662,9 +14555,6 @@
         <v>360</v>
       </c>
       <c r="DW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX36" t="n">
         <v>8648</v>
       </c>
     </row>
@@ -15050,9 +14940,6 @@
         <v>90</v>
       </c>
       <c r="DW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX37" t="n">
         <v>6784</v>
       </c>
     </row>
@@ -15438,9 +15325,6 @@
         <v>100</v>
       </c>
       <c r="DW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX38" t="n">
         <v>8568</v>
       </c>
     </row>
@@ -15826,9 +15710,6 @@
         <v>340</v>
       </c>
       <c r="DW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX39" t="n">
         <v>11377</v>
       </c>
     </row>
@@ -16214,9 +16095,6 @@
         <v>230</v>
       </c>
       <c r="DW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX40" t="n">
         <v>13755</v>
       </c>
     </row>
@@ -16602,9 +16480,6 @@
         <v>200</v>
       </c>
       <c r="DW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX41" t="n">
         <v>15131</v>
       </c>
     </row>
@@ -16663,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3763</v>
+        <v>3788</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -16990,9 +16865,6 @@
         <v>295</v>
       </c>
       <c r="DW42" t="n">
-        <v>25</v>
-      </c>
-      <c r="DX42" t="n">
         <v>14730</v>
       </c>
     </row>
@@ -17378,9 +17250,6 @@
         <v>150</v>
       </c>
       <c r="DW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX43" t="n">
         <v>12610</v>
       </c>
     </row>
@@ -17766,9 +17635,6 @@
         <v>120</v>
       </c>
       <c r="DW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX44" t="n">
         <v>17534</v>
       </c>
     </row>
@@ -18154,9 +18020,6 @@
         <v>235</v>
       </c>
       <c r="DW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX45" t="n">
         <v>13384</v>
       </c>
     </row>
@@ -18542,9 +18405,6 @@
         <v>405</v>
       </c>
       <c r="DW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX46" t="n">
         <v>12785</v>
       </c>
     </row>
@@ -18930,9 +18790,6 @@
         <v>290</v>
       </c>
       <c r="DW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX47" t="n">
         <v>16316</v>
       </c>
     </row>
@@ -19318,9 +19175,6 @@
         <v>250</v>
       </c>
       <c r="DW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX48" t="n">
         <v>12160</v>
       </c>
     </row>
@@ -19706,9 +19560,6 @@
         <v>240</v>
       </c>
       <c r="DW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX49" t="n">
         <v>12983</v>
       </c>
     </row>
@@ -20094,9 +19945,6 @@
         <v>215</v>
       </c>
       <c r="DW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX50" t="n">
         <v>11689</v>
       </c>
     </row>
@@ -20482,9 +20330,6 @@
         <v>185</v>
       </c>
       <c r="DW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX51" t="n">
         <v>14564</v>
       </c>
     </row>
@@ -20870,9 +20715,6 @@
         <v>360</v>
       </c>
       <c r="DW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX52" t="n">
         <v>15290</v>
       </c>
     </row>
@@ -21258,9 +21100,6 @@
         <v>390</v>
       </c>
       <c r="DW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX53" t="n">
         <v>14760</v>
       </c>
     </row>
@@ -21646,9 +21485,6 @@
         <v>325</v>
       </c>
       <c r="DW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX54" t="n">
         <v>17060</v>
       </c>
     </row>
@@ -22034,9 +21870,6 @@
         <v>250</v>
       </c>
       <c r="DW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX55" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -22422,9 +22255,6 @@
         <v>575</v>
       </c>
       <c r="DW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX56" t="n">
         <v>16605</v>
       </c>
     </row>
@@ -22810,9 +22640,6 @@
         <v>0</v>
       </c>
       <c r="DW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX57" t="n">
         <v>12257</v>
       </c>
     </row>
@@ -23198,9 +23025,6 @@
         <v>230</v>
       </c>
       <c r="DW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX58" t="n">
         <v>13805</v>
       </c>
     </row>
@@ -23586,9 +23410,6 @@
         <v>225</v>
       </c>
       <c r="DW59" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX59" t="n">
         <v>17125</v>
       </c>
     </row>
@@ -23974,9 +23795,6 @@
         <v>0</v>
       </c>
       <c r="DW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX60" t="n">
         <v>14217</v>
       </c>
     </row>
@@ -24362,9 +24180,6 @@
         <v>490</v>
       </c>
       <c r="DW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX61" t="n">
         <v>13660</v>
       </c>
     </row>
@@ -24750,9 +24565,6 @@
         <v>160</v>
       </c>
       <c r="DW62" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX62" t="n">
         <v>13706</v>
       </c>
     </row>
@@ -25138,9 +24950,6 @@
         <v>175</v>
       </c>
       <c r="DW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX63" t="n">
         <v>12776</v>
       </c>
     </row>
@@ -25199,7 +25008,7 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2510</v>
+        <v>2525</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -25526,9 +25335,6 @@
         <v>270</v>
       </c>
       <c r="DW64" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX64" t="n">
         <v>14345</v>
       </c>
     </row>
@@ -25914,9 +25720,6 @@
         <v>0</v>
       </c>
       <c r="DW65" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX65" t="n">
         <v>15526</v>
       </c>
     </row>
@@ -26302,9 +26105,6 @@
         <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX66" t="n">
         <v>5925</v>
       </c>
     </row>
@@ -26690,9 +26490,6 @@
         <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX67" t="n">
         <v>11805</v>
       </c>
     </row>
@@ -27078,9 +26875,6 @@
         <v>350</v>
       </c>
       <c r="DW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX68" t="n">
         <v>12175</v>
       </c>
     </row>
@@ -27466,9 +27260,6 @@
         <v>200</v>
       </c>
       <c r="DW69" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX69" t="n">
         <v>9840</v>
       </c>
     </row>
@@ -27854,9 +27645,6 @@
         <v>470</v>
       </c>
       <c r="DW70" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX70" t="n">
         <v>12013</v>
       </c>
     </row>
@@ -28242,9 +28030,6 @@
         <v>0</v>
       </c>
       <c r="DW71" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX71" t="n">
         <v>12670</v>
       </c>
     </row>
@@ -28630,9 +28415,6 @@
         <v>325</v>
       </c>
       <c r="DW72" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX72" t="n">
         <v>11765</v>
       </c>
     </row>
@@ -29018,9 +28800,6 @@
         <v>145</v>
       </c>
       <c r="DW73" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX73" t="n">
         <v>14015</v>
       </c>
     </row>
@@ -29406,9 +29185,6 @@
         <v>90</v>
       </c>
       <c r="DW74" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX74" t="n">
         <v>11560</v>
       </c>
     </row>
@@ -29794,9 +29570,6 @@
         <v>0</v>
       </c>
       <c r="DW75" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX75" t="n">
         <v>8840</v>
       </c>
     </row>
@@ -30182,9 +29955,6 @@
         <v>0</v>
       </c>
       <c r="DW76" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX76" t="n">
         <v>11850</v>
       </c>
     </row>
@@ -30570,9 +30340,6 @@
         <v>0</v>
       </c>
       <c r="DW77" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX77" t="n">
         <v>9130</v>
       </c>
     </row>
@@ -30958,9 +30725,6 @@
         <v>450</v>
       </c>
       <c r="DW78" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX78" t="n">
         <v>13910</v>
       </c>
     </row>
@@ -31346,9 +31110,6 @@
         <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX79" t="n">
         <v>16004</v>
       </c>
     </row>
@@ -31734,9 +31495,6 @@
         <v>280</v>
       </c>
       <c r="DW80" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX80" t="n">
         <v>15277</v>
       </c>
     </row>
@@ -32122,9 +31880,6 @@
         <v>375</v>
       </c>
       <c r="DW81" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX81" t="n">
         <v>18620</v>
       </c>
     </row>
@@ -32510,9 +32265,6 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX82" t="n">
         <v>13578</v>
       </c>
     </row>
@@ -32571,7 +32323,7 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2505</v>
+        <v>2525</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -32898,9 +32650,6 @@
         <v>170</v>
       </c>
       <c r="DW83" t="n">
-        <v>20</v>
-      </c>
-      <c r="DX83" t="n">
         <v>15190</v>
       </c>
     </row>
@@ -33286,9 +33035,6 @@
         <v>0</v>
       </c>
       <c r="DW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX84" t="n">
         <v>16001</v>
       </c>
     </row>
@@ -33674,9 +33420,6 @@
         <v>215</v>
       </c>
       <c r="DW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX85" t="n">
         <v>17947</v>
       </c>
     </row>
@@ -34062,9 +33805,6 @@
         <v>0</v>
       </c>
       <c r="DW86" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX86" t="n">
         <v>9626</v>
       </c>
     </row>
@@ -34450,9 +34190,6 @@
         <v>95</v>
       </c>
       <c r="DW87" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX87" t="n">
         <v>13102</v>
       </c>
     </row>
@@ -34838,9 +34575,6 @@
         <v>100</v>
       </c>
       <c r="DW88" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX88" t="n">
         <v>22746</v>
       </c>
     </row>
@@ -35226,9 +34960,6 @@
         <v>0</v>
       </c>
       <c r="DW89" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX89" t="n">
         <v>21050</v>
       </c>
     </row>
@@ -35614,9 +35345,6 @@
         <v>140</v>
       </c>
       <c r="DW90" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX90" t="n">
         <v>17690</v>
       </c>
     </row>
@@ -36002,9 +35730,6 @@
         <v>170</v>
       </c>
       <c r="DW91" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX91" t="n">
         <v>18845</v>
       </c>
     </row>
@@ -36390,9 +36115,6 @@
         <v>240</v>
       </c>
       <c r="DW92" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX92" t="n">
         <v>18167</v>
       </c>
     </row>
@@ -36778,9 +36500,6 @@
         <v>265</v>
       </c>
       <c r="DW93" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX93" t="n">
         <v>23259</v>
       </c>
     </row>
@@ -37166,9 +36885,6 @@
         <v>120</v>
       </c>
       <c r="DW94" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX94" t="n">
         <v>23761</v>
       </c>
     </row>
@@ -37554,9 +37270,6 @@
         <v>440</v>
       </c>
       <c r="DW95" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX95" t="n">
         <v>20768</v>
       </c>
     </row>
@@ -37615,7 +37328,7 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3658</v>
+        <v>3678</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -37942,9 +37655,6 @@
         <v>185</v>
       </c>
       <c r="DW96" t="n">
-        <v>20</v>
-      </c>
-      <c r="DX96" t="n">
         <v>20799</v>
       </c>
     </row>
@@ -38330,9 +38040,6 @@
         <v>0</v>
       </c>
       <c r="DW97" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX97" t="n">
         <v>16576</v>
       </c>
     </row>
@@ -38718,9 +38425,6 @@
         <v>200</v>
       </c>
       <c r="DW98" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX98" t="n">
         <v>16360</v>
       </c>
     </row>
@@ -39106,9 +38810,6 @@
         <v>40</v>
       </c>
       <c r="DW99" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX99" t="n">
         <v>21630</v>
       </c>
     </row>
@@ -39494,9 +39195,6 @@
         <v>90</v>
       </c>
       <c r="DW100" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX100" t="n">
         <v>20500</v>
       </c>
     </row>
@@ -39882,9 +39580,6 @@
         <v>325</v>
       </c>
       <c r="DW101" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX101" t="n">
         <v>19064</v>
       </c>
     </row>
@@ -40270,9 +39965,6 @@
         <v>0</v>
       </c>
       <c r="DW102" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX102" t="n">
         <v>21982</v>
       </c>
     </row>
@@ -40658,9 +40350,6 @@
         <v>187</v>
       </c>
       <c r="DW103" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX103" t="n">
         <v>24960</v>
       </c>
     </row>
@@ -41046,9 +40735,6 @@
         <v>150</v>
       </c>
       <c r="DW104" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX104" t="n">
         <v>18055</v>
       </c>
     </row>
@@ -41434,9 +41120,6 @@
         <v>445</v>
       </c>
       <c r="DW105" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX105" t="n">
         <v>24501</v>
       </c>
     </row>
@@ -41822,9 +41505,6 @@
         <v>0</v>
       </c>
       <c r="DW106" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX106" t="n">
         <v>17565</v>
       </c>
     </row>
@@ -42210,9 +41890,6 @@
         <v>620</v>
       </c>
       <c r="DW107" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX107" t="n">
         <v>23263</v>
       </c>
     </row>
@@ -42598,9 +42275,6 @@
         <v>280</v>
       </c>
       <c r="DW108" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX108" t="n">
         <v>18300</v>
       </c>
     </row>
@@ -42986,9 +42660,6 @@
         <v>260</v>
       </c>
       <c r="DW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX109" t="n">
         <v>18226</v>
       </c>
     </row>
@@ -43374,9 +43045,6 @@
         <v>255</v>
       </c>
       <c r="DW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX110" t="n">
         <v>19982</v>
       </c>
     </row>
@@ -43762,9 +43430,6 @@
         <v>390</v>
       </c>
       <c r="DW111" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX111" t="n">
         <v>21041</v>
       </c>
     </row>
@@ -44150,9 +43815,6 @@
         <v>200</v>
       </c>
       <c r="DW112" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX112" t="n">
         <v>20551</v>
       </c>
     </row>
@@ -44538,9 +44200,6 @@
         <v>390</v>
       </c>
       <c r="DW113" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX113" t="n">
         <v>25985</v>
       </c>
     </row>
@@ -44926,9 +44585,6 @@
         <v>210</v>
       </c>
       <c r="DW114" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX114" t="n">
         <v>20431</v>
       </c>
     </row>
@@ -45314,9 +44970,6 @@
         <v>390</v>
       </c>
       <c r="DW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX115" t="n">
         <v>22304</v>
       </c>
     </row>
@@ -45702,9 +45355,6 @@
         <v>160</v>
       </c>
       <c r="DW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX116" t="n">
         <v>24250</v>
       </c>
     </row>
@@ -46090,9 +45740,6 @@
         <v>520</v>
       </c>
       <c r="DW117" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX117" t="n">
         <v>21683</v>
       </c>
     </row>
@@ -46478,9 +46125,6 @@
         <v>70</v>
       </c>
       <c r="DW118" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX118" t="n">
         <v>23851</v>
       </c>
     </row>
@@ -46539,7 +46183,7 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>5018</v>
+        <v>5028</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -46866,9 +46510,6 @@
         <v>510</v>
       </c>
       <c r="DW119" t="n">
-        <v>10</v>
-      </c>
-      <c r="DX119" t="n">
         <v>22607</v>
       </c>
     </row>
@@ -47254,9 +46895,6 @@
         <v>470</v>
       </c>
       <c r="DW120" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX120" t="n">
         <v>20266</v>
       </c>
     </row>
@@ -47642,9 +47280,6 @@
         <v>135</v>
       </c>
       <c r="DW121" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX121" t="n">
         <v>20384</v>
       </c>
     </row>
@@ -48030,9 +47665,6 @@
         <v>95</v>
       </c>
       <c r="DW122" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX122" t="n">
         <v>19150</v>
       </c>
     </row>
@@ -48418,9 +48050,6 @@
         <v>165</v>
       </c>
       <c r="DW123" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX123" t="n">
         <v>18144</v>
       </c>
     </row>
@@ -48806,9 +48435,6 @@
         <v>350</v>
       </c>
       <c r="DW124" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX124" t="n">
         <v>26985</v>
       </c>
     </row>
@@ -49194,9 +48820,6 @@
         <v>60</v>
       </c>
       <c r="DW125" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX125" t="n">
         <v>27151</v>
       </c>
     </row>
@@ -49582,9 +49205,6 @@
         <v>115</v>
       </c>
       <c r="DW126" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX126" t="n">
         <v>20765</v>
       </c>
     </row>
@@ -49970,9 +49590,6 @@
         <v>282</v>
       </c>
       <c r="DW127" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX127" t="n">
         <v>23443</v>
       </c>
     </row>
@@ -50358,9 +49975,6 @@
         <v>485</v>
       </c>
       <c r="DW128" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX128" t="n">
         <v>22680</v>
       </c>
     </row>
@@ -50746,9 +50360,6 @@
         <v>350</v>
       </c>
       <c r="DW129" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX129" t="n">
         <v>25127</v>
       </c>
     </row>
@@ -51134,9 +50745,6 @@
         <v>130</v>
       </c>
       <c r="DW130" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX130" t="n">
         <v>25506</v>
       </c>
     </row>
@@ -51522,9 +51130,6 @@
         <v>372</v>
       </c>
       <c r="DW131" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX131" t="n">
         <v>21978</v>
       </c>
     </row>
@@ -51910,9 +51515,6 @@
         <v>445</v>
       </c>
       <c r="DW132" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX132" t="n">
         <v>20167</v>
       </c>
     </row>
@@ -52298,9 +51900,6 @@
         <v>185</v>
       </c>
       <c r="DW133" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX133" t="n">
         <v>18881</v>
       </c>
     </row>
@@ -52686,9 +52285,6 @@
         <v>240</v>
       </c>
       <c r="DW134" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX134" t="n">
         <v>22058</v>
       </c>
     </row>
@@ -53074,9 +52670,6 @@
         <v>185</v>
       </c>
       <c r="DW135" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX135" t="n">
         <v>20695</v>
       </c>
     </row>
@@ -53462,9 +53055,6 @@
         <v>335</v>
       </c>
       <c r="DW136" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX136" t="n">
         <v>25977</v>
       </c>
     </row>
@@ -53850,9 +53440,6 @@
         <v>250</v>
       </c>
       <c r="DW137" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX137" t="n">
         <v>27829</v>
       </c>
     </row>
@@ -53911,7 +53498,7 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="S138" t="n">
         <v>65</v>
@@ -54103,7 +53690,7 @@
         <v>0</v>
       </c>
       <c r="CD138" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="CE138" t="n">
         <v>138</v>
@@ -54238,9 +53825,6 @@
         <v>150</v>
       </c>
       <c r="DW138" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX138" t="n">
         <v>20343</v>
       </c>
     </row>
@@ -54260,7 +53844,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -54299,7 +53883,7 @@
         <v>35</v>
       </c>
       <c r="R139" t="n">
-        <v>4164</v>
+        <v>4514</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -54317,7 +53901,7 @@
         <v>120</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
@@ -54329,7 +53913,7 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -54362,7 +53946,7 @@
         <v>0</v>
       </c>
       <c r="AM139" t="n">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="AN139" t="n">
         <v>90</v>
@@ -54434,7 +54018,7 @@
         <v>50</v>
       </c>
       <c r="BK139" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BL139" t="n">
         <v>260</v>
@@ -54452,7 +54036,7 @@
         <v>0</v>
       </c>
       <c r="BQ139" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="BR139" t="n">
         <v>215</v>
@@ -54491,10 +54075,10 @@
         <v>0</v>
       </c>
       <c r="CD139" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="CE139" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="CF139" t="n">
         <v>0</v>
@@ -54533,13 +54117,13 @@
         <v>0</v>
       </c>
       <c r="CR139" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CS139" t="n">
         <v>0</v>
       </c>
       <c r="CT139" t="n">
-        <v>310</v>
+        <v>640</v>
       </c>
       <c r="CU139" t="n">
         <v>75</v>
@@ -54551,25 +54135,25 @@
         <v>0</v>
       </c>
       <c r="CX139" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="CY139" t="n">
         <v>64</v>
       </c>
       <c r="CZ139" t="n">
-        <v>165</v>
+        <v>495</v>
       </c>
       <c r="DA139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB139" t="n">
-        <v>795</v>
+        <v>1610</v>
       </c>
       <c r="DC139" t="n">
         <v>0</v>
       </c>
       <c r="DD139" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="DE139" t="n">
         <v>0</v>
@@ -54587,7 +54171,7 @@
         <v>205</v>
       </c>
       <c r="DJ139" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="DK139" t="n">
         <v>200</v>
@@ -54611,7 +54195,7 @@
         <v>0</v>
       </c>
       <c r="DR139" t="n">
-        <v>700</v>
+        <v>923</v>
       </c>
       <c r="DS139" t="n">
         <v>0</v>
@@ -54626,10 +54210,7 @@
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX139" t="n">
-        <v>22927</v>
+        <v>26657</v>
       </c>
     </row>
     <row r="140">
@@ -54648,7 +54229,7 @@
         <v>150</v>
       </c>
       <c r="E140" t="n">
-        <v>71345</v>
+        <v>71465</v>
       </c>
       <c r="F140" t="n">
         <v>500</v>
@@ -54687,7 +54268,7 @@
         <v>107</v>
       </c>
       <c r="R140" t="n">
-        <v>428686</v>
+        <v>429168</v>
       </c>
       <c r="S140" t="n">
         <v>925</v>
@@ -54705,7 +54286,7 @@
         <v>23953</v>
       </c>
       <c r="X140" t="n">
-        <v>4542</v>
+        <v>4712</v>
       </c>
       <c r="Y140" t="n">
         <v>2947</v>
@@ -54717,7 +54298,7 @@
         <v>2</v>
       </c>
       <c r="AB140" t="n">
-        <v>8979</v>
+        <v>9129</v>
       </c>
       <c r="AC140" t="n">
         <v>212</v>
@@ -54750,7 +54331,7 @@
         <v>374</v>
       </c>
       <c r="AM140" t="n">
-        <v>50594</v>
+        <v>50659</v>
       </c>
       <c r="AN140" t="n">
         <v>4755</v>
@@ -54822,7 +54403,7 @@
         <v>1007</v>
       </c>
       <c r="BK140" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="BL140" t="n">
         <v>47345</v>
@@ -54840,7 +54421,7 @@
         <v>7365</v>
       </c>
       <c r="BQ140" t="n">
-        <v>94080</v>
+        <v>94095</v>
       </c>
       <c r="BR140" t="n">
         <v>22072</v>
@@ -54879,10 +54460,10 @@
         <v>435</v>
       </c>
       <c r="CD140" t="n">
-        <v>15275</v>
+        <v>15373</v>
       </c>
       <c r="CE140" t="n">
-        <v>5629</v>
+        <v>5771</v>
       </c>
       <c r="CF140" t="n">
         <v>145</v>
@@ -54921,13 +54502,13 @@
         <v>277</v>
       </c>
       <c r="CR140" t="n">
-        <v>11874</v>
+        <v>11904</v>
       </c>
       <c r="CS140" t="n">
         <v>2</v>
       </c>
       <c r="CT140" t="n">
-        <v>64775</v>
+        <v>65105</v>
       </c>
       <c r="CU140" t="n">
         <v>2384</v>
@@ -54939,25 +54520,25 @@
         <v>2698</v>
       </c>
       <c r="CX140" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="CY140" t="n">
         <v>8936</v>
       </c>
       <c r="CZ140" t="n">
-        <v>18166</v>
+        <v>18496</v>
       </c>
       <c r="DA140" t="n">
-        <v>13716</v>
+        <v>13766</v>
       </c>
       <c r="DB140" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
       <c r="DC140" t="n">
         <v>1030</v>
       </c>
       <c r="DD140" t="n">
-        <v>1281</v>
+        <v>1351</v>
       </c>
       <c r="DE140" t="n">
         <v>1485</v>
@@ -54975,7 +54556,7 @@
         <v>23863</v>
       </c>
       <c r="DJ140" t="n">
-        <v>99229</v>
+        <v>99974</v>
       </c>
       <c r="DK140" t="n">
         <v>1240</v>
@@ -54999,7 +54580,7 @@
         <v>7725</v>
       </c>
       <c r="DR140" t="n">
-        <v>57518</v>
+        <v>57741</v>
       </c>
       <c r="DS140" t="n">
         <v>1450</v>
@@ -55014,10 +54595,7 @@
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>130</v>
-      </c>
-      <c r="DX140" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -55350,10 +54928,10 @@
         <v>1497</v>
       </c>
       <c r="N6" t="n">
-        <v>3363</v>
+        <v>3388</v>
       </c>
       <c r="O6" t="n">
-        <v>9190</v>
+        <v>9215</v>
       </c>
     </row>
     <row r="7">
@@ -55742,10 +55320,10 @@
         <v>21112</v>
       </c>
       <c r="N14" t="n">
-        <v>41697</v>
+        <v>41722</v>
       </c>
       <c r="O14" t="n">
-        <v>117677</v>
+        <v>117702</v>
       </c>
     </row>
   </sheetData>
@@ -56708,10 +56286,10 @@
         <v>1165</v>
       </c>
       <c r="N4" t="n">
-        <v>2510</v>
+        <v>2525</v>
       </c>
       <c r="O4" t="n">
-        <v>9695</v>
+        <v>9710</v>
       </c>
     </row>
     <row r="5">
@@ -57198,10 +56776,10 @@
         <v>15805</v>
       </c>
       <c r="N14" t="n">
-        <v>23257</v>
+        <v>23272</v>
       </c>
       <c r="O14" t="n">
-        <v>90008</v>
+        <v>90023</v>
       </c>
     </row>
   </sheetData>
@@ -57779,10 +57357,10 @@
         <v>2095</v>
       </c>
       <c r="N11" t="n">
-        <v>2355</v>
+        <v>2375</v>
       </c>
       <c r="O11" t="n">
-        <v>10435</v>
+        <v>10455</v>
       </c>
     </row>
     <row r="12">
@@ -57926,10 +57504,10 @@
         <v>18542</v>
       </c>
       <c r="N14" t="n">
-        <v>26144</v>
+        <v>26164</v>
       </c>
       <c r="O14" t="n">
-        <v>102866</v>
+        <v>102886</v>
       </c>
     </row>
   </sheetData>
@@ -58556,10 +58134,10 @@
         <v>2384</v>
       </c>
       <c r="N12" t="n">
-        <v>3088</v>
+        <v>3108</v>
       </c>
       <c r="O12" t="n">
-        <v>12143</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="13">
@@ -58654,10 +58232,10 @@
         <v>22238</v>
       </c>
       <c r="N14" t="n">
-        <v>34219</v>
+        <v>34239</v>
       </c>
       <c r="O14" t="n">
-        <v>125343</v>
+        <v>125363</v>
       </c>
     </row>
   </sheetData>
@@ -59963,10 +59541,10 @@
         <v>1554</v>
       </c>
       <c r="N11" t="n">
-        <v>4468</v>
+        <v>4478</v>
       </c>
       <c r="O11" t="n">
-        <v>12972</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="12">
@@ -60110,10 +59688,10 @@
         <v>27438</v>
       </c>
       <c r="N14" t="n">
-        <v>39604</v>
+        <v>39614</v>
       </c>
       <c r="O14" t="n">
-        <v>158260</v>
+        <v>158270</v>
       </c>
     </row>
   </sheetData>
@@ -61174,10 +60752,10 @@
         <v>2564</v>
       </c>
       <c r="N6" t="n">
-        <v>3220</v>
+        <v>3222</v>
       </c>
       <c r="O6" t="n">
-        <v>12471</v>
+        <v>12473</v>
       </c>
     </row>
     <row r="7">
@@ -61187,10 +60765,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>795</v>
+        <v>1610</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="D7" t="n">
         <v>425</v>
@@ -61220,13 +60798,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>780</v>
+        <v>915</v>
       </c>
       <c r="N7" t="n">
-        <v>4164</v>
+        <v>4514</v>
       </c>
       <c r="O7" t="n">
-        <v>8349</v>
+        <v>10394</v>
       </c>
     </row>
     <row r="8">
@@ -61236,10 +60814,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12965</v>
+        <v>13780</v>
       </c>
       <c r="C8" t="n">
-        <v>4720</v>
+        <v>5465</v>
       </c>
       <c r="D8" t="n">
         <v>5000</v>
@@ -61269,13 +60847,13 @@
         <v>2690</v>
       </c>
       <c r="M8" t="n">
-        <v>12326</v>
+        <v>12461</v>
       </c>
       <c r="N8" t="n">
-        <v>20805</v>
+        <v>21157</v>
       </c>
       <c r="O8" t="n">
-        <v>81134</v>
+        <v>83181</v>
       </c>
     </row>
   </sheetData>
@@ -62681,7 +62259,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>795</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="140">
@@ -62691,7 +62269,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
     </row>
     <row r="142">
@@ -62799,7 +62377,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>12965</v>
+        <v>13780</v>
       </c>
     </row>
     <row r="155">
@@ -62809,7 +62387,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
     </row>
   </sheetData>
@@ -63244,7 +62822,7 @@
         <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>1946</v>
+        <v>1971</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -63277,7 +62855,7 @@
         <v>30</v>
       </c>
       <c r="P7" t="n">
-        <v>1257</v>
+        <v>1232</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -63610,7 +63188,7 @@
         <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>2615</v>
+        <v>2630</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -63643,7 +63221,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -65379,7 +64957,7 @@
         <v>485</v>
       </c>
       <c r="E42" t="n">
-        <v>7768</v>
+        <v>7793</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -65412,7 +64990,7 @@
         <v>275</v>
       </c>
       <c r="P42" t="n">
-        <v>2517</v>
+        <v>2492</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -66721,7 +66299,7 @@
         <v>990</v>
       </c>
       <c r="E64" t="n">
-        <v>4360</v>
+        <v>4375</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -66754,7 +66332,7 @@
         <v>165</v>
       </c>
       <c r="P64" t="n">
-        <v>3350</v>
+        <v>3335</v>
       </c>
       <c r="Q64" t="n">
         <v>925</v>
@@ -67880,7 +67458,7 @@
         <v>110</v>
       </c>
       <c r="E83" t="n">
-        <v>5573</v>
+        <v>5593</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -67898,13 +67476,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1070</v>
+        <v>990</v>
       </c>
       <c r="L83" t="n">
         <v>205</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -67913,7 +67491,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3777</v>
+        <v>3757</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -67959,13 +67537,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L84" t="n">
         <v>155</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -68020,13 +67598,13 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>991</v>
+        <v>891</v>
       </c>
       <c r="L85" t="n">
         <v>210</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N85" t="n">
         <v>25</v>
@@ -68142,13 +67720,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1425</v>
+        <v>1395</v>
       </c>
       <c r="L87" t="n">
         <v>260</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -68203,13 +67781,13 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>405</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
@@ -68264,13 +67842,13 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>2100</v>
+        <v>1920</v>
       </c>
       <c r="L89" t="n">
         <v>210</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -68325,13 +67903,13 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>205</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -68447,13 +68025,13 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="L92" t="n">
         <v>415</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -68508,13 +68086,13 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1360</v>
+        <v>1290</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -68630,13 +68208,13 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="L95" t="n">
         <v>367</v>
       </c>
       <c r="M95" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -68673,7 +68251,7 @@
         <v>515</v>
       </c>
       <c r="E96" t="n">
-        <v>7375</v>
+        <v>7395</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -68706,7 +68284,7 @@
         <v>352</v>
       </c>
       <c r="P96" t="n">
-        <v>4034</v>
+        <v>4014</v>
       </c>
       <c r="Q96" t="n">
         <v>210</v>
@@ -68813,13 +68391,13 @@
         <v>85</v>
       </c>
       <c r="K98" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>354</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -68935,13 +68513,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="L100" t="n">
         <v>284</v>
       </c>
       <c r="M100" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -69057,13 +68635,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="n">
-        <v>745</v>
+        <v>675</v>
       </c>
       <c r="L102" t="n">
         <v>313</v>
       </c>
       <c r="M102" t="n">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -69118,13 +68696,13 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>1847</v>
+        <v>1780</v>
       </c>
       <c r="L103" t="n">
         <v>440</v>
       </c>
       <c r="M103" t="n">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -69301,13 +68879,13 @@
         <v>163</v>
       </c>
       <c r="K106" t="n">
-        <v>862</v>
+        <v>762</v>
       </c>
       <c r="L106" t="n">
         <v>378</v>
       </c>
       <c r="M106" t="n">
-        <v>128</v>
+        <v>228</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
@@ -69423,13 +69001,13 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1015</v>
+        <v>955</v>
       </c>
       <c r="L108" t="n">
         <v>439</v>
       </c>
       <c r="M108" t="n">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
@@ -69606,13 +69184,13 @@
         <v>45</v>
       </c>
       <c r="K111" t="n">
-        <v>2026</v>
+        <v>1936</v>
       </c>
       <c r="L111" t="n">
         <v>414</v>
       </c>
       <c r="M111" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -69850,13 +69428,13 @@
         <v>90</v>
       </c>
       <c r="K115" t="n">
-        <v>1005</v>
+        <v>940</v>
       </c>
       <c r="L115" t="n">
         <v>629</v>
       </c>
       <c r="M115" t="n">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -69972,13 +69550,13 @@
         <v>302</v>
       </c>
       <c r="K117" t="n">
-        <v>1050</v>
+        <v>910</v>
       </c>
       <c r="L117" t="n">
         <v>464</v>
       </c>
       <c r="M117" t="n">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -70076,7 +69654,7 @@
         <v>830</v>
       </c>
       <c r="E119" t="n">
-        <v>11966</v>
+        <v>11976</v>
       </c>
       <c r="F119" t="n">
         <v>197</v>
@@ -70094,13 +69672,13 @@
         <v>100</v>
       </c>
       <c r="K119" t="n">
-        <v>1449</v>
+        <v>1364</v>
       </c>
       <c r="L119" t="n">
         <v>506</v>
       </c>
       <c r="M119" t="n">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -70109,7 +69687,7 @@
         <v>165</v>
       </c>
       <c r="P119" t="n">
-        <v>3254</v>
+        <v>3244</v>
       </c>
       <c r="Q119" t="n">
         <v>270</v>
@@ -70216,13 +69794,13 @@
         <v>255</v>
       </c>
       <c r="K121" t="n">
-        <v>1608</v>
+        <v>1518</v>
       </c>
       <c r="L121" t="n">
         <v>394</v>
       </c>
       <c r="M121" t="n">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -70399,13 +69977,13 @@
         <v>144</v>
       </c>
       <c r="K124" t="n">
-        <v>2475</v>
+        <v>2385</v>
       </c>
       <c r="L124" t="n">
         <v>308</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -70521,13 +70099,13 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>148</v>
+        <v>268</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
@@ -70643,13 +70221,13 @@
         <v>135</v>
       </c>
       <c r="K128" t="n">
-        <v>1005</v>
+        <v>870</v>
       </c>
       <c r="L128" t="n">
         <v>282</v>
       </c>
       <c r="M128" t="n">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -70826,13 +70404,13 @@
         <v>411</v>
       </c>
       <c r="K131" t="n">
-        <v>1779</v>
+        <v>1624</v>
       </c>
       <c r="L131" t="n">
         <v>240</v>
       </c>
       <c r="M131" t="n">
-        <v>149</v>
+        <v>304</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -70948,13 +70526,13 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>1923</v>
+        <v>1803</v>
       </c>
       <c r="L133" t="n">
         <v>277</v>
       </c>
       <c r="M133" t="n">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -71070,13 +70648,13 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1795</v>
+        <v>1710</v>
       </c>
       <c r="L135" t="n">
         <v>250</v>
       </c>
       <c r="M135" t="n">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -71192,13 +70770,13 @@
         <v>314</v>
       </c>
       <c r="K137" t="n">
-        <v>3060</v>
+        <v>2965</v>
       </c>
       <c r="L137" t="n">
         <v>708</v>
       </c>
       <c r="M137" t="n">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -71235,7 +70813,7 @@
         <v>935</v>
       </c>
       <c r="E138" t="n">
-        <v>6856</v>
+        <v>6858</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -71268,7 +70846,7 @@
         <v>70</v>
       </c>
       <c r="P138" t="n">
-        <v>4756</v>
+        <v>4754</v>
       </c>
       <c r="Q138" t="n">
         <v>127</v>
@@ -71293,22 +70871,22 @@
         <v>255</v>
       </c>
       <c r="D139" t="n">
-        <v>290</v>
+        <v>670</v>
       </c>
       <c r="E139" t="n">
-        <v>16175</v>
+        <v>17173</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>339</v>
+        <v>754</v>
       </c>
       <c r="H139" t="n">
         <v>75</v>
       </c>
       <c r="I139" t="n">
-        <v>1090</v>
+        <v>1905</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -71320,7 +70898,7 @@
         <v>269</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -71329,7 +70907,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>1600</v>
+        <v>2580</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -71338,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>22927</v>
+        <v>26657</v>
       </c>
     </row>
     <row r="140">
@@ -71354,34 +70932,34 @@
         <v>17331</v>
       </c>
       <c r="D140" t="n">
-        <v>61678</v>
+        <v>62058</v>
       </c>
       <c r="E140" t="n">
-        <v>850112</v>
+        <v>851242</v>
       </c>
       <c r="F140" t="n">
         <v>5932</v>
       </c>
       <c r="G140" t="n">
-        <v>33600</v>
+        <v>34015</v>
       </c>
       <c r="H140" t="n">
         <v>7499</v>
       </c>
       <c r="I140" t="n">
-        <v>282329</v>
+        <v>283144</v>
       </c>
       <c r="J140" t="n">
         <v>4939</v>
       </c>
       <c r="K140" t="n">
-        <v>111442</v>
+        <v>109060</v>
       </c>
       <c r="L140" t="n">
         <v>35385</v>
       </c>
       <c r="M140" t="n">
-        <v>5629</v>
+        <v>8153</v>
       </c>
       <c r="N140" t="n">
         <v>42</v>
@@ -71390,7 +70968,7 @@
         <v>22052</v>
       </c>
       <c r="P140" t="n">
-        <v>419016</v>
+        <v>419864</v>
       </c>
       <c r="Q140" t="n">
         <v>36635</v>
@@ -71399,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -71413,7 +70991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72801,129 +72379,139 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>99229</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="B140" t="n">
+        <v>99974</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B142" t="n">
-        <v>4620</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B143" t="n">
-        <v>9287</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B144" t="n">
-        <v>9052</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B145" t="n">
-        <v>11885</v>
+        <v>9052</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B146" t="n">
-        <v>10945</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B147" t="n">
-        <v>5985</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B148" t="n">
-        <v>7702</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B149" t="n">
-        <v>7774</v>
+        <v>7702</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B150" t="n">
-        <v>7025</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B151" t="n">
-        <v>9804</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B152" t="n">
-        <v>10430</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B153" t="n">
+        <v>10430</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
         <v>2026</v>
       </c>
-      <c r="B153" t="n">
-        <v>4720</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="B154" t="n">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>99229</v>
+      <c r="B155" t="n">
+        <v>99974</v>
       </c>
     </row>
   </sheetData>
@@ -82985,7 +82573,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1581</v>
+        <v>1606</v>
       </c>
       <c r="C7" t="n">
         <v>830</v>
@@ -83006,7 +82594,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>765</v>
+        <v>740</v>
       </c>
       <c r="J7" t="n">
         <v>470</v>
@@ -83297,7 +82885,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2077</v>
+        <v>2092</v>
       </c>
       <c r="C13" t="n">
         <v>482</v>
@@ -83318,7 +82906,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="J13" t="n">
         <v>865</v>
@@ -84805,7 +84393,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3363</v>
+        <v>3388</v>
       </c>
       <c r="C42" t="n">
         <v>1497</v>
@@ -84826,7 +84414,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>5540</v>
+        <v>5515</v>
       </c>
       <c r="J42" t="n">
         <v>1015</v>
@@ -85949,7 +85537,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2510</v>
+        <v>2525</v>
       </c>
       <c r="C64" t="n">
         <v>1165</v>
@@ -85970,7 +85558,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>4650</v>
+        <v>4635</v>
       </c>
       <c r="J64" t="n">
         <v>1725</v>
@@ -86937,7 +86525,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2355</v>
+        <v>2375</v>
       </c>
       <c r="C83" t="n">
         <v>2095</v>
@@ -86958,7 +86546,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>4755</v>
+        <v>4735</v>
       </c>
       <c r="J83" t="n">
         <v>2140</v>
@@ -87613,7 +87201,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3088</v>
+        <v>3108</v>
       </c>
       <c r="C96" t="n">
         <v>2384</v>
@@ -87634,7 +87222,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>8656</v>
+        <v>8636</v>
       </c>
       <c r="J96" t="n">
         <v>2140</v>
@@ -88809,7 +88397,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4468</v>
+        <v>4478</v>
       </c>
       <c r="C119" t="n">
         <v>1554</v>
@@ -88830,7 +88418,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>9635</v>
+        <v>9625</v>
       </c>
       <c r="J119" t="n">
         <v>1110</v>
@@ -89797,7 +89385,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3220</v>
+        <v>3222</v>
       </c>
       <c r="C138" t="n">
         <v>2564</v>
@@ -89818,7 +89406,7 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>7872</v>
+        <v>7870</v>
       </c>
       <c r="J138" t="n">
         <v>1720</v>
@@ -89849,10 +89437,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4164</v>
+        <v>4514</v>
       </c>
       <c r="C139" t="n">
-        <v>780</v>
+        <v>915</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89870,10 +89458,10 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>14578</v>
+        <v>16263</v>
       </c>
       <c r="J139" t="n">
-        <v>795</v>
+        <v>1610</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -89882,7 +89470,7 @@
         <v>425</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="N139" t="n">
         <v>405</v>
@@ -89891,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>22927</v>
+        <v>26657</v>
       </c>
     </row>
     <row r="140">
@@ -89901,10 +89489,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396026</v>
+        <v>396508</v>
       </c>
       <c r="C140" t="n">
-        <v>221351</v>
+        <v>221486</v>
       </c>
       <c r="D140" t="n">
         <v>58168</v>
@@ -89922,10 +89510,10 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>741698</v>
+        <v>743251</v>
       </c>
       <c r="J140" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
       <c r="K140" t="n">
         <v>32660</v>
@@ -89934,7 +89522,7 @@
         <v>61344</v>
       </c>
       <c r="M140" t="n">
-        <v>99229</v>
+        <v>99974</v>
       </c>
       <c r="N140" t="n">
         <v>70576</v>
@@ -89943,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -91349,7 +90937,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>780</v>
+        <v>915</v>
       </c>
     </row>
     <row r="140">
@@ -91359,7 +90947,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>221351</v>
+        <v>221486</v>
       </c>
     </row>
     <row r="142">
@@ -91467,7 +91055,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>12326</v>
+        <v>12461</v>
       </c>
     </row>
     <row r="155">
@@ -91477,7 +91065,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>221351</v>
+        <v>221486</v>
       </c>
     </row>
   </sheetData>
@@ -91563,7 +91151,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1581</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="8">
@@ -91623,7 +91211,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2077</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="14">
@@ -91913,7 +91501,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3363</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="43">
@@ -92133,7 +91721,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2510</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="65">
@@ -92323,7 +91911,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2355</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="84">
@@ -92453,7 +92041,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3088</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="97">
@@ -92683,7 +92271,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4468</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="120">
@@ -92873,7 +92461,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3220</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="139">
@@ -92883,7 +92471,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4164</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="140">
@@ -92893,7 +92481,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396026</v>
+        <v>396508</v>
       </c>
     </row>
     <row r="142">
@@ -92913,7 +92501,7 @@
         <v>2015</v>
       </c>
       <c r="B143" t="n">
-        <v>21247</v>
+        <v>21287</v>
       </c>
     </row>
     <row r="144">
@@ -92937,7 +92525,7 @@
         <v>2018</v>
       </c>
       <c r="B146" t="n">
-        <v>41697</v>
+        <v>41722</v>
       </c>
     </row>
     <row r="147">
@@ -92953,7 +92541,7 @@
         <v>2020</v>
       </c>
       <c r="B148" t="n">
-        <v>23257</v>
+        <v>23272</v>
       </c>
     </row>
     <row r="149">
@@ -92961,7 +92549,7 @@
         <v>2021</v>
       </c>
       <c r="B149" t="n">
-        <v>26144</v>
+        <v>26164</v>
       </c>
     </row>
     <row r="150">
@@ -92969,7 +92557,7 @@
         <v>2022</v>
       </c>
       <c r="B150" t="n">
-        <v>34219</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="151">
@@ -92985,7 +92573,7 @@
         <v>2024</v>
       </c>
       <c r="B152" t="n">
-        <v>39604</v>
+        <v>39614</v>
       </c>
     </row>
     <row r="153">
@@ -93001,7 +92589,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>20805</v>
+        <v>21157</v>
       </c>
     </row>
     <row r="155">
@@ -93011,7 +92599,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>396026</v>
+        <v>396508</v>
       </c>
     </row>
   </sheetData>
@@ -93025,7 +92613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX14"/>
+  <dimension ref="A1:DW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93661,11 +93249,6 @@
       </c>
       <c r="DW1" t="inlineStr">
         <is>
-          <t>Worcester</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
           <t>ROW_TOTAL</t>
         </is>
       </c>
@@ -93723,7 +93306,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>21247</v>
+        <v>21287</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -94050,9 +93633,6 @@
         <v>1082</v>
       </c>
       <c r="DW2" t="n">
-        <v>40</v>
-      </c>
-      <c r="DX2" t="n">
         <v>56684</v>
       </c>
     </row>
@@ -94436,9 +94016,6 @@
         <v>1675</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX3" t="n">
         <v>90368</v>
       </c>
     </row>
@@ -94822,9 +94399,6 @@
         <v>2250</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX4" t="n">
         <v>115971</v>
       </c>
     </row>
@@ -94881,7 +94455,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>45252</v>
+        <v>45277</v>
       </c>
       <c r="S5" t="n">
         <v>175</v>
@@ -95208,9 +94782,6 @@
         <v>2855</v>
       </c>
       <c r="DW5" t="n">
-        <v>25</v>
-      </c>
-      <c r="DX5" t="n">
         <v>161333</v>
       </c>
     </row>
@@ -95594,9 +95165,6 @@
         <v>3245</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
         <v>176032</v>
       </c>
     </row>
@@ -95653,7 +95221,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>25877</v>
+        <v>25892</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -95980,9 +95548,6 @@
         <v>2095</v>
       </c>
       <c r="DW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="DX7" t="n">
         <v>146561</v>
       </c>
     </row>
@@ -96039,7 +95604,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>28879</v>
+        <v>28899</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -96366,9 +95931,6 @@
         <v>1580</v>
       </c>
       <c r="DW8" t="n">
-        <v>20</v>
-      </c>
-      <c r="DX8" t="n">
         <v>167907</v>
       </c>
     </row>
@@ -96425,7 +95987,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>37809</v>
+        <v>37829</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -96752,9 +96314,6 @@
         <v>1755</v>
       </c>
       <c r="DW9" t="n">
-        <v>20</v>
-      </c>
-      <c r="DX9" t="n">
         <v>226389</v>
       </c>
     </row>
@@ -97138,9 +96697,6 @@
         <v>2597</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
         <v>244406</v>
       </c>
     </row>
@@ -97197,7 +96753,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>44579</v>
+        <v>44589</v>
       </c>
       <c r="S11" t="n">
         <v>85</v>
@@ -97524,9 +97080,6 @@
         <v>3700</v>
       </c>
       <c r="DW11" t="n">
-        <v>10</v>
-      </c>
-      <c r="DX11" t="n">
         <v>263335</v>
       </c>
     </row>
@@ -97910,9 +97463,6 @@
         <v>3034</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX12" t="n">
         <v>269977</v>
       </c>
     </row>
@@ -97930,7 +97480,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3950</v>
+        <v>4070</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97969,7 +97519,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>23250</v>
+        <v>23602</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -97987,7 +97537,7 @@
         <v>1960</v>
       </c>
       <c r="X13" t="n">
-        <v>550</v>
+        <v>720</v>
       </c>
       <c r="Y13" t="n">
         <v>95</v>
@@ -97999,7 +97549,7 @@
         <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>665</v>
+        <v>815</v>
       </c>
       <c r="AC13" t="n">
         <v>210</v>
@@ -98032,7 +97582,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>2051</v>
+        <v>2116</v>
       </c>
       <c r="AN13" t="n">
         <v>165</v>
@@ -98104,7 +97654,7 @@
         <v>320</v>
       </c>
       <c r="BK13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BL13" t="n">
         <v>2541</v>
@@ -98122,7 +97672,7 @@
         <v>335</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4942</v>
+        <v>4957</v>
       </c>
       <c r="BR13" t="n">
         <v>1510</v>
@@ -98161,10 +97711,10 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>1537</v>
+        <v>1635</v>
       </c>
       <c r="CE13" t="n">
-        <v>714</v>
+        <v>856</v>
       </c>
       <c r="CF13" t="n">
         <v>30</v>
@@ -98203,13 +97753,13 @@
         <v>0</v>
       </c>
       <c r="CR13" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="CS13" t="n">
         <v>2</v>
       </c>
       <c r="CT13" t="n">
-        <v>4045</v>
+        <v>4375</v>
       </c>
       <c r="CU13" t="n">
         <v>925</v>
@@ -98221,25 +97771,25 @@
         <v>80</v>
       </c>
       <c r="CX13" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="CY13" t="n">
         <v>190</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1860</v>
+        <v>2190</v>
       </c>
       <c r="DA13" t="n">
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="DB13" t="n">
-        <v>12965</v>
+        <v>13780</v>
       </c>
       <c r="DC13" t="n">
         <v>30</v>
       </c>
       <c r="DD13" t="n">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -98257,7 +97807,7 @@
         <v>2195</v>
       </c>
       <c r="DJ13" t="n">
-        <v>4720</v>
+        <v>5465</v>
       </c>
       <c r="DK13" t="n">
         <v>420</v>
@@ -98281,7 +97831,7 @@
         <v>395</v>
       </c>
       <c r="DR13" t="n">
-        <v>4223</v>
+        <v>4446</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -98296,10 +97846,7 @@
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>139829</v>
+        <v>143559</v>
       </c>
     </row>
     <row r="14">
@@ -98318,7 +97865,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>71345</v>
+        <v>71465</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98357,7 +97904,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>428686</v>
+        <v>429168</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98375,7 +97922,7 @@
         <v>23953</v>
       </c>
       <c r="X14" t="n">
-        <v>4542</v>
+        <v>4712</v>
       </c>
       <c r="Y14" t="n">
         <v>2947</v>
@@ -98387,7 +97934,7 @@
         <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>8979</v>
+        <v>9129</v>
       </c>
       <c r="AC14" t="n">
         <v>212</v>
@@ -98420,7 +97967,7 @@
         <v>374</v>
       </c>
       <c r="AM14" t="n">
-        <v>50594</v>
+        <v>50659</v>
       </c>
       <c r="AN14" t="n">
         <v>4755</v>
@@ -98492,7 +98039,7 @@
         <v>1007</v>
       </c>
       <c r="BK14" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="BL14" t="n">
         <v>47345</v>
@@ -98510,7 +98057,7 @@
         <v>7365</v>
       </c>
       <c r="BQ14" t="n">
-        <v>94080</v>
+        <v>94095</v>
       </c>
       <c r="BR14" t="n">
         <v>22072</v>
@@ -98549,10 +98096,10 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>15275</v>
+        <v>15373</v>
       </c>
       <c r="CE14" t="n">
-        <v>5629</v>
+        <v>5771</v>
       </c>
       <c r="CF14" t="n">
         <v>145</v>
@@ -98591,13 +98138,13 @@
         <v>277</v>
       </c>
       <c r="CR14" t="n">
-        <v>11874</v>
+        <v>11904</v>
       </c>
       <c r="CS14" t="n">
         <v>2</v>
       </c>
       <c r="CT14" t="n">
-        <v>64775</v>
+        <v>65105</v>
       </c>
       <c r="CU14" t="n">
         <v>2384</v>
@@ -98609,25 +98156,25 @@
         <v>2698</v>
       </c>
       <c r="CX14" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="CY14" t="n">
         <v>8936</v>
       </c>
       <c r="CZ14" t="n">
-        <v>18166</v>
+        <v>18496</v>
       </c>
       <c r="DA14" t="n">
-        <v>13716</v>
+        <v>13766</v>
       </c>
       <c r="DB14" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
       <c r="DC14" t="n">
         <v>1030</v>
       </c>
       <c r="DD14" t="n">
-        <v>1281</v>
+        <v>1351</v>
       </c>
       <c r="DE14" t="n">
         <v>1485</v>
@@ -98645,7 +98192,7 @@
         <v>23863</v>
       </c>
       <c r="DJ14" t="n">
-        <v>99229</v>
+        <v>99974</v>
       </c>
       <c r="DK14" t="n">
         <v>1240</v>
@@ -98669,7 +98216,7 @@
         <v>7725</v>
       </c>
       <c r="DR14" t="n">
-        <v>57518</v>
+        <v>57741</v>
       </c>
       <c r="DS14" t="n">
         <v>1450</v>
@@ -98684,10 +98231,7 @@
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>130</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -98815,7 +98359,7 @@
         <v>840</v>
       </c>
       <c r="E2" t="n">
-        <v>25851</v>
+        <v>25891</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -98848,7 +98392,7 @@
         <v>327</v>
       </c>
       <c r="P2" t="n">
-        <v>12980</v>
+        <v>12940</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -98992,7 +98536,7 @@
         <v>4090</v>
       </c>
       <c r="E5" t="n">
-        <v>71642</v>
+        <v>71667</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -99025,7 +98569,7 @@
         <v>1915</v>
       </c>
       <c r="P5" t="n">
-        <v>38452</v>
+        <v>38427</v>
       </c>
       <c r="Q5" t="n">
         <v>2850</v>
@@ -99110,7 +98654,7 @@
         <v>7463</v>
       </c>
       <c r="E7" t="n">
-        <v>57878</v>
+        <v>57893</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -99143,7 +98687,7 @@
         <v>1455</v>
       </c>
       <c r="P7" t="n">
-        <v>29055</v>
+        <v>29040</v>
       </c>
       <c r="Q7" t="n">
         <v>2250</v>
@@ -99169,7 +98713,7 @@
         <v>5949</v>
       </c>
       <c r="E8" t="n">
-        <v>64998</v>
+        <v>65018</v>
       </c>
       <c r="F8" t="n">
         <v>1141</v>
@@ -99187,13 +98731,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7521</v>
+        <v>7266</v>
       </c>
       <c r="L8" t="n">
         <v>3015</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="N8" t="n">
         <v>25</v>
@@ -99202,7 +98746,7 @@
         <v>1090</v>
       </c>
       <c r="P8" t="n">
-        <v>35089</v>
+        <v>35069</v>
       </c>
       <c r="Q8" t="n">
         <v>3365</v>
@@ -99228,7 +98772,7 @@
         <v>8150</v>
       </c>
       <c r="E9" t="n">
-        <v>95265</v>
+        <v>95285</v>
       </c>
       <c r="F9" t="n">
         <v>1875</v>
@@ -99246,13 +98790,13 @@
         <v>94</v>
       </c>
       <c r="K9" t="n">
-        <v>10425</v>
+        <v>9985</v>
       </c>
       <c r="L9" t="n">
         <v>3855</v>
       </c>
       <c r="M9" t="n">
-        <v>618</v>
+        <v>1058</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -99261,7 +98805,7 @@
         <v>3273</v>
       </c>
       <c r="P9" t="n">
-        <v>40897</v>
+        <v>40877</v>
       </c>
       <c r="Q9" t="n">
         <v>4700</v>
@@ -99305,13 +98849,13 @@
         <v>498</v>
       </c>
       <c r="K10" t="n">
-        <v>12017</v>
+        <v>11600</v>
       </c>
       <c r="L10" t="n">
         <v>3155</v>
       </c>
       <c r="M10" t="n">
-        <v>1039</v>
+        <v>1456</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -99346,7 +98890,7 @@
         <v>8374</v>
       </c>
       <c r="E11" t="n">
-        <v>104799</v>
+        <v>104809</v>
       </c>
       <c r="F11" t="n">
         <v>714</v>
@@ -99364,13 +98908,13 @@
         <v>1970</v>
       </c>
       <c r="K11" t="n">
-        <v>13887</v>
+        <v>13417</v>
       </c>
       <c r="L11" t="n">
         <v>5151</v>
       </c>
       <c r="M11" t="n">
-        <v>1429</v>
+        <v>1899</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -99379,7 +98923,7 @@
         <v>2692</v>
       </c>
       <c r="P11" t="n">
-        <v>50534</v>
+        <v>50524</v>
       </c>
       <c r="Q11" t="n">
         <v>6476</v>
@@ -99423,13 +98967,13 @@
         <v>1465</v>
       </c>
       <c r="K12" t="n">
-        <v>17019</v>
+        <v>16399</v>
       </c>
       <c r="L12" t="n">
         <v>3284</v>
       </c>
       <c r="M12" t="n">
-        <v>1829</v>
+        <v>2449</v>
       </c>
       <c r="N12" t="n">
         <v>17</v>
@@ -99461,34 +99005,34 @@
         <v>2075</v>
       </c>
       <c r="D13" t="n">
-        <v>4400</v>
+        <v>4780</v>
       </c>
       <c r="E13" t="n">
-        <v>58520</v>
+        <v>59520</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
       </c>
       <c r="G13" t="n">
-        <v>2410</v>
+        <v>2825</v>
       </c>
       <c r="H13" t="n">
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>17431</v>
+        <v>18246</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
       </c>
       <c r="K13" t="n">
-        <v>8943</v>
+        <v>8763</v>
       </c>
       <c r="L13" t="n">
         <v>2177</v>
       </c>
       <c r="M13" t="n">
-        <v>714</v>
+        <v>1036</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -99497,7 +99041,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>24365</v>
+        <v>25343</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99506,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>139829</v>
+        <v>143559</v>
       </c>
     </row>
     <row r="14">
@@ -99522,34 +99066,34 @@
         <v>17331</v>
       </c>
       <c r="D14" t="n">
-        <v>61678</v>
+        <v>62058</v>
       </c>
       <c r="E14" t="n">
-        <v>850112</v>
+        <v>851242</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
       </c>
       <c r="G14" t="n">
-        <v>33600</v>
+        <v>34015</v>
       </c>
       <c r="H14" t="n">
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>282329</v>
+        <v>283144</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
       </c>
       <c r="K14" t="n">
-        <v>111442</v>
+        <v>109060</v>
       </c>
       <c r="L14" t="n">
         <v>35385</v>
       </c>
       <c r="M14" t="n">
-        <v>5629</v>
+        <v>8153</v>
       </c>
       <c r="N14" t="n">
         <v>42</v>
@@ -99558,7 +99102,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>419016</v>
+        <v>419864</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99567,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -99671,7 +99215,7 @@
         <v>2015</v>
       </c>
       <c r="B2" t="n">
-        <v>21247</v>
+        <v>21287</v>
       </c>
       <c r="C2" t="n">
         <v>6670</v>
@@ -99692,7 +99236,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8126</v>
+        <v>8086</v>
       </c>
       <c r="J2" t="n">
         <v>6885</v>
@@ -99821,7 +99365,7 @@
         <v>2018</v>
       </c>
       <c r="B5" t="n">
-        <v>41697</v>
+        <v>41722</v>
       </c>
       <c r="C5" t="n">
         <v>21112</v>
@@ -99842,7 +99386,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>43656</v>
+        <v>43631</v>
       </c>
       <c r="J5" t="n">
         <v>13913</v>
@@ -99921,7 +99465,7 @@
         <v>2020</v>
       </c>
       <c r="B7" t="n">
-        <v>23257</v>
+        <v>23272</v>
       </c>
       <c r="C7" t="n">
         <v>15805</v>
@@ -99942,7 +99486,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>56553</v>
+        <v>56538</v>
       </c>
       <c r="J7" t="n">
         <v>17285</v>
@@ -99971,7 +99515,7 @@
         <v>2021</v>
       </c>
       <c r="B8" t="n">
-        <v>26144</v>
+        <v>26164</v>
       </c>
       <c r="C8" t="n">
         <v>18542</v>
@@ -99992,7 +99536,7 @@
         <v>825</v>
       </c>
       <c r="I8" t="n">
-        <v>65041</v>
+        <v>65021</v>
       </c>
       <c r="J8" t="n">
         <v>21884</v>
@@ -100021,7 +99565,7 @@
         <v>2022</v>
       </c>
       <c r="B9" t="n">
-        <v>34219</v>
+        <v>34239</v>
       </c>
       <c r="C9" t="n">
         <v>22238</v>
@@ -100042,7 +99586,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>101046</v>
+        <v>101026</v>
       </c>
       <c r="J9" t="n">
         <v>25698</v>
@@ -100121,7 +99665,7 @@
         <v>2024</v>
       </c>
       <c r="B11" t="n">
-        <v>39604</v>
+        <v>39614</v>
       </c>
       <c r="C11" t="n">
         <v>27438</v>
@@ -100142,7 +99686,7 @@
         <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>105075</v>
+        <v>105065</v>
       </c>
       <c r="J11" t="n">
         <v>26942</v>
@@ -100221,10 +99765,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>20805</v>
+        <v>21157</v>
       </c>
       <c r="C13" t="n">
-        <v>12326</v>
+        <v>12461</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -100242,10 +99786,10 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>58695</v>
+        <v>60378</v>
       </c>
       <c r="J13" t="n">
-        <v>12965</v>
+        <v>13780</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -100254,7 +99798,7 @@
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>4720</v>
+        <v>5465</v>
       </c>
       <c r="N13" t="n">
         <v>4790</v>
@@ -100263,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>139829</v>
+        <v>143559</v>
       </c>
     </row>
     <row r="14">
@@ -100273,10 +99817,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>396026</v>
+        <v>396508</v>
       </c>
       <c r="C14" t="n">
-        <v>221351</v>
+        <v>221486</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -100294,10 +99838,10 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>741698</v>
+        <v>743251</v>
       </c>
       <c r="J14" t="n">
-        <v>217038</v>
+        <v>217853</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -100306,7 +99850,7 @@
         <v>61344</v>
       </c>
       <c r="M14" t="n">
-        <v>99229</v>
+        <v>99974</v>
       </c>
       <c r="N14" t="n">
         <v>70576</v>
@@ -100315,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2058792</v>
+        <v>2062522</v>
       </c>
     </row>
   </sheetData>
@@ -100697,10 +100241,10 @@
         <v>830</v>
       </c>
       <c r="N7" t="n">
-        <v>1581</v>
+        <v>1606</v>
       </c>
       <c r="O7" t="n">
-        <v>3653</v>
+        <v>3678</v>
       </c>
     </row>
     <row r="8">
@@ -100991,10 +100535,10 @@
         <v>482</v>
       </c>
       <c r="N13" t="n">
-        <v>2077</v>
+        <v>2092</v>
       </c>
       <c r="O13" t="n">
-        <v>4513</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="14">
@@ -101040,10 +100584,10 @@
         <v>6670</v>
       </c>
       <c r="N14" t="n">
-        <v>21247</v>
+        <v>21287</v>
       </c>
       <c r="O14" t="n">
-        <v>48558</v>
+        <v>48598</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53844,7 +53844,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>250</v>
+        <v>812</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -53958,7 +53958,7 @@
         <v>0</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR139" t="n">
         <v>0</v>
@@ -53976,7 +53976,7 @@
         <v>0</v>
       </c>
       <c r="AW139" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AX139" t="n">
         <v>0</v>
@@ -54027,7 +54027,7 @@
         <v>0</v>
       </c>
       <c r="BN139" t="n">
-        <v>10256</v>
+        <v>13556</v>
       </c>
       <c r="BO139" t="n">
         <v>0</v>
@@ -54042,7 +54042,7 @@
         <v>215</v>
       </c>
       <c r="BS139" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BT139" t="n">
         <v>225</v>
@@ -54204,13 +54204,13 @@
         <v>405</v>
       </c>
       <c r="DU139" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="DV139" t="n">
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>26657</v>
+        <v>30814</v>
       </c>
     </row>
     <row r="140">
@@ -54229,7 +54229,7 @@
         <v>150</v>
       </c>
       <c r="E140" t="n">
-        <v>71465</v>
+        <v>72027</v>
       </c>
       <c r="F140" t="n">
         <v>500</v>
@@ -54343,7 +54343,7 @@
         <v>277</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1979</v>
+        <v>2009</v>
       </c>
       <c r="AR140" t="n">
         <v>387</v>
@@ -54361,7 +54361,7 @@
         <v>2627</v>
       </c>
       <c r="AW140" t="n">
-        <v>6789</v>
+        <v>6939</v>
       </c>
       <c r="AX140" t="n">
         <v>5655</v>
@@ -54412,7 +54412,7 @@
         <v>1992</v>
       </c>
       <c r="BN140" t="n">
-        <v>109239</v>
+        <v>112539</v>
       </c>
       <c r="BO140" t="n">
         <v>4080</v>
@@ -54427,7 +54427,7 @@
         <v>22072</v>
       </c>
       <c r="BS140" t="n">
-        <v>13174</v>
+        <v>13249</v>
       </c>
       <c r="BT140" t="n">
         <v>26576</v>
@@ -54589,13 +54589,13 @@
         <v>70576</v>
       </c>
       <c r="DU140" t="n">
-        <v>4887</v>
+        <v>4927</v>
       </c>
       <c r="DV140" t="n">
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>
@@ -60798,13 +60798,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>915</v>
+        <v>1477</v>
       </c>
       <c r="N7" t="n">
         <v>4514</v>
       </c>
       <c r="O7" t="n">
-        <v>10394</v>
+        <v>10956</v>
       </c>
     </row>
     <row r="8">
@@ -60847,13 +60847,13 @@
         <v>2690</v>
       </c>
       <c r="M8" t="n">
-        <v>12461</v>
+        <v>13023</v>
       </c>
       <c r="N8" t="n">
         <v>21157</v>
       </c>
       <c r="O8" t="n">
-        <v>83181</v>
+        <v>83743</v>
       </c>
     </row>
   </sheetData>
@@ -70874,7 +70874,7 @@
         <v>670</v>
       </c>
       <c r="E139" t="n">
-        <v>17173</v>
+        <v>20473</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -70886,7 +70886,7 @@
         <v>75</v>
       </c>
       <c r="I139" t="n">
-        <v>1905</v>
+        <v>2170</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -70907,7 +70907,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>2580</v>
+        <v>3172</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -70916,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>26657</v>
+        <v>30814</v>
       </c>
     </row>
     <row r="140">
@@ -70935,7 +70935,7 @@
         <v>62058</v>
       </c>
       <c r="E140" t="n">
-        <v>851242</v>
+        <v>854542</v>
       </c>
       <c r="F140" t="n">
         <v>5932</v>
@@ -70947,7 +70947,7 @@
         <v>7499</v>
       </c>
       <c r="I140" t="n">
-        <v>283144</v>
+        <v>283409</v>
       </c>
       <c r="J140" t="n">
         <v>4939</v>
@@ -70968,7 +70968,7 @@
         <v>22052</v>
       </c>
       <c r="P140" t="n">
-        <v>419864</v>
+        <v>420456</v>
       </c>
       <c r="Q140" t="n">
         <v>36635</v>
@@ -70977,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>
@@ -89440,7 +89440,7 @@
         <v>4514</v>
       </c>
       <c r="C139" t="n">
-        <v>915</v>
+        <v>1477</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89458,7 +89458,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>16263</v>
+        <v>19858</v>
       </c>
       <c r="J139" t="n">
         <v>1610</v>
@@ -89479,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>26657</v>
+        <v>30814</v>
       </c>
     </row>
     <row r="140">
@@ -89492,7 +89492,7 @@
         <v>396508</v>
       </c>
       <c r="C140" t="n">
-        <v>221486</v>
+        <v>222048</v>
       </c>
       <c r="D140" t="n">
         <v>58168</v>
@@ -89510,7 +89510,7 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>743251</v>
+        <v>746846</v>
       </c>
       <c r="J140" t="n">
         <v>217853</v>
@@ -89531,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>
@@ -90937,7 +90937,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>915</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="140">
@@ -90947,7 +90947,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>221486</v>
+        <v>222048</v>
       </c>
     </row>
     <row r="142">
@@ -91055,7 +91055,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>12461</v>
+        <v>13023</v>
       </c>
     </row>
     <row r="155">
@@ -91065,7 +91065,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>221486</v>
+        <v>222048</v>
       </c>
     </row>
   </sheetData>
@@ -97480,7 +97480,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4070</v>
+        <v>4632</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97594,7 +97594,7 @@
         <v>110</v>
       </c>
       <c r="AQ13" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AR13" t="n">
         <v>35</v>
@@ -97612,7 +97612,7 @@
         <v>265</v>
       </c>
       <c r="AW13" t="n">
-        <v>290</v>
+        <v>440</v>
       </c>
       <c r="AX13" t="n">
         <v>355</v>
@@ -97663,7 +97663,7 @@
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>15632</v>
+        <v>18932</v>
       </c>
       <c r="BO13" t="n">
         <v>235</v>
@@ -97678,7 +97678,7 @@
         <v>1510</v>
       </c>
       <c r="BS13" t="n">
-        <v>804</v>
+        <v>879</v>
       </c>
       <c r="BT13" t="n">
         <v>2882</v>
@@ -97840,13 +97840,13 @@
         <v>4790</v>
       </c>
       <c r="DU13" t="n">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="DV13" t="n">
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>143559</v>
+        <v>147716</v>
       </c>
     </row>
     <row r="14">
@@ -97865,7 +97865,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>71465</v>
+        <v>72027</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -97979,7 +97979,7 @@
         <v>277</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1979</v>
+        <v>2009</v>
       </c>
       <c r="AR14" t="n">
         <v>387</v>
@@ -97997,7 +97997,7 @@
         <v>2627</v>
       </c>
       <c r="AW14" t="n">
-        <v>6789</v>
+        <v>6939</v>
       </c>
       <c r="AX14" t="n">
         <v>5655</v>
@@ -98048,7 +98048,7 @@
         <v>1992</v>
       </c>
       <c r="BN14" t="n">
-        <v>109239</v>
+        <v>112539</v>
       </c>
       <c r="BO14" t="n">
         <v>4080</v>
@@ -98063,7 +98063,7 @@
         <v>22072</v>
       </c>
       <c r="BS14" t="n">
-        <v>13174</v>
+        <v>13249</v>
       </c>
       <c r="BT14" t="n">
         <v>26576</v>
@@ -98225,13 +98225,13 @@
         <v>70576</v>
       </c>
       <c r="DU14" t="n">
-        <v>4887</v>
+        <v>4927</v>
       </c>
       <c r="DV14" t="n">
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>
@@ -99008,7 +99008,7 @@
         <v>4780</v>
       </c>
       <c r="E13" t="n">
-        <v>59520</v>
+        <v>62820</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99020,7 +99020,7 @@
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>18246</v>
+        <v>18511</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99041,7 +99041,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>25343</v>
+        <v>25935</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99050,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>143559</v>
+        <v>147716</v>
       </c>
     </row>
     <row r="14">
@@ -99069,7 +99069,7 @@
         <v>62058</v>
       </c>
       <c r="E14" t="n">
-        <v>851242</v>
+        <v>854542</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99081,7 +99081,7 @@
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>283144</v>
+        <v>283409</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99102,7 +99102,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>419864</v>
+        <v>420456</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99111,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>
@@ -99768,7 +99768,7 @@
         <v>21157</v>
       </c>
       <c r="C13" t="n">
-        <v>12461</v>
+        <v>13023</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -99786,7 +99786,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>60378</v>
+        <v>63973</v>
       </c>
       <c r="J13" t="n">
         <v>13780</v>
@@ -99807,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>143559</v>
+        <v>147716</v>
       </c>
     </row>
     <row r="14">
@@ -99820,7 +99820,7 @@
         <v>396508</v>
       </c>
       <c r="C14" t="n">
-        <v>221486</v>
+        <v>222048</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -99838,7 +99838,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>743251</v>
+        <v>746846</v>
       </c>
       <c r="J14" t="n">
         <v>217853</v>
@@ -99859,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2062522</v>
+        <v>2066679</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53883,13 +53883,13 @@
         <v>35</v>
       </c>
       <c r="R139" t="n">
-        <v>4514</v>
+        <v>4654</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -53988,7 +53988,7 @@
         <v>80</v>
       </c>
       <c r="BA139" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BB139" t="n">
         <v>0</v>
@@ -54147,7 +54147,7 @@
         <v>50</v>
       </c>
       <c r="DB139" t="n">
-        <v>1610</v>
+        <v>1670</v>
       </c>
       <c r="DC139" t="n">
         <v>0</v>
@@ -54210,7 +54210,7 @@
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>30814</v>
+        <v>31259</v>
       </c>
     </row>
     <row r="140">
@@ -54268,13 +54268,13 @@
         <v>107</v>
       </c>
       <c r="R140" t="n">
-        <v>429168</v>
+        <v>429308</v>
       </c>
       <c r="S140" t="n">
         <v>925</v>
       </c>
       <c r="T140" t="n">
-        <v>797</v>
+        <v>872</v>
       </c>
       <c r="U140" t="n">
         <v>2001</v>
@@ -54373,7 +54373,7 @@
         <v>40932</v>
       </c>
       <c r="BA140" t="n">
-        <v>6496</v>
+        <v>6666</v>
       </c>
       <c r="BB140" t="n">
         <v>3155</v>
@@ -54532,7 +54532,7 @@
         <v>13766</v>
       </c>
       <c r="DB140" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
       <c r="DC140" t="n">
         <v>1030</v>
@@ -54595,7 +54595,7 @@
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>
@@ -60765,7 +60765,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1610</v>
+        <v>1670</v>
       </c>
       <c r="C7" t="n">
         <v>745</v>
@@ -60801,10 +60801,10 @@
         <v>1477</v>
       </c>
       <c r="N7" t="n">
-        <v>4514</v>
+        <v>4654</v>
       </c>
       <c r="O7" t="n">
-        <v>10956</v>
+        <v>11156</v>
       </c>
     </row>
     <row r="8">
@@ -60814,7 +60814,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13780</v>
+        <v>13840</v>
       </c>
       <c r="C8" t="n">
         <v>5465</v>
@@ -60850,10 +60850,10 @@
         <v>13023</v>
       </c>
       <c r="N8" t="n">
-        <v>21157</v>
+        <v>21297</v>
       </c>
       <c r="O8" t="n">
-        <v>83743</v>
+        <v>83943</v>
       </c>
     </row>
   </sheetData>
@@ -62259,7 +62259,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1610</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="140">
@@ -62269,7 +62269,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
     </row>
     <row r="142">
@@ -62377,7 +62377,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>13780</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="155">
@@ -62387,7 +62387,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
     </row>
   </sheetData>
@@ -70874,7 +70874,7 @@
         <v>670</v>
       </c>
       <c r="E139" t="n">
-        <v>20473</v>
+        <v>20613</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -70886,7 +70886,7 @@
         <v>75</v>
       </c>
       <c r="I139" t="n">
-        <v>2170</v>
+        <v>2475</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -70916,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>30814</v>
+        <v>31259</v>
       </c>
     </row>
     <row r="140">
@@ -70935,7 +70935,7 @@
         <v>62058</v>
       </c>
       <c r="E140" t="n">
-        <v>854542</v>
+        <v>854682</v>
       </c>
       <c r="F140" t="n">
         <v>5932</v>
@@ -70947,7 +70947,7 @@
         <v>7499</v>
       </c>
       <c r="I140" t="n">
-        <v>283409</v>
+        <v>283714</v>
       </c>
       <c r="J140" t="n">
         <v>4939</v>
@@ -70977,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>
@@ -89437,7 +89437,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4514</v>
+        <v>4654</v>
       </c>
       <c r="C139" t="n">
         <v>1477</v>
@@ -89458,10 +89458,10 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>19858</v>
+        <v>20103</v>
       </c>
       <c r="J139" t="n">
-        <v>1610</v>
+        <v>1670</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -89479,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>30814</v>
+        <v>31259</v>
       </c>
     </row>
     <row r="140">
@@ -89489,7 +89489,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396508</v>
+        <v>396648</v>
       </c>
       <c r="C140" t="n">
         <v>222048</v>
@@ -89510,10 +89510,10 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>746846</v>
+        <v>747091</v>
       </c>
       <c r="J140" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
       <c r="K140" t="n">
         <v>32660</v>
@@ -89531,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>
@@ -92471,7 +92471,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4514</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="140">
@@ -92481,7 +92481,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396508</v>
+        <v>396648</v>
       </c>
     </row>
     <row r="142">
@@ -92589,7 +92589,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>21157</v>
+        <v>21297</v>
       </c>
     </row>
     <row r="155">
@@ -92599,7 +92599,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>396508</v>
+        <v>396648</v>
       </c>
     </row>
   </sheetData>
@@ -97519,13 +97519,13 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>23602</v>
+        <v>23742</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
       </c>
       <c r="T13" t="n">
-        <v>425</v>
+        <v>500</v>
       </c>
       <c r="U13" t="n">
         <v>45</v>
@@ -97624,7 +97624,7 @@
         <v>2500</v>
       </c>
       <c r="BA13" t="n">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="BB13" t="n">
         <v>210</v>
@@ -97783,7 +97783,7 @@
         <v>910</v>
       </c>
       <c r="DB13" t="n">
-        <v>13780</v>
+        <v>13840</v>
       </c>
       <c r="DC13" t="n">
         <v>30</v>
@@ -97846,7 +97846,7 @@
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>147716</v>
+        <v>148161</v>
       </c>
     </row>
     <row r="14">
@@ -97904,13 +97904,13 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>429168</v>
+        <v>429308</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
       </c>
       <c r="T14" t="n">
-        <v>797</v>
+        <v>872</v>
       </c>
       <c r="U14" t="n">
         <v>2001</v>
@@ -98009,7 +98009,7 @@
         <v>40932</v>
       </c>
       <c r="BA14" t="n">
-        <v>6496</v>
+        <v>6666</v>
       </c>
       <c r="BB14" t="n">
         <v>3155</v>
@@ -98168,7 +98168,7 @@
         <v>13766</v>
       </c>
       <c r="DB14" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
       <c r="DC14" t="n">
         <v>1030</v>
@@ -98231,7 +98231,7 @@
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>
@@ -99008,7 +99008,7 @@
         <v>4780</v>
       </c>
       <c r="E13" t="n">
-        <v>62820</v>
+        <v>62960</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99020,7 +99020,7 @@
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>18511</v>
+        <v>18816</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99050,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>147716</v>
+        <v>148161</v>
       </c>
     </row>
     <row r="14">
@@ -99069,7 +99069,7 @@
         <v>62058</v>
       </c>
       <c r="E14" t="n">
-        <v>854542</v>
+        <v>854682</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99081,7 +99081,7 @@
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>283409</v>
+        <v>283714</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99111,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>
@@ -99765,7 +99765,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>21157</v>
+        <v>21297</v>
       </c>
       <c r="C13" t="n">
         <v>13023</v>
@@ -99786,10 +99786,10 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>63973</v>
+        <v>64218</v>
       </c>
       <c r="J13" t="n">
-        <v>13780</v>
+        <v>13840</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -99807,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>147716</v>
+        <v>148161</v>
       </c>
     </row>
     <row r="14">
@@ -99817,7 +99817,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>396508</v>
+        <v>396648</v>
       </c>
       <c r="C14" t="n">
         <v>222048</v>
@@ -99838,10 +99838,10 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>746846</v>
+        <v>747091</v>
       </c>
       <c r="J14" t="n">
-        <v>217853</v>
+        <v>217913</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -99859,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2066679</v>
+        <v>2067124</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53883,7 +53883,7 @@
         <v>35</v>
       </c>
       <c r="R139" t="n">
-        <v>4654</v>
+        <v>4729</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -54036,7 +54036,7 @@
         <v>0</v>
       </c>
       <c r="BQ139" t="n">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="BR139" t="n">
         <v>215</v>
@@ -54099,7 +54099,7 @@
         <v>0</v>
       </c>
       <c r="CL139" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="CM139" t="n">
         <v>0</v>
@@ -54123,7 +54123,7 @@
         <v>0</v>
       </c>
       <c r="CT139" t="n">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="CU139" t="n">
         <v>75</v>
@@ -54210,7 +54210,7 @@
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>31259</v>
+        <v>31544</v>
       </c>
     </row>
     <row r="140">
@@ -54268,7 +54268,7 @@
         <v>107</v>
       </c>
       <c r="R140" t="n">
-        <v>429308</v>
+        <v>429383</v>
       </c>
       <c r="S140" t="n">
         <v>925</v>
@@ -54421,7 +54421,7 @@
         <v>7365</v>
       </c>
       <c r="BQ140" t="n">
-        <v>94095</v>
+        <v>94145</v>
       </c>
       <c r="BR140" t="n">
         <v>22072</v>
@@ -54484,7 +54484,7 @@
         <v>350</v>
       </c>
       <c r="CL140" t="n">
-        <v>17884</v>
+        <v>17994</v>
       </c>
       <c r="CM140" t="n">
         <v>345</v>
@@ -54508,7 +54508,7 @@
         <v>2</v>
       </c>
       <c r="CT140" t="n">
-        <v>65105</v>
+        <v>65155</v>
       </c>
       <c r="CU140" t="n">
         <v>2384</v>
@@ -54595,7 +54595,7 @@
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>
@@ -60798,13 +60798,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1477</v>
+        <v>1527</v>
       </c>
       <c r="N7" t="n">
-        <v>4654</v>
+        <v>4729</v>
       </c>
       <c r="O7" t="n">
-        <v>11156</v>
+        <v>11281</v>
       </c>
     </row>
     <row r="8">
@@ -60847,13 +60847,13 @@
         <v>2690</v>
       </c>
       <c r="M8" t="n">
-        <v>13023</v>
+        <v>13073</v>
       </c>
       <c r="N8" t="n">
-        <v>21297</v>
+        <v>21372</v>
       </c>
       <c r="O8" t="n">
-        <v>83943</v>
+        <v>84068</v>
       </c>
     </row>
   </sheetData>
@@ -70874,7 +70874,7 @@
         <v>670</v>
       </c>
       <c r="E139" t="n">
-        <v>20613</v>
+        <v>20848</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -70907,7 +70907,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>3172</v>
+        <v>3222</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -70916,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>31259</v>
+        <v>31544</v>
       </c>
     </row>
     <row r="140">
@@ -70935,7 +70935,7 @@
         <v>62058</v>
       </c>
       <c r="E140" t="n">
-        <v>854682</v>
+        <v>854917</v>
       </c>
       <c r="F140" t="n">
         <v>5932</v>
@@ -70968,7 +70968,7 @@
         <v>22052</v>
       </c>
       <c r="P140" t="n">
-        <v>420456</v>
+        <v>420506</v>
       </c>
       <c r="Q140" t="n">
         <v>36635</v>
@@ -70977,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>
@@ -89437,10 +89437,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4654</v>
+        <v>4729</v>
       </c>
       <c r="C139" t="n">
-        <v>1477</v>
+        <v>1527</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89458,7 +89458,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>20103</v>
+        <v>20263</v>
       </c>
       <c r="J139" t="n">
         <v>1670</v>
@@ -89479,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>31259</v>
+        <v>31544</v>
       </c>
     </row>
     <row r="140">
@@ -89489,10 +89489,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396648</v>
+        <v>396723</v>
       </c>
       <c r="C140" t="n">
-        <v>222048</v>
+        <v>222098</v>
       </c>
       <c r="D140" t="n">
         <v>58168</v>
@@ -89510,7 +89510,7 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>747091</v>
+        <v>747251</v>
       </c>
       <c r="J140" t="n">
         <v>217913</v>
@@ -89531,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>
@@ -90937,7 +90937,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1477</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="140">
@@ -90947,7 +90947,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>222048</v>
+        <v>222098</v>
       </c>
     </row>
     <row r="142">
@@ -91055,7 +91055,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>13023</v>
+        <v>13073</v>
       </c>
     </row>
     <row r="155">
@@ -91065,7 +91065,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>222048</v>
+        <v>222098</v>
       </c>
     </row>
   </sheetData>
@@ -92471,7 +92471,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4654</v>
+        <v>4729</v>
       </c>
     </row>
     <row r="140">
@@ -92481,7 +92481,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>396648</v>
+        <v>396723</v>
       </c>
     </row>
     <row r="142">
@@ -92589,7 +92589,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>21297</v>
+        <v>21372</v>
       </c>
     </row>
     <row r="155">
@@ -92599,7 +92599,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>396648</v>
+        <v>396723</v>
       </c>
     </row>
   </sheetData>
@@ -97519,7 +97519,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>23742</v>
+        <v>23817</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -97672,7 +97672,7 @@
         <v>335</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4957</v>
+        <v>5007</v>
       </c>
       <c r="BR13" t="n">
         <v>1510</v>
@@ -97735,7 +97735,7 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>270</v>
+        <v>380</v>
       </c>
       <c r="CM13" t="n">
         <v>50</v>
@@ -97759,7 +97759,7 @@
         <v>2</v>
       </c>
       <c r="CT13" t="n">
-        <v>4375</v>
+        <v>4425</v>
       </c>
       <c r="CU13" t="n">
         <v>925</v>
@@ -97846,7 +97846,7 @@
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>148161</v>
+        <v>148446</v>
       </c>
     </row>
     <row r="14">
@@ -97904,7 +97904,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>429308</v>
+        <v>429383</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98057,7 +98057,7 @@
         <v>7365</v>
       </c>
       <c r="BQ14" t="n">
-        <v>94095</v>
+        <v>94145</v>
       </c>
       <c r="BR14" t="n">
         <v>22072</v>
@@ -98120,7 +98120,7 @@
         <v>350</v>
       </c>
       <c r="CL14" t="n">
-        <v>17884</v>
+        <v>17994</v>
       </c>
       <c r="CM14" t="n">
         <v>345</v>
@@ -98144,7 +98144,7 @@
         <v>2</v>
       </c>
       <c r="CT14" t="n">
-        <v>65105</v>
+        <v>65155</v>
       </c>
       <c r="CU14" t="n">
         <v>2384</v>
@@ -98231,7 +98231,7 @@
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>
@@ -99008,7 +99008,7 @@
         <v>4780</v>
       </c>
       <c r="E13" t="n">
-        <v>62960</v>
+        <v>63195</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99041,7 +99041,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>25935</v>
+        <v>25985</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99050,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>148161</v>
+        <v>148446</v>
       </c>
     </row>
     <row r="14">
@@ -99069,7 +99069,7 @@
         <v>62058</v>
       </c>
       <c r="E14" t="n">
-        <v>854682</v>
+        <v>854917</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99102,7 +99102,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>420456</v>
+        <v>420506</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99111,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>
@@ -99765,10 +99765,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>21297</v>
+        <v>21372</v>
       </c>
       <c r="C13" t="n">
-        <v>13023</v>
+        <v>13073</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -99786,7 +99786,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>64218</v>
+        <v>64378</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -99807,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>148161</v>
+        <v>148446</v>
       </c>
     </row>
     <row r="14">
@@ -99817,10 +99817,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>396648</v>
+        <v>396723</v>
       </c>
       <c r="C14" t="n">
-        <v>222048</v>
+        <v>222098</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -99838,7 +99838,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>747091</v>
+        <v>747251</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -99859,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2067124</v>
+        <v>2067409</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54036,10 +54036,10 @@
         <v>0</v>
       </c>
       <c r="BQ139" t="n">
-        <v>265</v>
+        <v>1075</v>
       </c>
       <c r="BR139" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="BS139" t="n">
         <v>75</v>
@@ -54075,7 +54075,7 @@
         <v>0</v>
       </c>
       <c r="CD139" t="n">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="CE139" t="n">
         <v>142</v>
@@ -54210,7 +54210,7 @@
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>31544</v>
+        <v>32689</v>
       </c>
     </row>
     <row r="140">
@@ -54421,10 +54421,10 @@
         <v>7365</v>
       </c>
       <c r="BQ140" t="n">
-        <v>94145</v>
+        <v>94955</v>
       </c>
       <c r="BR140" t="n">
-        <v>22072</v>
+        <v>22107</v>
       </c>
       <c r="BS140" t="n">
         <v>13249</v>
@@ -54460,7 +54460,7 @@
         <v>435</v>
       </c>
       <c r="CD140" t="n">
-        <v>15373</v>
+        <v>15673</v>
       </c>
       <c r="CE140" t="n">
         <v>5771</v>
@@ -54595,7 +54595,7 @@
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>
@@ -60798,13 +60798,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1527</v>
+        <v>2337</v>
       </c>
       <c r="N7" t="n">
         <v>4729</v>
       </c>
       <c r="O7" t="n">
-        <v>11281</v>
+        <v>12091</v>
       </c>
     </row>
     <row r="8">
@@ -60847,13 +60847,13 @@
         <v>2690</v>
       </c>
       <c r="M8" t="n">
-        <v>13073</v>
+        <v>13883</v>
       </c>
       <c r="N8" t="n">
         <v>21372</v>
       </c>
       <c r="O8" t="n">
-        <v>84068</v>
+        <v>84878</v>
       </c>
     </row>
   </sheetData>
@@ -70886,7 +70886,7 @@
         <v>75</v>
       </c>
       <c r="I139" t="n">
-        <v>2475</v>
+        <v>2510</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -70907,7 +70907,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>3222</v>
+        <v>4332</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -70916,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>31544</v>
+        <v>32689</v>
       </c>
     </row>
     <row r="140">
@@ -70947,7 +70947,7 @@
         <v>7499</v>
       </c>
       <c r="I140" t="n">
-        <v>283714</v>
+        <v>283749</v>
       </c>
       <c r="J140" t="n">
         <v>4939</v>
@@ -70968,7 +70968,7 @@
         <v>22052</v>
       </c>
       <c r="P140" t="n">
-        <v>420506</v>
+        <v>421616</v>
       </c>
       <c r="Q140" t="n">
         <v>36635</v>
@@ -70977,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>
@@ -89440,7 +89440,7 @@
         <v>4729</v>
       </c>
       <c r="C139" t="n">
-        <v>1527</v>
+        <v>2337</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89458,7 +89458,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>20263</v>
+        <v>20598</v>
       </c>
       <c r="J139" t="n">
         <v>1670</v>
@@ -89479,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>31544</v>
+        <v>32689</v>
       </c>
     </row>
     <row r="140">
@@ -89492,7 +89492,7 @@
         <v>396723</v>
       </c>
       <c r="C140" t="n">
-        <v>222098</v>
+        <v>222908</v>
       </c>
       <c r="D140" t="n">
         <v>58168</v>
@@ -89510,7 +89510,7 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>747251</v>
+        <v>747586</v>
       </c>
       <c r="J140" t="n">
         <v>217913</v>
@@ -89531,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>
@@ -90937,7 +90937,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1527</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="140">
@@ -90947,7 +90947,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>222098</v>
+        <v>222908</v>
       </c>
     </row>
     <row r="142">
@@ -91055,7 +91055,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>13073</v>
+        <v>13883</v>
       </c>
     </row>
     <row r="155">
@@ -91065,7 +91065,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>222098</v>
+        <v>222908</v>
       </c>
     </row>
   </sheetData>
@@ -97672,10 +97672,10 @@
         <v>335</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5007</v>
+        <v>5817</v>
       </c>
       <c r="BR13" t="n">
-        <v>1510</v>
+        <v>1545</v>
       </c>
       <c r="BS13" t="n">
         <v>879</v>
@@ -97711,7 +97711,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>1635</v>
+        <v>1935</v>
       </c>
       <c r="CE13" t="n">
         <v>856</v>
@@ -97846,7 +97846,7 @@
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>148446</v>
+        <v>149591</v>
       </c>
     </row>
     <row r="14">
@@ -98057,10 +98057,10 @@
         <v>7365</v>
       </c>
       <c r="BQ14" t="n">
-        <v>94145</v>
+        <v>94955</v>
       </c>
       <c r="BR14" t="n">
-        <v>22072</v>
+        <v>22107</v>
       </c>
       <c r="BS14" t="n">
         <v>13249</v>
@@ -98096,7 +98096,7 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>15373</v>
+        <v>15673</v>
       </c>
       <c r="CE14" t="n">
         <v>5771</v>
@@ -98231,7 +98231,7 @@
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>
@@ -99020,7 +99020,7 @@
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>18816</v>
+        <v>18851</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99041,7 +99041,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>25985</v>
+        <v>27095</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99050,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>148446</v>
+        <v>149591</v>
       </c>
     </row>
     <row r="14">
@@ -99081,7 +99081,7 @@
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>283714</v>
+        <v>283749</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99102,7 +99102,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>420506</v>
+        <v>421616</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99111,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>
@@ -99768,7 +99768,7 @@
         <v>21372</v>
       </c>
       <c r="C13" t="n">
-        <v>13073</v>
+        <v>13883</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -99786,7 +99786,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>64378</v>
+        <v>64713</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -99807,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>148446</v>
+        <v>149591</v>
       </c>
     </row>
     <row r="14">
@@ -99820,7 +99820,7 @@
         <v>396723</v>
       </c>
       <c r="C14" t="n">
-        <v>222098</v>
+        <v>222908</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -99838,7 +99838,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>747251</v>
+        <v>747586</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -99859,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2067409</v>
+        <v>2068554</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -51314,7 +51314,7 @@
         <v>0</v>
       </c>
       <c r="BH132" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="BI132" t="n">
         <v>0</v>
@@ -51515,7 +51515,7 @@
         <v>445</v>
       </c>
       <c r="DW132" t="n">
-        <v>20167</v>
+        <v>20217</v>
       </c>
     </row>
     <row r="133">
@@ -53844,7 +53844,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>812</v>
+        <v>952</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -53967,7 +53967,7 @@
         <v>50</v>
       </c>
       <c r="AT139" t="n">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="AU139" t="n">
         <v>0</v>
@@ -54039,10 +54039,10 @@
         <v>1075</v>
       </c>
       <c r="BR139" t="n">
-        <v>250</v>
+        <v>435</v>
       </c>
       <c r="BS139" t="n">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="BT139" t="n">
         <v>225</v>
@@ -54210,7 +54210,7 @@
         <v>310</v>
       </c>
       <c r="DW139" t="n">
-        <v>32689</v>
+        <v>33254</v>
       </c>
     </row>
     <row r="140">
@@ -54229,7 +54229,7 @@
         <v>150</v>
       </c>
       <c r="E140" t="n">
-        <v>72027</v>
+        <v>72167</v>
       </c>
       <c r="F140" t="n">
         <v>500</v>
@@ -54352,7 +54352,7 @@
         <v>262</v>
       </c>
       <c r="AT140" t="n">
-        <v>26549</v>
+        <v>26604</v>
       </c>
       <c r="AU140" t="n">
         <v>437</v>
@@ -54394,7 +54394,7 @@
         <v>10010</v>
       </c>
       <c r="BH140" t="n">
-        <v>1096</v>
+        <v>1146</v>
       </c>
       <c r="BI140" t="n">
         <v>13284</v>
@@ -54424,10 +54424,10 @@
         <v>94955</v>
       </c>
       <c r="BR140" t="n">
-        <v>22107</v>
+        <v>22292</v>
       </c>
       <c r="BS140" t="n">
-        <v>13249</v>
+        <v>13434</v>
       </c>
       <c r="BT140" t="n">
         <v>26576</v>
@@ -54595,7 +54595,7 @@
         <v>27338</v>
       </c>
       <c r="DW140" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>
@@ -60798,13 +60798,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2337</v>
+        <v>2477</v>
       </c>
       <c r="N7" t="n">
         <v>4729</v>
       </c>
       <c r="O7" t="n">
-        <v>12091</v>
+        <v>12231</v>
       </c>
     </row>
     <row r="8">
@@ -60847,13 +60847,13 @@
         <v>2690</v>
       </c>
       <c r="M8" t="n">
-        <v>13883</v>
+        <v>14023</v>
       </c>
       <c r="N8" t="n">
         <v>21372</v>
       </c>
       <c r="O8" t="n">
-        <v>84878</v>
+        <v>85018</v>
       </c>
     </row>
   </sheetData>
@@ -70444,7 +70444,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>934</v>
+        <v>984</v>
       </c>
       <c r="E132" t="n">
         <v>7071</v>
@@ -70489,7 +70489,7 @@
         <v>857</v>
       </c>
       <c r="S132" t="n">
-        <v>20167</v>
+        <v>20217</v>
       </c>
     </row>
     <row r="133">
@@ -70871,7 +70871,7 @@
         <v>255</v>
       </c>
       <c r="D139" t="n">
-        <v>670</v>
+        <v>725</v>
       </c>
       <c r="E139" t="n">
         <v>20848</v>
@@ -70886,7 +70886,7 @@
         <v>75</v>
       </c>
       <c r="I139" t="n">
-        <v>2510</v>
+        <v>2880</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -70907,7 +70907,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>4332</v>
+        <v>4472</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -70916,7 +70916,7 @@
         <v>1410</v>
       </c>
       <c r="S139" t="n">
-        <v>32689</v>
+        <v>33254</v>
       </c>
     </row>
     <row r="140">
@@ -70932,7 +70932,7 @@
         <v>17331</v>
       </c>
       <c r="D140" t="n">
-        <v>62058</v>
+        <v>62163</v>
       </c>
       <c r="E140" t="n">
         <v>854917</v>
@@ -70947,7 +70947,7 @@
         <v>7499</v>
       </c>
       <c r="I140" t="n">
-        <v>283749</v>
+        <v>284119</v>
       </c>
       <c r="J140" t="n">
         <v>4939</v>
@@ -70968,7 +70968,7 @@
         <v>22052</v>
       </c>
       <c r="P140" t="n">
-        <v>421616</v>
+        <v>421756</v>
       </c>
       <c r="Q140" t="n">
         <v>36635</v>
@@ -70977,7 +70977,7 @@
         <v>87453</v>
       </c>
       <c r="S140" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>
@@ -89094,7 +89094,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>6451</v>
+        <v>6501</v>
       </c>
       <c r="J132" t="n">
         <v>2700</v>
@@ -89115,7 +89115,7 @@
         <v>752</v>
       </c>
       <c r="P132" t="n">
-        <v>20167</v>
+        <v>20217</v>
       </c>
     </row>
     <row r="133">
@@ -89440,7 +89440,7 @@
         <v>4729</v>
       </c>
       <c r="C139" t="n">
-        <v>2337</v>
+        <v>2477</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89458,7 +89458,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>20598</v>
+        <v>21023</v>
       </c>
       <c r="J139" t="n">
         <v>1670</v>
@@ -89479,7 +89479,7 @@
         <v>690</v>
       </c>
       <c r="P139" t="n">
-        <v>32689</v>
+        <v>33254</v>
       </c>
     </row>
     <row r="140">
@@ -89492,7 +89492,7 @@
         <v>396723</v>
       </c>
       <c r="C140" t="n">
-        <v>222908</v>
+        <v>223048</v>
       </c>
       <c r="D140" t="n">
         <v>58168</v>
@@ -89510,7 +89510,7 @@
         <v>6860</v>
       </c>
       <c r="I140" t="n">
-        <v>747586</v>
+        <v>748061</v>
       </c>
       <c r="J140" t="n">
         <v>217913</v>
@@ -89531,7 +89531,7 @@
         <v>48134</v>
       </c>
       <c r="P140" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>
@@ -90937,7 +90937,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2337</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="140">
@@ -90947,7 +90947,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>222908</v>
+        <v>223048</v>
       </c>
     </row>
     <row r="142">
@@ -91055,7 +91055,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>13883</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="155">
@@ -91065,7 +91065,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>222908</v>
+        <v>223048</v>
       </c>
     </row>
   </sheetData>
@@ -97262,7 +97262,7 @@
         <v>3365</v>
       </c>
       <c r="BH12" t="n">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="BI12" t="n">
         <v>1782</v>
@@ -97463,7 +97463,7 @@
         <v>3034</v>
       </c>
       <c r="DW12" t="n">
-        <v>269977</v>
+        <v>270027</v>
       </c>
     </row>
     <row r="13">
@@ -97480,7 +97480,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4632</v>
+        <v>4772</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97603,7 +97603,7 @@
         <v>262</v>
       </c>
       <c r="AT13" t="n">
-        <v>1810</v>
+        <v>1865</v>
       </c>
       <c r="AU13" t="n">
         <v>437</v>
@@ -97675,10 +97675,10 @@
         <v>5817</v>
       </c>
       <c r="BR13" t="n">
-        <v>1545</v>
+        <v>1730</v>
       </c>
       <c r="BS13" t="n">
-        <v>879</v>
+        <v>1064</v>
       </c>
       <c r="BT13" t="n">
         <v>2882</v>
@@ -97846,7 +97846,7 @@
         <v>1470</v>
       </c>
       <c r="DW13" t="n">
-        <v>149591</v>
+        <v>150156</v>
       </c>
     </row>
     <row r="14">
@@ -97865,7 +97865,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72027</v>
+        <v>72167</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -97988,7 +97988,7 @@
         <v>262</v>
       </c>
       <c r="AT14" t="n">
-        <v>26549</v>
+        <v>26604</v>
       </c>
       <c r="AU14" t="n">
         <v>437</v>
@@ -98030,7 +98030,7 @@
         <v>10010</v>
       </c>
       <c r="BH14" t="n">
-        <v>1096</v>
+        <v>1146</v>
       </c>
       <c r="BI14" t="n">
         <v>13284</v>
@@ -98060,10 +98060,10 @@
         <v>94955</v>
       </c>
       <c r="BR14" t="n">
-        <v>22107</v>
+        <v>22292</v>
       </c>
       <c r="BS14" t="n">
-        <v>13249</v>
+        <v>13434</v>
       </c>
       <c r="BT14" t="n">
         <v>26576</v>
@@ -98231,7 +98231,7 @@
         <v>27338</v>
       </c>
       <c r="DW14" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>
@@ -98946,7 +98946,7 @@
         <v>3299</v>
       </c>
       <c r="D12" t="n">
-        <v>8231</v>
+        <v>8281</v>
       </c>
       <c r="E12" t="n">
         <v>101634</v>
@@ -98991,7 +98991,7 @@
         <v>15263</v>
       </c>
       <c r="S12" t="n">
-        <v>269977</v>
+        <v>270027</v>
       </c>
     </row>
     <row r="13">
@@ -99005,7 +99005,7 @@
         <v>2075</v>
       </c>
       <c r="D13" t="n">
-        <v>4780</v>
+        <v>4835</v>
       </c>
       <c r="E13" t="n">
         <v>63195</v>
@@ -99020,7 +99020,7 @@
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>18851</v>
+        <v>19221</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99041,7 +99041,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>27095</v>
+        <v>27235</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99050,7 +99050,7 @@
         <v>8112</v>
       </c>
       <c r="S13" t="n">
-        <v>149591</v>
+        <v>150156</v>
       </c>
     </row>
     <row r="14">
@@ -99066,7 +99066,7 @@
         <v>17331</v>
       </c>
       <c r="D14" t="n">
-        <v>62058</v>
+        <v>62163</v>
       </c>
       <c r="E14" t="n">
         <v>854917</v>
@@ -99081,7 +99081,7 @@
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>283749</v>
+        <v>284119</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99102,7 +99102,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>421616</v>
+        <v>421756</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99111,7 +99111,7 @@
         <v>87453</v>
       </c>
       <c r="S14" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>
@@ -99736,7 +99736,7 @@
         <v>3250</v>
       </c>
       <c r="I12" t="n">
-        <v>101735</v>
+        <v>101785</v>
       </c>
       <c r="J12" t="n">
         <v>28487</v>
@@ -99757,7 +99757,7 @@
         <v>7031</v>
       </c>
       <c r="P12" t="n">
-        <v>269977</v>
+        <v>270027</v>
       </c>
     </row>
     <row r="13">
@@ -99768,7 +99768,7 @@
         <v>21372</v>
       </c>
       <c r="C13" t="n">
-        <v>13883</v>
+        <v>14023</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -99786,7 +99786,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>64713</v>
+        <v>65138</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -99807,7 +99807,7 @@
         <v>3160</v>
       </c>
       <c r="P13" t="n">
-        <v>149591</v>
+        <v>150156</v>
       </c>
     </row>
     <row r="14">
@@ -99820,7 +99820,7 @@
         <v>396723</v>
       </c>
       <c r="C14" t="n">
-        <v>222908</v>
+        <v>223048</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -99838,7 +99838,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>747586</v>
+        <v>748061</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -99859,7 +99859,7 @@
         <v>48134</v>
       </c>
       <c r="P14" t="n">
-        <v>2068554</v>
+        <v>2069169</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW140"/>
+  <dimension ref="A1:DW141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53859,10 +53859,10 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="K139" t="n">
-        <v>180</v>
+        <v>430</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -54084,7 +54084,7 @@
         <v>0</v>
       </c>
       <c r="CG139" t="n">
-        <v>380</v>
+        <v>675</v>
       </c>
       <c r="CH139" t="n">
         <v>110</v>
@@ -54207,395 +54207,780 @@
         <v>40</v>
       </c>
       <c r="DV139" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="DW139" t="n">
-        <v>33254</v>
+        <v>34149</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR140" t="n">
+        <v>150</v>
+      </c>
+      <c r="DS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW140" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B141" t="n">
         <v>2382</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C141" t="n">
         <v>935</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D141" t="n">
         <v>150</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E141" t="n">
         <v>72167</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F141" t="n">
         <v>500</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G141" t="n">
         <v>400</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H141" t="n">
         <v>2718</v>
       </c>
-      <c r="I140" t="n">
+      <c r="I141" t="n">
         <v>3040</v>
       </c>
-      <c r="J140" t="n">
-        <v>21435</v>
-      </c>
-      <c r="K140" t="n">
-        <v>16672</v>
-      </c>
-      <c r="L140" t="n">
+      <c r="J141" t="n">
+        <v>21595</v>
+      </c>
+      <c r="K141" t="n">
+        <v>16922</v>
+      </c>
+      <c r="L141" t="n">
         <v>5790</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M141" t="n">
         <v>1582</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N141" t="n">
         <v>2935</v>
       </c>
-      <c r="O140" t="n">
+      <c r="O141" t="n">
         <v>5786</v>
       </c>
-      <c r="P140" t="n">
+      <c r="P141" t="n">
         <v>6712</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="Q141" t="n">
         <v>107</v>
       </c>
-      <c r="R140" t="n">
-        <v>429383</v>
-      </c>
-      <c r="S140" t="n">
+      <c r="R141" t="n">
+        <v>430658</v>
+      </c>
+      <c r="S141" t="n">
         <v>925</v>
       </c>
-      <c r="T140" t="n">
+      <c r="T141" t="n">
         <v>872</v>
       </c>
-      <c r="U140" t="n">
+      <c r="U141" t="n">
         <v>2001</v>
       </c>
-      <c r="V140" t="n">
+      <c r="V141" t="n">
         <v>14436</v>
       </c>
-      <c r="W140" t="n">
+      <c r="W141" t="n">
         <v>23953</v>
       </c>
-      <c r="X140" t="n">
+      <c r="X141" t="n">
         <v>4712</v>
       </c>
-      <c r="Y140" t="n">
+      <c r="Y141" t="n">
         <v>2947</v>
       </c>
-      <c r="Z140" t="n">
+      <c r="Z141" t="n">
         <v>485</v>
       </c>
-      <c r="AA140" t="n">
+      <c r="AA141" t="n">
         <v>2</v>
       </c>
-      <c r="AB140" t="n">
+      <c r="AB141" t="n">
         <v>9129</v>
       </c>
-      <c r="AC140" t="n">
+      <c r="AC141" t="n">
         <v>212</v>
       </c>
-      <c r="AD140" t="n">
+      <c r="AD141" t="n">
         <v>10770</v>
       </c>
-      <c r="AE140" t="n">
+      <c r="AE141" t="n">
         <v>12</v>
       </c>
-      <c r="AF140" t="n">
+      <c r="AF141" t="n">
         <v>545</v>
       </c>
-      <c r="AG140" t="n">
+      <c r="AG141" t="n">
         <v>145</v>
       </c>
-      <c r="AH140" t="n">
+      <c r="AH141" t="n">
         <v>1509</v>
       </c>
-      <c r="AI140" t="n">
+      <c r="AI141" t="n">
         <v>522</v>
       </c>
-      <c r="AJ140" t="n">
+      <c r="AJ141" t="n">
         <v>790</v>
       </c>
-      <c r="AK140" t="n">
+      <c r="AK141" t="n">
         <v>12358</v>
       </c>
-      <c r="AL140" t="n">
+      <c r="AL141" t="n">
         <v>374</v>
       </c>
-      <c r="AM140" t="n">
+      <c r="AM141" t="n">
         <v>50659</v>
       </c>
-      <c r="AN140" t="n">
+      <c r="AN141" t="n">
         <v>4755</v>
       </c>
-      <c r="AO140" t="n">
+      <c r="AO141" t="n">
         <v>3357</v>
       </c>
-      <c r="AP140" t="n">
+      <c r="AP141" t="n">
         <v>277</v>
       </c>
-      <c r="AQ140" t="n">
+      <c r="AQ141" t="n">
         <v>2009</v>
       </c>
-      <c r="AR140" t="n">
+      <c r="AR141" t="n">
         <v>387</v>
       </c>
-      <c r="AS140" t="n">
+      <c r="AS141" t="n">
         <v>262</v>
       </c>
-      <c r="AT140" t="n">
+      <c r="AT141" t="n">
         <v>26604</v>
       </c>
-      <c r="AU140" t="n">
+      <c r="AU141" t="n">
         <v>437</v>
       </c>
-      <c r="AV140" t="n">
+      <c r="AV141" t="n">
         <v>2627</v>
       </c>
-      <c r="AW140" t="n">
+      <c r="AW141" t="n">
         <v>6939</v>
       </c>
-      <c r="AX140" t="n">
+      <c r="AX141" t="n">
         <v>5655</v>
       </c>
-      <c r="AY140" t="n">
+      <c r="AY141" t="n">
         <v>460</v>
       </c>
-      <c r="AZ140" t="n">
+      <c r="AZ141" t="n">
         <v>40932</v>
       </c>
-      <c r="BA140" t="n">
+      <c r="BA141" t="n">
         <v>6666</v>
       </c>
-      <c r="BB140" t="n">
+      <c r="BB141" t="n">
         <v>3155</v>
       </c>
-      <c r="BC140" t="n">
+      <c r="BC141" t="n">
         <v>9764</v>
       </c>
-      <c r="BD140" t="n">
+      <c r="BD141" t="n">
         <v>6787</v>
       </c>
-      <c r="BE140" t="n">
+      <c r="BE141" t="n">
         <v>52</v>
       </c>
-      <c r="BF140" t="n">
+      <c r="BF141" t="n">
         <v>435</v>
       </c>
-      <c r="BG140" t="n">
+      <c r="BG141" t="n">
         <v>10010</v>
       </c>
-      <c r="BH140" t="n">
+      <c r="BH141" t="n">
         <v>1146</v>
       </c>
-      <c r="BI140" t="n">
+      <c r="BI141" t="n">
         <v>13284</v>
       </c>
-      <c r="BJ140" t="n">
+      <c r="BJ141" t="n">
         <v>1007</v>
       </c>
-      <c r="BK140" t="n">
+      <c r="BK141" t="n">
         <v>660</v>
       </c>
-      <c r="BL140" t="n">
+      <c r="BL141" t="n">
         <v>47345</v>
       </c>
-      <c r="BM140" t="n">
+      <c r="BM141" t="n">
         <v>1992</v>
       </c>
-      <c r="BN140" t="n">
+      <c r="BN141" t="n">
         <v>112539</v>
       </c>
-      <c r="BO140" t="n">
+      <c r="BO141" t="n">
         <v>4080</v>
       </c>
-      <c r="BP140" t="n">
+      <c r="BP141" t="n">
         <v>7365</v>
       </c>
-      <c r="BQ140" t="n">
+      <c r="BQ141" t="n">
         <v>94955</v>
       </c>
-      <c r="BR140" t="n">
+      <c r="BR141" t="n">
         <v>22292</v>
       </c>
-      <c r="BS140" t="n">
+      <c r="BS141" t="n">
         <v>13434</v>
       </c>
-      <c r="BT140" t="n">
+      <c r="BT141" t="n">
         <v>26576</v>
       </c>
-      <c r="BU140" t="n">
+      <c r="BU141" t="n">
         <v>5115</v>
       </c>
-      <c r="BV140" t="n">
+      <c r="BV141" t="n">
         <v>5791</v>
       </c>
-      <c r="BW140" t="n">
+      <c r="BW141" t="n">
         <v>34491</v>
       </c>
-      <c r="BX140" t="n">
+      <c r="BX141" t="n">
         <v>5175</v>
       </c>
-      <c r="BY140" t="n">
+      <c r="BY141" t="n">
         <v>696</v>
       </c>
-      <c r="BZ140" t="n">
+      <c r="BZ141" t="n">
         <v>42</v>
       </c>
-      <c r="CA140" t="n">
+      <c r="CA141" t="n">
         <v>215</v>
       </c>
-      <c r="CB140" t="n">
+      <c r="CB141" t="n">
         <v>3350</v>
       </c>
-      <c r="CC140" t="n">
+      <c r="CC141" t="n">
         <v>435</v>
       </c>
-      <c r="CD140" t="n">
+      <c r="CD141" t="n">
         <v>15673</v>
       </c>
-      <c r="CE140" t="n">
+      <c r="CE141" t="n">
         <v>5771</v>
       </c>
-      <c r="CF140" t="n">
+      <c r="CF141" t="n">
         <v>145</v>
       </c>
-      <c r="CG140" t="n">
-        <v>20796</v>
-      </c>
-      <c r="CH140" t="n">
+      <c r="CG141" t="n">
+        <v>21091</v>
+      </c>
+      <c r="CH141" t="n">
         <v>3642</v>
       </c>
-      <c r="CI140" t="n">
+      <c r="CI141" t="n">
         <v>1645</v>
       </c>
-      <c r="CJ140" t="n">
+      <c r="CJ141" t="n">
         <v>470</v>
       </c>
-      <c r="CK140" t="n">
+      <c r="CK141" t="n">
         <v>350</v>
       </c>
-      <c r="CL140" t="n">
+      <c r="CL141" t="n">
         <v>17994</v>
       </c>
-      <c r="CM140" t="n">
+      <c r="CM141" t="n">
         <v>345</v>
       </c>
-      <c r="CN140" t="n">
+      <c r="CN141" t="n">
         <v>220</v>
       </c>
-      <c r="CO140" t="n">
+      <c r="CO141" t="n">
         <v>11135</v>
       </c>
-      <c r="CP140" t="n">
+      <c r="CP141" t="n">
         <v>140</v>
       </c>
-      <c r="CQ140" t="n">
+      <c r="CQ141" t="n">
         <v>277</v>
       </c>
-      <c r="CR140" t="n">
+      <c r="CR141" t="n">
         <v>11904</v>
       </c>
-      <c r="CS140" t="n">
+      <c r="CS141" t="n">
         <v>2</v>
       </c>
-      <c r="CT140" t="n">
+      <c r="CT141" t="n">
         <v>65155</v>
       </c>
-      <c r="CU140" t="n">
+      <c r="CU141" t="n">
         <v>2384</v>
       </c>
-      <c r="CV140" t="n">
+      <c r="CV141" t="n">
         <v>1310</v>
       </c>
-      <c r="CW140" t="n">
+      <c r="CW141" t="n">
         <v>2698</v>
       </c>
-      <c r="CX140" t="n">
+      <c r="CX141" t="n">
         <v>127</v>
       </c>
-      <c r="CY140" t="n">
+      <c r="CY141" t="n">
         <v>8936</v>
       </c>
-      <c r="CZ140" t="n">
+      <c r="CZ141" t="n">
         <v>18496</v>
       </c>
-      <c r="DA140" t="n">
+      <c r="DA141" t="n">
         <v>13766</v>
       </c>
-      <c r="DB140" t="n">
+      <c r="DB141" t="n">
         <v>217913</v>
       </c>
-      <c r="DC140" t="n">
+      <c r="DC141" t="n">
         <v>1030</v>
       </c>
-      <c r="DD140" t="n">
+      <c r="DD141" t="n">
         <v>1351</v>
       </c>
-      <c r="DE140" t="n">
+      <c r="DE141" t="n">
         <v>1485</v>
       </c>
-      <c r="DF140" t="n">
+      <c r="DF141" t="n">
         <v>47</v>
       </c>
-      <c r="DG140" t="n">
+      <c r="DG141" t="n">
         <v>20580</v>
       </c>
-      <c r="DH140" t="n">
+      <c r="DH141" t="n">
         <v>37481</v>
       </c>
-      <c r="DI140" t="n">
+      <c r="DI141" t="n">
         <v>23863</v>
       </c>
-      <c r="DJ140" t="n">
+      <c r="DJ141" t="n">
         <v>99974</v>
       </c>
-      <c r="DK140" t="n">
+      <c r="DK141" t="n">
         <v>1240</v>
       </c>
-      <c r="DL140" t="n">
+      <c r="DL141" t="n">
         <v>15334</v>
       </c>
-      <c r="DM140" t="n">
+      <c r="DM141" t="n">
         <v>10550</v>
       </c>
-      <c r="DN140" t="n">
+      <c r="DN141" t="n">
         <v>17967</v>
       </c>
-      <c r="DO140" t="n">
+      <c r="DO141" t="n">
         <v>582</v>
       </c>
-      <c r="DP140" t="n">
+      <c r="DP141" t="n">
         <v>3027</v>
       </c>
-      <c r="DQ140" t="n">
+      <c r="DQ141" t="n">
         <v>7725</v>
       </c>
-      <c r="DR140" t="n">
-        <v>57741</v>
-      </c>
-      <c r="DS140" t="n">
+      <c r="DR141" t="n">
+        <v>57891</v>
+      </c>
+      <c r="DS141" t="n">
         <v>1450</v>
       </c>
-      <c r="DT140" t="n">
+      <c r="DT141" t="n">
         <v>70576</v>
       </c>
-      <c r="DU140" t="n">
+      <c r="DU141" t="n">
         <v>4927</v>
       </c>
-      <c r="DV140" t="n">
-        <v>27338</v>
-      </c>
-      <c r="DW140" t="n">
-        <v>2069169</v>
+      <c r="DV141" t="n">
+        <v>27528</v>
+      </c>
+      <c r="DW141" t="n">
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>
@@ -60433,7 +60818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60786,7 +61171,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>690</v>
+        <v>1175</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -60798,62 +61183,111 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2477</v>
+        <v>2637</v>
       </c>
       <c r="N7" t="n">
         <v>4729</v>
       </c>
       <c r="O7" t="n">
-        <v>12231</v>
+        <v>12876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1275</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>13840</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>5465</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>5000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>3606</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>4107</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>4790</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>2445</v>
       </c>
-      <c r="I8" t="n">
-        <v>3160</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="I9" t="n">
+        <v>3645</v>
+      </c>
+      <c r="J9" t="n">
         <v>2880</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>1640</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>2690</v>
       </c>
-      <c r="M8" t="n">
-        <v>14023</v>
-      </c>
-      <c r="N8" t="n">
-        <v>21372</v>
-      </c>
-      <c r="O8" t="n">
-        <v>85018</v>
+      <c r="M9" t="n">
+        <v>14183</v>
+      </c>
+      <c r="N9" t="n">
+        <v>22647</v>
+      </c>
+      <c r="O9" t="n">
+        <v>86938</v>
       </c>
     </row>
   </sheetData>
@@ -62401,7 +62835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S140"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70907,77 +71341,138 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>4472</v>
+        <v>4632</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1410</v>
+        <v>2145</v>
       </c>
       <c r="S139" t="n">
-        <v>33254</v>
+        <v>34149</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B141" t="n">
         <v>77718</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C141" t="n">
         <v>17331</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D141" t="n">
         <v>62163</v>
       </c>
-      <c r="E140" t="n">
-        <v>854917</v>
-      </c>
-      <c r="F140" t="n">
+      <c r="E141" t="n">
+        <v>856342</v>
+      </c>
+      <c r="F141" t="n">
         <v>5932</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G141" t="n">
         <v>34015</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H141" t="n">
         <v>7499</v>
       </c>
-      <c r="I140" t="n">
+      <c r="I141" t="n">
         <v>284119</v>
       </c>
-      <c r="J140" t="n">
+      <c r="J141" t="n">
         <v>4939</v>
       </c>
-      <c r="K140" t="n">
+      <c r="K141" t="n">
         <v>109060</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L141" t="n">
         <v>35385</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M141" t="n">
         <v>8153</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N141" t="n">
         <v>42</v>
       </c>
-      <c r="O140" t="n">
+      <c r="O141" t="n">
         <v>22052</v>
       </c>
-      <c r="P140" t="n">
-        <v>421756</v>
-      </c>
-      <c r="Q140" t="n">
+      <c r="P141" t="n">
+        <v>421916</v>
+      </c>
+      <c r="Q141" t="n">
         <v>36635</v>
       </c>
-      <c r="R140" t="n">
-        <v>87453</v>
-      </c>
-      <c r="S140" t="n">
-        <v>2069169</v>
+      <c r="R141" t="n">
+        <v>88188</v>
+      </c>
+      <c r="S141" t="n">
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>
@@ -80333,7 +80828,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>690</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="133">
@@ -80343,7 +80838,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>48134</v>
+        <v>48619</v>
       </c>
     </row>
     <row r="135">
@@ -80451,7 +80946,7 @@
         <v>2026</v>
       </c>
       <c r="B147" t="n">
-        <v>3160</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="148">
@@ -80461,7 +80956,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>48134</v>
+        <v>48619</v>
       </c>
     </row>
   </sheetData>
@@ -82221,7 +82716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89440,7 +89935,7 @@
         <v>4729</v>
       </c>
       <c r="C139" t="n">
-        <v>2477</v>
+        <v>2637</v>
       </c>
       <c r="D139" t="n">
         <v>385</v>
@@ -89458,7 +89953,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>21023</v>
+        <v>21273</v>
       </c>
       <c r="J139" t="n">
         <v>1670</v>
@@ -89476,62 +89971,114 @@
         <v>405</v>
       </c>
       <c r="O139" t="n">
-        <v>690</v>
+        <v>1175</v>
       </c>
       <c r="P139" t="n">
-        <v>33254</v>
+        <v>34149</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1275</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>150</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>396723</v>
-      </c>
-      <c r="C140" t="n">
-        <v>223048</v>
-      </c>
-      <c r="D140" t="n">
+      <c r="B141" t="n">
+        <v>397998</v>
+      </c>
+      <c r="C141" t="n">
+        <v>223208</v>
+      </c>
+      <c r="D141" t="n">
         <v>58168</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E141" t="n">
         <v>14291</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F141" t="n">
         <v>67925</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G141" t="n">
         <v>23492</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H141" t="n">
         <v>6860</v>
       </c>
-      <c r="I140" t="n">
-        <v>748061</v>
-      </c>
-      <c r="J140" t="n">
+      <c r="I141" t="n">
+        <v>748461</v>
+      </c>
+      <c r="J141" t="n">
         <v>217913</v>
       </c>
-      <c r="K140" t="n">
+      <c r="K141" t="n">
         <v>32660</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L141" t="n">
         <v>61344</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M141" t="n">
         <v>99974</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N141" t="n">
         <v>70576</v>
       </c>
-      <c r="O140" t="n">
-        <v>48134</v>
-      </c>
-      <c r="P140" t="n">
-        <v>2069169</v>
+      <c r="O141" t="n">
+        <v>48619</v>
+      </c>
+      <c r="P141" t="n">
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>
@@ -90937,7 +91484,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2477</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="140">
@@ -90947,7 +91494,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>223048</v>
+        <v>223208</v>
       </c>
     </row>
     <row r="142">
@@ -91055,7 +91602,7 @@
         <v>2026</v>
       </c>
       <c r="B154" t="n">
-        <v>14023</v>
+        <v>14183</v>
       </c>
     </row>
     <row r="155">
@@ -91065,7 +91612,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>223048</v>
+        <v>223208</v>
       </c>
     </row>
   </sheetData>
@@ -91079,7 +91626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92477,129 +93024,139 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>396723</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="B141" t="n">
+        <v>397998</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B143" t="n">
-        <v>21287</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B144" t="n">
-        <v>31458</v>
+        <v>21287</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B145" t="n">
-        <v>36331</v>
+        <v>31458</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B146" t="n">
-        <v>41722</v>
+        <v>36331</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B147" t="n">
-        <v>35690</v>
+        <v>41722</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B148" t="n">
-        <v>23272</v>
+        <v>35690</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B149" t="n">
-        <v>26164</v>
+        <v>23272</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B150" t="n">
-        <v>34239</v>
+        <v>26164</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B151" t="n">
-        <v>43529</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B152" t="n">
-        <v>39614</v>
+        <v>43529</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="n">
-        <v>42045</v>
+        <v>39614</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>42045</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>2026</v>
       </c>
-      <c r="B154" t="n">
-        <v>21372</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>22647</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>396723</v>
+      <c r="B156" t="n">
+        <v>397998</v>
       </c>
     </row>
   </sheetData>
@@ -97495,10 +98052,10 @@
         <v>435</v>
       </c>
       <c r="J13" t="n">
-        <v>1160</v>
+        <v>1320</v>
       </c>
       <c r="K13" t="n">
-        <v>745</v>
+        <v>995</v>
       </c>
       <c r="L13" t="n">
         <v>825</v>
@@ -97519,7 +98076,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>23817</v>
+        <v>25092</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -97720,7 +98277,7 @@
         <v>30</v>
       </c>
       <c r="CG13" t="n">
-        <v>1690</v>
+        <v>1985</v>
       </c>
       <c r="CH13" t="n">
         <v>467</v>
@@ -97831,7 +98388,7 @@
         <v>395</v>
       </c>
       <c r="DR13" t="n">
-        <v>4446</v>
+        <v>4596</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -97843,10 +98400,10 @@
         <v>275</v>
       </c>
       <c r="DV13" t="n">
-        <v>1470</v>
+        <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>150156</v>
+        <v>152476</v>
       </c>
     </row>
     <row r="14">
@@ -97880,10 +98437,10 @@
         <v>3040</v>
       </c>
       <c r="J14" t="n">
-        <v>21435</v>
+        <v>21595</v>
       </c>
       <c r="K14" t="n">
-        <v>16672</v>
+        <v>16922</v>
       </c>
       <c r="L14" t="n">
         <v>5790</v>
@@ -97904,7 +98461,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>429383</v>
+        <v>430658</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98105,7 +98662,7 @@
         <v>145</v>
       </c>
       <c r="CG14" t="n">
-        <v>20796</v>
+        <v>21091</v>
       </c>
       <c r="CH14" t="n">
         <v>3642</v>
@@ -98216,7 +98773,7 @@
         <v>7725</v>
       </c>
       <c r="DR14" t="n">
-        <v>57741</v>
+        <v>57891</v>
       </c>
       <c r="DS14" t="n">
         <v>1450</v>
@@ -98228,10 +98785,10 @@
         <v>4927</v>
       </c>
       <c r="DV14" t="n">
-        <v>27338</v>
+        <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2069169</v>
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>
@@ -99008,7 +99565,7 @@
         <v>4835</v>
       </c>
       <c r="E13" t="n">
-        <v>63195</v>
+        <v>64620</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99041,16 +99598,16 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>27235</v>
+        <v>27395</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
       </c>
       <c r="R13" t="n">
-        <v>8112</v>
+        <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>150156</v>
+        <v>152476</v>
       </c>
     </row>
     <row r="14">
@@ -99069,7 +99626,7 @@
         <v>62163</v>
       </c>
       <c r="E14" t="n">
-        <v>854917</v>
+        <v>856342</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99102,16 +99659,16 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>421756</v>
+        <v>421916</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
       </c>
       <c r="R14" t="n">
-        <v>87453</v>
+        <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2069169</v>
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>
@@ -99765,10 +100322,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>21372</v>
+        <v>22647</v>
       </c>
       <c r="C13" t="n">
-        <v>14023</v>
+        <v>14183</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -99786,7 +100343,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>65138</v>
+        <v>65538</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -99804,10 +100361,10 @@
         <v>4790</v>
       </c>
       <c r="O13" t="n">
-        <v>3160</v>
+        <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>150156</v>
+        <v>152476</v>
       </c>
     </row>
     <row r="14">
@@ -99817,10 +100374,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>396723</v>
+        <v>397998</v>
       </c>
       <c r="C14" t="n">
-        <v>223048</v>
+        <v>223208</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -99838,7 +100395,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>748061</v>
+        <v>748461</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -99856,10 +100413,10 @@
         <v>70576</v>
       </c>
       <c r="O14" t="n">
-        <v>48134</v>
+        <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2069169</v>
+        <v>2071489</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54346,7 +54346,7 @@
         <v>0</v>
       </c>
       <c r="AR140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS140" t="n">
         <v>0</v>
@@ -54379,7 +54379,7 @@
         <v>0</v>
       </c>
       <c r="BC140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="141">
@@ -54731,7 +54731,7 @@
         <v>2009</v>
       </c>
       <c r="AR141" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AS141" t="n">
         <v>262</v>
@@ -54764,7 +54764,7 @@
         <v>3155</v>
       </c>
       <c r="BC141" t="n">
-        <v>9764</v>
+        <v>9766</v>
       </c>
       <c r="BD141" t="n">
         <v>6787</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>
@@ -71366,7 +71366,7 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>1425</v>
@@ -71381,7 +71381,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -71411,7 +71411,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="141">
@@ -71427,7 +71427,7 @@
         <v>17331</v>
       </c>
       <c r="D141" t="n">
-        <v>62163</v>
+        <v>62165</v>
       </c>
       <c r="E141" t="n">
         <v>856342</v>
@@ -71442,7 +71442,7 @@
         <v>7499</v>
       </c>
       <c r="I141" t="n">
-        <v>284119</v>
+        <v>284121</v>
       </c>
       <c r="J141" t="n">
         <v>4939</v>
@@ -71472,7 +71472,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>
@@ -90005,7 +90005,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -90026,7 +90026,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="141">
@@ -90057,7 +90057,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>748461</v>
+        <v>748465</v>
       </c>
       <c r="J141" t="n">
         <v>217913</v>
@@ -90078,7 +90078,7 @@
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>
@@ -98154,7 +98154,7 @@
         <v>140</v>
       </c>
       <c r="AR13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AS13" t="n">
         <v>262</v>
@@ -98187,7 +98187,7 @@
         <v>210</v>
       </c>
       <c r="BC13" t="n">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="BD13" t="n">
         <v>80</v>
@@ -98403,7 +98403,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>152476</v>
+        <v>152480</v>
       </c>
     </row>
     <row r="14">
@@ -98539,7 +98539,7 @@
         <v>2009</v>
       </c>
       <c r="AR14" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AS14" t="n">
         <v>262</v>
@@ -98572,7 +98572,7 @@
         <v>3155</v>
       </c>
       <c r="BC14" t="n">
-        <v>9764</v>
+        <v>9766</v>
       </c>
       <c r="BD14" t="n">
         <v>6787</v>
@@ -98788,7 +98788,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>
@@ -99562,7 +99562,7 @@
         <v>2075</v>
       </c>
       <c r="D13" t="n">
-        <v>4835</v>
+        <v>4837</v>
       </c>
       <c r="E13" t="n">
         <v>64620</v>
@@ -99577,7 +99577,7 @@
         <v>1215</v>
       </c>
       <c r="I13" t="n">
-        <v>19221</v>
+        <v>19223</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99607,7 +99607,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>152476</v>
+        <v>152480</v>
       </c>
     </row>
     <row r="14">
@@ -99623,7 +99623,7 @@
         <v>17331</v>
       </c>
       <c r="D14" t="n">
-        <v>62163</v>
+        <v>62165</v>
       </c>
       <c r="E14" t="n">
         <v>856342</v>
@@ -99638,7 +99638,7 @@
         <v>7499</v>
       </c>
       <c r="I14" t="n">
-        <v>284119</v>
+        <v>284121</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99668,7 +99668,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>
@@ -100343,7 +100343,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>65538</v>
+        <v>65542</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -100364,7 +100364,7 @@
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>152476</v>
+        <v>152480</v>
       </c>
     </row>
     <row r="14">
@@ -100395,7 +100395,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>748461</v>
+        <v>748465</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -100416,7 +100416,7 @@
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2071489</v>
+        <v>2071493</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54394,7 +54394,7 @@
         <v>0</v>
       </c>
       <c r="BH140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BI140" t="n">
         <v>0</v>
@@ -54412,7 +54412,7 @@
         <v>0</v>
       </c>
       <c r="BN140" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="BO140" t="n">
         <v>0</v>
@@ -54430,7 +54430,7 @@
         <v>0</v>
       </c>
       <c r="BT140" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="BU140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>1429</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="141">
@@ -54779,7 +54779,7 @@
         <v>10010</v>
       </c>
       <c r="BH141" t="n">
-        <v>1146</v>
+        <v>1196</v>
       </c>
       <c r="BI141" t="n">
         <v>13284</v>
@@ -54797,7 +54797,7 @@
         <v>1992</v>
       </c>
       <c r="BN141" t="n">
-        <v>112539</v>
+        <v>114139</v>
       </c>
       <c r="BO141" t="n">
         <v>4080</v>
@@ -54815,7 +54815,7 @@
         <v>13434</v>
       </c>
       <c r="BT141" t="n">
-        <v>26576</v>
+        <v>26996</v>
       </c>
       <c r="BU141" t="n">
         <v>5115</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>
@@ -71366,10 +71366,10 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="E140" t="n">
-        <v>1425</v>
+        <v>3025</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71387,7 +71387,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -71411,7 +71411,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>1429</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="141">
@@ -71427,10 +71427,10 @@
         <v>17331</v>
       </c>
       <c r="D141" t="n">
-        <v>62165</v>
+        <v>62215</v>
       </c>
       <c r="E141" t="n">
-        <v>856342</v>
+        <v>857942</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71448,7 +71448,7 @@
         <v>4939</v>
       </c>
       <c r="K141" t="n">
-        <v>109060</v>
+        <v>109480</v>
       </c>
       <c r="L141" t="n">
         <v>35385</v>
@@ -71472,7 +71472,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>
@@ -90005,7 +90005,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>154</v>
+        <v>2224</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -90026,7 +90026,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>1429</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="141">
@@ -90057,7 +90057,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>748465</v>
+        <v>750535</v>
       </c>
       <c r="J141" t="n">
         <v>217913</v>
@@ -90078,7 +90078,7 @@
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>
@@ -98202,7 +98202,7 @@
         <v>2840</v>
       </c>
       <c r="BH13" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="BI13" t="n">
         <v>1320</v>
@@ -98220,7 +98220,7 @@
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>18932</v>
+        <v>20532</v>
       </c>
       <c r="BO13" t="n">
         <v>235</v>
@@ -98238,7 +98238,7 @@
         <v>1064</v>
       </c>
       <c r="BT13" t="n">
-        <v>2882</v>
+        <v>3302</v>
       </c>
       <c r="BU13" t="n">
         <v>290</v>
@@ -98403,7 +98403,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>152480</v>
+        <v>154550</v>
       </c>
     </row>
     <row r="14">
@@ -98587,7 +98587,7 @@
         <v>10010</v>
       </c>
       <c r="BH14" t="n">
-        <v>1146</v>
+        <v>1196</v>
       </c>
       <c r="BI14" t="n">
         <v>13284</v>
@@ -98605,7 +98605,7 @@
         <v>1992</v>
       </c>
       <c r="BN14" t="n">
-        <v>112539</v>
+        <v>114139</v>
       </c>
       <c r="BO14" t="n">
         <v>4080</v>
@@ -98623,7 +98623,7 @@
         <v>13434</v>
       </c>
       <c r="BT14" t="n">
-        <v>26576</v>
+        <v>26996</v>
       </c>
       <c r="BU14" t="n">
         <v>5115</v>
@@ -98788,7 +98788,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>
@@ -99562,10 +99562,10 @@
         <v>2075</v>
       </c>
       <c r="D13" t="n">
-        <v>4837</v>
+        <v>4887</v>
       </c>
       <c r="E13" t="n">
-        <v>64620</v>
+        <v>66220</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99583,7 +99583,7 @@
         <v>912</v>
       </c>
       <c r="K13" t="n">
-        <v>8763</v>
+        <v>9183</v>
       </c>
       <c r="L13" t="n">
         <v>2177</v>
@@ -99607,7 +99607,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>152480</v>
+        <v>154550</v>
       </c>
     </row>
     <row r="14">
@@ -99623,10 +99623,10 @@
         <v>17331</v>
       </c>
       <c r="D14" t="n">
-        <v>62165</v>
+        <v>62215</v>
       </c>
       <c r="E14" t="n">
-        <v>856342</v>
+        <v>857942</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99644,7 +99644,7 @@
         <v>4939</v>
       </c>
       <c r="K14" t="n">
-        <v>109060</v>
+        <v>109480</v>
       </c>
       <c r="L14" t="n">
         <v>35385</v>
@@ -99668,7 +99668,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>
@@ -100343,7 +100343,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>65542</v>
+        <v>67612</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -100364,7 +100364,7 @@
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>152480</v>
+        <v>154550</v>
       </c>
     </row>
     <row r="14">
@@ -100395,7 +100395,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>748465</v>
+        <v>750535</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -100416,7 +100416,7 @@
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2071493</v>
+        <v>2073563</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54220,7 +54220,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -54268,7 +54268,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1275</v>
+        <v>1490</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -54283,7 +54283,7 @@
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="X140" t="n">
         <v>0</v>
@@ -54331,7 +54331,7 @@
         <v>0</v>
       </c>
       <c r="AM140" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN140" t="n">
         <v>0</v>
@@ -54376,7 +54376,7 @@
         <v>0</v>
       </c>
       <c r="BB140" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="BC140" t="n">
         <v>2</v>
@@ -54406,7 +54406,7 @@
         <v>0</v>
       </c>
       <c r="BL140" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="BM140" t="n">
         <v>0</v>
@@ -54433,13 +54433,13 @@
         <v>420</v>
       </c>
       <c r="BU140" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="BV140" t="n">
         <v>0</v>
       </c>
       <c r="BW140" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BX140" t="n">
         <v>0</v>
@@ -54460,7 +54460,7 @@
         <v>0</v>
       </c>
       <c r="CD140" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="CE140" t="n">
         <v>0</v>
@@ -54511,7 +54511,7 @@
         <v>0</v>
       </c>
       <c r="CU140" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CV140" t="n">
         <v>0</v>
@@ -54547,7 +54547,7 @@
         <v>0</v>
       </c>
       <c r="DG140" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DH140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>3499</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="141">
@@ -54605,7 +54605,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2382</v>
+        <v>2547</v>
       </c>
       <c r="C141" t="n">
         <v>935</v>
@@ -54653,7 +54653,7 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>430658</v>
+        <v>430873</v>
       </c>
       <c r="S141" t="n">
         <v>925</v>
@@ -54668,7 +54668,7 @@
         <v>14436</v>
       </c>
       <c r="W141" t="n">
-        <v>23953</v>
+        <v>24363</v>
       </c>
       <c r="X141" t="n">
         <v>4712</v>
@@ -54716,7 +54716,7 @@
         <v>374</v>
       </c>
       <c r="AM141" t="n">
-        <v>50659</v>
+        <v>50699</v>
       </c>
       <c r="AN141" t="n">
         <v>4755</v>
@@ -54761,7 +54761,7 @@
         <v>6666</v>
       </c>
       <c r="BB141" t="n">
-        <v>3155</v>
+        <v>3280</v>
       </c>
       <c r="BC141" t="n">
         <v>9766</v>
@@ -54791,7 +54791,7 @@
         <v>660</v>
       </c>
       <c r="BL141" t="n">
-        <v>47345</v>
+        <v>47670</v>
       </c>
       <c r="BM141" t="n">
         <v>1992</v>
@@ -54818,13 +54818,13 @@
         <v>26996</v>
       </c>
       <c r="BU141" t="n">
-        <v>5115</v>
+        <v>5420</v>
       </c>
       <c r="BV141" t="n">
         <v>5791</v>
       </c>
       <c r="BW141" t="n">
-        <v>34491</v>
+        <v>34641</v>
       </c>
       <c r="BX141" t="n">
         <v>5175</v>
@@ -54845,7 +54845,7 @@
         <v>435</v>
       </c>
       <c r="CD141" t="n">
-        <v>15673</v>
+        <v>16073</v>
       </c>
       <c r="CE141" t="n">
         <v>5771</v>
@@ -54896,7 +54896,7 @@
         <v>65155</v>
       </c>
       <c r="CU141" t="n">
-        <v>2384</v>
+        <v>2509</v>
       </c>
       <c r="CV141" t="n">
         <v>1310</v>
@@ -54932,7 +54932,7 @@
         <v>47</v>
       </c>
       <c r="DG141" t="n">
-        <v>20580</v>
+        <v>20680</v>
       </c>
       <c r="DH141" t="n">
         <v>37481</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>
@@ -61208,7 +61208,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -61232,13 +61232,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N8" t="n">
-        <v>1275</v>
+        <v>1490</v>
       </c>
       <c r="O8" t="n">
-        <v>1275</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="9">
@@ -61257,7 +61257,7 @@
         <v>5000</v>
       </c>
       <c r="E9" t="n">
-        <v>3606</v>
+        <v>4031</v>
       </c>
       <c r="F9" t="n">
         <v>4107</v>
@@ -61281,13 +61281,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>14183</v>
+        <v>14333</v>
       </c>
       <c r="N9" t="n">
-        <v>22647</v>
+        <v>22862</v>
       </c>
       <c r="O9" t="n">
-        <v>86938</v>
+        <v>87728</v>
       </c>
     </row>
   </sheetData>
@@ -71360,7 +71360,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -71369,7 +71369,7 @@
         <v>52</v>
       </c>
       <c r="E140" t="n">
-        <v>3025</v>
+        <v>3815</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71378,7 +71378,7 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="I140" t="n">
         <v>2</v>
@@ -71393,7 +71393,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -71402,7 +71402,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -71411,7 +71411,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>3499</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="141">
@@ -71421,7 +71421,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>77718</v>
+        <v>78143</v>
       </c>
       <c r="C141" t="n">
         <v>17331</v>
@@ -71430,7 +71430,7 @@
         <v>62215</v>
       </c>
       <c r="E141" t="n">
-        <v>857942</v>
+        <v>858732</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71439,7 +71439,7 @@
         <v>34015</v>
       </c>
       <c r="H141" t="n">
-        <v>7499</v>
+        <v>7929</v>
       </c>
       <c r="I141" t="n">
         <v>284121</v>
@@ -71454,7 +71454,7 @@
         <v>35385</v>
       </c>
       <c r="M141" t="n">
-        <v>8153</v>
+        <v>8318</v>
       </c>
       <c r="N141" t="n">
         <v>42</v>
@@ -71463,7 +71463,7 @@
         <v>22052</v>
       </c>
       <c r="P141" t="n">
-        <v>421916</v>
+        <v>422466</v>
       </c>
       <c r="Q141" t="n">
         <v>36635</v>
@@ -71472,7 +71472,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>
@@ -74434,7 +74434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75692,129 +75692,139 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>67925</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="B127" t="n">
+        <v>68350</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B129" t="n">
-        <v>1095</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B130" t="n">
-        <v>2905</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B131" t="n">
-        <v>3064</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B132" t="n">
-        <v>5885</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B133" t="n">
-        <v>6805</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B134" t="n">
-        <v>6325</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B135" t="n">
-        <v>4515</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B136" t="n">
-        <v>7158</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B137" t="n">
-        <v>7879</v>
+        <v>7158</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B138" t="n">
-        <v>9963</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B139" t="n">
-        <v>8725</v>
+        <v>9963</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8725</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
         <v>2026</v>
       </c>
-      <c r="B140" t="n">
-        <v>3606</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="B141" t="n">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>67925</v>
+      <c r="B142" t="n">
+        <v>68350</v>
       </c>
     </row>
   </sheetData>
@@ -89984,10 +89994,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1275</v>
+        <v>1490</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -89996,7 +90006,7 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -90005,7 +90015,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>2224</v>
+        <v>3794</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -90026,7 +90036,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>3499</v>
+        <v>5859</v>
       </c>
     </row>
     <row r="141">
@@ -90036,10 +90046,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>397998</v>
+        <v>398213</v>
       </c>
       <c r="C141" t="n">
-        <v>223208</v>
+        <v>223358</v>
       </c>
       <c r="D141" t="n">
         <v>58168</v>
@@ -90048,7 +90058,7 @@
         <v>14291</v>
       </c>
       <c r="F141" t="n">
-        <v>67925</v>
+        <v>68350</v>
       </c>
       <c r="G141" t="n">
         <v>23492</v>
@@ -90057,7 +90067,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>750535</v>
+        <v>752105</v>
       </c>
       <c r="J141" t="n">
         <v>217913</v>
@@ -90078,7 +90088,7 @@
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>
@@ -90092,7 +90102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91490,129 +91500,139 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>223208</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="B141" t="n">
+        <v>223358</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B143" t="n">
-        <v>6670</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B144" t="n">
-        <v>8792</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B145" t="n">
-        <v>15242</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B146" t="n">
-        <v>21112</v>
+        <v>15242</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B147" t="n">
-        <v>21273</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B148" t="n">
-        <v>15805</v>
+        <v>21273</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B149" t="n">
-        <v>18542</v>
+        <v>15805</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B150" t="n">
-        <v>22238</v>
+        <v>18542</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B151" t="n">
-        <v>23463</v>
+        <v>22238</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B152" t="n">
-        <v>27438</v>
+        <v>23463</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="n">
-        <v>28450</v>
+        <v>27438</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>28450</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>2026</v>
       </c>
-      <c r="B154" t="n">
-        <v>14183</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>14333</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>223208</v>
+      <c r="B156" t="n">
+        <v>223358</v>
       </c>
     </row>
   </sheetData>
@@ -93028,7 +93048,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1275</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="141">
@@ -93038,7 +93058,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>397998</v>
+        <v>398213</v>
       </c>
     </row>
     <row r="143">
@@ -93146,7 +93166,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>22647</v>
+        <v>22862</v>
       </c>
     </row>
     <row r="156">
@@ -93156,7 +93176,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>397998</v>
+        <v>398213</v>
       </c>
     </row>
   </sheetData>
@@ -98028,7 +98048,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>345</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -98076,7 +98096,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>25092</v>
+        <v>25307</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -98091,7 +98111,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>1960</v>
+        <v>2370</v>
       </c>
       <c r="X13" t="n">
         <v>720</v>
@@ -98139,7 +98159,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>2116</v>
+        <v>2156</v>
       </c>
       <c r="AN13" t="n">
         <v>165</v>
@@ -98184,7 +98204,7 @@
         <v>460</v>
       </c>
       <c r="BB13" t="n">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="BC13" t="n">
         <v>599</v>
@@ -98214,7 +98234,7 @@
         <v>40</v>
       </c>
       <c r="BL13" t="n">
-        <v>2541</v>
+        <v>2866</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
@@ -98241,13 +98261,13 @@
         <v>3302</v>
       </c>
       <c r="BU13" t="n">
-        <v>290</v>
+        <v>595</v>
       </c>
       <c r="BV13" t="n">
         <v>1037</v>
       </c>
       <c r="BW13" t="n">
-        <v>2274</v>
+        <v>2424</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
@@ -98268,7 +98288,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>1935</v>
+        <v>2335</v>
       </c>
       <c r="CE13" t="n">
         <v>856</v>
@@ -98319,7 +98339,7 @@
         <v>4425</v>
       </c>
       <c r="CU13" t="n">
-        <v>925</v>
+        <v>1050</v>
       </c>
       <c r="CV13" t="n">
         <v>125</v>
@@ -98355,7 +98375,7 @@
         <v>47</v>
       </c>
       <c r="DG13" t="n">
-        <v>1065</v>
+        <v>1165</v>
       </c>
       <c r="DH13" t="n">
         <v>2805</v>
@@ -98403,7 +98423,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>154550</v>
+        <v>156910</v>
       </c>
     </row>
     <row r="14">
@@ -98413,7 +98433,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2382</v>
+        <v>2547</v>
       </c>
       <c r="C14" t="n">
         <v>935</v>
@@ -98461,7 +98481,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>430658</v>
+        <v>430873</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98476,7 +98496,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>23953</v>
+        <v>24363</v>
       </c>
       <c r="X14" t="n">
         <v>4712</v>
@@ -98524,7 +98544,7 @@
         <v>374</v>
       </c>
       <c r="AM14" t="n">
-        <v>50659</v>
+        <v>50699</v>
       </c>
       <c r="AN14" t="n">
         <v>4755</v>
@@ -98569,7 +98589,7 @@
         <v>6666</v>
       </c>
       <c r="BB14" t="n">
-        <v>3155</v>
+        <v>3280</v>
       </c>
       <c r="BC14" t="n">
         <v>9766</v>
@@ -98599,7 +98619,7 @@
         <v>660</v>
       </c>
       <c r="BL14" t="n">
-        <v>47345</v>
+        <v>47670</v>
       </c>
       <c r="BM14" t="n">
         <v>1992</v>
@@ -98626,13 +98646,13 @@
         <v>26996</v>
       </c>
       <c r="BU14" t="n">
-        <v>5115</v>
+        <v>5420</v>
       </c>
       <c r="BV14" t="n">
         <v>5791</v>
       </c>
       <c r="BW14" t="n">
-        <v>34491</v>
+        <v>34641</v>
       </c>
       <c r="BX14" t="n">
         <v>5175</v>
@@ -98653,7 +98673,7 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>15673</v>
+        <v>16073</v>
       </c>
       <c r="CE14" t="n">
         <v>5771</v>
@@ -98704,7 +98724,7 @@
         <v>65155</v>
       </c>
       <c r="CU14" t="n">
-        <v>2384</v>
+        <v>2509</v>
       </c>
       <c r="CV14" t="n">
         <v>1310</v>
@@ -98740,7 +98760,7 @@
         <v>47</v>
       </c>
       <c r="DG14" t="n">
-        <v>20580</v>
+        <v>20680</v>
       </c>
       <c r="DH14" t="n">
         <v>37481</v>
@@ -98788,7 +98808,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>
@@ -99556,7 +99576,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>4663</v>
+        <v>5088</v>
       </c>
       <c r="C13" t="n">
         <v>2075</v>
@@ -99565,7 +99585,7 @@
         <v>4887</v>
       </c>
       <c r="E13" t="n">
-        <v>66220</v>
+        <v>67010</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99574,7 +99594,7 @@
         <v>2825</v>
       </c>
       <c r="H13" t="n">
-        <v>1215</v>
+        <v>1645</v>
       </c>
       <c r="I13" t="n">
         <v>19223</v>
@@ -99589,7 +99609,7 @@
         <v>2177</v>
       </c>
       <c r="M13" t="n">
-        <v>1036</v>
+        <v>1201</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -99598,7 +99618,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>27395</v>
+        <v>27945</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99607,7 +99627,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>154550</v>
+        <v>156910</v>
       </c>
     </row>
     <row r="14">
@@ -99617,7 +99637,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77718</v>
+        <v>78143</v>
       </c>
       <c r="C14" t="n">
         <v>17331</v>
@@ -99626,7 +99646,7 @@
         <v>62215</v>
       </c>
       <c r="E14" t="n">
-        <v>857942</v>
+        <v>858732</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99635,7 +99655,7 @@
         <v>34015</v>
       </c>
       <c r="H14" t="n">
-        <v>7499</v>
+        <v>7929</v>
       </c>
       <c r="I14" t="n">
         <v>284121</v>
@@ -99650,7 +99670,7 @@
         <v>35385</v>
       </c>
       <c r="M14" t="n">
-        <v>8153</v>
+        <v>8318</v>
       </c>
       <c r="N14" t="n">
         <v>42</v>
@@ -99659,7 +99679,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>421916</v>
+        <v>422466</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99668,7 +99688,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>
@@ -100322,10 +100342,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>22647</v>
+        <v>22862</v>
       </c>
       <c r="C13" t="n">
-        <v>14183</v>
+        <v>14333</v>
       </c>
       <c r="D13" t="n">
         <v>4107</v>
@@ -100334,7 +100354,7 @@
         <v>1640</v>
       </c>
       <c r="F13" t="n">
-        <v>3606</v>
+        <v>4031</v>
       </c>
       <c r="G13" t="n">
         <v>2880</v>
@@ -100343,7 +100363,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>67612</v>
+        <v>69182</v>
       </c>
       <c r="J13" t="n">
         <v>13840</v>
@@ -100364,7 +100384,7 @@
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>154550</v>
+        <v>156910</v>
       </c>
     </row>
     <row r="14">
@@ -100374,10 +100394,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>397998</v>
+        <v>398213</v>
       </c>
       <c r="C14" t="n">
-        <v>223208</v>
+        <v>223358</v>
       </c>
       <c r="D14" t="n">
         <v>58168</v>
@@ -100386,7 +100406,7 @@
         <v>14291</v>
       </c>
       <c r="F14" t="n">
-        <v>67925</v>
+        <v>68350</v>
       </c>
       <c r="G14" t="n">
         <v>23492</v>
@@ -100395,7 +100415,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>750535</v>
+        <v>752105</v>
       </c>
       <c r="J14" t="n">
         <v>217913</v>
@@ -100416,7 +100436,7 @@
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2073563</v>
+        <v>2075923</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54277,7 +54277,7 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -54511,7 +54511,7 @@
         <v>0</v>
       </c>
       <c r="CU140" t="n">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="CV140" t="n">
         <v>0</v>
@@ -54532,7 +54532,7 @@
         <v>0</v>
       </c>
       <c r="DB140" t="n">
-        <v>0</v>
+        <v>1245</v>
       </c>
       <c r="DC140" t="n">
         <v>0</v>
@@ -54556,7 +54556,7 @@
         <v>0</v>
       </c>
       <c r="DJ140" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="DK140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>5859</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="141">
@@ -54662,7 +54662,7 @@
         <v>872</v>
       </c>
       <c r="U141" t="n">
-        <v>2001</v>
+        <v>2146</v>
       </c>
       <c r="V141" t="n">
         <v>14436</v>
@@ -54896,7 +54896,7 @@
         <v>65155</v>
       </c>
       <c r="CU141" t="n">
-        <v>2509</v>
+        <v>2579</v>
       </c>
       <c r="CV141" t="n">
         <v>1310</v>
@@ -54917,7 +54917,7 @@
         <v>13766</v>
       </c>
       <c r="DB141" t="n">
-        <v>217913</v>
+        <v>219158</v>
       </c>
       <c r="DC141" t="n">
         <v>1030</v>
@@ -54941,7 +54941,7 @@
         <v>23863</v>
       </c>
       <c r="DJ141" t="n">
-        <v>99974</v>
+        <v>100064</v>
       </c>
       <c r="DK141" t="n">
         <v>1240</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>
@@ -61199,10 +61199,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1245</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -61238,7 +61238,7 @@
         <v>1490</v>
       </c>
       <c r="O8" t="n">
-        <v>2065</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="9">
@@ -61248,10 +61248,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13840</v>
+        <v>15085</v>
       </c>
       <c r="C9" t="n">
-        <v>5465</v>
+        <v>5555</v>
       </c>
       <c r="D9" t="n">
         <v>5000</v>
@@ -61287,7 +61287,7 @@
         <v>22862</v>
       </c>
       <c r="O9" t="n">
-        <v>87728</v>
+        <v>89063</v>
       </c>
     </row>
   </sheetData>
@@ -61301,7 +61301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62699,129 +62699,139 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>217913</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="B141" t="n">
+        <v>219158</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B143" t="n">
-        <v>6885</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B144" t="n">
-        <v>10546</v>
+        <v>6885</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B145" t="n">
-        <v>10537</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B146" t="n">
-        <v>13913</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B147" t="n">
-        <v>16988</v>
+        <v>13913</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B148" t="n">
-        <v>17285</v>
+        <v>16988</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B149" t="n">
-        <v>21884</v>
+        <v>17285</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B150" t="n">
-        <v>25698</v>
+        <v>21884</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B151" t="n">
-        <v>24908</v>
+        <v>25698</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B152" t="n">
-        <v>26942</v>
+        <v>24908</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="n">
-        <v>28487</v>
+        <v>26942</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>28487</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>2026</v>
       </c>
-      <c r="B154" t="n">
-        <v>13840</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>15085</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>217913</v>
+      <c r="B156" t="n">
+        <v>219158</v>
       </c>
     </row>
   </sheetData>
@@ -71369,7 +71379,7 @@
         <v>52</v>
       </c>
       <c r="E140" t="n">
-        <v>3815</v>
+        <v>3960</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71378,10 +71388,10 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1247</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -71402,7 +71412,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>550</v>
+        <v>640</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -71411,7 +71421,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>5859</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="141">
@@ -71430,7 +71440,7 @@
         <v>62215</v>
       </c>
       <c r="E141" t="n">
-        <v>858732</v>
+        <v>858877</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71439,10 +71449,10 @@
         <v>34015</v>
       </c>
       <c r="H141" t="n">
-        <v>7929</v>
+        <v>7999</v>
       </c>
       <c r="I141" t="n">
-        <v>284121</v>
+        <v>285366</v>
       </c>
       <c r="J141" t="n">
         <v>4939</v>
@@ -71463,7 +71473,7 @@
         <v>22052</v>
       </c>
       <c r="P141" t="n">
-        <v>422466</v>
+        <v>422556</v>
       </c>
       <c r="Q141" t="n">
         <v>36635</v>
@@ -71472,7 +71482,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>
@@ -71486,7 +71496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72884,129 +72894,139 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>99974</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="B141" t="n">
+        <v>100064</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B143" t="n">
-        <v>4620</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B144" t="n">
-        <v>9287</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B145" t="n">
-        <v>9052</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B146" t="n">
-        <v>11885</v>
+        <v>9052</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B147" t="n">
-        <v>10945</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B148" t="n">
-        <v>5985</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B149" t="n">
-        <v>7702</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B150" t="n">
-        <v>7774</v>
+        <v>7702</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B151" t="n">
-        <v>7025</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B152" t="n">
-        <v>9804</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B153" t="n">
-        <v>10430</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>10430</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>2026</v>
       </c>
-      <c r="B154" t="n">
-        <v>5465</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>99974</v>
+      <c r="B156" t="n">
+        <v>100064</v>
       </c>
     </row>
   </sheetData>
@@ -90015,10 +90035,10 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>3794</v>
+        <v>4009</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1245</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -90027,7 +90047,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -90036,7 +90056,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>5859</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="141">
@@ -90067,10 +90087,10 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>752105</v>
+        <v>752320</v>
       </c>
       <c r="J141" t="n">
-        <v>217913</v>
+        <v>219158</v>
       </c>
       <c r="K141" t="n">
         <v>32660</v>
@@ -90079,7 +90099,7 @@
         <v>61344</v>
       </c>
       <c r="M141" t="n">
-        <v>99974</v>
+        <v>100064</v>
       </c>
       <c r="N141" t="n">
         <v>70576</v>
@@ -90088,7 +90108,7 @@
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>
@@ -98105,7 +98125,7 @@
         <v>500</v>
       </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="V13" t="n">
         <v>111</v>
@@ -98339,7 +98359,7 @@
         <v>4425</v>
       </c>
       <c r="CU13" t="n">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="CV13" t="n">
         <v>125</v>
@@ -98360,7 +98380,7 @@
         <v>910</v>
       </c>
       <c r="DB13" t="n">
-        <v>13840</v>
+        <v>15085</v>
       </c>
       <c r="DC13" t="n">
         <v>30</v>
@@ -98384,7 +98404,7 @@
         <v>2195</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5465</v>
+        <v>5555</v>
       </c>
       <c r="DK13" t="n">
         <v>420</v>
@@ -98423,7 +98443,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>156910</v>
+        <v>158460</v>
       </c>
     </row>
     <row r="14">
@@ -98490,7 +98510,7 @@
         <v>872</v>
       </c>
       <c r="U14" t="n">
-        <v>2001</v>
+        <v>2146</v>
       </c>
       <c r="V14" t="n">
         <v>14436</v>
@@ -98724,7 +98744,7 @@
         <v>65155</v>
       </c>
       <c r="CU14" t="n">
-        <v>2509</v>
+        <v>2579</v>
       </c>
       <c r="CV14" t="n">
         <v>1310</v>
@@ -98745,7 +98765,7 @@
         <v>13766</v>
       </c>
       <c r="DB14" t="n">
-        <v>217913</v>
+        <v>219158</v>
       </c>
       <c r="DC14" t="n">
         <v>1030</v>
@@ -98769,7 +98789,7 @@
         <v>23863</v>
       </c>
       <c r="DJ14" t="n">
-        <v>99974</v>
+        <v>100064</v>
       </c>
       <c r="DK14" t="n">
         <v>1240</v>
@@ -98808,7 +98828,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>
@@ -99585,7 +99605,7 @@
         <v>4887</v>
       </c>
       <c r="E13" t="n">
-        <v>67010</v>
+        <v>67155</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99594,10 +99614,10 @@
         <v>2825</v>
       </c>
       <c r="H13" t="n">
-        <v>1645</v>
+        <v>1715</v>
       </c>
       <c r="I13" t="n">
-        <v>19223</v>
+        <v>20468</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99618,7 +99638,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>27945</v>
+        <v>28035</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99627,7 +99647,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>156910</v>
+        <v>158460</v>
       </c>
     </row>
     <row r="14">
@@ -99646,7 +99666,7 @@
         <v>62215</v>
       </c>
       <c r="E14" t="n">
-        <v>858732</v>
+        <v>858877</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99655,10 +99675,10 @@
         <v>34015</v>
       </c>
       <c r="H14" t="n">
-        <v>7929</v>
+        <v>7999</v>
       </c>
       <c r="I14" t="n">
-        <v>284121</v>
+        <v>285366</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99679,7 +99699,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>422466</v>
+        <v>422556</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99688,7 +99708,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>
@@ -100363,10 +100383,10 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>69182</v>
+        <v>69397</v>
       </c>
       <c r="J13" t="n">
-        <v>13840</v>
+        <v>15085</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -100375,7 +100395,7 @@
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>5465</v>
+        <v>5555</v>
       </c>
       <c r="N13" t="n">
         <v>4790</v>
@@ -100384,7 +100404,7 @@
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>156910</v>
+        <v>158460</v>
       </c>
     </row>
     <row r="14">
@@ -100415,10 +100435,10 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>752105</v>
+        <v>752320</v>
       </c>
       <c r="J14" t="n">
-        <v>217913</v>
+        <v>219158</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -100427,7 +100447,7 @@
         <v>61344</v>
       </c>
       <c r="M14" t="n">
-        <v>99974</v>
+        <v>100064</v>
       </c>
       <c r="N14" t="n">
         <v>70576</v>
@@ -100436,7 +100456,7 @@
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2075923</v>
+        <v>2077473</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
         <v>30</v>
@@ -6874,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
         <v>35</v>
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -8814,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K22" t="n">
         <v>180</v>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K26" t="n">
         <v>45</v>
@@ -11494,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -11509,7 +11509,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
@@ -12649,7 +12649,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="F32" t="n">
         <v>40</v>
@@ -12664,7 +12664,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K32" t="n">
         <v>165</v>
@@ -13034,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="K33" t="n">
         <v>85</v>
@@ -13419,7 +13419,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="F34" t="n">
         <v>20</v>
@@ -13434,7 +13434,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K34" t="n">
         <v>100</v>
@@ -16114,7 +16114,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>785</v>
+        <v>760</v>
       </c>
       <c r="F41" t="n">
         <v>50</v>
@@ -16129,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -16884,7 +16884,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>565</v>
+        <v>540</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="K43" t="n">
         <v>130</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -18824,7 +18824,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -21119,7 +21119,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -23044,7 +23044,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -23059,7 +23059,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K59" t="n">
         <v>75</v>
@@ -28819,7 +28819,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -28834,7 +28834,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -29589,7 +29589,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -29604,7 +29604,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -37304,7 +37304,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="K96" t="n">
         <v>75</v>
@@ -38444,7 +38444,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>761</v>
+        <v>741</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -38459,7 +38459,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -44989,7 +44989,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>767</v>
+        <v>727</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -45004,7 +45004,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K116" t="n">
         <v>440</v>
@@ -46914,7 +46914,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -46929,7 +46929,7 @@
         <v>75</v>
       </c>
       <c r="J121" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="K121" t="n">
         <v>70</v>
@@ -48839,7 +48839,7 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -48854,7 +48854,7 @@
         <v>190</v>
       </c>
       <c r="J126" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K126" t="n">
         <v>455</v>
@@ -54268,7 +54268,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1490</v>
+        <v>1795</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -54508,7 +54508,7 @@
         <v>0</v>
       </c>
       <c r="CT140" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="CU140" t="n">
         <v>195</v>
@@ -54580,13 +54580,13 @@
         <v>0</v>
       </c>
       <c r="DR140" t="n">
-        <v>150</v>
+        <v>570</v>
       </c>
       <c r="DS140" t="n">
         <v>0</v>
       </c>
       <c r="DT140" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="DU140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>7409</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="141">
@@ -54614,7 +54614,7 @@
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>72167</v>
+        <v>71467</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -54629,7 +54629,7 @@
         <v>3040</v>
       </c>
       <c r="J141" t="n">
-        <v>21595</v>
+        <v>22295</v>
       </c>
       <c r="K141" t="n">
         <v>16922</v>
@@ -54653,7 +54653,7 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>430873</v>
+        <v>431178</v>
       </c>
       <c r="S141" t="n">
         <v>925</v>
@@ -54893,7 +54893,7 @@
         <v>2</v>
       </c>
       <c r="CT141" t="n">
-        <v>65155</v>
+        <v>65475</v>
       </c>
       <c r="CU141" t="n">
         <v>2579</v>
@@ -54965,13 +54965,13 @@
         <v>7725</v>
       </c>
       <c r="DR141" t="n">
-        <v>57891</v>
+        <v>58311</v>
       </c>
       <c r="DS141" t="n">
         <v>1450</v>
       </c>
       <c r="DT141" t="n">
-        <v>70576</v>
+        <v>71211</v>
       </c>
       <c r="DU141" t="n">
         <v>4927</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>
@@ -61214,7 +61214,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -61235,10 +61235,10 @@
         <v>150</v>
       </c>
       <c r="N8" t="n">
-        <v>1490</v>
+        <v>1795</v>
       </c>
       <c r="O8" t="n">
-        <v>3400</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="9">
@@ -61263,7 +61263,7 @@
         <v>4107</v>
       </c>
       <c r="G9" t="n">
-        <v>4790</v>
+        <v>5425</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -61284,10 +61284,10 @@
         <v>14333</v>
       </c>
       <c r="N9" t="n">
-        <v>22862</v>
+        <v>23167</v>
       </c>
       <c r="O9" t="n">
-        <v>89063</v>
+        <v>90003</v>
       </c>
     </row>
   </sheetData>
@@ -71379,7 +71379,7 @@
         <v>52</v>
       </c>
       <c r="E140" t="n">
-        <v>3960</v>
+        <v>5640</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>7409</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="141">
@@ -71440,7 +71440,7 @@
         <v>62215</v>
       </c>
       <c r="E141" t="n">
-        <v>858877</v>
+        <v>860557</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71482,7 +71482,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>
@@ -77122,7 +77122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78480,129 +78480,139 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>70576</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="B137" t="n">
+        <v>71211</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B139" t="n">
-        <v>1540</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B140" t="n">
-        <v>1524</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B141" t="n">
-        <v>1647</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B142" t="n">
-        <v>4030</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B143" t="n">
-        <v>6012</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B144" t="n">
-        <v>4976</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B145" t="n">
-        <v>4864</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B146" t="n">
-        <v>7007</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B147" t="n">
-        <v>8675</v>
+        <v>7007</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B148" t="n">
-        <v>12945</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B149" t="n">
-        <v>12566</v>
+        <v>12945</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B150" t="n">
+        <v>12566</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
         <v>2026</v>
       </c>
-      <c r="B150" t="n">
-        <v>4790</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="B151" t="n">
+        <v>5425</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>70576</v>
+      <c r="B152" t="n">
+        <v>71211</v>
       </c>
     </row>
   </sheetData>
@@ -90014,7 +90024,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1490</v>
+        <v>1795</v>
       </c>
       <c r="C140" t="n">
         <v>150</v>
@@ -90035,7 +90045,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>4009</v>
+        <v>4749</v>
       </c>
       <c r="J140" t="n">
         <v>1245</v>
@@ -90050,13 +90060,13 @@
         <v>90</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>7409</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="141">
@@ -90066,7 +90076,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398213</v>
+        <v>398518</v>
       </c>
       <c r="C141" t="n">
         <v>223358</v>
@@ -90087,7 +90097,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>752320</v>
+        <v>753060</v>
       </c>
       <c r="J141" t="n">
         <v>219158</v>
@@ -90102,13 +90112,13 @@
         <v>100064</v>
       </c>
       <c r="N141" t="n">
-        <v>70576</v>
+        <v>71211</v>
       </c>
       <c r="O141" t="n">
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>
@@ -93068,7 +93078,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1490</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="141">
@@ -93078,7 +93088,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398213</v>
+        <v>398518</v>
       </c>
     </row>
     <row r="143">
@@ -93186,7 +93196,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>22862</v>
+        <v>23167</v>
       </c>
     </row>
     <row r="156">
@@ -93196,7 +93206,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>398213</v>
+        <v>398518</v>
       </c>
     </row>
   </sheetData>
@@ -94247,7 +94257,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2407</v>
+        <v>2247</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -94262,7 +94272,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="K3" t="n">
         <v>690</v>
@@ -94630,7 +94640,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4545</v>
+        <v>4360</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
@@ -94645,7 +94655,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>870</v>
+        <v>1055</v>
       </c>
       <c r="K4" t="n">
         <v>760</v>
@@ -95013,7 +95023,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6490</v>
+        <v>6400</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -95028,7 +95038,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>775</v>
       </c>
       <c r="K5" t="n">
         <v>1165</v>
@@ -95396,7 +95406,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6550</v>
+        <v>6470</v>
       </c>
       <c r="F6" t="n">
         <v>150</v>
@@ -95411,7 +95421,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2000</v>
+        <v>2080</v>
       </c>
       <c r="K6" t="n">
         <v>1265</v>
@@ -96162,7 +96172,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6595</v>
+        <v>6505</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -96177,7 +96187,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3175</v>
+        <v>3265</v>
       </c>
       <c r="K8" t="n">
         <v>1220</v>
@@ -96545,7 +96555,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7964</v>
+        <v>7949</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -96560,7 +96570,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3148</v>
+        <v>3163</v>
       </c>
       <c r="K9" t="n">
         <v>2105</v>
@@ -96928,7 +96938,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7798</v>
+        <v>7778</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -96943,7 +96953,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3005</v>
+        <v>3025</v>
       </c>
       <c r="K10" t="n">
         <v>2010</v>
@@ -97311,7 +97321,7 @@
         <v>85</v>
       </c>
       <c r="E11" t="n">
-        <v>9463</v>
+        <v>9413</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -97326,7 +97336,7 @@
         <v>1310</v>
       </c>
       <c r="J11" t="n">
-        <v>2395</v>
+        <v>2445</v>
       </c>
       <c r="K11" t="n">
         <v>2702</v>
@@ -97694,7 +97704,7 @@
         <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>9123</v>
+        <v>9113</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -97709,7 +97719,7 @@
         <v>1295</v>
       </c>
       <c r="J12" t="n">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="K12" t="n">
         <v>2790</v>
@@ -98116,7 +98126,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>25307</v>
+        <v>25612</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -98356,7 +98366,7 @@
         <v>2</v>
       </c>
       <c r="CT13" t="n">
-        <v>4425</v>
+        <v>4745</v>
       </c>
       <c r="CU13" t="n">
         <v>1120</v>
@@ -98428,13 +98438,13 @@
         <v>395</v>
       </c>
       <c r="DR13" t="n">
-        <v>4596</v>
+        <v>5016</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>4790</v>
+        <v>5425</v>
       </c>
       <c r="DU13" t="n">
         <v>275</v>
@@ -98443,7 +98453,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>158460</v>
+        <v>160140</v>
       </c>
     </row>
     <row r="14">
@@ -98462,7 +98472,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72167</v>
+        <v>71467</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98477,7 +98487,7 @@
         <v>3040</v>
       </c>
       <c r="J14" t="n">
-        <v>21595</v>
+        <v>22295</v>
       </c>
       <c r="K14" t="n">
         <v>16922</v>
@@ -98501,7 +98511,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>430873</v>
+        <v>431178</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98741,7 +98751,7 @@
         <v>2</v>
       </c>
       <c r="CT14" t="n">
-        <v>65155</v>
+        <v>65475</v>
       </c>
       <c r="CU14" t="n">
         <v>2579</v>
@@ -98813,13 +98823,13 @@
         <v>7725</v>
       </c>
       <c r="DR14" t="n">
-        <v>57891</v>
+        <v>58311</v>
       </c>
       <c r="DS14" t="n">
         <v>1450</v>
       </c>
       <c r="DT14" t="n">
-        <v>70576</v>
+        <v>71211</v>
       </c>
       <c r="DU14" t="n">
         <v>4927</v>
@@ -98828,7 +98838,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>
@@ -99605,7 +99615,7 @@
         <v>4887</v>
       </c>
       <c r="E13" t="n">
-        <v>67155</v>
+        <v>68835</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99647,7 +99657,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>158460</v>
+        <v>160140</v>
       </c>
     </row>
     <row r="14">
@@ -99666,7 +99676,7 @@
         <v>62215</v>
       </c>
       <c r="E14" t="n">
-        <v>858877</v>
+        <v>860557</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99708,7 +99718,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>
@@ -100362,7 +100372,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>22862</v>
+        <v>23167</v>
       </c>
       <c r="C13" t="n">
         <v>14333</v>
@@ -100383,7 +100393,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>69397</v>
+        <v>70137</v>
       </c>
       <c r="J13" t="n">
         <v>15085</v>
@@ -100398,13 +100408,13 @@
         <v>5555</v>
       </c>
       <c r="N13" t="n">
-        <v>4790</v>
+        <v>5425</v>
       </c>
       <c r="O13" t="n">
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>158460</v>
+        <v>160140</v>
       </c>
     </row>
     <row r="14">
@@ -100414,7 +100424,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>398213</v>
+        <v>398518</v>
       </c>
       <c r="C14" t="n">
         <v>223358</v>
@@ -100435,7 +100445,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>752320</v>
+        <v>753060</v>
       </c>
       <c r="J14" t="n">
         <v>219158</v>
@@ -100450,13 +100460,13 @@
         <v>100064</v>
       </c>
       <c r="N14" t="n">
-        <v>70576</v>
+        <v>71211</v>
       </c>
       <c r="O14" t="n">
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2077473</v>
+        <v>2079153</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54319,10 +54319,10 @@
         <v>0</v>
       </c>
       <c r="AI140" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK140" t="n">
         <v>0</v>
@@ -54352,7 +54352,7 @@
         <v>0</v>
       </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="AU140" t="n">
         <v>0</v>
@@ -54370,7 +54370,7 @@
         <v>0</v>
       </c>
       <c r="AZ140" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="BA140" t="n">
         <v>0</v>
@@ -54415,10 +54415,10 @@
         <v>1600</v>
       </c>
       <c r="BO140" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BP140" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BQ140" t="n">
         <v>0</v>
@@ -54532,7 +54532,7 @@
         <v>0</v>
       </c>
       <c r="DB140" t="n">
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="DC140" t="n">
         <v>0</v>
@@ -54556,7 +54556,7 @@
         <v>0</v>
       </c>
       <c r="DJ140" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="DK140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
       <c r="DW140" t="n">
-        <v>9089</v>
+        <v>10239</v>
       </c>
     </row>
     <row r="141">
@@ -54704,10 +54704,10 @@
         <v>1509</v>
       </c>
       <c r="AI141" t="n">
-        <v>522</v>
+        <v>617</v>
       </c>
       <c r="AJ141" t="n">
-        <v>790</v>
+        <v>840</v>
       </c>
       <c r="AK141" t="n">
         <v>12358</v>
@@ -54737,7 +54737,7 @@
         <v>262</v>
       </c>
       <c r="AT141" t="n">
-        <v>26604</v>
+        <v>26879</v>
       </c>
       <c r="AU141" t="n">
         <v>437</v>
@@ -54755,7 +54755,7 @@
         <v>460</v>
       </c>
       <c r="AZ141" t="n">
-        <v>40932</v>
+        <v>41222</v>
       </c>
       <c r="BA141" t="n">
         <v>6666</v>
@@ -54800,10 +54800,10 @@
         <v>114139</v>
       </c>
       <c r="BO141" t="n">
-        <v>4080</v>
+        <v>4120</v>
       </c>
       <c r="BP141" t="n">
-        <v>7365</v>
+        <v>7460</v>
       </c>
       <c r="BQ141" t="n">
         <v>94955</v>
@@ -54917,7 +54917,7 @@
         <v>13766</v>
       </c>
       <c r="DB141" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
       <c r="DC141" t="n">
         <v>1030</v>
@@ -54941,7 +54941,7 @@
         <v>23863</v>
       </c>
       <c r="DJ141" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
       <c r="DK141" t="n">
         <v>1240</v>
@@ -54980,7 +54980,7 @@
         <v>27528</v>
       </c>
       <c r="DW141" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>
@@ -61199,10 +61199,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -61211,7 +61211,7 @@
         <v>425</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="G8" t="n">
         <v>635</v>
@@ -61238,7 +61238,7 @@
         <v>1795</v>
       </c>
       <c r="O8" t="n">
-        <v>4340</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="9">
@@ -61248,10 +61248,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15085</v>
+        <v>15220</v>
       </c>
       <c r="C9" t="n">
-        <v>5555</v>
+        <v>5725</v>
       </c>
       <c r="D9" t="n">
         <v>5000</v>
@@ -61260,7 +61260,7 @@
         <v>4031</v>
       </c>
       <c r="F9" t="n">
-        <v>4107</v>
+        <v>4532</v>
       </c>
       <c r="G9" t="n">
         <v>5425</v>
@@ -61287,7 +61287,7 @@
         <v>23167</v>
       </c>
       <c r="O9" t="n">
-        <v>90003</v>
+        <v>90733</v>
       </c>
     </row>
   </sheetData>
@@ -62703,7 +62703,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1245</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="141">
@@ -62713,7 +62713,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
     </row>
     <row r="143">
@@ -62821,7 +62821,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>15085</v>
+        <v>15220</v>
       </c>
     </row>
     <row r="156">
@@ -62831,7 +62831,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
     </row>
   </sheetData>
@@ -71376,7 +71376,7 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>52</v>
+        <v>327</v>
       </c>
       <c r="E140" t="n">
         <v>5640</v>
@@ -71391,13 +71391,13 @@
         <v>500</v>
       </c>
       <c r="I140" t="n">
-        <v>1247</v>
+        <v>1527</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>420</v>
+        <v>845</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -71412,7 +71412,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>640</v>
+        <v>810</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>9089</v>
+        <v>10239</v>
       </c>
     </row>
     <row r="141">
@@ -71437,7 +71437,7 @@
         <v>17331</v>
       </c>
       <c r="D141" t="n">
-        <v>62215</v>
+        <v>62490</v>
       </c>
       <c r="E141" t="n">
         <v>860557</v>
@@ -71452,13 +71452,13 @@
         <v>7999</v>
       </c>
       <c r="I141" t="n">
-        <v>285366</v>
+        <v>285646</v>
       </c>
       <c r="J141" t="n">
         <v>4939</v>
       </c>
       <c r="K141" t="n">
-        <v>109480</v>
+        <v>109905</v>
       </c>
       <c r="L141" t="n">
         <v>35385</v>
@@ -71473,7 +71473,7 @@
         <v>22052</v>
       </c>
       <c r="P141" t="n">
-        <v>422556</v>
+        <v>422726</v>
       </c>
       <c r="Q141" t="n">
         <v>36635</v>
@@ -71482,7 +71482,7 @@
         <v>88188</v>
       </c>
       <c r="S141" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>
@@ -72898,7 +72898,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141">
@@ -72908,7 +72908,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
     </row>
     <row r="143">
@@ -73016,7 +73016,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>5555</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="156">
@@ -73026,7 +73026,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
     </row>
   </sheetData>
@@ -75858,7 +75858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76986,129 +76986,139 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>58168</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="B114" t="n">
+        <v>58593</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B116" t="n">
-        <v>4297</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B117" t="n">
-        <v>3945</v>
+        <v>4297</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B118" t="n">
-        <v>4200</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B119" t="n">
-        <v>4280</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B120" t="n">
-        <v>6480</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B121" t="n">
-        <v>2685</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B122" t="n">
-        <v>3115</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B123" t="n">
-        <v>4745</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B124" t="n">
-        <v>5860</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B125" t="n">
-        <v>6490</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B126" t="n">
-        <v>7964</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B127" t="n">
+        <v>7964</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
         <v>2026</v>
       </c>
-      <c r="B127" t="n">
-        <v>4107</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="B128" t="n">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>58168</v>
+      <c r="B129" t="n">
+        <v>58593</v>
       </c>
     </row>
   </sheetData>
@@ -90030,7 +90040,7 @@
         <v>150</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -90045,10 +90055,10 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>4749</v>
+        <v>5169</v>
       </c>
       <c r="J140" t="n">
-        <v>1245</v>
+        <v>1380</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -90057,7 +90067,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="N140" t="n">
         <v>635</v>
@@ -90066,7 +90076,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>9089</v>
+        <v>10239</v>
       </c>
     </row>
     <row r="141">
@@ -90082,7 +90092,7 @@
         <v>223358</v>
       </c>
       <c r="D141" t="n">
-        <v>58168</v>
+        <v>58593</v>
       </c>
       <c r="E141" t="n">
         <v>14291</v>
@@ -90097,10 +90107,10 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>753060</v>
+        <v>753480</v>
       </c>
       <c r="J141" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
       <c r="K141" t="n">
         <v>32660</v>
@@ -90109,7 +90119,7 @@
         <v>61344</v>
       </c>
       <c r="M141" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
       <c r="N141" t="n">
         <v>71211</v>
@@ -90118,7 +90128,7 @@
         <v>48619</v>
       </c>
       <c r="P141" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>
@@ -98177,10 +98187,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="AJ13" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="AK13" t="n">
         <v>1064</v>
@@ -98210,7 +98220,7 @@
         <v>262</v>
       </c>
       <c r="AT13" t="n">
-        <v>1865</v>
+        <v>2140</v>
       </c>
       <c r="AU13" t="n">
         <v>437</v>
@@ -98228,7 +98238,7 @@
         <v>50</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2500</v>
+        <v>2790</v>
       </c>
       <c r="BA13" t="n">
         <v>460</v>
@@ -98273,10 +98283,10 @@
         <v>20532</v>
       </c>
       <c r="BO13" t="n">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="BP13" t="n">
-        <v>335</v>
+        <v>430</v>
       </c>
       <c r="BQ13" t="n">
         <v>5817</v>
@@ -98390,7 +98400,7 @@
         <v>910</v>
       </c>
       <c r="DB13" t="n">
-        <v>15085</v>
+        <v>15220</v>
       </c>
       <c r="DC13" t="n">
         <v>30</v>
@@ -98414,7 +98424,7 @@
         <v>2195</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5555</v>
+        <v>5725</v>
       </c>
       <c r="DK13" t="n">
         <v>420</v>
@@ -98453,7 +98463,7 @@
         <v>1660</v>
       </c>
       <c r="DW13" t="n">
-        <v>160140</v>
+        <v>161290</v>
       </c>
     </row>
     <row r="14">
@@ -98562,10 +98572,10 @@
         <v>1509</v>
       </c>
       <c r="AI14" t="n">
-        <v>522</v>
+        <v>617</v>
       </c>
       <c r="AJ14" t="n">
-        <v>790</v>
+        <v>840</v>
       </c>
       <c r="AK14" t="n">
         <v>12358</v>
@@ -98595,7 +98605,7 @@
         <v>262</v>
       </c>
       <c r="AT14" t="n">
-        <v>26604</v>
+        <v>26879</v>
       </c>
       <c r="AU14" t="n">
         <v>437</v>
@@ -98613,7 +98623,7 @@
         <v>460</v>
       </c>
       <c r="AZ14" t="n">
-        <v>40932</v>
+        <v>41222</v>
       </c>
       <c r="BA14" t="n">
         <v>6666</v>
@@ -98658,10 +98668,10 @@
         <v>114139</v>
       </c>
       <c r="BO14" t="n">
-        <v>4080</v>
+        <v>4120</v>
       </c>
       <c r="BP14" t="n">
-        <v>7365</v>
+        <v>7460</v>
       </c>
       <c r="BQ14" t="n">
         <v>94955</v>
@@ -98775,7 +98785,7 @@
         <v>13766</v>
       </c>
       <c r="DB14" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
       <c r="DC14" t="n">
         <v>1030</v>
@@ -98799,7 +98809,7 @@
         <v>23863</v>
       </c>
       <c r="DJ14" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
       <c r="DK14" t="n">
         <v>1240</v>
@@ -98838,7 +98848,7 @@
         <v>27528</v>
       </c>
       <c r="DW14" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>
@@ -99612,7 +99622,7 @@
         <v>2075</v>
       </c>
       <c r="D13" t="n">
-        <v>4887</v>
+        <v>5162</v>
       </c>
       <c r="E13" t="n">
         <v>68835</v>
@@ -99627,13 +99637,13 @@
         <v>1715</v>
       </c>
       <c r="I13" t="n">
-        <v>20468</v>
+        <v>20748</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
       </c>
       <c r="K13" t="n">
-        <v>9183</v>
+        <v>9608</v>
       </c>
       <c r="L13" t="n">
         <v>2177</v>
@@ -99648,7 +99658,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>28035</v>
+        <v>28205</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99657,7 +99667,7 @@
         <v>8847</v>
       </c>
       <c r="S13" t="n">
-        <v>160140</v>
+        <v>161290</v>
       </c>
     </row>
     <row r="14">
@@ -99673,7 +99683,7 @@
         <v>17331</v>
       </c>
       <c r="D14" t="n">
-        <v>62215</v>
+        <v>62490</v>
       </c>
       <c r="E14" t="n">
         <v>860557</v>
@@ -99688,13 +99698,13 @@
         <v>7999</v>
       </c>
       <c r="I14" t="n">
-        <v>285366</v>
+        <v>285646</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
       </c>
       <c r="K14" t="n">
-        <v>109480</v>
+        <v>109905</v>
       </c>
       <c r="L14" t="n">
         <v>35385</v>
@@ -99709,7 +99719,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>422556</v>
+        <v>422726</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99718,7 +99728,7 @@
         <v>88188</v>
       </c>
       <c r="S14" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>
@@ -100378,7 +100388,7 @@
         <v>14333</v>
       </c>
       <c r="D13" t="n">
-        <v>4107</v>
+        <v>4532</v>
       </c>
       <c r="E13" t="n">
         <v>1640</v>
@@ -100393,10 +100403,10 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>70137</v>
+        <v>70557</v>
       </c>
       <c r="J13" t="n">
-        <v>15085</v>
+        <v>15220</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -100405,7 +100415,7 @@
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>5555</v>
+        <v>5725</v>
       </c>
       <c r="N13" t="n">
         <v>5425</v>
@@ -100414,7 +100424,7 @@
         <v>3645</v>
       </c>
       <c r="P13" t="n">
-        <v>160140</v>
+        <v>161290</v>
       </c>
     </row>
     <row r="14">
@@ -100430,7 +100440,7 @@
         <v>223358</v>
       </c>
       <c r="D14" t="n">
-        <v>58168</v>
+        <v>58593</v>
       </c>
       <c r="E14" t="n">
         <v>14291</v>
@@ -100445,10 +100455,10 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>753060</v>
+        <v>753480</v>
       </c>
       <c r="J14" t="n">
-        <v>219158</v>
+        <v>219293</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -100457,7 +100467,7 @@
         <v>61344</v>
       </c>
       <c r="M14" t="n">
-        <v>100064</v>
+        <v>100234</v>
       </c>
       <c r="N14" t="n">
         <v>71211</v>
@@ -100466,7 +100476,7 @@
         <v>48619</v>
       </c>
       <c r="P14" t="n">
-        <v>2079153</v>
+        <v>2080303</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54229,7 +54229,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -54244,10 +54244,10 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -54421,7 +54421,7 @@
         <v>95</v>
       </c>
       <c r="BQ140" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BR140" t="n">
         <v>0</v>
@@ -54469,7 +54469,7 @@
         <v>0</v>
       </c>
       <c r="CG140" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="CH140" t="n">
         <v>0</v>
@@ -54517,7 +54517,7 @@
         <v>0</v>
       </c>
       <c r="CW140" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CX140" t="n">
         <v>0</v>
@@ -54568,7 +54568,7 @@
         <v>0</v>
       </c>
       <c r="DN140" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="DO140" t="n">
         <v>0</v>
@@ -54592,10 +54592,10 @@
         <v>0</v>
       </c>
       <c r="DV140" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>10239</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="141">
@@ -54614,7 +54614,7 @@
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>71467</v>
+        <v>71597</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -54629,10 +54629,10 @@
         <v>3040</v>
       </c>
       <c r="J141" t="n">
-        <v>22295</v>
+        <v>22345</v>
       </c>
       <c r="K141" t="n">
-        <v>16922</v>
+        <v>17042</v>
       </c>
       <c r="L141" t="n">
         <v>5790</v>
@@ -54806,7 +54806,7 @@
         <v>7460</v>
       </c>
       <c r="BQ141" t="n">
-        <v>94955</v>
+        <v>95020</v>
       </c>
       <c r="BR141" t="n">
         <v>22292</v>
@@ -54854,7 +54854,7 @@
         <v>145</v>
       </c>
       <c r="CG141" t="n">
-        <v>21091</v>
+        <v>21241</v>
       </c>
       <c r="CH141" t="n">
         <v>3642</v>
@@ -54902,7 +54902,7 @@
         <v>1310</v>
       </c>
       <c r="CW141" t="n">
-        <v>2698</v>
+        <v>2738</v>
       </c>
       <c r="CX141" t="n">
         <v>127</v>
@@ -54953,7 +54953,7 @@
         <v>10550</v>
       </c>
       <c r="DN141" t="n">
-        <v>17967</v>
+        <v>18218</v>
       </c>
       <c r="DO141" t="n">
         <v>582</v>
@@ -54977,10 +54977,10 @@
         <v>4927</v>
       </c>
       <c r="DV141" t="n">
-        <v>27528</v>
+        <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>
@@ -61220,7 +61220,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -61232,13 +61232,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>150</v>
+        <v>395</v>
       </c>
       <c r="N8" t="n">
         <v>1795</v>
       </c>
       <c r="O8" t="n">
-        <v>5070</v>
+        <v>5535</v>
       </c>
     </row>
     <row r="9">
@@ -61269,7 +61269,7 @@
         <v>2445</v>
       </c>
       <c r="I9" t="n">
-        <v>3645</v>
+        <v>3865</v>
       </c>
       <c r="J9" t="n">
         <v>2880</v>
@@ -61281,13 +61281,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>14333</v>
+        <v>14578</v>
       </c>
       <c r="N9" t="n">
         <v>23167</v>
       </c>
       <c r="O9" t="n">
-        <v>90733</v>
+        <v>91198</v>
       </c>
     </row>
   </sheetData>
@@ -71400,7 +71400,7 @@
         <v>845</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M140" t="n">
         <v>165</v>
@@ -71412,16 +71412,16 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>810</v>
+        <v>1055</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="S140" t="n">
-        <v>10239</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="141">
@@ -71461,7 +71461,7 @@
         <v>109905</v>
       </c>
       <c r="L141" t="n">
-        <v>35385</v>
+        <v>35636</v>
       </c>
       <c r="M141" t="n">
         <v>8318</v>
@@ -71473,16 +71473,16 @@
         <v>22052</v>
       </c>
       <c r="P141" t="n">
-        <v>422726</v>
+        <v>422971</v>
       </c>
       <c r="Q141" t="n">
         <v>36635</v>
       </c>
       <c r="R141" t="n">
-        <v>88188</v>
+        <v>88568</v>
       </c>
       <c r="S141" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>
@@ -79556,7 +79556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80884,129 +80884,139 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>48619</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="B134" t="n">
+        <v>48839</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B136" t="n">
-        <v>1867</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B137" t="n">
-        <v>2625</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B138" t="n">
-        <v>3270</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B139" t="n">
-        <v>3960</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B140" t="n">
-        <v>4420</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B141" t="n">
-        <v>3140</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B142" t="n">
-        <v>3010</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B143" t="n">
-        <v>3854</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B144" t="n">
-        <v>5282</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B145" t="n">
-        <v>6515</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B146" t="n">
-        <v>7031</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B147" t="n">
+        <v>7031</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
         <v>2026</v>
       </c>
-      <c r="B147" t="n">
-        <v>3645</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="B148" t="n">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>48619</v>
+      <c r="B149" t="n">
+        <v>48839</v>
       </c>
     </row>
   </sheetData>
@@ -90037,7 +90047,7 @@
         <v>1795</v>
       </c>
       <c r="C140" t="n">
-        <v>150</v>
+        <v>395</v>
       </c>
       <c r="D140" t="n">
         <v>425</v>
@@ -90055,7 +90065,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>5169</v>
+        <v>5580</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90073,10 +90083,10 @@
         <v>635</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>10239</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="141">
@@ -90089,7 +90099,7 @@
         <v>398518</v>
       </c>
       <c r="C141" t="n">
-        <v>223358</v>
+        <v>223603</v>
       </c>
       <c r="D141" t="n">
         <v>58593</v>
@@ -90107,7 +90117,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>753480</v>
+        <v>753891</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90125,10 +90135,10 @@
         <v>71211</v>
       </c>
       <c r="O141" t="n">
-        <v>48619</v>
+        <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>
@@ -91544,7 +91554,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>150</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141">
@@ -91554,7 +91564,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>223358</v>
+        <v>223603</v>
       </c>
     </row>
     <row r="143">
@@ -91662,7 +91672,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>14333</v>
+        <v>14578</v>
       </c>
     </row>
     <row r="156">
@@ -91672,7 +91682,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>223358</v>
+        <v>223603</v>
       </c>
     </row>
   </sheetData>
@@ -98097,7 +98107,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4772</v>
+        <v>4902</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -98112,10 +98122,10 @@
         <v>435</v>
       </c>
       <c r="J13" t="n">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="K13" t="n">
-        <v>995</v>
+        <v>1115</v>
       </c>
       <c r="L13" t="n">
         <v>825</v>
@@ -98289,7 +98299,7 @@
         <v>430</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5817</v>
+        <v>5882</v>
       </c>
       <c r="BR13" t="n">
         <v>1730</v>
@@ -98337,7 +98347,7 @@
         <v>30</v>
       </c>
       <c r="CG13" t="n">
-        <v>1985</v>
+        <v>2135</v>
       </c>
       <c r="CH13" t="n">
         <v>467</v>
@@ -98385,7 +98395,7 @@
         <v>125</v>
       </c>
       <c r="CW13" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="CX13" t="n">
         <v>127</v>
@@ -98436,7 +98446,7 @@
         <v>410</v>
       </c>
       <c r="DN13" t="n">
-        <v>1652</v>
+        <v>1903</v>
       </c>
       <c r="DO13" t="n">
         <v>0</v>
@@ -98460,10 +98470,10 @@
         <v>275</v>
       </c>
       <c r="DV13" t="n">
-        <v>1660</v>
+        <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>161290</v>
+        <v>162166</v>
       </c>
     </row>
     <row r="14">
@@ -98482,7 +98492,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>71467</v>
+        <v>71597</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98497,10 +98507,10 @@
         <v>3040</v>
       </c>
       <c r="J14" t="n">
-        <v>22295</v>
+        <v>22345</v>
       </c>
       <c r="K14" t="n">
-        <v>16922</v>
+        <v>17042</v>
       </c>
       <c r="L14" t="n">
         <v>5790</v>
@@ -98674,7 +98684,7 @@
         <v>7460</v>
       </c>
       <c r="BQ14" t="n">
-        <v>94955</v>
+        <v>95020</v>
       </c>
       <c r="BR14" t="n">
         <v>22292</v>
@@ -98722,7 +98732,7 @@
         <v>145</v>
       </c>
       <c r="CG14" t="n">
-        <v>21091</v>
+        <v>21241</v>
       </c>
       <c r="CH14" t="n">
         <v>3642</v>
@@ -98770,7 +98780,7 @@
         <v>1310</v>
       </c>
       <c r="CW14" t="n">
-        <v>2698</v>
+        <v>2738</v>
       </c>
       <c r="CX14" t="n">
         <v>127</v>
@@ -98821,7 +98831,7 @@
         <v>10550</v>
       </c>
       <c r="DN14" t="n">
-        <v>17967</v>
+        <v>18218</v>
       </c>
       <c r="DO14" t="n">
         <v>582</v>
@@ -98845,10 +98855,10 @@
         <v>4927</v>
       </c>
       <c r="DV14" t="n">
-        <v>27528</v>
+        <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>
@@ -99646,7 +99656,7 @@
         <v>9608</v>
       </c>
       <c r="L13" t="n">
-        <v>2177</v>
+        <v>2428</v>
       </c>
       <c r="M13" t="n">
         <v>1201</v>
@@ -99658,16 +99668,16 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>28205</v>
+        <v>28450</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
       </c>
       <c r="R13" t="n">
-        <v>8847</v>
+        <v>9227</v>
       </c>
       <c r="S13" t="n">
-        <v>161290</v>
+        <v>162166</v>
       </c>
     </row>
     <row r="14">
@@ -99707,7 +99717,7 @@
         <v>109905</v>
       </c>
       <c r="L14" t="n">
-        <v>35385</v>
+        <v>35636</v>
       </c>
       <c r="M14" t="n">
         <v>8318</v>
@@ -99719,16 +99729,16 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>422726</v>
+        <v>422971</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
       </c>
       <c r="R14" t="n">
-        <v>88188</v>
+        <v>88568</v>
       </c>
       <c r="S14" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>
@@ -100385,7 +100395,7 @@
         <v>23167</v>
       </c>
       <c r="C13" t="n">
-        <v>14333</v>
+        <v>14578</v>
       </c>
       <c r="D13" t="n">
         <v>4532</v>
@@ -100403,7 +100413,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>70557</v>
+        <v>70968</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100421,10 +100431,10 @@
         <v>5425</v>
       </c>
       <c r="O13" t="n">
-        <v>3645</v>
+        <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>161290</v>
+        <v>162166</v>
       </c>
     </row>
     <row r="14">
@@ -100437,7 +100447,7 @@
         <v>398518</v>
       </c>
       <c r="C14" t="n">
-        <v>223358</v>
+        <v>223603</v>
       </c>
       <c r="D14" t="n">
         <v>58593</v>
@@ -100455,7 +100465,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>753480</v>
+        <v>753891</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100473,10 +100483,10 @@
         <v>71211</v>
       </c>
       <c r="O14" t="n">
-        <v>48619</v>
+        <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2080303</v>
+        <v>2081179</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54268,7 +54268,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1795</v>
+        <v>2055</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -54328,10 +54328,10 @@
         <v>0</v>
       </c>
       <c r="AL140" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM140" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AN140" t="n">
         <v>0</v>
@@ -54355,10 +54355,10 @@
         <v>275</v>
       </c>
       <c r="AU140" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AV140" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AW140" t="n">
         <v>0</v>
@@ -54484,7 +54484,7 @@
         <v>0</v>
       </c>
       <c r="CL140" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="CM140" t="n">
         <v>0</v>
@@ -54502,13 +54502,13 @@
         <v>0</v>
       </c>
       <c r="CR140" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="CS140" t="n">
         <v>0</v>
       </c>
       <c r="CT140" t="n">
-        <v>320</v>
+        <v>415</v>
       </c>
       <c r="CU140" t="n">
         <v>195</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>11115</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="141">
@@ -54653,7 +54653,7 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>431178</v>
+        <v>431438</v>
       </c>
       <c r="S141" t="n">
         <v>925</v>
@@ -54713,10 +54713,10 @@
         <v>12358</v>
       </c>
       <c r="AL141" t="n">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="AM141" t="n">
-        <v>50699</v>
+        <v>50734</v>
       </c>
       <c r="AN141" t="n">
         <v>4755</v>
@@ -54740,10 +54740,10 @@
         <v>26879</v>
       </c>
       <c r="AU141" t="n">
-        <v>437</v>
+        <v>567</v>
       </c>
       <c r="AV141" t="n">
-        <v>2627</v>
+        <v>2707</v>
       </c>
       <c r="AW141" t="n">
         <v>6939</v>
@@ -54869,7 +54869,7 @@
         <v>350</v>
       </c>
       <c r="CL141" t="n">
-        <v>17994</v>
+        <v>18054</v>
       </c>
       <c r="CM141" t="n">
         <v>345</v>
@@ -54887,13 +54887,13 @@
         <v>277</v>
       </c>
       <c r="CR141" t="n">
-        <v>11904</v>
+        <v>12114</v>
       </c>
       <c r="CS141" t="n">
         <v>2</v>
       </c>
       <c r="CT141" t="n">
-        <v>65475</v>
+        <v>65570</v>
       </c>
       <c r="CU141" t="n">
         <v>2579</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>
@@ -61235,10 +61235,10 @@
         <v>395</v>
       </c>
       <c r="N8" t="n">
-        <v>1795</v>
+        <v>2055</v>
       </c>
       <c r="O8" t="n">
-        <v>5535</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="9">
@@ -61284,10 +61284,10 @@
         <v>14578</v>
       </c>
       <c r="N9" t="n">
-        <v>23167</v>
+        <v>23427</v>
       </c>
       <c r="O9" t="n">
-        <v>91198</v>
+        <v>91458</v>
       </c>
     </row>
   </sheetData>
@@ -71379,7 +71379,7 @@
         <v>327</v>
       </c>
       <c r="E140" t="n">
-        <v>5640</v>
+        <v>6565</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>380</v>
       </c>
       <c r="S140" t="n">
-        <v>11115</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="141">
@@ -71440,7 +71440,7 @@
         <v>62490</v>
       </c>
       <c r="E141" t="n">
-        <v>860557</v>
+        <v>861482</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71482,7 +71482,7 @@
         <v>88568</v>
       </c>
       <c r="S141" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>
@@ -90044,7 +90044,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1795</v>
+        <v>2055</v>
       </c>
       <c r="C140" t="n">
         <v>395</v>
@@ -90065,7 +90065,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>5580</v>
+        <v>6245</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90086,7 +90086,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>11115</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="141">
@@ -90096,7 +90096,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398518</v>
+        <v>398778</v>
       </c>
       <c r="C141" t="n">
         <v>223603</v>
@@ -90117,7 +90117,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>753891</v>
+        <v>754556</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90138,7 +90138,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>
@@ -93098,7 +93098,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1795</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="141">
@@ -93108,7 +93108,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398518</v>
+        <v>398778</v>
       </c>
     </row>
     <row r="143">
@@ -93216,7 +93216,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>23167</v>
+        <v>23427</v>
       </c>
     </row>
     <row r="156">
@@ -93226,7 +93226,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>398518</v>
+        <v>398778</v>
       </c>
     </row>
   </sheetData>
@@ -98146,7 +98146,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>25612</v>
+        <v>25872</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -98206,10 +98206,10 @@
         <v>1064</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>2156</v>
+        <v>2191</v>
       </c>
       <c r="AN13" t="n">
         <v>165</v>
@@ -98233,10 +98233,10 @@
         <v>2140</v>
       </c>
       <c r="AU13" t="n">
-        <v>437</v>
+        <v>567</v>
       </c>
       <c r="AV13" t="n">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="AW13" t="n">
         <v>440</v>
@@ -98362,7 +98362,7 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="CM13" t="n">
         <v>50</v>
@@ -98380,13 +98380,13 @@
         <v>0</v>
       </c>
       <c r="CR13" t="n">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="CS13" t="n">
         <v>2</v>
       </c>
       <c r="CT13" t="n">
-        <v>4745</v>
+        <v>4840</v>
       </c>
       <c r="CU13" t="n">
         <v>1120</v>
@@ -98473,7 +98473,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>162166</v>
+        <v>163091</v>
       </c>
     </row>
     <row r="14">
@@ -98531,7 +98531,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>431178</v>
+        <v>431438</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98591,10 +98591,10 @@
         <v>12358</v>
       </c>
       <c r="AL14" t="n">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="AM14" t="n">
-        <v>50699</v>
+        <v>50734</v>
       </c>
       <c r="AN14" t="n">
         <v>4755</v>
@@ -98618,10 +98618,10 @@
         <v>26879</v>
       </c>
       <c r="AU14" t="n">
-        <v>437</v>
+        <v>567</v>
       </c>
       <c r="AV14" t="n">
-        <v>2627</v>
+        <v>2707</v>
       </c>
       <c r="AW14" t="n">
         <v>6939</v>
@@ -98747,7 +98747,7 @@
         <v>350</v>
       </c>
       <c r="CL14" t="n">
-        <v>17994</v>
+        <v>18054</v>
       </c>
       <c r="CM14" t="n">
         <v>345</v>
@@ -98765,13 +98765,13 @@
         <v>277</v>
       </c>
       <c r="CR14" t="n">
-        <v>11904</v>
+        <v>12114</v>
       </c>
       <c r="CS14" t="n">
         <v>2</v>
       </c>
       <c r="CT14" t="n">
-        <v>65475</v>
+        <v>65570</v>
       </c>
       <c r="CU14" t="n">
         <v>2579</v>
@@ -98858,7 +98858,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>
@@ -99635,7 +99635,7 @@
         <v>5162</v>
       </c>
       <c r="E13" t="n">
-        <v>68835</v>
+        <v>69760</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99677,7 +99677,7 @@
         <v>9227</v>
       </c>
       <c r="S13" t="n">
-        <v>162166</v>
+        <v>163091</v>
       </c>
     </row>
     <row r="14">
@@ -99696,7 +99696,7 @@
         <v>62490</v>
       </c>
       <c r="E14" t="n">
-        <v>860557</v>
+        <v>861482</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99738,7 +99738,7 @@
         <v>88568</v>
       </c>
       <c r="S14" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>
@@ -100392,7 +100392,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>23167</v>
+        <v>23427</v>
       </c>
       <c r="C13" t="n">
         <v>14578</v>
@@ -100413,7 +100413,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>70968</v>
+        <v>71633</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100434,7 +100434,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>162166</v>
+        <v>163091</v>
       </c>
     </row>
     <row r="14">
@@ -100444,7 +100444,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>398518</v>
+        <v>398778</v>
       </c>
       <c r="C14" t="n">
         <v>223603</v>
@@ -100465,7 +100465,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>753891</v>
+        <v>754556</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100486,7 +100486,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2081179</v>
+        <v>2082104</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54268,7 +54268,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2055</v>
+        <v>3155</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -54460,7 +54460,7 @@
         <v>0</v>
       </c>
       <c r="CD140" t="n">
-        <v>400</v>
+        <v>525</v>
       </c>
       <c r="CE140" t="n">
         <v>0</v>
@@ -54586,7 +54586,7 @@
         <v>0</v>
       </c>
       <c r="DT140" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="DU140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>12040</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="141">
@@ -54653,7 +54653,7 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>431438</v>
+        <v>432538</v>
       </c>
       <c r="S141" t="n">
         <v>925</v>
@@ -54845,7 +54845,7 @@
         <v>435</v>
       </c>
       <c r="CD141" t="n">
-        <v>16073</v>
+        <v>16198</v>
       </c>
       <c r="CE141" t="n">
         <v>5771</v>
@@ -54971,7 +54971,7 @@
         <v>1450</v>
       </c>
       <c r="DT141" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
       <c r="DU141" t="n">
         <v>4927</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>
@@ -61214,7 +61214,7 @@
         <v>425</v>
       </c>
       <c r="G8" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -61235,10 +61235,10 @@
         <v>395</v>
       </c>
       <c r="N8" t="n">
-        <v>2055</v>
+        <v>3155</v>
       </c>
       <c r="O8" t="n">
-        <v>5795</v>
+        <v>6897</v>
       </c>
     </row>
     <row r="9">
@@ -61263,7 +61263,7 @@
         <v>4532</v>
       </c>
       <c r="G9" t="n">
-        <v>5425</v>
+        <v>5427</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -61284,10 +61284,10 @@
         <v>14578</v>
       </c>
       <c r="N9" t="n">
-        <v>23427</v>
+        <v>24527</v>
       </c>
       <c r="O9" t="n">
-        <v>91458</v>
+        <v>92560</v>
       </c>
     </row>
   </sheetData>
@@ -71379,7 +71379,7 @@
         <v>327</v>
       </c>
       <c r="E140" t="n">
-        <v>6565</v>
+        <v>7667</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71412,7 +71412,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>380</v>
       </c>
       <c r="S140" t="n">
-        <v>12040</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="141">
@@ -71440,7 +71440,7 @@
         <v>62490</v>
       </c>
       <c r="E141" t="n">
-        <v>861482</v>
+        <v>862584</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71473,7 +71473,7 @@
         <v>22052</v>
       </c>
       <c r="P141" t="n">
-        <v>422971</v>
+        <v>423096</v>
       </c>
       <c r="Q141" t="n">
         <v>36635</v>
@@ -71482,7 +71482,7 @@
         <v>88568</v>
       </c>
       <c r="S141" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>
@@ -78494,7 +78494,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="137">
@@ -78504,7 +78504,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
     </row>
     <row r="139">
@@ -78612,7 +78612,7 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>5425</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="152">
@@ -78622,7 +78622,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
     </row>
   </sheetData>
@@ -90044,7 +90044,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2055</v>
+        <v>3155</v>
       </c>
       <c r="C140" t="n">
         <v>395</v>
@@ -90065,7 +90065,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>6245</v>
+        <v>6370</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90080,13 +90080,13 @@
         <v>260</v>
       </c>
       <c r="N140" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O140" t="n">
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>12040</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="141">
@@ -90096,7 +90096,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398778</v>
+        <v>399878</v>
       </c>
       <c r="C141" t="n">
         <v>223603</v>
@@ -90117,7 +90117,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>754556</v>
+        <v>754681</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90132,13 +90132,13 @@
         <v>100234</v>
       </c>
       <c r="N141" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
       <c r="O141" t="n">
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>
@@ -93098,7 +93098,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2055</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="141">
@@ -93108,7 +93108,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>398778</v>
+        <v>399878</v>
       </c>
     </row>
     <row r="143">
@@ -93216,7 +93216,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>23427</v>
+        <v>24527</v>
       </c>
     </row>
     <row r="156">
@@ -93226,7 +93226,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>398778</v>
+        <v>399878</v>
       </c>
     </row>
   </sheetData>
@@ -98146,7 +98146,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>25872</v>
+        <v>26972</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -98338,7 +98338,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>2335</v>
+        <v>2460</v>
       </c>
       <c r="CE13" t="n">
         <v>856</v>
@@ -98464,7 +98464,7 @@
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>5425</v>
+        <v>5427</v>
       </c>
       <c r="DU13" t="n">
         <v>275</v>
@@ -98473,7 +98473,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>163091</v>
+        <v>164318</v>
       </c>
     </row>
     <row r="14">
@@ -98531,7 +98531,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>431438</v>
+        <v>432538</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98723,7 +98723,7 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>16073</v>
+        <v>16198</v>
       </c>
       <c r="CE14" t="n">
         <v>5771</v>
@@ -98849,7 +98849,7 @@
         <v>1450</v>
       </c>
       <c r="DT14" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
       <c r="DU14" t="n">
         <v>4927</v>
@@ -98858,7 +98858,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>
@@ -99635,7 +99635,7 @@
         <v>5162</v>
       </c>
       <c r="E13" t="n">
-        <v>69760</v>
+        <v>70862</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99668,7 +99668,7 @@
         <v>200</v>
       </c>
       <c r="P13" t="n">
-        <v>28450</v>
+        <v>28575</v>
       </c>
       <c r="Q13" t="n">
         <v>3227</v>
@@ -99677,7 +99677,7 @@
         <v>9227</v>
       </c>
       <c r="S13" t="n">
-        <v>163091</v>
+        <v>164318</v>
       </c>
     </row>
     <row r="14">
@@ -99696,7 +99696,7 @@
         <v>62490</v>
       </c>
       <c r="E14" t="n">
-        <v>861482</v>
+        <v>862584</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99729,7 +99729,7 @@
         <v>22052</v>
       </c>
       <c r="P14" t="n">
-        <v>422971</v>
+        <v>423096</v>
       </c>
       <c r="Q14" t="n">
         <v>36635</v>
@@ -99738,7 +99738,7 @@
         <v>88568</v>
       </c>
       <c r="S14" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>
@@ -100392,7 +100392,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>23427</v>
+        <v>24527</v>
       </c>
       <c r="C13" t="n">
         <v>14578</v>
@@ -100413,7 +100413,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>71633</v>
+        <v>71758</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100428,13 +100428,13 @@
         <v>5725</v>
       </c>
       <c r="N13" t="n">
-        <v>5425</v>
+        <v>5427</v>
       </c>
       <c r="O13" t="n">
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>163091</v>
+        <v>164318</v>
       </c>
     </row>
     <row r="14">
@@ -100444,7 +100444,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>398778</v>
+        <v>399878</v>
       </c>
       <c r="C14" t="n">
         <v>223603</v>
@@ -100465,7 +100465,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>754556</v>
+        <v>754681</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100480,13 +100480,13 @@
         <v>100234</v>
       </c>
       <c r="N14" t="n">
-        <v>71211</v>
+        <v>71213</v>
       </c>
       <c r="O14" t="n">
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2082104</v>
+        <v>2083331</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54223,13 +54223,13 @@
         <v>165</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -54241,13 +54241,13 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J140" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K140" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -54382,7 +54382,7 @@
         <v>2</v>
       </c>
       <c r="BD140" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE140" t="n">
         <v>0</v>
@@ -54397,10 +54397,10 @@
         <v>50</v>
       </c>
       <c r="BI140" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="BJ140" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BK140" t="n">
         <v>0</v>
@@ -54460,7 +54460,7 @@
         <v>0</v>
       </c>
       <c r="CD140" t="n">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="CE140" t="n">
         <v>0</v>
@@ -54535,7 +54535,7 @@
         <v>1380</v>
       </c>
       <c r="DC140" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="DD140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>13267</v>
+        <v>14127</v>
       </c>
     </row>
     <row r="141">
@@ -54608,13 +54608,13 @@
         <v>2547</v>
       </c>
       <c r="C141" t="n">
-        <v>935</v>
+        <v>995</v>
       </c>
       <c r="D141" t="n">
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>71597</v>
+        <v>71632</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -54626,13 +54626,13 @@
         <v>2718</v>
       </c>
       <c r="I141" t="n">
-        <v>3040</v>
+        <v>3200</v>
       </c>
       <c r="J141" t="n">
-        <v>22345</v>
+        <v>22375</v>
       </c>
       <c r="K141" t="n">
-        <v>17042</v>
+        <v>17092</v>
       </c>
       <c r="L141" t="n">
         <v>5790</v>
@@ -54767,7 +54767,7 @@
         <v>9766</v>
       </c>
       <c r="BD141" t="n">
-        <v>6787</v>
+        <v>6847</v>
       </c>
       <c r="BE141" t="n">
         <v>52</v>
@@ -54782,10 +54782,10 @@
         <v>1196</v>
       </c>
       <c r="BI141" t="n">
-        <v>13284</v>
+        <v>13569</v>
       </c>
       <c r="BJ141" t="n">
-        <v>1007</v>
+        <v>1037</v>
       </c>
       <c r="BK141" t="n">
         <v>660</v>
@@ -54845,7 +54845,7 @@
         <v>435</v>
       </c>
       <c r="CD141" t="n">
-        <v>16198</v>
+        <v>16253</v>
       </c>
       <c r="CE141" t="n">
         <v>5771</v>
@@ -54920,7 +54920,7 @@
         <v>219293</v>
       </c>
       <c r="DC141" t="n">
-        <v>1030</v>
+        <v>1125</v>
       </c>
       <c r="DD141" t="n">
         <v>1351</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>
@@ -61226,19 +61226,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="N8" t="n">
         <v>3155</v>
       </c>
       <c r="O8" t="n">
-        <v>6897</v>
+        <v>7277</v>
       </c>
     </row>
     <row r="9">
@@ -61275,19 +61275,19 @@
         <v>2880</v>
       </c>
       <c r="K9" t="n">
-        <v>1640</v>
+        <v>1955</v>
       </c>
       <c r="L9" t="n">
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>14578</v>
+        <v>14643</v>
       </c>
       <c r="N9" t="n">
         <v>24527</v>
       </c>
       <c r="O9" t="n">
-        <v>92560</v>
+        <v>92940</v>
       </c>
     </row>
   </sheetData>
@@ -71373,7 +71373,7 @@
         <v>425</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="D140" t="n">
         <v>327</v>
@@ -71409,19 +71409,19 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="R140" t="n">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>13267</v>
+        <v>14127</v>
       </c>
     </row>
     <row r="141">
@@ -71434,7 +71434,7 @@
         <v>78143</v>
       </c>
       <c r="C141" t="n">
-        <v>17331</v>
+        <v>17806</v>
       </c>
       <c r="D141" t="n">
         <v>62490</v>
@@ -71470,19 +71470,19 @@
         <v>42</v>
       </c>
       <c r="O141" t="n">
-        <v>22052</v>
+        <v>22112</v>
       </c>
       <c r="P141" t="n">
-        <v>423096</v>
+        <v>423216</v>
       </c>
       <c r="Q141" t="n">
-        <v>36635</v>
+        <v>36790</v>
       </c>
       <c r="R141" t="n">
-        <v>88568</v>
+        <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>
@@ -81658,7 +81658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82416,113 +82416,123 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>14291</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="B77" t="n">
+        <v>14606</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B79" t="n">
-        <v>1085</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B80" t="n">
-        <v>1525</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B81" t="n">
-        <v>1000</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B82" t="n">
-        <v>730</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B83" t="n">
-        <v>910</v>
+        <v>730</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B84" t="n">
-        <v>635</v>
+        <v>910</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B85" t="n">
-        <v>2487</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B86" t="n">
-        <v>2275</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B87" t="n">
-        <v>2004</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>2026</v>
       </c>
-      <c r="B88" t="n">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="B89" t="n">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>14291</v>
+      <c r="B90" t="n">
+        <v>14606</v>
       </c>
     </row>
   </sheetData>
@@ -90047,13 +90057,13 @@
         <v>3155</v>
       </c>
       <c r="C140" t="n">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D140" t="n">
         <v>425</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="F140" t="n">
         <v>425</v>
@@ -90065,7 +90075,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>6370</v>
+        <v>6850</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90086,7 +90096,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>13267</v>
+        <v>14127</v>
       </c>
     </row>
     <row r="141">
@@ -90099,13 +90109,13 @@
         <v>399878</v>
       </c>
       <c r="C141" t="n">
-        <v>223603</v>
+        <v>223668</v>
       </c>
       <c r="D141" t="n">
         <v>58593</v>
       </c>
       <c r="E141" t="n">
-        <v>14291</v>
+        <v>14606</v>
       </c>
       <c r="F141" t="n">
         <v>68350</v>
@@ -90117,7 +90127,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>754681</v>
+        <v>755161</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90138,7 +90148,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>
@@ -91554,7 +91564,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>395</v>
+        <v>460</v>
       </c>
     </row>
     <row r="141">
@@ -91564,7 +91574,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>223603</v>
+        <v>223668</v>
       </c>
     </row>
     <row r="143">
@@ -91672,7 +91682,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>14578</v>
+        <v>14643</v>
       </c>
     </row>
     <row r="156">
@@ -91682,7 +91692,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>223603</v>
+        <v>223668</v>
       </c>
     </row>
   </sheetData>
@@ -98101,13 +98111,13 @@
         <v>345</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4902</v>
+        <v>4937</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -98119,13 +98129,13 @@
         <v>150</v>
       </c>
       <c r="I13" t="n">
-        <v>435</v>
+        <v>595</v>
       </c>
       <c r="J13" t="n">
-        <v>1370</v>
+        <v>1400</v>
       </c>
       <c r="K13" t="n">
-        <v>1115</v>
+        <v>1165</v>
       </c>
       <c r="L13" t="n">
         <v>825</v>
@@ -98260,7 +98270,7 @@
         <v>599</v>
       </c>
       <c r="BD13" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -98275,10 +98285,10 @@
         <v>85</v>
       </c>
       <c r="BI13" t="n">
-        <v>1320</v>
+        <v>1605</v>
       </c>
       <c r="BJ13" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="BK13" t="n">
         <v>40</v>
@@ -98338,7 +98348,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>2460</v>
+        <v>2515</v>
       </c>
       <c r="CE13" t="n">
         <v>856</v>
@@ -98413,7 +98423,7 @@
         <v>15220</v>
       </c>
       <c r="DC13" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="DD13" t="n">
         <v>153</v>
@@ -98473,7 +98483,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>164318</v>
+        <v>165178</v>
       </c>
     </row>
     <row r="14">
@@ -98486,13 +98496,13 @@
         <v>2547</v>
       </c>
       <c r="C14" t="n">
-        <v>935</v>
+        <v>995</v>
       </c>
       <c r="D14" t="n">
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>71597</v>
+        <v>71632</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98504,13 +98514,13 @@
         <v>2718</v>
       </c>
       <c r="I14" t="n">
-        <v>3040</v>
+        <v>3200</v>
       </c>
       <c r="J14" t="n">
-        <v>22345</v>
+        <v>22375</v>
       </c>
       <c r="K14" t="n">
-        <v>17042</v>
+        <v>17092</v>
       </c>
       <c r="L14" t="n">
         <v>5790</v>
@@ -98645,7 +98655,7 @@
         <v>9766</v>
       </c>
       <c r="BD14" t="n">
-        <v>6787</v>
+        <v>6847</v>
       </c>
       <c r="BE14" t="n">
         <v>52</v>
@@ -98660,10 +98670,10 @@
         <v>1196</v>
       </c>
       <c r="BI14" t="n">
-        <v>13284</v>
+        <v>13569</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1007</v>
+        <v>1037</v>
       </c>
       <c r="BK14" t="n">
         <v>660</v>
@@ -98723,7 +98733,7 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>16198</v>
+        <v>16253</v>
       </c>
       <c r="CE14" t="n">
         <v>5771</v>
@@ -98798,7 +98808,7 @@
         <v>219293</v>
       </c>
       <c r="DC14" t="n">
-        <v>1030</v>
+        <v>1125</v>
       </c>
       <c r="DD14" t="n">
         <v>1351</v>
@@ -98858,7 +98868,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>
@@ -99629,7 +99639,7 @@
         <v>5088</v>
       </c>
       <c r="C13" t="n">
-        <v>2075</v>
+        <v>2550</v>
       </c>
       <c r="D13" t="n">
         <v>5162</v>
@@ -99665,19 +99675,19 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="P13" t="n">
-        <v>28575</v>
+        <v>28695</v>
       </c>
       <c r="Q13" t="n">
-        <v>3227</v>
+        <v>3382</v>
       </c>
       <c r="R13" t="n">
-        <v>9227</v>
+        <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>164318</v>
+        <v>165178</v>
       </c>
     </row>
     <row r="14">
@@ -99690,7 +99700,7 @@
         <v>78143</v>
       </c>
       <c r="C14" t="n">
-        <v>17331</v>
+        <v>17806</v>
       </c>
       <c r="D14" t="n">
         <v>62490</v>
@@ -99726,19 +99736,19 @@
         <v>42</v>
       </c>
       <c r="O14" t="n">
-        <v>22052</v>
+        <v>22112</v>
       </c>
       <c r="P14" t="n">
-        <v>423096</v>
+        <v>423216</v>
       </c>
       <c r="Q14" t="n">
-        <v>36635</v>
+        <v>36790</v>
       </c>
       <c r="R14" t="n">
-        <v>88568</v>
+        <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>
@@ -100395,13 +100405,13 @@
         <v>24527</v>
       </c>
       <c r="C13" t="n">
-        <v>14578</v>
+        <v>14643</v>
       </c>
       <c r="D13" t="n">
         <v>4532</v>
       </c>
       <c r="E13" t="n">
-        <v>1640</v>
+        <v>1955</v>
       </c>
       <c r="F13" t="n">
         <v>4031</v>
@@ -100413,7 +100423,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>71758</v>
+        <v>72238</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100434,7 +100444,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>164318</v>
+        <v>165178</v>
       </c>
     </row>
     <row r="14">
@@ -100447,13 +100457,13 @@
         <v>399878</v>
       </c>
       <c r="C14" t="n">
-        <v>223603</v>
+        <v>223668</v>
       </c>
       <c r="D14" t="n">
         <v>58593</v>
       </c>
       <c r="E14" t="n">
-        <v>14291</v>
+        <v>14606</v>
       </c>
       <c r="F14" t="n">
         <v>68350</v>
@@ -100465,7 +100475,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>754681</v>
+        <v>755161</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100486,7 +100496,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2083331</v>
+        <v>2084191</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54460,7 +54460,7 @@
         <v>0</v>
       </c>
       <c r="CD140" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="CE140" t="n">
         <v>0</v>
@@ -54550,10 +54550,10 @@
         <v>100</v>
       </c>
       <c r="DH140" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="DI140" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="DJ140" t="n">
         <v>260</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>14127</v>
+        <v>15132</v>
       </c>
     </row>
     <row r="141">
@@ -54845,7 +54845,7 @@
         <v>435</v>
       </c>
       <c r="CD141" t="n">
-        <v>16253</v>
+        <v>16293</v>
       </c>
       <c r="CE141" t="n">
         <v>5771</v>
@@ -54935,10 +54935,10 @@
         <v>20680</v>
       </c>
       <c r="DH141" t="n">
-        <v>37481</v>
+        <v>38191</v>
       </c>
       <c r="DI141" t="n">
-        <v>23863</v>
+        <v>24118</v>
       </c>
       <c r="DJ141" t="n">
         <v>100234</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>
@@ -61205,7 +61205,7 @@
         <v>260</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="E8" t="n">
         <v>425</v>
@@ -61238,7 +61238,7 @@
         <v>3155</v>
       </c>
       <c r="O8" t="n">
-        <v>7277</v>
+        <v>8242</v>
       </c>
     </row>
     <row r="9">
@@ -61254,7 +61254,7 @@
         <v>5725</v>
       </c>
       <c r="D9" t="n">
-        <v>5000</v>
+        <v>5965</v>
       </c>
       <c r="E9" t="n">
         <v>4031</v>
@@ -61287,7 +61287,7 @@
         <v>24527</v>
       </c>
       <c r="O9" t="n">
-        <v>92940</v>
+        <v>93905</v>
       </c>
     </row>
   </sheetData>
@@ -71412,7 +71412,7 @@
         <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>1300</v>
+        <v>2305</v>
       </c>
       <c r="Q140" t="n">
         <v>155</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>14127</v>
+        <v>15132</v>
       </c>
     </row>
     <row r="141">
@@ -71473,7 +71473,7 @@
         <v>22112</v>
       </c>
       <c r="P141" t="n">
-        <v>423216</v>
+        <v>424221</v>
       </c>
       <c r="Q141" t="n">
         <v>36790</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>
@@ -73040,7 +73040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B143"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74318,129 +74318,139 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>61344</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="B129" t="n">
+        <v>62309</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B131" t="n">
-        <v>337</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B132" t="n">
-        <v>2431</v>
+        <v>337</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B133" t="n">
-        <v>2574</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B134" t="n">
-        <v>2985</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B135" t="n">
-        <v>4530</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B136" t="n">
-        <v>5425</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B137" t="n">
-        <v>6245</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B138" t="n">
-        <v>6030</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B139" t="n">
-        <v>7580</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B140" t="n">
-        <v>8604</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B141" t="n">
-        <v>9603</v>
+        <v>8604</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B142" t="n">
+        <v>9603</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
         <v>2026</v>
       </c>
-      <c r="B142" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="B143" t="n">
+        <v>5965</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>61344</v>
+      <c r="B144" t="n">
+        <v>62309</v>
       </c>
     </row>
   </sheetData>
@@ -90075,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>6850</v>
+        <v>6890</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90084,7 +90094,7 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="M140" t="n">
         <v>260</v>
@@ -90096,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>14127</v>
+        <v>15132</v>
       </c>
     </row>
     <row r="141">
@@ -90127,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>755161</v>
+        <v>755201</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90136,7 +90146,7 @@
         <v>32660</v>
       </c>
       <c r="L141" t="n">
-        <v>61344</v>
+        <v>62309</v>
       </c>
       <c r="M141" t="n">
         <v>100234</v>
@@ -90148,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>
@@ -98348,7 +98358,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>2515</v>
+        <v>2555</v>
       </c>
       <c r="CE13" t="n">
         <v>856</v>
@@ -98438,10 +98448,10 @@
         <v>1165</v>
       </c>
       <c r="DH13" t="n">
-        <v>2805</v>
+        <v>3515</v>
       </c>
       <c r="DI13" t="n">
-        <v>2195</v>
+        <v>2450</v>
       </c>
       <c r="DJ13" t="n">
         <v>5725</v>
@@ -98483,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>165178</v>
+        <v>166183</v>
       </c>
     </row>
     <row r="14">
@@ -98733,7 +98743,7 @@
         <v>435</v>
       </c>
       <c r="CD14" t="n">
-        <v>16253</v>
+        <v>16293</v>
       </c>
       <c r="CE14" t="n">
         <v>5771</v>
@@ -98823,10 +98833,10 @@
         <v>20680</v>
       </c>
       <c r="DH14" t="n">
-        <v>37481</v>
+        <v>38191</v>
       </c>
       <c r="DI14" t="n">
-        <v>23863</v>
+        <v>24118</v>
       </c>
       <c r="DJ14" t="n">
         <v>100234</v>
@@ -98868,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>
@@ -99678,7 +99688,7 @@
         <v>260</v>
       </c>
       <c r="P13" t="n">
-        <v>28695</v>
+        <v>29700</v>
       </c>
       <c r="Q13" t="n">
         <v>3382</v>
@@ -99687,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>165178</v>
+        <v>166183</v>
       </c>
     </row>
     <row r="14">
@@ -99739,7 +99749,7 @@
         <v>22112</v>
       </c>
       <c r="P14" t="n">
-        <v>423216</v>
+        <v>424221</v>
       </c>
       <c r="Q14" t="n">
         <v>36790</v>
@@ -99748,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>
@@ -100423,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>72238</v>
+        <v>72278</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100432,7 +100442,7 @@
         <v>2445</v>
       </c>
       <c r="L13" t="n">
-        <v>5000</v>
+        <v>5965</v>
       </c>
       <c r="M13" t="n">
         <v>5725</v>
@@ -100444,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>165178</v>
+        <v>166183</v>
       </c>
     </row>
     <row r="14">
@@ -100475,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>755161</v>
+        <v>755201</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100484,7 +100494,7 @@
         <v>32660</v>
       </c>
       <c r="L14" t="n">
-        <v>61344</v>
+        <v>62309</v>
       </c>
       <c r="M14" t="n">
         <v>100234</v>
@@ -100496,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2084191</v>
+        <v>2085196</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54262,13 +54262,13 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3155</v>
+        <v>3240</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -54277,7 +54277,7 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -54406,7 +54406,7 @@
         <v>0</v>
       </c>
       <c r="BL140" t="n">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="BM140" t="n">
         <v>0</v>
@@ -54508,7 +54508,7 @@
         <v>0</v>
       </c>
       <c r="CT140" t="n">
-        <v>415</v>
+        <v>505</v>
       </c>
       <c r="CU140" t="n">
         <v>195</v>
@@ -54547,7 +54547,7 @@
         <v>0</v>
       </c>
       <c r="DG140" t="n">
-        <v>100</v>
+        <v>505</v>
       </c>
       <c r="DH140" t="n">
         <v>710</v>
@@ -54580,13 +54580,13 @@
         <v>0</v>
       </c>
       <c r="DR140" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="DS140" t="n">
         <v>0</v>
       </c>
       <c r="DT140" t="n">
-        <v>637</v>
+        <v>757</v>
       </c>
       <c r="DU140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>15132</v>
+        <v>16172</v>
       </c>
     </row>
     <row r="141">
@@ -54647,13 +54647,13 @@
         <v>5786</v>
       </c>
       <c r="P141" t="n">
-        <v>6712</v>
+        <v>6847</v>
       </c>
       <c r="Q141" t="n">
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>432538</v>
+        <v>432623</v>
       </c>
       <c r="S141" t="n">
         <v>925</v>
@@ -54662,7 +54662,7 @@
         <v>872</v>
       </c>
       <c r="U141" t="n">
-        <v>2146</v>
+        <v>2176</v>
       </c>
       <c r="V141" t="n">
         <v>14436</v>
@@ -54791,7 +54791,7 @@
         <v>660</v>
       </c>
       <c r="BL141" t="n">
-        <v>47670</v>
+        <v>47755</v>
       </c>
       <c r="BM141" t="n">
         <v>1992</v>
@@ -54893,7 +54893,7 @@
         <v>2</v>
       </c>
       <c r="CT141" t="n">
-        <v>65570</v>
+        <v>65660</v>
       </c>
       <c r="CU141" t="n">
         <v>2579</v>
@@ -54932,7 +54932,7 @@
         <v>47</v>
       </c>
       <c r="DG141" t="n">
-        <v>20680</v>
+        <v>21085</v>
       </c>
       <c r="DH141" t="n">
         <v>38191</v>
@@ -54965,13 +54965,13 @@
         <v>7725</v>
       </c>
       <c r="DR141" t="n">
-        <v>58311</v>
+        <v>58401</v>
       </c>
       <c r="DS141" t="n">
         <v>1450</v>
       </c>
       <c r="DT141" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
       <c r="DU141" t="n">
         <v>4927</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>
@@ -61208,13 +61208,13 @@
         <v>965</v>
       </c>
       <c r="E8" t="n">
-        <v>425</v>
+        <v>915</v>
       </c>
       <c r="F8" t="n">
         <v>425</v>
       </c>
       <c r="G8" t="n">
-        <v>637</v>
+        <v>757</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -61235,10 +61235,10 @@
         <v>460</v>
       </c>
       <c r="N8" t="n">
-        <v>3155</v>
+        <v>3240</v>
       </c>
       <c r="O8" t="n">
-        <v>8242</v>
+        <v>8937</v>
       </c>
     </row>
     <row r="9">
@@ -61257,13 +61257,13 @@
         <v>5965</v>
       </c>
       <c r="E9" t="n">
-        <v>4031</v>
+        <v>4521</v>
       </c>
       <c r="F9" t="n">
         <v>4532</v>
       </c>
       <c r="G9" t="n">
-        <v>5427</v>
+        <v>5547</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -61284,10 +61284,10 @@
         <v>14643</v>
       </c>
       <c r="N9" t="n">
-        <v>24527</v>
+        <v>24612</v>
       </c>
       <c r="O9" t="n">
-        <v>93905</v>
+        <v>94600</v>
       </c>
     </row>
   </sheetData>
@@ -71370,7 +71370,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>425</v>
+        <v>1050</v>
       </c>
       <c r="C140" t="n">
         <v>475</v>
@@ -71379,7 +71379,7 @@
         <v>327</v>
       </c>
       <c r="E140" t="n">
-        <v>7667</v>
+        <v>8082</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>15132</v>
+        <v>16172</v>
       </c>
     </row>
     <row r="141">
@@ -71431,7 +71431,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>78143</v>
+        <v>78768</v>
       </c>
       <c r="C141" t="n">
         <v>17806</v>
@@ -71440,7 +71440,7 @@
         <v>62490</v>
       </c>
       <c r="E141" t="n">
-        <v>862584</v>
+        <v>862999</v>
       </c>
       <c r="F141" t="n">
         <v>5932</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>
@@ -75726,7 +75726,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>425</v>
+        <v>915</v>
       </c>
     </row>
     <row r="127">
@@ -75736,7 +75736,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>68350</v>
+        <v>68840</v>
       </c>
     </row>
     <row r="129">
@@ -75844,7 +75844,7 @@
         <v>2026</v>
       </c>
       <c r="B141" t="n">
-        <v>4031</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="142">
@@ -75854,7 +75854,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>68350</v>
+        <v>68840</v>
       </c>
     </row>
   </sheetData>
@@ -78504,7 +78504,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>637</v>
+        <v>757</v>
       </c>
     </row>
     <row r="137">
@@ -78514,7 +78514,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
     </row>
     <row r="139">
@@ -78622,7 +78622,7 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>5427</v>
+        <v>5547</v>
       </c>
     </row>
     <row r="152">
@@ -78632,7 +78632,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
     </row>
   </sheetData>
@@ -90064,7 +90064,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3155</v>
+        <v>3240</v>
       </c>
       <c r="C140" t="n">
         <v>460</v>
@@ -90076,7 +90076,7 @@
         <v>315</v>
       </c>
       <c r="F140" t="n">
-        <v>425</v>
+        <v>915</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>6890</v>
+        <v>7235</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90100,13 +90100,13 @@
         <v>260</v>
       </c>
       <c r="N140" t="n">
-        <v>637</v>
+        <v>757</v>
       </c>
       <c r="O140" t="n">
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>15132</v>
+        <v>16172</v>
       </c>
     </row>
     <row r="141">
@@ -90116,7 +90116,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>399878</v>
+        <v>399963</v>
       </c>
       <c r="C141" t="n">
         <v>223668</v>
@@ -90128,7 +90128,7 @@
         <v>14606</v>
       </c>
       <c r="F141" t="n">
-        <v>68350</v>
+        <v>68840</v>
       </c>
       <c r="G141" t="n">
         <v>23492</v>
@@ -90137,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>755201</v>
+        <v>755546</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90152,13 +90152,13 @@
         <v>100234</v>
       </c>
       <c r="N141" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
       <c r="O141" t="n">
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>
@@ -93118,7 +93118,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3155</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="141">
@@ -93128,7 +93128,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>399878</v>
+        <v>399963</v>
       </c>
     </row>
     <row r="143">
@@ -93236,7 +93236,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>24527</v>
+        <v>24612</v>
       </c>
     </row>
     <row r="156">
@@ -93246,7 +93246,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>399878</v>
+        <v>399963</v>
       </c>
     </row>
   </sheetData>
@@ -98160,13 +98160,13 @@
         <v>72</v>
       </c>
       <c r="P13" t="n">
-        <v>675</v>
+        <v>810</v>
       </c>
       <c r="Q13" t="n">
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>26972</v>
+        <v>27057</v>
       </c>
       <c r="S13" t="n">
         <v>140</v>
@@ -98175,7 +98175,7 @@
         <v>500</v>
       </c>
       <c r="U13" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="V13" t="n">
         <v>111</v>
@@ -98304,7 +98304,7 @@
         <v>40</v>
       </c>
       <c r="BL13" t="n">
-        <v>2866</v>
+        <v>2951</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
@@ -98406,7 +98406,7 @@
         <v>2</v>
       </c>
       <c r="CT13" t="n">
-        <v>4840</v>
+        <v>4930</v>
       </c>
       <c r="CU13" t="n">
         <v>1120</v>
@@ -98445,7 +98445,7 @@
         <v>47</v>
       </c>
       <c r="DG13" t="n">
-        <v>1165</v>
+        <v>1570</v>
       </c>
       <c r="DH13" t="n">
         <v>3515</v>
@@ -98478,13 +98478,13 @@
         <v>395</v>
       </c>
       <c r="DR13" t="n">
-        <v>5016</v>
+        <v>5106</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>5427</v>
+        <v>5547</v>
       </c>
       <c r="DU13" t="n">
         <v>275</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>166183</v>
+        <v>167223</v>
       </c>
     </row>
     <row r="14">
@@ -98545,13 +98545,13 @@
         <v>5786</v>
       </c>
       <c r="P14" t="n">
-        <v>6712</v>
+        <v>6847</v>
       </c>
       <c r="Q14" t="n">
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>432538</v>
+        <v>432623</v>
       </c>
       <c r="S14" t="n">
         <v>925</v>
@@ -98560,7 +98560,7 @@
         <v>872</v>
       </c>
       <c r="U14" t="n">
-        <v>2146</v>
+        <v>2176</v>
       </c>
       <c r="V14" t="n">
         <v>14436</v>
@@ -98689,7 +98689,7 @@
         <v>660</v>
       </c>
       <c r="BL14" t="n">
-        <v>47670</v>
+        <v>47755</v>
       </c>
       <c r="BM14" t="n">
         <v>1992</v>
@@ -98791,7 +98791,7 @@
         <v>2</v>
       </c>
       <c r="CT14" t="n">
-        <v>65570</v>
+        <v>65660</v>
       </c>
       <c r="CU14" t="n">
         <v>2579</v>
@@ -98830,7 +98830,7 @@
         <v>47</v>
       </c>
       <c r="DG14" t="n">
-        <v>20680</v>
+        <v>21085</v>
       </c>
       <c r="DH14" t="n">
         <v>38191</v>
@@ -98863,13 +98863,13 @@
         <v>7725</v>
       </c>
       <c r="DR14" t="n">
-        <v>58311</v>
+        <v>58401</v>
       </c>
       <c r="DS14" t="n">
         <v>1450</v>
       </c>
       <c r="DT14" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
       <c r="DU14" t="n">
         <v>4927</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>
@@ -99646,7 +99646,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>5088</v>
+        <v>5713</v>
       </c>
       <c r="C13" t="n">
         <v>2550</v>
@@ -99655,7 +99655,7 @@
         <v>5162</v>
       </c>
       <c r="E13" t="n">
-        <v>70862</v>
+        <v>71277</v>
       </c>
       <c r="F13" t="n">
         <v>465</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>166183</v>
+        <v>167223</v>
       </c>
     </row>
     <row r="14">
@@ -99707,7 +99707,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78143</v>
+        <v>78768</v>
       </c>
       <c r="C14" t="n">
         <v>17806</v>
@@ -99716,7 +99716,7 @@
         <v>62490</v>
       </c>
       <c r="E14" t="n">
-        <v>862584</v>
+        <v>862999</v>
       </c>
       <c r="F14" t="n">
         <v>5932</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>
@@ -100412,7 +100412,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>24527</v>
+        <v>24612</v>
       </c>
       <c r="C13" t="n">
         <v>14643</v>
@@ -100424,7 +100424,7 @@
         <v>1955</v>
       </c>
       <c r="F13" t="n">
-        <v>4031</v>
+        <v>4521</v>
       </c>
       <c r="G13" t="n">
         <v>2880</v>
@@ -100433,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>72278</v>
+        <v>72623</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100448,13 +100448,13 @@
         <v>5725</v>
       </c>
       <c r="N13" t="n">
-        <v>5427</v>
+        <v>5547</v>
       </c>
       <c r="O13" t="n">
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>166183</v>
+        <v>167223</v>
       </c>
     </row>
     <row r="14">
@@ -100464,7 +100464,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>399878</v>
+        <v>399963</v>
       </c>
       <c r="C14" t="n">
         <v>223668</v>
@@ -100476,7 +100476,7 @@
         <v>14606</v>
       </c>
       <c r="F14" t="n">
-        <v>68350</v>
+        <v>68840</v>
       </c>
       <c r="G14" t="n">
         <v>23492</v>
@@ -100485,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>755201</v>
+        <v>755546</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100500,13 +100500,13 @@
         <v>100234</v>
       </c>
       <c r="N14" t="n">
-        <v>71213</v>
+        <v>71333</v>
       </c>
       <c r="O14" t="n">
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2085196</v>
+        <v>2086236</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54229,7 +54229,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>165</v>
+        <v>595</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -54343,7 +54343,7 @@
         <v>0</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR140" t="n">
         <v>2</v>
@@ -54439,7 +54439,7 @@
         <v>0</v>
       </c>
       <c r="BW140" t="n">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="BX140" t="n">
         <v>0</v>
@@ -54577,7 +54577,7 @@
         <v>0</v>
       </c>
       <c r="DQ140" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="DR140" t="n">
         <v>660</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>16172</v>
+        <v>17137</v>
       </c>
     </row>
     <row r="141">
@@ -54614,7 +54614,7 @@
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>71632</v>
+        <v>72062</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -54728,7 +54728,7 @@
         <v>277</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2009</v>
+        <v>2039</v>
       </c>
       <c r="AR141" t="n">
         <v>389</v>
@@ -54824,7 +54824,7 @@
         <v>5791</v>
       </c>
       <c r="BW141" t="n">
-        <v>34641</v>
+        <v>34946</v>
       </c>
       <c r="BX141" t="n">
         <v>5175</v>
@@ -54962,7 +54962,7 @@
         <v>3027</v>
       </c>
       <c r="DQ141" t="n">
-        <v>7725</v>
+        <v>7925</v>
       </c>
       <c r="DR141" t="n">
         <v>58401</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>
@@ -61232,13 +61232,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>460</v>
+        <v>1195</v>
       </c>
       <c r="N8" t="n">
         <v>3240</v>
       </c>
       <c r="O8" t="n">
-        <v>8937</v>
+        <v>9672</v>
       </c>
     </row>
     <row r="9">
@@ -61281,13 +61281,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>14643</v>
+        <v>15378</v>
       </c>
       <c r="N9" t="n">
         <v>24612</v>
       </c>
       <c r="O9" t="n">
-        <v>94600</v>
+        <v>95335</v>
       </c>
     </row>
   </sheetData>
@@ -71412,7 +71412,7 @@
         <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>2305</v>
+        <v>3270</v>
       </c>
       <c r="Q140" t="n">
         <v>155</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>16172</v>
+        <v>17137</v>
       </c>
     </row>
     <row r="141">
@@ -71473,7 +71473,7 @@
         <v>22112</v>
       </c>
       <c r="P141" t="n">
-        <v>424221</v>
+        <v>425186</v>
       </c>
       <c r="Q141" t="n">
         <v>36790</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>
@@ -90067,7 +90067,7 @@
         <v>3240</v>
       </c>
       <c r="C140" t="n">
-        <v>460</v>
+        <v>1195</v>
       </c>
       <c r="D140" t="n">
         <v>425</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>7235</v>
+        <v>7465</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90106,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>16172</v>
+        <v>17137</v>
       </c>
     </row>
     <row r="141">
@@ -90119,7 +90119,7 @@
         <v>399963</v>
       </c>
       <c r="C141" t="n">
-        <v>223668</v>
+        <v>224403</v>
       </c>
       <c r="D141" t="n">
         <v>58593</v>
@@ -90137,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>755546</v>
+        <v>755776</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90158,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>
@@ -91574,7 +91574,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>460</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="141">
@@ -91584,7 +91584,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>223668</v>
+        <v>224403</v>
       </c>
     </row>
     <row r="143">
@@ -91692,7 +91692,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>14643</v>
+        <v>15378</v>
       </c>
     </row>
     <row r="156">
@@ -91702,7 +91702,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>223668</v>
+        <v>224403</v>
       </c>
     </row>
   </sheetData>
@@ -98127,7 +98127,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4937</v>
+        <v>5367</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -98241,7 +98241,7 @@
         <v>110</v>
       </c>
       <c r="AQ13" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AR13" t="n">
         <v>37</v>
@@ -98337,7 +98337,7 @@
         <v>1037</v>
       </c>
       <c r="BW13" t="n">
-        <v>2424</v>
+        <v>2729</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
@@ -98475,7 +98475,7 @@
         <v>380</v>
       </c>
       <c r="DQ13" t="n">
-        <v>395</v>
+        <v>595</v>
       </c>
       <c r="DR13" t="n">
         <v>5106</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>167223</v>
+        <v>168188</v>
       </c>
     </row>
     <row r="14">
@@ -98512,7 +98512,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>71632</v>
+        <v>72062</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98626,7 +98626,7 @@
         <v>277</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2009</v>
+        <v>2039</v>
       </c>
       <c r="AR14" t="n">
         <v>389</v>
@@ -98722,7 +98722,7 @@
         <v>5791</v>
       </c>
       <c r="BW14" t="n">
-        <v>34641</v>
+        <v>34946</v>
       </c>
       <c r="BX14" t="n">
         <v>5175</v>
@@ -98860,7 +98860,7 @@
         <v>3027</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7725</v>
+        <v>7925</v>
       </c>
       <c r="DR14" t="n">
         <v>58401</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>
@@ -99688,7 +99688,7 @@
         <v>260</v>
       </c>
       <c r="P13" t="n">
-        <v>29700</v>
+        <v>30665</v>
       </c>
       <c r="Q13" t="n">
         <v>3382</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>167223</v>
+        <v>168188</v>
       </c>
     </row>
     <row r="14">
@@ -99749,7 +99749,7 @@
         <v>22112</v>
       </c>
       <c r="P14" t="n">
-        <v>424221</v>
+        <v>425186</v>
       </c>
       <c r="Q14" t="n">
         <v>36790</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>
@@ -100415,7 +100415,7 @@
         <v>24612</v>
       </c>
       <c r="C13" t="n">
-        <v>14643</v>
+        <v>15378</v>
       </c>
       <c r="D13" t="n">
         <v>4532</v>
@@ -100433,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>72623</v>
+        <v>72853</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100454,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>167223</v>
+        <v>168188</v>
       </c>
     </row>
     <row r="14">
@@ -100467,7 +100467,7 @@
         <v>399963</v>
       </c>
       <c r="C14" t="n">
-        <v>223668</v>
+        <v>224403</v>
       </c>
       <c r="D14" t="n">
         <v>58593</v>
@@ -100485,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>755546</v>
+        <v>755776</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100506,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2086236</v>
+        <v>2087201</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54268,10 +54268,10 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3240</v>
+        <v>3435</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T140" t="n">
         <v>0</v>
@@ -54286,7 +54286,7 @@
         <v>410</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
@@ -54298,7 +54298,7 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -54340,7 +54340,7 @@
         <v>0</v>
       </c>
       <c r="AP140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ140" t="n">
         <v>30</v>
@@ -54529,7 +54529,7 @@
         <v>0</v>
       </c>
       <c r="DA140" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="DB140" t="n">
         <v>1380</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>17137</v>
+        <v>17729</v>
       </c>
     </row>
     <row r="141">
@@ -54653,10 +54653,10 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>432623</v>
+        <v>432818</v>
       </c>
       <c r="S141" t="n">
-        <v>925</v>
+        <v>975</v>
       </c>
       <c r="T141" t="n">
         <v>872</v>
@@ -54671,7 +54671,7 @@
         <v>24363</v>
       </c>
       <c r="X141" t="n">
-        <v>4712</v>
+        <v>4822</v>
       </c>
       <c r="Y141" t="n">
         <v>2947</v>
@@ -54683,7 +54683,7 @@
         <v>2</v>
       </c>
       <c r="AB141" t="n">
-        <v>9129</v>
+        <v>9239</v>
       </c>
       <c r="AC141" t="n">
         <v>212</v>
@@ -54725,7 +54725,7 @@
         <v>3357</v>
       </c>
       <c r="AP141" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AQ141" t="n">
         <v>2039</v>
@@ -54914,7 +54914,7 @@
         <v>18496</v>
       </c>
       <c r="DA141" t="n">
-        <v>13766</v>
+        <v>13886</v>
       </c>
       <c r="DB141" t="n">
         <v>219293</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>
@@ -61235,10 +61235,10 @@
         <v>1195</v>
       </c>
       <c r="N8" t="n">
-        <v>3240</v>
+        <v>3435</v>
       </c>
       <c r="O8" t="n">
-        <v>9672</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="9">
@@ -61284,10 +61284,10 @@
         <v>15378</v>
       </c>
       <c r="N9" t="n">
-        <v>24612</v>
+        <v>24807</v>
       </c>
       <c r="O9" t="n">
-        <v>95335</v>
+        <v>95530</v>
       </c>
     </row>
   </sheetData>
@@ -71376,13 +71376,13 @@
         <v>475</v>
       </c>
       <c r="D140" t="n">
-        <v>327</v>
+        <v>717</v>
       </c>
       <c r="E140" t="n">
-        <v>8082</v>
+        <v>8277</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>17137</v>
+        <v>17729</v>
       </c>
     </row>
     <row r="141">
@@ -71437,13 +71437,13 @@
         <v>17806</v>
       </c>
       <c r="D141" t="n">
-        <v>62490</v>
+        <v>62880</v>
       </c>
       <c r="E141" t="n">
-        <v>862999</v>
+        <v>863194</v>
       </c>
       <c r="F141" t="n">
-        <v>5932</v>
+        <v>5939</v>
       </c>
       <c r="G141" t="n">
         <v>34015</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>
@@ -90064,7 +90064,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3240</v>
+        <v>3435</v>
       </c>
       <c r="C140" t="n">
         <v>1195</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>7465</v>
+        <v>7862</v>
       </c>
       <c r="J140" t="n">
         <v>1380</v>
@@ -90106,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>17137</v>
+        <v>17729</v>
       </c>
     </row>
     <row r="141">
@@ -90116,7 +90116,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>399963</v>
+        <v>400158</v>
       </c>
       <c r="C141" t="n">
         <v>224403</v>
@@ -90137,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>755776</v>
+        <v>756173</v>
       </c>
       <c r="J141" t="n">
         <v>219293</v>
@@ -90158,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>
@@ -93118,7 +93118,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3240</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="141">
@@ -93128,7 +93128,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>399963</v>
+        <v>400158</v>
       </c>
     </row>
     <row r="143">
@@ -93236,7 +93236,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>24612</v>
+        <v>24807</v>
       </c>
     </row>
     <row r="156">
@@ -93246,7 +93246,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>399963</v>
+        <v>400158</v>
       </c>
     </row>
   </sheetData>
@@ -98166,10 +98166,10 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>27057</v>
+        <v>27252</v>
       </c>
       <c r="S13" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="T13" t="n">
         <v>500</v>
@@ -98184,7 +98184,7 @@
         <v>2370</v>
       </c>
       <c r="X13" t="n">
-        <v>720</v>
+        <v>830</v>
       </c>
       <c r="Y13" t="n">
         <v>95</v>
@@ -98196,7 +98196,7 @@
         <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>815</v>
+        <v>925</v>
       </c>
       <c r="AC13" t="n">
         <v>210</v>
@@ -98238,7 +98238,7 @@
         <v>650</v>
       </c>
       <c r="AP13" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AQ13" t="n">
         <v>170</v>
@@ -98427,7 +98427,7 @@
         <v>2190</v>
       </c>
       <c r="DA13" t="n">
-        <v>910</v>
+        <v>1030</v>
       </c>
       <c r="DB13" t="n">
         <v>15220</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>168188</v>
+        <v>168780</v>
       </c>
     </row>
     <row r="14">
@@ -98551,10 +98551,10 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>432623</v>
+        <v>432818</v>
       </c>
       <c r="S14" t="n">
-        <v>925</v>
+        <v>975</v>
       </c>
       <c r="T14" t="n">
         <v>872</v>
@@ -98569,7 +98569,7 @@
         <v>24363</v>
       </c>
       <c r="X14" t="n">
-        <v>4712</v>
+        <v>4822</v>
       </c>
       <c r="Y14" t="n">
         <v>2947</v>
@@ -98581,7 +98581,7 @@
         <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>9129</v>
+        <v>9239</v>
       </c>
       <c r="AC14" t="n">
         <v>212</v>
@@ -98623,7 +98623,7 @@
         <v>3357</v>
       </c>
       <c r="AP14" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AQ14" t="n">
         <v>2039</v>
@@ -98812,7 +98812,7 @@
         <v>18496</v>
       </c>
       <c r="DA14" t="n">
-        <v>13766</v>
+        <v>13886</v>
       </c>
       <c r="DB14" t="n">
         <v>219293</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>
@@ -99652,13 +99652,13 @@
         <v>2550</v>
       </c>
       <c r="D13" t="n">
-        <v>5162</v>
+        <v>5552</v>
       </c>
       <c r="E13" t="n">
-        <v>71277</v>
+        <v>71472</v>
       </c>
       <c r="F13" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G13" t="n">
         <v>2825</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>168188</v>
+        <v>168780</v>
       </c>
     </row>
     <row r="14">
@@ -99713,13 +99713,13 @@
         <v>17806</v>
       </c>
       <c r="D14" t="n">
-        <v>62490</v>
+        <v>62880</v>
       </c>
       <c r="E14" t="n">
-        <v>862999</v>
+        <v>863194</v>
       </c>
       <c r="F14" t="n">
-        <v>5932</v>
+        <v>5939</v>
       </c>
       <c r="G14" t="n">
         <v>34015</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>
@@ -100412,7 +100412,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>24612</v>
+        <v>24807</v>
       </c>
       <c r="C13" t="n">
         <v>15378</v>
@@ -100433,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>72853</v>
+        <v>73250</v>
       </c>
       <c r="J13" t="n">
         <v>15220</v>
@@ -100454,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>168188</v>
+        <v>168780</v>
       </c>
     </row>
     <row r="14">
@@ -100464,7 +100464,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>399963</v>
+        <v>400158</v>
       </c>
       <c r="C14" t="n">
         <v>224403</v>
@@ -100485,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>755776</v>
+        <v>756173</v>
       </c>
       <c r="J14" t="n">
         <v>219293</v>
@@ -100506,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2087201</v>
+        <v>2087793</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54421,7 +54421,7 @@
         <v>95</v>
       </c>
       <c r="BQ140" t="n">
-        <v>65</v>
+        <v>680</v>
       </c>
       <c r="BR140" t="n">
         <v>0</v>
@@ -54556,7 +54556,7 @@
         <v>255</v>
       </c>
       <c r="DJ140" t="n">
-        <v>260</v>
+        <v>795</v>
       </c>
       <c r="DK140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>17729</v>
+        <v>18879</v>
       </c>
     </row>
     <row r="141">
@@ -54806,7 +54806,7 @@
         <v>7460</v>
       </c>
       <c r="BQ141" t="n">
-        <v>95020</v>
+        <v>95635</v>
       </c>
       <c r="BR141" t="n">
         <v>22292</v>
@@ -54941,7 +54941,7 @@
         <v>24118</v>
       </c>
       <c r="DJ141" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
       <c r="DK141" t="n">
         <v>1240</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>
@@ -61202,7 +61202,7 @@
         <v>1380</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>795</v>
       </c>
       <c r="D8" t="n">
         <v>965</v>
@@ -61232,13 +61232,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1195</v>
+        <v>1810</v>
       </c>
       <c r="N8" t="n">
         <v>3435</v>
       </c>
       <c r="O8" t="n">
-        <v>9867</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="9">
@@ -61251,7 +61251,7 @@
         <v>15220</v>
       </c>
       <c r="C9" t="n">
-        <v>5725</v>
+        <v>6260</v>
       </c>
       <c r="D9" t="n">
         <v>5965</v>
@@ -61281,13 +61281,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>15378</v>
+        <v>15993</v>
       </c>
       <c r="N9" t="n">
         <v>24807</v>
       </c>
       <c r="O9" t="n">
-        <v>95530</v>
+        <v>96680</v>
       </c>
     </row>
   </sheetData>
@@ -71412,7 +71412,7 @@
         <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>3270</v>
+        <v>4420</v>
       </c>
       <c r="Q140" t="n">
         <v>155</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>17729</v>
+        <v>18879</v>
       </c>
     </row>
     <row r="141">
@@ -71473,7 +71473,7 @@
         <v>22112</v>
       </c>
       <c r="P141" t="n">
-        <v>425186</v>
+        <v>426336</v>
       </c>
       <c r="Q141" t="n">
         <v>36790</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>
@@ -72898,7 +72898,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>260</v>
+        <v>795</v>
       </c>
     </row>
     <row r="141">
@@ -72908,7 +72908,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
     </row>
     <row r="143">
@@ -73016,7 +73016,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>5725</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="156">
@@ -73026,7 +73026,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
     </row>
   </sheetData>
@@ -90067,7 +90067,7 @@
         <v>3435</v>
       </c>
       <c r="C140" t="n">
-        <v>1195</v>
+        <v>1810</v>
       </c>
       <c r="D140" t="n">
         <v>425</v>
@@ -90097,7 +90097,7 @@
         <v>965</v>
       </c>
       <c r="M140" t="n">
-        <v>260</v>
+        <v>795</v>
       </c>
       <c r="N140" t="n">
         <v>757</v>
@@ -90106,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>17729</v>
+        <v>18879</v>
       </c>
     </row>
     <row r="141">
@@ -90119,7 +90119,7 @@
         <v>400158</v>
       </c>
       <c r="C141" t="n">
-        <v>224403</v>
+        <v>225018</v>
       </c>
       <c r="D141" t="n">
         <v>58593</v>
@@ -90149,7 +90149,7 @@
         <v>62309</v>
       </c>
       <c r="M141" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
       <c r="N141" t="n">
         <v>71333</v>
@@ -90158,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>
@@ -91574,7 +91574,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1195</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="141">
@@ -91584,7 +91584,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>224403</v>
+        <v>225018</v>
       </c>
     </row>
     <row r="143">
@@ -91692,7 +91692,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>15378</v>
+        <v>15993</v>
       </c>
     </row>
     <row r="156">
@@ -91702,7 +91702,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>224403</v>
+        <v>225018</v>
       </c>
     </row>
   </sheetData>
@@ -98319,7 +98319,7 @@
         <v>430</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5882</v>
+        <v>6497</v>
       </c>
       <c r="BR13" t="n">
         <v>1730</v>
@@ -98454,7 +98454,7 @@
         <v>2450</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5725</v>
+        <v>6260</v>
       </c>
       <c r="DK13" t="n">
         <v>420</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>168780</v>
+        <v>169930</v>
       </c>
     </row>
     <row r="14">
@@ -98704,7 +98704,7 @@
         <v>7460</v>
       </c>
       <c r="BQ14" t="n">
-        <v>95020</v>
+        <v>95635</v>
       </c>
       <c r="BR14" t="n">
         <v>22292</v>
@@ -98839,7 +98839,7 @@
         <v>24118</v>
       </c>
       <c r="DJ14" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
       <c r="DK14" t="n">
         <v>1240</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>
@@ -99688,7 +99688,7 @@
         <v>260</v>
       </c>
       <c r="P13" t="n">
-        <v>30665</v>
+        <v>31815</v>
       </c>
       <c r="Q13" t="n">
         <v>3382</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>168780</v>
+        <v>169930</v>
       </c>
     </row>
     <row r="14">
@@ -99749,7 +99749,7 @@
         <v>22112</v>
       </c>
       <c r="P14" t="n">
-        <v>425186</v>
+        <v>426336</v>
       </c>
       <c r="Q14" t="n">
         <v>36790</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>
@@ -100415,7 +100415,7 @@
         <v>24807</v>
       </c>
       <c r="C13" t="n">
-        <v>15378</v>
+        <v>15993</v>
       </c>
       <c r="D13" t="n">
         <v>4532</v>
@@ -100445,7 +100445,7 @@
         <v>5965</v>
       </c>
       <c r="M13" t="n">
-        <v>5725</v>
+        <v>6260</v>
       </c>
       <c r="N13" t="n">
         <v>5547</v>
@@ -100454,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>168780</v>
+        <v>169930</v>
       </c>
     </row>
     <row r="14">
@@ -100467,7 +100467,7 @@
         <v>400158</v>
       </c>
       <c r="C14" t="n">
-        <v>224403</v>
+        <v>225018</v>
       </c>
       <c r="D14" t="n">
         <v>58593</v>
@@ -100497,7 +100497,7 @@
         <v>62309</v>
       </c>
       <c r="M14" t="n">
-        <v>100234</v>
+        <v>100769</v>
       </c>
       <c r="N14" t="n">
         <v>71333</v>
@@ -100506,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2087793</v>
+        <v>2088943</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54532,7 +54532,7 @@
         <v>120</v>
       </c>
       <c r="DB140" t="n">
-        <v>1380</v>
+        <v>2490</v>
       </c>
       <c r="DC140" t="n">
         <v>95</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>18879</v>
+        <v>19989</v>
       </c>
     </row>
     <row r="141">
@@ -54917,7 +54917,7 @@
         <v>13886</v>
       </c>
       <c r="DB141" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
       <c r="DC141" t="n">
         <v>1125</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>
@@ -61199,7 +61199,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1380</v>
+        <v>2490</v>
       </c>
       <c r="C8" t="n">
         <v>795</v>
@@ -61238,7 +61238,7 @@
         <v>3435</v>
       </c>
       <c r="O8" t="n">
-        <v>11017</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="9">
@@ -61248,7 +61248,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15220</v>
+        <v>16330</v>
       </c>
       <c r="C9" t="n">
         <v>6260</v>
@@ -61287,7 +61287,7 @@
         <v>24807</v>
       </c>
       <c r="O9" t="n">
-        <v>96680</v>
+        <v>97790</v>
       </c>
     </row>
   </sheetData>
@@ -62703,7 +62703,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1380</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="141">
@@ -62713,7 +62713,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
     </row>
     <row r="143">
@@ -62821,7 +62821,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>15220</v>
+        <v>16330</v>
       </c>
     </row>
     <row r="156">
@@ -62831,7 +62831,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
     </row>
   </sheetData>
@@ -71391,7 +71391,7 @@
         <v>500</v>
       </c>
       <c r="I140" t="n">
-        <v>1527</v>
+        <v>2637</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>18879</v>
+        <v>19989</v>
       </c>
     </row>
     <row r="141">
@@ -71452,7 +71452,7 @@
         <v>7999</v>
       </c>
       <c r="I141" t="n">
-        <v>285646</v>
+        <v>286756</v>
       </c>
       <c r="J141" t="n">
         <v>4939</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>
@@ -90088,7 +90088,7 @@
         <v>7862</v>
       </c>
       <c r="J140" t="n">
-        <v>1380</v>
+        <v>2490</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -90106,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>18879</v>
+        <v>19989</v>
       </c>
     </row>
     <row r="141">
@@ -90140,7 +90140,7 @@
         <v>756173</v>
       </c>
       <c r="J141" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
       <c r="K141" t="n">
         <v>32660</v>
@@ -90158,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>
@@ -98430,7 +98430,7 @@
         <v>1030</v>
       </c>
       <c r="DB13" t="n">
-        <v>15220</v>
+        <v>16330</v>
       </c>
       <c r="DC13" t="n">
         <v>125</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>169930</v>
+        <v>171040</v>
       </c>
     </row>
     <row r="14">
@@ -98815,7 +98815,7 @@
         <v>13886</v>
       </c>
       <c r="DB14" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
       <c r="DC14" t="n">
         <v>1125</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>
@@ -99667,7 +99667,7 @@
         <v>1715</v>
       </c>
       <c r="I13" t="n">
-        <v>20748</v>
+        <v>21858</v>
       </c>
       <c r="J13" t="n">
         <v>912</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>169930</v>
+        <v>171040</v>
       </c>
     </row>
     <row r="14">
@@ -99728,7 +99728,7 @@
         <v>7999</v>
       </c>
       <c r="I14" t="n">
-        <v>285646</v>
+        <v>286756</v>
       </c>
       <c r="J14" t="n">
         <v>4939</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>
@@ -100436,7 +100436,7 @@
         <v>73250</v>
       </c>
       <c r="J13" t="n">
-        <v>15220</v>
+        <v>16330</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -100454,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>169930</v>
+        <v>171040</v>
       </c>
     </row>
     <row r="14">
@@ -100488,7 +100488,7 @@
         <v>756173</v>
       </c>
       <c r="J14" t="n">
-        <v>219293</v>
+        <v>220403</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -100506,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2088943</v>
+        <v>2090053</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54253,7 +54253,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -54268,7 +54268,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="S140" t="n">
         <v>50</v>
@@ -54283,7 +54283,7 @@
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="X140" t="n">
         <v>110</v>
@@ -54331,13 +54331,13 @@
         <v>55</v>
       </c>
       <c r="AM140" t="n">
-        <v>75</v>
+        <v>746</v>
       </c>
       <c r="AN140" t="n">
         <v>0</v>
       </c>
       <c r="AO140" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AP140" t="n">
         <v>7</v>
@@ -54349,7 +54349,7 @@
         <v>2</v>
       </c>
       <c r="AS140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT140" t="n">
         <v>275</v>
@@ -54370,7 +54370,7 @@
         <v>0</v>
       </c>
       <c r="AZ140" t="n">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="BA140" t="n">
         <v>0</v>
@@ -54430,13 +54430,13 @@
         <v>0</v>
       </c>
       <c r="BT140" t="n">
-        <v>420</v>
+        <v>950</v>
       </c>
       <c r="BU140" t="n">
         <v>305</v>
       </c>
       <c r="BV140" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="BW140" t="n">
         <v>455</v>
@@ -54565,7 +54565,7 @@
         <v>0</v>
       </c>
       <c r="DM140" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="DN140" t="n">
         <v>251</v>
@@ -54586,7 +54586,7 @@
         <v>0</v>
       </c>
       <c r="DT140" t="n">
-        <v>757</v>
+        <v>997</v>
       </c>
       <c r="DU140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>19989</v>
+        <v>23110</v>
       </c>
     </row>
     <row r="141">
@@ -54638,7 +54638,7 @@
         <v>5790</v>
       </c>
       <c r="M141" t="n">
-        <v>1582</v>
+        <v>1742</v>
       </c>
       <c r="N141" t="n">
         <v>2935</v>
@@ -54653,7 +54653,7 @@
         <v>107</v>
       </c>
       <c r="R141" t="n">
-        <v>432818</v>
+        <v>433093</v>
       </c>
       <c r="S141" t="n">
         <v>975</v>
@@ -54668,7 +54668,7 @@
         <v>14436</v>
       </c>
       <c r="W141" t="n">
-        <v>24363</v>
+        <v>24413</v>
       </c>
       <c r="X141" t="n">
         <v>4822</v>
@@ -54716,13 +54716,13 @@
         <v>429</v>
       </c>
       <c r="AM141" t="n">
-        <v>50734</v>
+        <v>51405</v>
       </c>
       <c r="AN141" t="n">
         <v>4755</v>
       </c>
       <c r="AO141" t="n">
-        <v>3357</v>
+        <v>3717</v>
       </c>
       <c r="AP141" t="n">
         <v>284</v>
@@ -54734,7 +54734,7 @@
         <v>389</v>
       </c>
       <c r="AS141" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AT141" t="n">
         <v>26879</v>
@@ -54755,7 +54755,7 @@
         <v>460</v>
       </c>
       <c r="AZ141" t="n">
-        <v>41222</v>
+        <v>41302</v>
       </c>
       <c r="BA141" t="n">
         <v>6666</v>
@@ -54815,13 +54815,13 @@
         <v>13434</v>
       </c>
       <c r="BT141" t="n">
-        <v>26996</v>
+        <v>27526</v>
       </c>
       <c r="BU141" t="n">
         <v>5420</v>
       </c>
       <c r="BV141" t="n">
-        <v>5791</v>
+        <v>6296</v>
       </c>
       <c r="BW141" t="n">
         <v>34946</v>
@@ -54950,7 +54950,7 @@
         <v>15334</v>
       </c>
       <c r="DM141" t="n">
-        <v>10550</v>
+        <v>10780</v>
       </c>
       <c r="DN141" t="n">
         <v>18218</v>
@@ -54971,7 +54971,7 @@
         <v>1450</v>
       </c>
       <c r="DT141" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
       <c r="DU141" t="n">
         <v>4927</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>
@@ -61211,10 +61211,10 @@
         <v>915</v>
       </c>
       <c r="F8" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
       <c r="G8" t="n">
-        <v>757</v>
+        <v>997</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -61235,10 +61235,10 @@
         <v>1810</v>
       </c>
       <c r="N8" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="O8" t="n">
-        <v>12127</v>
+        <v>13227</v>
       </c>
     </row>
     <row r="9">
@@ -61260,10 +61260,10 @@
         <v>4521</v>
       </c>
       <c r="F9" t="n">
-        <v>4532</v>
+        <v>5117</v>
       </c>
       <c r="G9" t="n">
-        <v>5547</v>
+        <v>5787</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -61284,10 +61284,10 @@
         <v>15993</v>
       </c>
       <c r="N9" t="n">
-        <v>24807</v>
+        <v>25082</v>
       </c>
       <c r="O9" t="n">
-        <v>97790</v>
+        <v>98890</v>
       </c>
     </row>
   </sheetData>
@@ -71379,7 +71379,7 @@
         <v>717</v>
       </c>
       <c r="E140" t="n">
-        <v>8277</v>
+        <v>9513</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
@@ -71394,13 +71394,13 @@
         <v>2637</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="K140" t="n">
-        <v>845</v>
+        <v>2190</v>
       </c>
       <c r="L140" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M140" t="n">
         <v>165</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>19989</v>
+        <v>23110</v>
       </c>
     </row>
     <row r="141">
@@ -71440,7 +71440,7 @@
         <v>62880</v>
       </c>
       <c r="E141" t="n">
-        <v>863194</v>
+        <v>864430</v>
       </c>
       <c r="F141" t="n">
         <v>5939</v>
@@ -71455,13 +71455,13 @@
         <v>286756</v>
       </c>
       <c r="J141" t="n">
-        <v>4939</v>
+        <v>5459</v>
       </c>
       <c r="K141" t="n">
-        <v>109905</v>
+        <v>111250</v>
       </c>
       <c r="L141" t="n">
-        <v>35636</v>
+        <v>35656</v>
       </c>
       <c r="M141" t="n">
         <v>8318</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>
@@ -77000,7 +77000,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="114">
@@ -77010,7 +77010,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>58593</v>
+        <v>59178</v>
       </c>
     </row>
     <row r="116">
@@ -77118,7 +77118,7 @@
         <v>2026</v>
       </c>
       <c r="B128" t="n">
-        <v>4532</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="129">
@@ -77128,7 +77128,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>58593</v>
+        <v>59178</v>
       </c>
     </row>
   </sheetData>
@@ -78504,7 +78504,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>757</v>
+        <v>997</v>
       </c>
     </row>
     <row r="137">
@@ -78514,7 +78514,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
     </row>
     <row r="139">
@@ -78622,7 +78622,7 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>5547</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="152">
@@ -78632,7 +78632,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
     </row>
   </sheetData>
@@ -90064,13 +90064,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="C140" t="n">
         <v>1810</v>
       </c>
       <c r="D140" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
       <c r="E140" t="n">
         <v>315</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>7862</v>
+        <v>9883</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -90100,13 +90100,13 @@
         <v>795</v>
       </c>
       <c r="N140" t="n">
-        <v>757</v>
+        <v>997</v>
       </c>
       <c r="O140" t="n">
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>19989</v>
+        <v>23110</v>
       </c>
     </row>
     <row r="141">
@@ -90116,13 +90116,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400158</v>
+        <v>400433</v>
       </c>
       <c r="C141" t="n">
         <v>225018</v>
       </c>
       <c r="D141" t="n">
-        <v>58593</v>
+        <v>59178</v>
       </c>
       <c r="E141" t="n">
         <v>14606</v>
@@ -90137,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>756173</v>
+        <v>758194</v>
       </c>
       <c r="J141" t="n">
         <v>220403</v>
@@ -90152,13 +90152,13 @@
         <v>100769</v>
       </c>
       <c r="N141" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
       <c r="O141" t="n">
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>
@@ -93118,7 +93118,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="141">
@@ -93128,7 +93128,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400158</v>
+        <v>400433</v>
       </c>
     </row>
     <row r="143">
@@ -93236,7 +93236,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>24807</v>
+        <v>25082</v>
       </c>
     </row>
     <row r="156">
@@ -93246,7 +93246,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>400158</v>
+        <v>400433</v>
       </c>
     </row>
   </sheetData>
@@ -98151,7 +98151,7 @@
         <v>825</v>
       </c>
       <c r="M13" t="n">
-        <v>262</v>
+        <v>422</v>
       </c>
       <c r="N13" t="n">
         <v>265</v>
@@ -98166,7 +98166,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>27252</v>
+        <v>27527</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -98181,7 +98181,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>2370</v>
+        <v>2420</v>
       </c>
       <c r="X13" t="n">
         <v>830</v>
@@ -98229,13 +98229,13 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>2191</v>
+        <v>2862</v>
       </c>
       <c r="AN13" t="n">
         <v>165</v>
       </c>
       <c r="AO13" t="n">
-        <v>650</v>
+        <v>1010</v>
       </c>
       <c r="AP13" t="n">
         <v>117</v>
@@ -98247,7 +98247,7 @@
         <v>37</v>
       </c>
       <c r="AS13" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AT13" t="n">
         <v>2140</v>
@@ -98268,7 +98268,7 @@
         <v>50</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2790</v>
+        <v>2870</v>
       </c>
       <c r="BA13" t="n">
         <v>460</v>
@@ -98328,13 +98328,13 @@
         <v>1064</v>
       </c>
       <c r="BT13" t="n">
-        <v>3302</v>
+        <v>3832</v>
       </c>
       <c r="BU13" t="n">
         <v>595</v>
       </c>
       <c r="BV13" t="n">
-        <v>1037</v>
+        <v>1542</v>
       </c>
       <c r="BW13" t="n">
         <v>2729</v>
@@ -98463,7 +98463,7 @@
         <v>1825</v>
       </c>
       <c r="DM13" t="n">
-        <v>410</v>
+        <v>640</v>
       </c>
       <c r="DN13" t="n">
         <v>1903</v>
@@ -98484,7 +98484,7 @@
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>5547</v>
+        <v>5787</v>
       </c>
       <c r="DU13" t="n">
         <v>275</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>171040</v>
+        <v>174161</v>
       </c>
     </row>
     <row r="14">
@@ -98536,7 +98536,7 @@
         <v>5790</v>
       </c>
       <c r="M14" t="n">
-        <v>1582</v>
+        <v>1742</v>
       </c>
       <c r="N14" t="n">
         <v>2935</v>
@@ -98551,7 +98551,7 @@
         <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>432818</v>
+        <v>433093</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98566,7 +98566,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>24363</v>
+        <v>24413</v>
       </c>
       <c r="X14" t="n">
         <v>4822</v>
@@ -98614,13 +98614,13 @@
         <v>429</v>
       </c>
       <c r="AM14" t="n">
-        <v>50734</v>
+        <v>51405</v>
       </c>
       <c r="AN14" t="n">
         <v>4755</v>
       </c>
       <c r="AO14" t="n">
-        <v>3357</v>
+        <v>3717</v>
       </c>
       <c r="AP14" t="n">
         <v>284</v>
@@ -98632,7 +98632,7 @@
         <v>389</v>
       </c>
       <c r="AS14" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AT14" t="n">
         <v>26879</v>
@@ -98653,7 +98653,7 @@
         <v>460</v>
       </c>
       <c r="AZ14" t="n">
-        <v>41222</v>
+        <v>41302</v>
       </c>
       <c r="BA14" t="n">
         <v>6666</v>
@@ -98713,13 +98713,13 @@
         <v>13434</v>
       </c>
       <c r="BT14" t="n">
-        <v>26996</v>
+        <v>27526</v>
       </c>
       <c r="BU14" t="n">
         <v>5420</v>
       </c>
       <c r="BV14" t="n">
-        <v>5791</v>
+        <v>6296</v>
       </c>
       <c r="BW14" t="n">
         <v>34946</v>
@@ -98848,7 +98848,7 @@
         <v>15334</v>
       </c>
       <c r="DM14" t="n">
-        <v>10550</v>
+        <v>10780</v>
       </c>
       <c r="DN14" t="n">
         <v>18218</v>
@@ -98869,7 +98869,7 @@
         <v>1450</v>
       </c>
       <c r="DT14" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
       <c r="DU14" t="n">
         <v>4927</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>
@@ -99655,7 +99655,7 @@
         <v>5552</v>
       </c>
       <c r="E13" t="n">
-        <v>71472</v>
+        <v>72708</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99670,13 +99670,13 @@
         <v>21858</v>
       </c>
       <c r="J13" t="n">
-        <v>912</v>
+        <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>9608</v>
+        <v>10953</v>
       </c>
       <c r="L13" t="n">
-        <v>2428</v>
+        <v>2448</v>
       </c>
       <c r="M13" t="n">
         <v>1201</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>171040</v>
+        <v>174161</v>
       </c>
     </row>
     <row r="14">
@@ -99716,7 +99716,7 @@
         <v>62880</v>
       </c>
       <c r="E14" t="n">
-        <v>863194</v>
+        <v>864430</v>
       </c>
       <c r="F14" t="n">
         <v>5939</v>
@@ -99731,13 +99731,13 @@
         <v>286756</v>
       </c>
       <c r="J14" t="n">
-        <v>4939</v>
+        <v>5459</v>
       </c>
       <c r="K14" t="n">
-        <v>109905</v>
+        <v>111250</v>
       </c>
       <c r="L14" t="n">
-        <v>35636</v>
+        <v>35656</v>
       </c>
       <c r="M14" t="n">
         <v>8318</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>
@@ -100412,13 +100412,13 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>24807</v>
+        <v>25082</v>
       </c>
       <c r="C13" t="n">
         <v>15993</v>
       </c>
       <c r="D13" t="n">
-        <v>4532</v>
+        <v>5117</v>
       </c>
       <c r="E13" t="n">
         <v>1955</v>
@@ -100433,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>73250</v>
+        <v>75271</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -100448,13 +100448,13 @@
         <v>6260</v>
       </c>
       <c r="N13" t="n">
-        <v>5547</v>
+        <v>5787</v>
       </c>
       <c r="O13" t="n">
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>171040</v>
+        <v>174161</v>
       </c>
     </row>
     <row r="14">
@@ -100464,13 +100464,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>400158</v>
+        <v>400433</v>
       </c>
       <c r="C14" t="n">
         <v>225018</v>
       </c>
       <c r="D14" t="n">
-        <v>58593</v>
+        <v>59178</v>
       </c>
       <c r="E14" t="n">
         <v>14606</v>
@@ -100485,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>756173</v>
+        <v>758194</v>
       </c>
       <c r="J14" t="n">
         <v>220403</v>
@@ -100500,13 +100500,13 @@
         <v>100769</v>
       </c>
       <c r="N14" t="n">
-        <v>71333</v>
+        <v>71573</v>
       </c>
       <c r="O14" t="n">
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2090053</v>
+        <v>2093174</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53415,7 +53415,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -53430,7 +53430,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="S140" t="n">
         <v>50</v>
@@ -53445,7 +53445,7 @@
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="X140" t="n">
         <v>110</v>
@@ -53490,13 +53490,13 @@
         <v>55</v>
       </c>
       <c r="AL140" t="n">
-        <v>75</v>
+        <v>746</v>
       </c>
       <c r="AM140" t="n">
         <v>0</v>
       </c>
       <c r="AN140" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AO140" t="n">
         <v>7</v>
@@ -53508,7 +53508,7 @@
         <v>0</v>
       </c>
       <c r="AR140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS140" t="n">
         <v>275</v>
@@ -53529,7 +53529,7 @@
         <v>0</v>
       </c>
       <c r="AY140" t="n">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="AZ140" t="n">
         <v>0</v>
@@ -53589,13 +53589,13 @@
         <v>0</v>
       </c>
       <c r="BS140" t="n">
-        <v>420</v>
+        <v>950</v>
       </c>
       <c r="BT140" t="n">
         <v>305</v>
       </c>
       <c r="BU140" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="BV140" t="n">
         <v>455</v>
@@ -53721,7 +53721,7 @@
         <v>0</v>
       </c>
       <c r="DK140" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="DL140" t="n">
         <v>251</v>
@@ -53742,7 +53742,7 @@
         <v>0</v>
       </c>
       <c r="DR140" t="n">
-        <v>755</v>
+        <v>995</v>
       </c>
       <c r="DS140" t="n">
         <v>0</v>
@@ -53751,7 +53751,7 @@
         <v>70</v>
       </c>
       <c r="DU140" t="n">
-        <v>19983</v>
+        <v>23104</v>
       </c>
     </row>
     <row r="141">
@@ -53794,7 +53794,7 @@
         <v>5790</v>
       </c>
       <c r="M141" t="n">
-        <v>1582</v>
+        <v>1742</v>
       </c>
       <c r="N141" t="n">
         <v>2935</v>
@@ -53809,7 +53809,7 @@
         <v>105</v>
       </c>
       <c r="R141" t="n">
-        <v>432768</v>
+        <v>433043</v>
       </c>
       <c r="S141" t="n">
         <v>975</v>
@@ -53824,7 +53824,7 @@
         <v>14436</v>
       </c>
       <c r="W141" t="n">
-        <v>24359</v>
+        <v>24409</v>
       </c>
       <c r="X141" t="n">
         <v>4820</v>
@@ -53869,13 +53869,13 @@
         <v>427</v>
       </c>
       <c r="AL141" t="n">
-        <v>50732</v>
+        <v>51403</v>
       </c>
       <c r="AM141" t="n">
         <v>4755</v>
       </c>
       <c r="AN141" t="n">
-        <v>3355</v>
+        <v>3715</v>
       </c>
       <c r="AO141" t="n">
         <v>282</v>
@@ -53887,7 +53887,7 @@
         <v>385</v>
       </c>
       <c r="AR141" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AS141" t="n">
         <v>26879</v>
@@ -53908,7 +53908,7 @@
         <v>460</v>
       </c>
       <c r="AY141" t="n">
-        <v>41222</v>
+        <v>41302</v>
       </c>
       <c r="AZ141" t="n">
         <v>6666</v>
@@ -53968,13 +53968,13 @@
         <v>13430</v>
       </c>
       <c r="BS141" t="n">
-        <v>26996</v>
+        <v>27526</v>
       </c>
       <c r="BT141" t="n">
         <v>5420</v>
       </c>
       <c r="BU141" t="n">
-        <v>5785</v>
+        <v>6290</v>
       </c>
       <c r="BV141" t="n">
         <v>34940</v>
@@ -54100,7 +54100,7 @@
         <v>15330</v>
       </c>
       <c r="DK141" t="n">
-        <v>10550</v>
+        <v>10780</v>
       </c>
       <c r="DL141" t="n">
         <v>18216</v>
@@ -54121,7 +54121,7 @@
         <v>1450</v>
       </c>
       <c r="DR141" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
       <c r="DS141" t="n">
         <v>4927</v>
@@ -54130,7 +54130,7 @@
         <v>27596</v>
       </c>
       <c r="DU141" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>
@@ -60361,10 +60361,10 @@
         <v>915</v>
       </c>
       <c r="F8" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
       <c r="G8" t="n">
-        <v>755</v>
+        <v>995</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -60385,10 +60385,10 @@
         <v>1810</v>
       </c>
       <c r="N8" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="O8" t="n">
-        <v>12125</v>
+        <v>13225</v>
       </c>
     </row>
     <row r="9">
@@ -60410,10 +60410,10 @@
         <v>4521</v>
       </c>
       <c r="F9" t="n">
-        <v>4530</v>
+        <v>5115</v>
       </c>
       <c r="G9" t="n">
-        <v>5545</v>
+        <v>5785</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -60434,10 +60434,10 @@
         <v>15989</v>
       </c>
       <c r="N9" t="n">
-        <v>24797</v>
+        <v>25072</v>
       </c>
       <c r="O9" t="n">
-        <v>97772</v>
+        <v>98872</v>
       </c>
     </row>
   </sheetData>
@@ -63657,7 +63657,7 @@
         <v>390</v>
       </c>
       <c r="L27" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -63666,7 +63666,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="P27" t="n">
         <v>2007</v>
@@ -63840,7 +63840,7 @@
         <v>270</v>
       </c>
       <c r="L30" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -63849,7 +63849,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="P30" t="n">
         <v>2738</v>
@@ -63962,7 +63962,7 @@
         <v>1280</v>
       </c>
       <c r="L32" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -63971,7 +63971,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="P32" t="n">
         <v>2590</v>
@@ -64023,7 +64023,7 @@
         <v>325</v>
       </c>
       <c r="L33" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -64032,7 +64032,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="P33" t="n">
         <v>2630</v>
@@ -64084,7 +64084,7 @@
         <v>720</v>
       </c>
       <c r="L34" t="n">
-        <v>335</v>
+        <v>250</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -64093,7 +64093,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P34" t="n">
         <v>4360</v>
@@ -64206,7 +64206,7 @@
         <v>385</v>
       </c>
       <c r="L36" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -64215,7 +64215,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="P36" t="n">
         <v>2225</v>
@@ -64328,7 +64328,7 @@
         <v>250</v>
       </c>
       <c r="L38" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -64337,7 +64337,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="P38" t="n">
         <v>2295</v>
@@ -64572,7 +64572,7 @@
         <v>550</v>
       </c>
       <c r="L42" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -64581,7 +64581,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>275</v>
+        <v>450</v>
       </c>
       <c r="P42" t="n">
         <v>2492</v>
@@ -64755,7 +64755,7 @@
         <v>1410</v>
       </c>
       <c r="L45" t="n">
-        <v>425</v>
+        <v>250</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -64764,7 +64764,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="P45" t="n">
         <v>3217</v>
@@ -64877,7 +64877,7 @@
         <v>1050</v>
       </c>
       <c r="L47" t="n">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -64886,7 +64886,7 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P47" t="n">
         <v>3385</v>
@@ -65182,7 +65182,7 @@
         <v>1010</v>
       </c>
       <c r="L52" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -65191,7 +65191,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="P52" t="n">
         <v>3350</v>
@@ -65304,7 +65304,7 @@
         <v>935</v>
       </c>
       <c r="L54" t="n">
-        <v>645</v>
+        <v>600</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -65313,7 +65313,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P54" t="n">
         <v>3975</v>
@@ -65487,7 +65487,7 @@
         <v>60</v>
       </c>
       <c r="L57" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -65496,7 +65496,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="P57" t="n">
         <v>2925</v>
@@ -65792,16 +65792,16 @@
         <v>910</v>
       </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>40</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>2400</v>
@@ -65914,7 +65914,7 @@
         <v>75</v>
       </c>
       <c r="L64" t="n">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -65923,7 +65923,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="P64" t="n">
         <v>3335</v>
@@ -66097,7 +66097,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -66106,7 +66106,7 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P67" t="n">
         <v>2670</v>
@@ -66280,7 +66280,7 @@
         <v>550</v>
       </c>
       <c r="L70" t="n">
-        <v>595</v>
+        <v>475</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -66289,7 +66289,7 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="P70" t="n">
         <v>2985</v>
@@ -66402,7 +66402,7 @@
         <v>1015</v>
       </c>
       <c r="L72" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -66411,7 +66411,7 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P72" t="n">
         <v>2865</v>
@@ -66524,7 +66524,7 @@
         <v>525</v>
       </c>
       <c r="L74" t="n">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -66533,7 +66533,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P74" t="n">
         <v>1985</v>
@@ -66768,7 +66768,7 @@
         <v>600</v>
       </c>
       <c r="L78" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -66777,7 +66777,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="P78" t="n">
         <v>2225</v>
@@ -66951,7 +66951,7 @@
         <v>940</v>
       </c>
       <c r="L81" t="n">
-        <v>380</v>
+        <v>305</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -66960,7 +66960,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="P81" t="n">
         <v>3530</v>
@@ -67012,7 +67012,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -67021,7 +67021,7 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="P82" t="n">
         <v>3570</v>
@@ -67070,13 +67070,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>990</v>
+        <v>1070</v>
       </c>
       <c r="L83" t="n">
         <v>205</v>
       </c>
       <c r="M83" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -67131,13 +67131,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="L84" t="n">
         <v>155</v>
       </c>
       <c r="M84" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -67192,19 +67192,19 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>891</v>
+        <v>991</v>
       </c>
       <c r="L85" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="M85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>25</v>
       </c>
       <c r="O85" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="P85" t="n">
         <v>3740</v>
@@ -67314,13 +67314,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="L87" t="n">
         <v>260</v>
       </c>
       <c r="M87" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -67375,19 +67375,19 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L88" t="n">
-        <v>405</v>
+        <v>255</v>
       </c>
       <c r="M88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P88" t="n">
         <v>3779</v>
@@ -67436,13 +67436,13 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1920</v>
+        <v>2100</v>
       </c>
       <c r="L89" t="n">
         <v>210</v>
       </c>
       <c r="M89" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -67497,13 +67497,13 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L90" t="n">
         <v>205</v>
       </c>
       <c r="M90" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -67561,7 +67561,7 @@
         <v>1030</v>
       </c>
       <c r="L91" t="n">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -67570,7 +67570,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="P91" t="n">
         <v>3435</v>
@@ -67619,13 +67619,13 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>453</v>
+        <v>493</v>
       </c>
       <c r="L92" t="n">
         <v>415</v>
       </c>
       <c r="M92" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -67680,13 +67680,13 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1290</v>
+        <v>1360</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -67744,7 +67744,7 @@
         <v>1182</v>
       </c>
       <c r="L94" t="n">
-        <v>692</v>
+        <v>612</v>
       </c>
       <c r="M94" t="n">
         <v>385</v>
@@ -67753,7 +67753,7 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>755</v>
+        <v>835</v>
       </c>
       <c r="P94" t="n">
         <v>4228</v>
@@ -67802,13 +67802,13 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="L95" t="n">
         <v>367</v>
       </c>
       <c r="M95" t="n">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -67927,7 +67927,7 @@
         <v>778</v>
       </c>
       <c r="L97" t="n">
-        <v>394</v>
+        <v>319</v>
       </c>
       <c r="M97" t="n">
         <v>107</v>
@@ -67936,7 +67936,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>470</v>
+        <v>545</v>
       </c>
       <c r="P97" t="n">
         <v>2444</v>
@@ -67985,13 +67985,13 @@
         <v>85</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L98" t="n">
         <v>354</v>
       </c>
       <c r="M98" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -68107,13 +68107,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>925</v>
+        <v>975</v>
       </c>
       <c r="L100" t="n">
         <v>284</v>
       </c>
       <c r="M100" t="n">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -68171,7 +68171,7 @@
         <v>895</v>
       </c>
       <c r="L101" t="n">
-        <v>375</v>
+        <v>285</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -68180,7 +68180,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>298</v>
+        <v>388</v>
       </c>
       <c r="P101" t="n">
         <v>3979</v>
@@ -68229,13 +68229,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="n">
-        <v>675</v>
+        <v>745</v>
       </c>
       <c r="L102" t="n">
         <v>313</v>
       </c>
       <c r="M102" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -68290,19 +68290,19 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>1780</v>
+        <v>1847</v>
       </c>
       <c r="L103" t="n">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="M103" t="n">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="P103" t="n">
         <v>5056</v>
@@ -68473,13 +68473,13 @@
         <v>163</v>
       </c>
       <c r="K106" t="n">
-        <v>762</v>
+        <v>862</v>
       </c>
       <c r="L106" t="n">
         <v>378</v>
       </c>
       <c r="M106" t="n">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
@@ -68537,7 +68537,7 @@
         <v>550</v>
       </c>
       <c r="L107" t="n">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="M107" t="n">
         <v>143</v>
@@ -68546,7 +68546,7 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="P107" t="n">
         <v>4725</v>
@@ -68595,13 +68595,13 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>955</v>
+        <v>1015</v>
       </c>
       <c r="L108" t="n">
         <v>439</v>
       </c>
       <c r="M108" t="n">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
@@ -68778,13 +68778,13 @@
         <v>45</v>
       </c>
       <c r="K111" t="n">
-        <v>1936</v>
+        <v>2026</v>
       </c>
       <c r="L111" t="n">
         <v>414</v>
       </c>
       <c r="M111" t="n">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -69022,19 +69022,19 @@
         <v>90</v>
       </c>
       <c r="K115" t="n">
-        <v>940</v>
+        <v>1005</v>
       </c>
       <c r="L115" t="n">
-        <v>629</v>
+        <v>579</v>
       </c>
       <c r="M115" t="n">
-        <v>213</v>
+        <v>148</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="P115" t="n">
         <v>4548</v>
@@ -69144,13 +69144,13 @@
         <v>302</v>
       </c>
       <c r="K117" t="n">
-        <v>910</v>
+        <v>1050</v>
       </c>
       <c r="L117" t="n">
         <v>464</v>
       </c>
       <c r="M117" t="n">
-        <v>271</v>
+        <v>131</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -69208,7 +69208,7 @@
         <v>946</v>
       </c>
       <c r="L118" t="n">
-        <v>635</v>
+        <v>550</v>
       </c>
       <c r="M118" t="n">
         <v>141</v>
@@ -69217,7 +69217,7 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="P118" t="n">
         <v>5746</v>
@@ -69266,13 +69266,13 @@
         <v>100</v>
       </c>
       <c r="K119" t="n">
-        <v>1364</v>
+        <v>1449</v>
       </c>
       <c r="L119" t="n">
         <v>506</v>
       </c>
       <c r="M119" t="n">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -69388,19 +69388,19 @@
         <v>255</v>
       </c>
       <c r="K121" t="n">
-        <v>1518</v>
+        <v>1608</v>
       </c>
       <c r="L121" t="n">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="M121" t="n">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="P121" t="n">
         <v>4283</v>
@@ -69571,13 +69571,13 @@
         <v>144</v>
       </c>
       <c r="K124" t="n">
-        <v>2385</v>
+        <v>2475</v>
       </c>
       <c r="L124" t="n">
         <v>308</v>
       </c>
       <c r="M124" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -69635,7 +69635,7 @@
         <v>549</v>
       </c>
       <c r="L125" t="n">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="M125" t="n">
         <v>165</v>
@@ -69644,7 +69644,7 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P125" t="n">
         <v>4924</v>
@@ -69693,13 +69693,13 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>268</v>
+        <v>148</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
@@ -69815,19 +69815,19 @@
         <v>135</v>
       </c>
       <c r="K128" t="n">
-        <v>870</v>
+        <v>1005</v>
       </c>
       <c r="L128" t="n">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="M128" t="n">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P128" t="n">
         <v>4220</v>
@@ -69998,13 +69998,13 @@
         <v>409</v>
       </c>
       <c r="K131" t="n">
-        <v>1624</v>
+        <v>1779</v>
       </c>
       <c r="L131" t="n">
         <v>240</v>
       </c>
       <c r="M131" t="n">
-        <v>304</v>
+        <v>149</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -70120,13 +70120,13 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>1801</v>
+        <v>1921</v>
       </c>
       <c r="L133" t="n">
         <v>277</v>
       </c>
       <c r="M133" t="n">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -70242,13 +70242,13 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>1710</v>
+        <v>1795</v>
       </c>
       <c r="L135" t="n">
         <v>250</v>
       </c>
       <c r="M135" t="n">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -70364,19 +70364,19 @@
         <v>314</v>
       </c>
       <c r="K137" t="n">
-        <v>2965</v>
+        <v>3060</v>
       </c>
       <c r="L137" t="n">
-        <v>708</v>
+        <v>558</v>
       </c>
       <c r="M137" t="n">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="P137" t="n">
         <v>4790</v>
@@ -70529,7 +70529,7 @@
         <v>715</v>
       </c>
       <c r="E140" t="n">
-        <v>8275</v>
+        <v>9511</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
@@ -70544,16 +70544,16 @@
         <v>2635</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="K140" t="n">
-        <v>845</v>
+        <v>2355</v>
       </c>
       <c r="L140" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M140" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -70571,7 +70571,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>19983</v>
+        <v>23104</v>
       </c>
     </row>
     <row r="141">
@@ -70590,7 +70590,7 @@
         <v>62862</v>
       </c>
       <c r="E141" t="n">
-        <v>863088</v>
+        <v>864324</v>
       </c>
       <c r="F141" t="n">
         <v>5937</v>
@@ -70605,22 +70605,22 @@
         <v>286740</v>
       </c>
       <c r="J141" t="n">
-        <v>4937</v>
+        <v>5457</v>
       </c>
       <c r="K141" t="n">
-        <v>109897</v>
+        <v>113789</v>
       </c>
       <c r="L141" t="n">
-        <v>35630</v>
+        <v>32932</v>
       </c>
       <c r="M141" t="n">
-        <v>8316</v>
+        <v>5769</v>
       </c>
       <c r="N141" t="n">
         <v>42</v>
       </c>
       <c r="O141" t="n">
-        <v>22098</v>
+        <v>24816</v>
       </c>
       <c r="P141" t="n">
         <v>426258</v>
@@ -70632,7 +70632,7 @@
         <v>88610</v>
       </c>
       <c r="S141" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>
@@ -76150,7 +76150,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="114">
@@ -76160,7 +76160,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>58587</v>
+        <v>59172</v>
       </c>
     </row>
     <row r="116">
@@ -76268,7 +76268,7 @@
         <v>2026</v>
       </c>
       <c r="B128" t="n">
-        <v>4530</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="129">
@@ -76278,7 +76278,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>58587</v>
+        <v>59172</v>
       </c>
     </row>
   </sheetData>
@@ -77654,7 +77654,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>755</v>
+        <v>995</v>
       </c>
     </row>
     <row r="137">
@@ -77664,7 +77664,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
     </row>
     <row r="139">
@@ -77772,7 +77772,7 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>5545</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="152">
@@ -77782,7 +77782,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
     </row>
   </sheetData>
@@ -89204,13 +89204,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
       <c r="C140" t="n">
         <v>1810</v>
       </c>
       <c r="D140" t="n">
-        <v>425</v>
+        <v>1010</v>
       </c>
       <c r="E140" t="n">
         <v>315</v>
@@ -89225,7 +89225,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>7858</v>
+        <v>9879</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -89240,13 +89240,13 @@
         <v>795</v>
       </c>
       <c r="N140" t="n">
-        <v>755</v>
+        <v>995</v>
       </c>
       <c r="O140" t="n">
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>19983</v>
+        <v>23104</v>
       </c>
     </row>
     <row r="141">
@@ -89256,13 +89256,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400108</v>
+        <v>400383</v>
       </c>
       <c r="C141" t="n">
         <v>224962</v>
       </c>
       <c r="D141" t="n">
-        <v>58587</v>
+        <v>59172</v>
       </c>
       <c r="E141" t="n">
         <v>14604</v>
@@ -89277,7 +89277,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>756021</v>
+        <v>758042</v>
       </c>
       <c r="J141" t="n">
         <v>220401</v>
@@ -89292,13 +89292,13 @@
         <v>100763</v>
       </c>
       <c r="N141" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
       <c r="O141" t="n">
         <v>48837</v>
       </c>
       <c r="P141" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>
@@ -92258,7 +92258,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3435</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="141">
@@ -92268,7 +92268,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400108</v>
+        <v>400383</v>
       </c>
     </row>
     <row r="143">
@@ -92376,7 +92376,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>24797</v>
+        <v>25072</v>
       </c>
     </row>
     <row r="156">
@@ -92386,7 +92386,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>400108</v>
+        <v>400383</v>
       </c>
     </row>
   </sheetData>
@@ -97215,7 +97215,7 @@
         <v>825</v>
       </c>
       <c r="M13" t="n">
-        <v>262</v>
+        <v>422</v>
       </c>
       <c r="N13" t="n">
         <v>265</v>
@@ -97230,7 +97230,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>27242</v>
+        <v>27517</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97245,7 +97245,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>2370</v>
+        <v>2420</v>
       </c>
       <c r="X13" t="n">
         <v>830</v>
@@ -97290,13 +97290,13 @@
         <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>2191</v>
+        <v>2862</v>
       </c>
       <c r="AM13" t="n">
         <v>165</v>
       </c>
       <c r="AN13" t="n">
-        <v>650</v>
+        <v>1010</v>
       </c>
       <c r="AO13" t="n">
         <v>117</v>
@@ -97308,7 +97308,7 @@
         <v>35</v>
       </c>
       <c r="AR13" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AS13" t="n">
         <v>2140</v>
@@ -97329,7 +97329,7 @@
         <v>50</v>
       </c>
       <c r="AY13" t="n">
-        <v>2790</v>
+        <v>2870</v>
       </c>
       <c r="AZ13" t="n">
         <v>460</v>
@@ -97389,13 +97389,13 @@
         <v>1062</v>
       </c>
       <c r="BS13" t="n">
-        <v>3302</v>
+        <v>3832</v>
       </c>
       <c r="BT13" t="n">
         <v>595</v>
       </c>
       <c r="BU13" t="n">
-        <v>1035</v>
+        <v>1540</v>
       </c>
       <c r="BV13" t="n">
         <v>2727</v>
@@ -97521,7 +97521,7 @@
         <v>1825</v>
       </c>
       <c r="DK13" t="n">
-        <v>410</v>
+        <v>640</v>
       </c>
       <c r="DL13" t="n">
         <v>1903</v>
@@ -97542,7 +97542,7 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>5545</v>
+        <v>5785</v>
       </c>
       <c r="DS13" t="n">
         <v>275</v>
@@ -97551,7 +97551,7 @@
         <v>1730</v>
       </c>
       <c r="DU13" t="n">
-        <v>170992</v>
+        <v>174113</v>
       </c>
     </row>
     <row r="14">
@@ -97594,7 +97594,7 @@
         <v>5790</v>
       </c>
       <c r="M14" t="n">
-        <v>1582</v>
+        <v>1742</v>
       </c>
       <c r="N14" t="n">
         <v>2935</v>
@@ -97609,7 +97609,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>432768</v>
+        <v>433043</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -97624,7 +97624,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>24359</v>
+        <v>24409</v>
       </c>
       <c r="X14" t="n">
         <v>4820</v>
@@ -97669,13 +97669,13 @@
         <v>427</v>
       </c>
       <c r="AL14" t="n">
-        <v>50732</v>
+        <v>51403</v>
       </c>
       <c r="AM14" t="n">
         <v>4755</v>
       </c>
       <c r="AN14" t="n">
-        <v>3355</v>
+        <v>3715</v>
       </c>
       <c r="AO14" t="n">
         <v>282</v>
@@ -97687,7 +97687,7 @@
         <v>385</v>
       </c>
       <c r="AR14" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AS14" t="n">
         <v>26879</v>
@@ -97708,7 +97708,7 @@
         <v>460</v>
       </c>
       <c r="AY14" t="n">
-        <v>41222</v>
+        <v>41302</v>
       </c>
       <c r="AZ14" t="n">
         <v>6666</v>
@@ -97768,13 +97768,13 @@
         <v>13430</v>
       </c>
       <c r="BS14" t="n">
-        <v>26996</v>
+        <v>27526</v>
       </c>
       <c r="BT14" t="n">
         <v>5420</v>
       </c>
       <c r="BU14" t="n">
-        <v>5785</v>
+        <v>6290</v>
       </c>
       <c r="BV14" t="n">
         <v>34940</v>
@@ -97900,7 +97900,7 @@
         <v>15330</v>
       </c>
       <c r="DK14" t="n">
-        <v>10550</v>
+        <v>10780</v>
       </c>
       <c r="DL14" t="n">
         <v>18216</v>
@@ -97921,7 +97921,7 @@
         <v>1450</v>
       </c>
       <c r="DR14" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
       <c r="DS14" t="n">
         <v>4927</v>
@@ -97930,7 +97930,7 @@
         <v>27596</v>
       </c>
       <c r="DU14" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>
@@ -98197,7 +98197,7 @@
         <v>7433</v>
       </c>
       <c r="L4" t="n">
-        <v>3070</v>
+        <v>2795</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -98206,7 +98206,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2065</v>
+        <v>2340</v>
       </c>
       <c r="P4" t="n">
         <v>30220</v>
@@ -98256,7 +98256,7 @@
         <v>7945</v>
       </c>
       <c r="L5" t="n">
-        <v>2808</v>
+        <v>2370</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -98265,7 +98265,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1915</v>
+        <v>2353</v>
       </c>
       <c r="P5" t="n">
         <v>38427</v>
@@ -98315,7 +98315,7 @@
         <v>11175</v>
       </c>
       <c r="L6" t="n">
-        <v>4190</v>
+        <v>3895</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -98324,7 +98324,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2115</v>
+        <v>2410</v>
       </c>
       <c r="P6" t="n">
         <v>39099</v>
@@ -98374,7 +98374,7 @@
         <v>6445</v>
       </c>
       <c r="L7" t="n">
-        <v>3210</v>
+        <v>2855</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -98383,7 +98383,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1455</v>
+        <v>1810</v>
       </c>
       <c r="P7" t="n">
         <v>29040</v>
@@ -98430,19 +98430,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7266</v>
+        <v>7521</v>
       </c>
       <c r="L8" t="n">
-        <v>3015</v>
+        <v>2640</v>
       </c>
       <c r="M8" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>25</v>
       </c>
       <c r="O8" t="n">
-        <v>1090</v>
+        <v>1465</v>
       </c>
       <c r="P8" t="n">
         <v>35067</v>
@@ -98489,19 +98489,19 @@
         <v>94</v>
       </c>
       <c r="K9" t="n">
-        <v>9985</v>
+        <v>10425</v>
       </c>
       <c r="L9" t="n">
-        <v>3855</v>
+        <v>3500</v>
       </c>
       <c r="M9" t="n">
-        <v>1058</v>
+        <v>618</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3273</v>
+        <v>3628</v>
       </c>
       <c r="P9" t="n">
         <v>40877</v>
@@ -98548,19 +98548,19 @@
         <v>498</v>
       </c>
       <c r="K10" t="n">
-        <v>11600</v>
+        <v>12017</v>
       </c>
       <c r="L10" t="n">
-        <v>3155</v>
+        <v>2980</v>
       </c>
       <c r="M10" t="n">
-        <v>1456</v>
+        <v>1039</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4696</v>
+        <v>4871</v>
       </c>
       <c r="P10" t="n">
         <v>42349</v>
@@ -98607,19 +98607,19 @@
         <v>1970</v>
       </c>
       <c r="K11" t="n">
-        <v>13417</v>
+        <v>13887</v>
       </c>
       <c r="L11" t="n">
-        <v>5149</v>
+        <v>4974</v>
       </c>
       <c r="M11" t="n">
-        <v>1899</v>
+        <v>1429</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2690</v>
+        <v>2865</v>
       </c>
       <c r="P11" t="n">
         <v>50500</v>
@@ -98666,19 +98666,19 @@
         <v>1463</v>
       </c>
       <c r="K12" t="n">
-        <v>16393</v>
+        <v>17013</v>
       </c>
       <c r="L12" t="n">
-        <v>3284</v>
+        <v>3159</v>
       </c>
       <c r="M12" t="n">
-        <v>2447</v>
+        <v>1827</v>
       </c>
       <c r="N12" t="n">
         <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>927</v>
+        <v>1052</v>
       </c>
       <c r="P12" t="n">
         <v>54184</v>
@@ -98707,7 +98707,7 @@
         <v>5550</v>
       </c>
       <c r="E13" t="n">
-        <v>71448</v>
+        <v>72684</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -98722,22 +98722,22 @@
         <v>21854</v>
       </c>
       <c r="J13" t="n">
-        <v>912</v>
+        <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>9606</v>
+        <v>11296</v>
       </c>
       <c r="L13" t="n">
-        <v>2424</v>
+        <v>2294</v>
       </c>
       <c r="M13" t="n">
-        <v>1201</v>
+        <v>856</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>260</v>
+        <v>410</v>
       </c>
       <c r="P13" t="n">
         <v>31809</v>
@@ -98749,7 +98749,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>170992</v>
+        <v>174113</v>
       </c>
     </row>
     <row r="14">
@@ -98768,7 +98768,7 @@
         <v>62862</v>
       </c>
       <c r="E14" t="n">
-        <v>863088</v>
+        <v>864324</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -98783,22 +98783,22 @@
         <v>286740</v>
       </c>
       <c r="J14" t="n">
-        <v>4937</v>
+        <v>5457</v>
       </c>
       <c r="K14" t="n">
-        <v>109897</v>
+        <v>113789</v>
       </c>
       <c r="L14" t="n">
-        <v>35630</v>
+        <v>32932</v>
       </c>
       <c r="M14" t="n">
-        <v>8316</v>
+        <v>5769</v>
       </c>
       <c r="N14" t="n">
         <v>42</v>
       </c>
       <c r="O14" t="n">
-        <v>22098</v>
+        <v>24816</v>
       </c>
       <c r="P14" t="n">
         <v>426258</v>
@@ -98810,7 +98810,7 @@
         <v>88610</v>
       </c>
       <c r="S14" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>
@@ -99464,13 +99464,13 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>24797</v>
+        <v>25072</v>
       </c>
       <c r="C13" t="n">
         <v>15989</v>
       </c>
       <c r="D13" t="n">
-        <v>4530</v>
+        <v>5115</v>
       </c>
       <c r="E13" t="n">
         <v>1955</v>
@@ -99485,7 +99485,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>73220</v>
+        <v>75241</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -99500,13 +99500,13 @@
         <v>6260</v>
       </c>
       <c r="N13" t="n">
-        <v>5545</v>
+        <v>5785</v>
       </c>
       <c r="O13" t="n">
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>170992</v>
+        <v>174113</v>
       </c>
     </row>
     <row r="14">
@@ -99516,13 +99516,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>400108</v>
+        <v>400383</v>
       </c>
       <c r="C14" t="n">
         <v>224962</v>
       </c>
       <c r="D14" t="n">
-        <v>58587</v>
+        <v>59172</v>
       </c>
       <c r="E14" t="n">
         <v>14604</v>
@@ -99537,7 +99537,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>756021</v>
+        <v>758042</v>
       </c>
       <c r="J14" t="n">
         <v>220401</v>
@@ -99552,13 +99552,13 @@
         <v>100763</v>
       </c>
       <c r="N14" t="n">
-        <v>71327</v>
+        <v>71567</v>
       </c>
       <c r="O14" t="n">
         <v>48837</v>
       </c>
       <c r="P14" t="n">
-        <v>2089759</v>
+        <v>2092880</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54352,13 +54352,13 @@
         <v>20</v>
       </c>
       <c r="AT140" t="n">
-        <v>275</v>
+        <v>385</v>
       </c>
       <c r="AU140" t="n">
         <v>130</v>
       </c>
       <c r="AV140" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AW140" t="n">
         <v>0</v>
@@ -54406,7 +54406,7 @@
         <v>0</v>
       </c>
       <c r="BL140" t="n">
-        <v>410</v>
+        <v>775</v>
       </c>
       <c r="BM140" t="n">
         <v>0</v>
@@ -54595,7 +54595,7 @@
         <v>70</v>
       </c>
       <c r="DW140" t="n">
-        <v>23110</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="141">
@@ -54737,13 +54737,13 @@
         <v>282</v>
       </c>
       <c r="AT141" t="n">
-        <v>26879</v>
+        <v>26989</v>
       </c>
       <c r="AU141" t="n">
         <v>567</v>
       </c>
       <c r="AV141" t="n">
-        <v>2707</v>
+        <v>2722</v>
       </c>
       <c r="AW141" t="n">
         <v>6939</v>
@@ -54791,7 +54791,7 @@
         <v>660</v>
       </c>
       <c r="BL141" t="n">
-        <v>47755</v>
+        <v>48120</v>
       </c>
       <c r="BM141" t="n">
         <v>1992</v>
@@ -54980,7 +54980,7 @@
         <v>27598</v>
       </c>
       <c r="DW141" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>
@@ -61208,7 +61208,7 @@
         <v>965</v>
       </c>
       <c r="E8" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
       <c r="F8" t="n">
         <v>1010</v>
@@ -61238,7 +61238,7 @@
         <v>3710</v>
       </c>
       <c r="O8" t="n">
-        <v>13227</v>
+        <v>13592</v>
       </c>
     </row>
     <row r="9">
@@ -61257,7 +61257,7 @@
         <v>5965</v>
       </c>
       <c r="E9" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
       <c r="F9" t="n">
         <v>5117</v>
@@ -61287,7 +61287,7 @@
         <v>25082</v>
       </c>
       <c r="O9" t="n">
-        <v>98890</v>
+        <v>99255</v>
       </c>
     </row>
   </sheetData>
@@ -71370,16 +71370,16 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1050</v>
+        <v>1415</v>
       </c>
       <c r="C140" t="n">
         <v>475</v>
       </c>
       <c r="D140" t="n">
-        <v>717</v>
+        <v>827</v>
       </c>
       <c r="E140" t="n">
-        <v>9513</v>
+        <v>9528</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
@@ -71421,7 +71421,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>23110</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="141">
@@ -71431,16 +71431,16 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>78768</v>
+        <v>79133</v>
       </c>
       <c r="C141" t="n">
         <v>17806</v>
       </c>
       <c r="D141" t="n">
-        <v>62880</v>
+        <v>62990</v>
       </c>
       <c r="E141" t="n">
-        <v>864430</v>
+        <v>864445</v>
       </c>
       <c r="F141" t="n">
         <v>5939</v>
@@ -71482,7 +71482,7 @@
         <v>88618</v>
       </c>
       <c r="S141" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>
@@ -75726,7 +75726,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="127">
@@ -75736,7 +75736,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>68840</v>
+        <v>69205</v>
       </c>
     </row>
     <row r="129">
@@ -75844,7 +75844,7 @@
         <v>2026</v>
       </c>
       <c r="B141" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
     </row>
     <row r="142">
@@ -75854,7 +75854,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>68840</v>
+        <v>69205</v>
       </c>
     </row>
   </sheetData>
@@ -90076,7 +90076,7 @@
         <v>315</v>
       </c>
       <c r="F140" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>9883</v>
+        <v>10008</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -90106,7 +90106,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>23110</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="141">
@@ -90128,7 +90128,7 @@
         <v>14606</v>
       </c>
       <c r="F141" t="n">
-        <v>68840</v>
+        <v>69205</v>
       </c>
       <c r="G141" t="n">
         <v>23492</v>
@@ -90137,7 +90137,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>758194</v>
+        <v>758319</v>
       </c>
       <c r="J141" t="n">
         <v>220403</v>
@@ -90158,7 +90158,7 @@
         <v>48839</v>
       </c>
       <c r="P141" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>
@@ -98250,13 +98250,13 @@
         <v>282</v>
       </c>
       <c r="AT13" t="n">
-        <v>2140</v>
+        <v>2250</v>
       </c>
       <c r="AU13" t="n">
         <v>567</v>
       </c>
       <c r="AV13" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="AW13" t="n">
         <v>440</v>
@@ -98304,7 +98304,7 @@
         <v>40</v>
       </c>
       <c r="BL13" t="n">
-        <v>2951</v>
+        <v>3316</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
@@ -98493,7 +98493,7 @@
         <v>1730</v>
       </c>
       <c r="DW13" t="n">
-        <v>174161</v>
+        <v>174651</v>
       </c>
     </row>
     <row r="14">
@@ -98635,13 +98635,13 @@
         <v>282</v>
       </c>
       <c r="AT14" t="n">
-        <v>26879</v>
+        <v>26989</v>
       </c>
       <c r="AU14" t="n">
         <v>567</v>
       </c>
       <c r="AV14" t="n">
-        <v>2707</v>
+        <v>2722</v>
       </c>
       <c r="AW14" t="n">
         <v>6939</v>
@@ -98689,7 +98689,7 @@
         <v>660</v>
       </c>
       <c r="BL14" t="n">
-        <v>47755</v>
+        <v>48120</v>
       </c>
       <c r="BM14" t="n">
         <v>1992</v>
@@ -98878,7 +98878,7 @@
         <v>27598</v>
       </c>
       <c r="DW14" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>
@@ -99646,16 +99646,16 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>5713</v>
+        <v>6078</v>
       </c>
       <c r="C13" t="n">
         <v>2550</v>
       </c>
       <c r="D13" t="n">
-        <v>5552</v>
+        <v>5662</v>
       </c>
       <c r="E13" t="n">
-        <v>72708</v>
+        <v>72723</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99697,7 +99697,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>174161</v>
+        <v>174651</v>
       </c>
     </row>
     <row r="14">
@@ -99707,16 +99707,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78768</v>
+        <v>79133</v>
       </c>
       <c r="C14" t="n">
         <v>17806</v>
       </c>
       <c r="D14" t="n">
-        <v>62880</v>
+        <v>62990</v>
       </c>
       <c r="E14" t="n">
-        <v>864430</v>
+        <v>864445</v>
       </c>
       <c r="F14" t="n">
         <v>5939</v>
@@ -99758,7 +99758,7 @@
         <v>88618</v>
       </c>
       <c r="S14" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>
@@ -100424,7 +100424,7 @@
         <v>1955</v>
       </c>
       <c r="F13" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
       <c r="G13" t="n">
         <v>2880</v>
@@ -100433,7 +100433,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>75271</v>
+        <v>75396</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -100454,7 +100454,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>174161</v>
+        <v>174651</v>
       </c>
     </row>
     <row r="14">
@@ -100476,7 +100476,7 @@
         <v>14606</v>
       </c>
       <c r="F14" t="n">
-        <v>68840</v>
+        <v>69205</v>
       </c>
       <c r="G14" t="n">
         <v>23492</v>
@@ -100485,7 +100485,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>758194</v>
+        <v>758319</v>
       </c>
       <c r="J14" t="n">
         <v>220403</v>
@@ -100506,7 +100506,7 @@
         <v>48839</v>
       </c>
       <c r="P14" t="n">
-        <v>2093174</v>
+        <v>2093664</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53430,7 +53430,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3710</v>
+        <v>4021</v>
       </c>
       <c r="S140" t="n">
         <v>50</v>
@@ -53445,7 +53445,7 @@
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>460</v>
+        <v>610</v>
       </c>
       <c r="X140" t="n">
         <v>110</v>
@@ -53511,13 +53511,13 @@
         <v>20</v>
       </c>
       <c r="AS140" t="n">
-        <v>275</v>
+        <v>385</v>
       </c>
       <c r="AT140" t="n">
         <v>130</v>
       </c>
       <c r="AU140" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AV140" t="n">
         <v>0</v>
@@ -53565,13 +53565,13 @@
         <v>0</v>
       </c>
       <c r="BK140" t="n">
-        <v>410</v>
+        <v>775</v>
       </c>
       <c r="BL140" t="n">
         <v>0</v>
       </c>
       <c r="BM140" t="n">
-        <v>1600</v>
+        <v>1879</v>
       </c>
       <c r="BN140" t="n">
         <v>40</v>
@@ -53664,10 +53664,10 @@
         <v>210</v>
       </c>
       <c r="CR140" t="n">
-        <v>505</v>
+        <v>855</v>
       </c>
       <c r="CS140" t="n">
-        <v>195</v>
+        <v>335</v>
       </c>
       <c r="CT140" t="n">
         <v>0</v>
@@ -53751,7 +53751,7 @@
         <v>70</v>
       </c>
       <c r="DU140" t="n">
-        <v>23104</v>
+        <v>24824</v>
       </c>
     </row>
     <row r="141">
@@ -53809,7 +53809,7 @@
         <v>105</v>
       </c>
       <c r="R141" t="n">
-        <v>433043</v>
+        <v>433354</v>
       </c>
       <c r="S141" t="n">
         <v>975</v>
@@ -53824,7 +53824,7 @@
         <v>14436</v>
       </c>
       <c r="W141" t="n">
-        <v>24409</v>
+        <v>24559</v>
       </c>
       <c r="X141" t="n">
         <v>4820</v>
@@ -53890,13 +53890,13 @@
         <v>280</v>
       </c>
       <c r="AS141" t="n">
-        <v>26879</v>
+        <v>26989</v>
       </c>
       <c r="AT141" t="n">
         <v>565</v>
       </c>
       <c r="AU141" t="n">
-        <v>2705</v>
+        <v>2720</v>
       </c>
       <c r="AV141" t="n">
         <v>6939</v>
@@ -53944,13 +53944,13 @@
         <v>660</v>
       </c>
       <c r="BK141" t="n">
-        <v>47751</v>
+        <v>48116</v>
       </c>
       <c r="BL141" t="n">
         <v>1992</v>
       </c>
       <c r="BM141" t="n">
-        <v>114131</v>
+        <v>114410</v>
       </c>
       <c r="BN141" t="n">
         <v>4120</v>
@@ -54043,10 +54043,10 @@
         <v>12112</v>
       </c>
       <c r="CR141" t="n">
-        <v>65646</v>
+        <v>65996</v>
       </c>
       <c r="CS141" t="n">
-        <v>2575</v>
+        <v>2715</v>
       </c>
       <c r="CT141" t="n">
         <v>1310</v>
@@ -54130,7 +54130,7 @@
         <v>27596</v>
       </c>
       <c r="DU141" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>
@@ -60358,7 +60358,7 @@
         <v>965</v>
       </c>
       <c r="E8" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
       <c r="F8" t="n">
         <v>1010</v>
@@ -60385,10 +60385,10 @@
         <v>1810</v>
       </c>
       <c r="N8" t="n">
-        <v>3710</v>
+        <v>4021</v>
       </c>
       <c r="O8" t="n">
-        <v>13225</v>
+        <v>13901</v>
       </c>
     </row>
     <row r="9">
@@ -60407,7 +60407,7 @@
         <v>5965</v>
       </c>
       <c r="E9" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
       <c r="F9" t="n">
         <v>5115</v>
@@ -60434,10 +60434,10 @@
         <v>15989</v>
       </c>
       <c r="N9" t="n">
-        <v>25072</v>
+        <v>25383</v>
       </c>
       <c r="O9" t="n">
-        <v>98872</v>
+        <v>99548</v>
       </c>
     </row>
   </sheetData>
@@ -70520,16 +70520,16 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1050</v>
+        <v>1415</v>
       </c>
       <c r="C140" t="n">
         <v>475</v>
       </c>
       <c r="D140" t="n">
-        <v>715</v>
+        <v>825</v>
       </c>
       <c r="E140" t="n">
-        <v>9511</v>
+        <v>10616</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
@@ -70538,7 +70538,7 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>500</v>
+        <v>640</v>
       </c>
       <c r="I140" t="n">
         <v>2635</v>
@@ -70571,7 +70571,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>23104</v>
+        <v>24824</v>
       </c>
     </row>
     <row r="141">
@@ -70581,16 +70581,16 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>78752</v>
+        <v>79117</v>
       </c>
       <c r="C141" t="n">
         <v>17804</v>
       </c>
       <c r="D141" t="n">
-        <v>62862</v>
+        <v>62972</v>
       </c>
       <c r="E141" t="n">
-        <v>864324</v>
+        <v>865429</v>
       </c>
       <c r="F141" t="n">
         <v>5937</v>
@@ -70599,7 +70599,7 @@
         <v>34009</v>
       </c>
       <c r="H141" t="n">
-        <v>7995</v>
+        <v>8135</v>
       </c>
       <c r="I141" t="n">
         <v>286740</v>
@@ -70632,7 +70632,7 @@
         <v>88610</v>
       </c>
       <c r="S141" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="127">
@@ -74886,7 +74886,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>68832</v>
+        <v>69197</v>
       </c>
     </row>
     <row r="129">
@@ -74994,7 +74994,7 @@
         <v>2026</v>
       </c>
       <c r="B141" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
     </row>
     <row r="142">
@@ -75004,7 +75004,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>68832</v>
+        <v>69197</v>
       </c>
     </row>
   </sheetData>
@@ -89204,7 +89204,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3710</v>
+        <v>4021</v>
       </c>
       <c r="C140" t="n">
         <v>1810</v>
@@ -89216,7 +89216,7 @@
         <v>315</v>
       </c>
       <c r="F140" t="n">
-        <v>915</v>
+        <v>1280</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -89225,7 +89225,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>9879</v>
+        <v>10923</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -89246,7 +89246,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>23104</v>
+        <v>24824</v>
       </c>
     </row>
     <row r="141">
@@ -89256,7 +89256,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400383</v>
+        <v>400694</v>
       </c>
       <c r="C141" t="n">
         <v>224962</v>
@@ -89268,7 +89268,7 @@
         <v>14604</v>
       </c>
       <c r="F141" t="n">
-        <v>68832</v>
+        <v>69197</v>
       </c>
       <c r="G141" t="n">
         <v>23490</v>
@@ -89277,7 +89277,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>758042</v>
+        <v>759086</v>
       </c>
       <c r="J141" t="n">
         <v>220401</v>
@@ -89298,7 +89298,7 @@
         <v>48837</v>
       </c>
       <c r="P141" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>
@@ -92258,7 +92258,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3710</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="141">
@@ -92268,7 +92268,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400383</v>
+        <v>400694</v>
       </c>
     </row>
     <row r="143">
@@ -92376,7 +92376,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>25072</v>
+        <v>25383</v>
       </c>
     </row>
     <row r="156">
@@ -92386,7 +92386,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>400383</v>
+        <v>400694</v>
       </c>
     </row>
   </sheetData>
@@ -97230,7 +97230,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>27517</v>
+        <v>27828</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97245,7 +97245,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>2420</v>
+        <v>2570</v>
       </c>
       <c r="X13" t="n">
         <v>830</v>
@@ -97311,13 +97311,13 @@
         <v>280</v>
       </c>
       <c r="AS13" t="n">
-        <v>2140</v>
+        <v>2250</v>
       </c>
       <c r="AT13" t="n">
         <v>565</v>
       </c>
       <c r="AU13" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="AV13" t="n">
         <v>440</v>
@@ -97365,13 +97365,13 @@
         <v>40</v>
       </c>
       <c r="BK13" t="n">
-        <v>2951</v>
+        <v>3316</v>
       </c>
       <c r="BL13" t="n">
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>20530</v>
+        <v>20809</v>
       </c>
       <c r="BN13" t="n">
         <v>275</v>
@@ -97464,10 +97464,10 @@
         <v>710</v>
       </c>
       <c r="CR13" t="n">
-        <v>4926</v>
+        <v>5276</v>
       </c>
       <c r="CS13" t="n">
-        <v>1120</v>
+        <v>1260</v>
       </c>
       <c r="CT13" t="n">
         <v>125</v>
@@ -97551,7 +97551,7 @@
         <v>1730</v>
       </c>
       <c r="DU13" t="n">
-        <v>174113</v>
+        <v>175833</v>
       </c>
     </row>
     <row r="14">
@@ -97609,7 +97609,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>433043</v>
+        <v>433354</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -97624,7 +97624,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>24409</v>
+        <v>24559</v>
       </c>
       <c r="X14" t="n">
         <v>4820</v>
@@ -97690,13 +97690,13 @@
         <v>280</v>
       </c>
       <c r="AS14" t="n">
-        <v>26879</v>
+        <v>26989</v>
       </c>
       <c r="AT14" t="n">
         <v>565</v>
       </c>
       <c r="AU14" t="n">
-        <v>2705</v>
+        <v>2720</v>
       </c>
       <c r="AV14" t="n">
         <v>6939</v>
@@ -97744,13 +97744,13 @@
         <v>660</v>
       </c>
       <c r="BK14" t="n">
-        <v>47751</v>
+        <v>48116</v>
       </c>
       <c r="BL14" t="n">
         <v>1992</v>
       </c>
       <c r="BM14" t="n">
-        <v>114131</v>
+        <v>114410</v>
       </c>
       <c r="BN14" t="n">
         <v>4120</v>
@@ -97843,10 +97843,10 @@
         <v>12112</v>
       </c>
       <c r="CR14" t="n">
-        <v>65646</v>
+        <v>65996</v>
       </c>
       <c r="CS14" t="n">
-        <v>2575</v>
+        <v>2715</v>
       </c>
       <c r="CT14" t="n">
         <v>1310</v>
@@ -97930,7 +97930,7 @@
         <v>27596</v>
       </c>
       <c r="DU14" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>
@@ -98698,16 +98698,16 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>5711</v>
+        <v>6076</v>
       </c>
       <c r="C13" t="n">
         <v>2550</v>
       </c>
       <c r="D13" t="n">
-        <v>5550</v>
+        <v>5660</v>
       </c>
       <c r="E13" t="n">
-        <v>72684</v>
+        <v>73789</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -98716,7 +98716,7 @@
         <v>2823</v>
       </c>
       <c r="H13" t="n">
-        <v>1715</v>
+        <v>1855</v>
       </c>
       <c r="I13" t="n">
         <v>21854</v>
@@ -98749,7 +98749,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>174113</v>
+        <v>175833</v>
       </c>
     </row>
     <row r="14">
@@ -98759,16 +98759,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78752</v>
+        <v>79117</v>
       </c>
       <c r="C14" t="n">
         <v>17804</v>
       </c>
       <c r="D14" t="n">
-        <v>62862</v>
+        <v>62972</v>
       </c>
       <c r="E14" t="n">
-        <v>864324</v>
+        <v>865429</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -98777,7 +98777,7 @@
         <v>34009</v>
       </c>
       <c r="H14" t="n">
-        <v>7995</v>
+        <v>8135</v>
       </c>
       <c r="I14" t="n">
         <v>286740</v>
@@ -98810,7 +98810,7 @@
         <v>88610</v>
       </c>
       <c r="S14" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>
@@ -99464,7 +99464,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>25072</v>
+        <v>25383</v>
       </c>
       <c r="C13" t="n">
         <v>15989</v>
@@ -99476,7 +99476,7 @@
         <v>1955</v>
       </c>
       <c r="F13" t="n">
-        <v>4521</v>
+        <v>4886</v>
       </c>
       <c r="G13" t="n">
         <v>2880</v>
@@ -99485,7 +99485,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>75241</v>
+        <v>76285</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -99506,7 +99506,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>174113</v>
+        <v>175833</v>
       </c>
     </row>
     <row r="14">
@@ -99516,7 +99516,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>400383</v>
+        <v>400694</v>
       </c>
       <c r="C14" t="n">
         <v>224962</v>
@@ -99528,7 +99528,7 @@
         <v>14604</v>
       </c>
       <c r="F14" t="n">
-        <v>68832</v>
+        <v>69197</v>
       </c>
       <c r="G14" t="n">
         <v>23490</v>
@@ -99537,7 +99537,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>758042</v>
+        <v>759086</v>
       </c>
       <c r="J14" t="n">
         <v>220401</v>
@@ -99558,7 +99558,7 @@
         <v>48837</v>
       </c>
       <c r="P14" t="n">
-        <v>2092880</v>
+        <v>2094600</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53430,7 +53430,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>4021</v>
+        <v>5651</v>
       </c>
       <c r="S140" t="n">
         <v>50</v>
@@ -53751,7 +53751,7 @@
         <v>70</v>
       </c>
       <c r="DU140" t="n">
-        <v>24824</v>
+        <v>26454</v>
       </c>
     </row>
     <row r="141">
@@ -53809,7 +53809,7 @@
         <v>105</v>
       </c>
       <c r="R141" t="n">
-        <v>433354</v>
+        <v>434984</v>
       </c>
       <c r="S141" t="n">
         <v>975</v>
@@ -54130,7 +54130,7 @@
         <v>27596</v>
       </c>
       <c r="DU141" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>
@@ -60385,10 +60385,10 @@
         <v>1810</v>
       </c>
       <c r="N8" t="n">
-        <v>4021</v>
+        <v>5651</v>
       </c>
       <c r="O8" t="n">
-        <v>13901</v>
+        <v>15531</v>
       </c>
     </row>
     <row r="9">
@@ -60434,10 +60434,10 @@
         <v>15989</v>
       </c>
       <c r="N9" t="n">
-        <v>25383</v>
+        <v>27013</v>
       </c>
       <c r="O9" t="n">
-        <v>99548</v>
+        <v>101178</v>
       </c>
     </row>
   </sheetData>
@@ -70529,7 +70529,7 @@
         <v>825</v>
       </c>
       <c r="E140" t="n">
-        <v>10616</v>
+        <v>12246</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
@@ -70571,7 +70571,7 @@
         <v>430</v>
       </c>
       <c r="S140" t="n">
-        <v>24824</v>
+        <v>26454</v>
       </c>
     </row>
     <row r="141">
@@ -70590,7 +70590,7 @@
         <v>62972</v>
       </c>
       <c r="E141" t="n">
-        <v>865429</v>
+        <v>867059</v>
       </c>
       <c r="F141" t="n">
         <v>5937</v>
@@ -70632,7 +70632,7 @@
         <v>88610</v>
       </c>
       <c r="S141" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>
@@ -89204,7 +89204,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4021</v>
+        <v>5651</v>
       </c>
       <c r="C140" t="n">
         <v>1810</v>
@@ -89246,7 +89246,7 @@
         <v>220</v>
       </c>
       <c r="P140" t="n">
-        <v>24824</v>
+        <v>26454</v>
       </c>
     </row>
     <row r="141">
@@ -89256,7 +89256,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400694</v>
+        <v>402324</v>
       </c>
       <c r="C141" t="n">
         <v>224962</v>
@@ -89298,7 +89298,7 @@
         <v>48837</v>
       </c>
       <c r="P141" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>
@@ -92258,7 +92258,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>4021</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="141">
@@ -92268,7 +92268,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>400694</v>
+        <v>402324</v>
       </c>
     </row>
     <row r="143">
@@ -92376,7 +92376,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>25383</v>
+        <v>27013</v>
       </c>
     </row>
     <row r="156">
@@ -92386,7 +92386,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>400694</v>
+        <v>402324</v>
       </c>
     </row>
   </sheetData>
@@ -97230,7 +97230,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>27828</v>
+        <v>29458</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97551,7 +97551,7 @@
         <v>1730</v>
       </c>
       <c r="DU13" t="n">
-        <v>175833</v>
+        <v>177463</v>
       </c>
     </row>
     <row r="14">
@@ -97609,7 +97609,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>433354</v>
+        <v>434984</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -97930,7 +97930,7 @@
         <v>27596</v>
       </c>
       <c r="DU14" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>
@@ -98707,7 +98707,7 @@
         <v>5660</v>
       </c>
       <c r="E13" t="n">
-        <v>73789</v>
+        <v>75419</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -98749,7 +98749,7 @@
         <v>9277</v>
       </c>
       <c r="S13" t="n">
-        <v>175833</v>
+        <v>177463</v>
       </c>
     </row>
     <row r="14">
@@ -98768,7 +98768,7 @@
         <v>62972</v>
       </c>
       <c r="E14" t="n">
-        <v>865429</v>
+        <v>867059</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -98810,7 +98810,7 @@
         <v>88610</v>
       </c>
       <c r="S14" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>
@@ -99464,7 +99464,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>25383</v>
+        <v>27013</v>
       </c>
       <c r="C13" t="n">
         <v>15989</v>
@@ -99506,7 +99506,7 @@
         <v>3865</v>
       </c>
       <c r="P13" t="n">
-        <v>175833</v>
+        <v>177463</v>
       </c>
     </row>
     <row r="14">
@@ -99516,7 +99516,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>400694</v>
+        <v>402324</v>
       </c>
       <c r="C14" t="n">
         <v>224962</v>
@@ -99558,7 +99558,7 @@
         <v>48837</v>
       </c>
       <c r="P14" t="n">
-        <v>2094600</v>
+        <v>2096230</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53391,7 +53391,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>595</v>
+        <v>695</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -53409,7 +53409,7 @@
         <v>80</v>
       </c>
       <c r="K140" t="n">
-        <v>170</v>
+        <v>385</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -53418,7 +53418,7 @@
         <v>160</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -53628,13 +53628,13 @@
         <v>0</v>
       </c>
       <c r="CF140" t="n">
-        <v>150</v>
+        <v>555</v>
       </c>
       <c r="CG140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CH140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CI140" t="n">
         <v>0</v>
@@ -53724,7 +53724,7 @@
         <v>230</v>
       </c>
       <c r="DL140" t="n">
-        <v>251</v>
+        <v>450</v>
       </c>
       <c r="DM140" t="n">
         <v>0</v>
@@ -53748,10 +53748,10 @@
         <v>0</v>
       </c>
       <c r="DT140" t="n">
-        <v>70</v>
+        <v>355</v>
       </c>
       <c r="DU140" t="n">
-        <v>26454</v>
+        <v>27798</v>
       </c>
     </row>
     <row r="141">
@@ -53770,7 +53770,7 @@
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>72048</v>
+        <v>72148</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -53788,7 +53788,7 @@
         <v>22373</v>
       </c>
       <c r="K141" t="n">
-        <v>17090</v>
+        <v>17305</v>
       </c>
       <c r="L141" t="n">
         <v>5790</v>
@@ -53797,7 +53797,7 @@
         <v>1742</v>
       </c>
       <c r="N141" t="n">
-        <v>2935</v>
+        <v>3005</v>
       </c>
       <c r="O141" t="n">
         <v>5784</v>
@@ -54007,13 +54007,13 @@
         <v>145</v>
       </c>
       <c r="CF141" t="n">
-        <v>21241</v>
+        <v>21646</v>
       </c>
       <c r="CG141" t="n">
-        <v>3642</v>
+        <v>3692</v>
       </c>
       <c r="CH141" t="n">
-        <v>1645</v>
+        <v>1665</v>
       </c>
       <c r="CI141" t="n">
         <v>470</v>
@@ -54103,7 +54103,7 @@
         <v>10780</v>
       </c>
       <c r="DL141" t="n">
-        <v>18216</v>
+        <v>18415</v>
       </c>
       <c r="DM141" t="n">
         <v>580</v>
@@ -54127,10 +54127,10 @@
         <v>4927</v>
       </c>
       <c r="DT141" t="n">
-        <v>27596</v>
+        <v>27881</v>
       </c>
       <c r="DU141" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>
@@ -60370,7 +60370,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>220</v>
+        <v>910</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -60382,13 +60382,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1810</v>
+        <v>1910</v>
       </c>
       <c r="N8" t="n">
         <v>5651</v>
       </c>
       <c r="O8" t="n">
-        <v>15531</v>
+        <v>16321</v>
       </c>
     </row>
     <row r="9">
@@ -60419,7 +60419,7 @@
         <v>2445</v>
       </c>
       <c r="I9" t="n">
-        <v>3865</v>
+        <v>4555</v>
       </c>
       <c r="J9" t="n">
         <v>2880</v>
@@ -60431,13 +60431,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>15989</v>
+        <v>16089</v>
       </c>
       <c r="N9" t="n">
         <v>27013</v>
       </c>
       <c r="O9" t="n">
-        <v>101178</v>
+        <v>101968</v>
       </c>
     </row>
   </sheetData>
@@ -70550,7 +70550,7 @@
         <v>2355</v>
       </c>
       <c r="L140" t="n">
-        <v>271</v>
+        <v>470</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -70562,16 +70562,16 @@
         <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>4420</v>
+        <v>4590</v>
       </c>
       <c r="Q140" t="n">
         <v>155</v>
       </c>
       <c r="R140" t="n">
-        <v>430</v>
+        <v>1405</v>
       </c>
       <c r="S140" t="n">
-        <v>26454</v>
+        <v>27798</v>
       </c>
     </row>
     <row r="141">
@@ -70611,7 +70611,7 @@
         <v>113789</v>
       </c>
       <c r="L141" t="n">
-        <v>32932</v>
+        <v>33131</v>
       </c>
       <c r="M141" t="n">
         <v>5769</v>
@@ -70623,16 +70623,16 @@
         <v>24816</v>
       </c>
       <c r="P141" t="n">
-        <v>426258</v>
+        <v>426428</v>
       </c>
       <c r="Q141" t="n">
         <v>36784</v>
       </c>
       <c r="R141" t="n">
-        <v>88610</v>
+        <v>89585</v>
       </c>
       <c r="S141" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>
@@ -80048,7 +80048,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>220</v>
+        <v>910</v>
       </c>
     </row>
     <row r="134">
@@ -80058,7 +80058,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>48837</v>
+        <v>49527</v>
       </c>
     </row>
     <row r="136">
@@ -80166,7 +80166,7 @@
         <v>2026</v>
       </c>
       <c r="B148" t="n">
-        <v>3865</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="149">
@@ -80176,7 +80176,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>48837</v>
+        <v>49527</v>
       </c>
     </row>
   </sheetData>
@@ -89207,7 +89207,7 @@
         <v>5651</v>
       </c>
       <c r="C140" t="n">
-        <v>1810</v>
+        <v>1910</v>
       </c>
       <c r="D140" t="n">
         <v>1010</v>
@@ -89225,7 +89225,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>10923</v>
+        <v>11477</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -89243,10 +89243,10 @@
         <v>995</v>
       </c>
       <c r="O140" t="n">
-        <v>220</v>
+        <v>910</v>
       </c>
       <c r="P140" t="n">
-        <v>26454</v>
+        <v>27798</v>
       </c>
     </row>
     <row r="141">
@@ -89259,7 +89259,7 @@
         <v>402324</v>
       </c>
       <c r="C141" t="n">
-        <v>224962</v>
+        <v>225062</v>
       </c>
       <c r="D141" t="n">
         <v>59172</v>
@@ -89277,7 +89277,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>759086</v>
+        <v>759640</v>
       </c>
       <c r="J141" t="n">
         <v>220401</v>
@@ -89295,10 +89295,10 @@
         <v>71567</v>
       </c>
       <c r="O141" t="n">
-        <v>48837</v>
+        <v>49527</v>
       </c>
       <c r="P141" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>
@@ -90714,7 +90714,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1810</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="141">
@@ -90724,7 +90724,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>224962</v>
+        <v>225062</v>
       </c>
     </row>
     <row r="143">
@@ -90832,7 +90832,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>15989</v>
+        <v>16089</v>
       </c>
     </row>
     <row r="156">
@@ -90842,7 +90842,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>224962</v>
+        <v>225062</v>
       </c>
     </row>
   </sheetData>
@@ -97191,7 +97191,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5367</v>
+        <v>5467</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97209,7 +97209,7 @@
         <v>1400</v>
       </c>
       <c r="K13" t="n">
-        <v>1165</v>
+        <v>1380</v>
       </c>
       <c r="L13" t="n">
         <v>825</v>
@@ -97218,7 +97218,7 @@
         <v>422</v>
       </c>
       <c r="N13" t="n">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="O13" t="n">
         <v>70</v>
@@ -97428,13 +97428,13 @@
         <v>30</v>
       </c>
       <c r="CF13" t="n">
-        <v>2135</v>
+        <v>2540</v>
       </c>
       <c r="CG13" t="n">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="CH13" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -97524,7 +97524,7 @@
         <v>640</v>
       </c>
       <c r="DL13" t="n">
-        <v>1903</v>
+        <v>2102</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -97548,10 +97548,10 @@
         <v>275</v>
       </c>
       <c r="DT13" t="n">
-        <v>1730</v>
+        <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>177463</v>
+        <v>178807</v>
       </c>
     </row>
     <row r="14">
@@ -97570,7 +97570,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72048</v>
+        <v>72148</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -97588,7 +97588,7 @@
         <v>22373</v>
       </c>
       <c r="K14" t="n">
-        <v>17090</v>
+        <v>17305</v>
       </c>
       <c r="L14" t="n">
         <v>5790</v>
@@ -97597,7 +97597,7 @@
         <v>1742</v>
       </c>
       <c r="N14" t="n">
-        <v>2935</v>
+        <v>3005</v>
       </c>
       <c r="O14" t="n">
         <v>5784</v>
@@ -97807,13 +97807,13 @@
         <v>145</v>
       </c>
       <c r="CF14" t="n">
-        <v>21241</v>
+        <v>21646</v>
       </c>
       <c r="CG14" t="n">
-        <v>3642</v>
+        <v>3692</v>
       </c>
       <c r="CH14" t="n">
-        <v>1645</v>
+        <v>1665</v>
       </c>
       <c r="CI14" t="n">
         <v>470</v>
@@ -97903,7 +97903,7 @@
         <v>10780</v>
       </c>
       <c r="DL14" t="n">
-        <v>18216</v>
+        <v>18415</v>
       </c>
       <c r="DM14" t="n">
         <v>580</v>
@@ -97927,10 +97927,10 @@
         <v>4927</v>
       </c>
       <c r="DT14" t="n">
-        <v>27596</v>
+        <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>
@@ -98728,7 +98728,7 @@
         <v>11296</v>
       </c>
       <c r="L13" t="n">
-        <v>2294</v>
+        <v>2493</v>
       </c>
       <c r="M13" t="n">
         <v>856</v>
@@ -98740,16 +98740,16 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>31809</v>
+        <v>31979</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
       </c>
       <c r="R13" t="n">
-        <v>9277</v>
+        <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>177463</v>
+        <v>178807</v>
       </c>
     </row>
     <row r="14">
@@ -98789,7 +98789,7 @@
         <v>113789</v>
       </c>
       <c r="L14" t="n">
-        <v>32932</v>
+        <v>33131</v>
       </c>
       <c r="M14" t="n">
         <v>5769</v>
@@ -98801,16 +98801,16 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>426258</v>
+        <v>426428</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
       </c>
       <c r="R14" t="n">
-        <v>88610</v>
+        <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>
@@ -99467,7 +99467,7 @@
         <v>27013</v>
       </c>
       <c r="C13" t="n">
-        <v>15989</v>
+        <v>16089</v>
       </c>
       <c r="D13" t="n">
         <v>5115</v>
@@ -99485,7 +99485,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>76285</v>
+        <v>76839</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -99503,10 +99503,10 @@
         <v>5785</v>
       </c>
       <c r="O13" t="n">
-        <v>3865</v>
+        <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>177463</v>
+        <v>178807</v>
       </c>
     </row>
     <row r="14">
@@ -99519,7 +99519,7 @@
         <v>402324</v>
       </c>
       <c r="C14" t="n">
-        <v>224962</v>
+        <v>225062</v>
       </c>
       <c r="D14" t="n">
         <v>59172</v>
@@ -99537,7 +99537,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>759086</v>
+        <v>759640</v>
       </c>
       <c r="J14" t="n">
         <v>220401</v>
@@ -99555,10 +99555,10 @@
         <v>71567</v>
       </c>
       <c r="O14" t="n">
-        <v>48837</v>
+        <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2096230</v>
+        <v>2097574</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53391,7 +53391,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>695</v>
+        <v>760</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -53592,7 +53592,7 @@
         <v>950</v>
       </c>
       <c r="BT140" t="n">
-        <v>305</v>
+        <v>410</v>
       </c>
       <c r="BU140" t="n">
         <v>505</v>
@@ -53622,7 +53622,7 @@
         <v>620</v>
       </c>
       <c r="CD140" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="CE140" t="n">
         <v>0</v>
@@ -53682,7 +53682,7 @@
         <v>0</v>
       </c>
       <c r="CX140" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="CY140" t="n">
         <v>120</v>
@@ -53736,13 +53736,13 @@
         <v>200</v>
       </c>
       <c r="DP140" t="n">
-        <v>660</v>
+        <v>930</v>
       </c>
       <c r="DQ140" t="n">
         <v>0</v>
       </c>
       <c r="DR140" t="n">
-        <v>995</v>
+        <v>1125</v>
       </c>
       <c r="DS140" t="n">
         <v>0</v>
@@ -53751,7 +53751,7 @@
         <v>355</v>
       </c>
       <c r="DU140" t="n">
-        <v>27798</v>
+        <v>28907</v>
       </c>
     </row>
     <row r="141">
@@ -53770,7 +53770,7 @@
         <v>150</v>
       </c>
       <c r="E141" t="n">
-        <v>72148</v>
+        <v>72213</v>
       </c>
       <c r="F141" t="n">
         <v>500</v>
@@ -53971,7 +53971,7 @@
         <v>27526</v>
       </c>
       <c r="BT141" t="n">
-        <v>5420</v>
+        <v>5525</v>
       </c>
       <c r="BU141" t="n">
         <v>6290</v>
@@ -54001,7 +54001,7 @@
         <v>16285</v>
       </c>
       <c r="CD141" t="n">
-        <v>5769</v>
+        <v>5908</v>
       </c>
       <c r="CE141" t="n">
         <v>145</v>
@@ -54061,7 +54061,7 @@
         <v>8936</v>
       </c>
       <c r="CX141" t="n">
-        <v>18492</v>
+        <v>18892</v>
       </c>
       <c r="CY141" t="n">
         <v>13884</v>
@@ -54115,13 +54115,13 @@
         <v>7925</v>
       </c>
       <c r="DP141" t="n">
-        <v>58393</v>
+        <v>58663</v>
       </c>
       <c r="DQ141" t="n">
         <v>1450</v>
       </c>
       <c r="DR141" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
       <c r="DS141" t="n">
         <v>4927</v>
@@ -54130,7 +54130,7 @@
         <v>27881</v>
       </c>
       <c r="DU141" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>
@@ -60364,7 +60364,7 @@
         <v>1010</v>
       </c>
       <c r="G8" t="n">
-        <v>995</v>
+        <v>1125</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -60382,13 +60382,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1910</v>
+        <v>1975</v>
       </c>
       <c r="N8" t="n">
         <v>5651</v>
       </c>
       <c r="O8" t="n">
-        <v>16321</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="9">
@@ -60413,7 +60413,7 @@
         <v>5115</v>
       </c>
       <c r="G9" t="n">
-        <v>5785</v>
+        <v>5915</v>
       </c>
       <c r="H9" t="n">
         <v>2445</v>
@@ -60431,13 +60431,13 @@
         <v>2690</v>
       </c>
       <c r="M9" t="n">
-        <v>16089</v>
+        <v>16154</v>
       </c>
       <c r="N9" t="n">
         <v>27013</v>
       </c>
       <c r="O9" t="n">
-        <v>101968</v>
+        <v>102163</v>
       </c>
     </row>
   </sheetData>
@@ -70529,16 +70529,16 @@
         <v>825</v>
       </c>
       <c r="E140" t="n">
-        <v>12246</v>
+        <v>12646</v>
       </c>
       <c r="F140" t="n">
         <v>7</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H140" t="n">
-        <v>640</v>
+        <v>745</v>
       </c>
       <c r="I140" t="n">
         <v>2635</v>
@@ -70553,7 +70553,7 @@
         <v>470</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -70562,7 +70562,7 @@
         <v>60</v>
       </c>
       <c r="P140" t="n">
-        <v>4590</v>
+        <v>4655</v>
       </c>
       <c r="Q140" t="n">
         <v>155</v>
@@ -70571,7 +70571,7 @@
         <v>1405</v>
       </c>
       <c r="S140" t="n">
-        <v>27798</v>
+        <v>28907</v>
       </c>
     </row>
     <row r="141">
@@ -70590,16 +70590,16 @@
         <v>62972</v>
       </c>
       <c r="E141" t="n">
-        <v>867059</v>
+        <v>867459</v>
       </c>
       <c r="F141" t="n">
         <v>5937</v>
       </c>
       <c r="G141" t="n">
-        <v>34009</v>
+        <v>34409</v>
       </c>
       <c r="H141" t="n">
-        <v>8135</v>
+        <v>8240</v>
       </c>
       <c r="I141" t="n">
         <v>286740</v>
@@ -70614,7 +70614,7 @@
         <v>33131</v>
       </c>
       <c r="M141" t="n">
-        <v>5769</v>
+        <v>5908</v>
       </c>
       <c r="N141" t="n">
         <v>42</v>
@@ -70623,7 +70623,7 @@
         <v>24816</v>
       </c>
       <c r="P141" t="n">
-        <v>426428</v>
+        <v>426493</v>
       </c>
       <c r="Q141" t="n">
         <v>36784</v>
@@ -70632,7 +70632,7 @@
         <v>89585</v>
       </c>
       <c r="S141" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>
@@ -77654,7 +77654,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>995</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="137">
@@ -77664,7 +77664,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
     </row>
     <row r="139">
@@ -77772,7 +77772,7 @@
         <v>2026</v>
       </c>
       <c r="B151" t="n">
-        <v>5785</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="152">
@@ -77782,7 +77782,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
     </row>
   </sheetData>
@@ -89207,7 +89207,7 @@
         <v>5651</v>
       </c>
       <c r="C140" t="n">
-        <v>1910</v>
+        <v>1975</v>
       </c>
       <c r="D140" t="n">
         <v>1010</v>
@@ -89225,7 +89225,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>11477</v>
+        <v>12391</v>
       </c>
       <c r="J140" t="n">
         <v>2490</v>
@@ -89240,13 +89240,13 @@
         <v>795</v>
       </c>
       <c r="N140" t="n">
-        <v>995</v>
+        <v>1125</v>
       </c>
       <c r="O140" t="n">
         <v>910</v>
       </c>
       <c r="P140" t="n">
-        <v>27798</v>
+        <v>28907</v>
       </c>
     </row>
     <row r="141">
@@ -89259,7 +89259,7 @@
         <v>402324</v>
       </c>
       <c r="C141" t="n">
-        <v>225062</v>
+        <v>225127</v>
       </c>
       <c r="D141" t="n">
         <v>59172</v>
@@ -89277,7 +89277,7 @@
         <v>6860</v>
       </c>
       <c r="I141" t="n">
-        <v>759640</v>
+        <v>760554</v>
       </c>
       <c r="J141" t="n">
         <v>220401</v>
@@ -89292,13 +89292,13 @@
         <v>100763</v>
       </c>
       <c r="N141" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
       <c r="O141" t="n">
         <v>49527</v>
       </c>
       <c r="P141" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>
@@ -90714,7 +90714,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1910</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="141">
@@ -90724,7 +90724,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>225062</v>
+        <v>225127</v>
       </c>
     </row>
     <row r="143">
@@ -90832,7 +90832,7 @@
         <v>2026</v>
       </c>
       <c r="B155" t="n">
-        <v>16089</v>
+        <v>16154</v>
       </c>
     </row>
     <row r="156">
@@ -90842,7 +90842,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>225062</v>
+        <v>225127</v>
       </c>
     </row>
   </sheetData>
@@ -97191,7 +97191,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5467</v>
+        <v>5532</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97392,7 +97392,7 @@
         <v>3832</v>
       </c>
       <c r="BT13" t="n">
-        <v>595</v>
+        <v>700</v>
       </c>
       <c r="BU13" t="n">
         <v>1540</v>
@@ -97422,7 +97422,7 @@
         <v>2555</v>
       </c>
       <c r="CD13" t="n">
-        <v>856</v>
+        <v>995</v>
       </c>
       <c r="CE13" t="n">
         <v>30</v>
@@ -97482,7 +97482,7 @@
         <v>190</v>
       </c>
       <c r="CX13" t="n">
-        <v>2190</v>
+        <v>2590</v>
       </c>
       <c r="CY13" t="n">
         <v>1030</v>
@@ -97536,13 +97536,13 @@
         <v>595</v>
       </c>
       <c r="DP13" t="n">
-        <v>5104</v>
+        <v>5374</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>5785</v>
+        <v>5915</v>
       </c>
       <c r="DS13" t="n">
         <v>275</v>
@@ -97551,7 +97551,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>178807</v>
+        <v>179916</v>
       </c>
     </row>
     <row r="14">
@@ -97570,7 +97570,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72148</v>
+        <v>72213</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -97771,7 +97771,7 @@
         <v>27526</v>
       </c>
       <c r="BT14" t="n">
-        <v>5420</v>
+        <v>5525</v>
       </c>
       <c r="BU14" t="n">
         <v>6290</v>
@@ -97801,7 +97801,7 @@
         <v>16285</v>
       </c>
       <c r="CD14" t="n">
-        <v>5769</v>
+        <v>5908</v>
       </c>
       <c r="CE14" t="n">
         <v>145</v>
@@ -97861,7 +97861,7 @@
         <v>8936</v>
       </c>
       <c r="CX14" t="n">
-        <v>18492</v>
+        <v>18892</v>
       </c>
       <c r="CY14" t="n">
         <v>13884</v>
@@ -97915,13 +97915,13 @@
         <v>7925</v>
       </c>
       <c r="DP14" t="n">
-        <v>58393</v>
+        <v>58663</v>
       </c>
       <c r="DQ14" t="n">
         <v>1450</v>
       </c>
       <c r="DR14" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
       <c r="DS14" t="n">
         <v>4927</v>
@@ -97930,7 +97930,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>
@@ -98707,16 +98707,16 @@
         <v>5660</v>
       </c>
       <c r="E13" t="n">
-        <v>75419</v>
+        <v>75819</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
       </c>
       <c r="G13" t="n">
-        <v>2823</v>
+        <v>3223</v>
       </c>
       <c r="H13" t="n">
-        <v>1855</v>
+        <v>1960</v>
       </c>
       <c r="I13" t="n">
         <v>21854</v>
@@ -98731,7 +98731,7 @@
         <v>2493</v>
       </c>
       <c r="M13" t="n">
-        <v>856</v>
+        <v>995</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -98740,7 +98740,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>31979</v>
+        <v>32044</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -98749,7 +98749,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>178807</v>
+        <v>179916</v>
       </c>
     </row>
     <row r="14">
@@ -98768,16 +98768,16 @@
         <v>62972</v>
       </c>
       <c r="E14" t="n">
-        <v>867059</v>
+        <v>867459</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
       </c>
       <c r="G14" t="n">
-        <v>34009</v>
+        <v>34409</v>
       </c>
       <c r="H14" t="n">
-        <v>8135</v>
+        <v>8240</v>
       </c>
       <c r="I14" t="n">
         <v>286740</v>
@@ -98792,7 +98792,7 @@
         <v>33131</v>
       </c>
       <c r="M14" t="n">
-        <v>5769</v>
+        <v>5908</v>
       </c>
       <c r="N14" t="n">
         <v>42</v>
@@ -98801,7 +98801,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>426428</v>
+        <v>426493</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -98810,7 +98810,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>
@@ -99467,7 +99467,7 @@
         <v>27013</v>
       </c>
       <c r="C13" t="n">
-        <v>16089</v>
+        <v>16154</v>
       </c>
       <c r="D13" t="n">
         <v>5115</v>
@@ -99485,7 +99485,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>76839</v>
+        <v>77753</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -99500,13 +99500,13 @@
         <v>6260</v>
       </c>
       <c r="N13" t="n">
-        <v>5785</v>
+        <v>5915</v>
       </c>
       <c r="O13" t="n">
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>178807</v>
+        <v>179916</v>
       </c>
     </row>
     <row r="14">
@@ -99519,7 +99519,7 @@
         <v>402324</v>
       </c>
       <c r="C14" t="n">
-        <v>225062</v>
+        <v>225127</v>
       </c>
       <c r="D14" t="n">
         <v>59172</v>
@@ -99537,7 +99537,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>759640</v>
+        <v>760554</v>
       </c>
       <c r="J14" t="n">
         <v>220401</v>
@@ -99552,13 +99552,13 @@
         <v>100763</v>
       </c>
       <c r="N14" t="n">
-        <v>71567</v>
+        <v>71697</v>
       </c>
       <c r="O14" t="n">
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2097574</v>
+        <v>2098683</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU141"/>
+  <dimension ref="A1:DU142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53757,380 +53757,759 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2547</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>995</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>72213</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>2718</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>22373</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>17305</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>5790</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>1742</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3005</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>6845</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>434984</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>870</v>
+        <v>90</v>
       </c>
       <c r="U141" t="n">
-        <v>2174</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>14436</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>24559</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>4820</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>2945</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>9239</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>10770</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>1505</v>
+        <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="AI141" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>12358</v>
+        <v>0</v>
       </c>
       <c r="AK141" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="AL141" t="n">
-        <v>51403</v>
+        <v>0</v>
       </c>
       <c r="AM141" t="n">
-        <v>4755</v>
+        <v>0</v>
       </c>
       <c r="AN141" t="n">
-        <v>3715</v>
+        <v>0</v>
       </c>
       <c r="AO141" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="AP141" t="n">
-        <v>2039</v>
+        <v>0</v>
       </c>
       <c r="AQ141" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="AR141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>185</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>140</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>125</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>200</v>
+      </c>
+      <c r="BR141" t="n">
         <v>280</v>
       </c>
-      <c r="AS141" t="n">
-        <v>26989</v>
-      </c>
-      <c r="AT141" t="n">
-        <v>565</v>
-      </c>
-      <c r="AU141" t="n">
-        <v>2720</v>
-      </c>
-      <c r="AV141" t="n">
-        <v>6939</v>
-      </c>
-      <c r="AW141" t="n">
-        <v>5655</v>
-      </c>
-      <c r="AX141" t="n">
-        <v>460</v>
-      </c>
-      <c r="AY141" t="n">
-        <v>41302</v>
-      </c>
-      <c r="AZ141" t="n">
-        <v>6666</v>
-      </c>
-      <c r="BA141" t="n">
-        <v>3280</v>
-      </c>
-      <c r="BB141" t="n">
-        <v>9762</v>
-      </c>
-      <c r="BC141" t="n">
-        <v>6845</v>
-      </c>
-      <c r="BD141" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE141" t="n">
-        <v>435</v>
-      </c>
-      <c r="BF141" t="n">
-        <v>10010</v>
-      </c>
-      <c r="BG141" t="n">
-        <v>1190</v>
-      </c>
-      <c r="BH141" t="n">
-        <v>13569</v>
-      </c>
-      <c r="BI141" t="n">
-        <v>1035</v>
-      </c>
-      <c r="BJ141" t="n">
-        <v>660</v>
-      </c>
-      <c r="BK141" t="n">
-        <v>48116</v>
-      </c>
-      <c r="BL141" t="n">
-        <v>1992</v>
-      </c>
-      <c r="BM141" t="n">
-        <v>114410</v>
-      </c>
-      <c r="BN141" t="n">
-        <v>4120</v>
-      </c>
-      <c r="BO141" t="n">
-        <v>7460</v>
-      </c>
-      <c r="BP141" t="n">
-        <v>95601</v>
-      </c>
-      <c r="BQ141" t="n">
-        <v>22290</v>
-      </c>
-      <c r="BR141" t="n">
-        <v>13430</v>
-      </c>
       <c r="BS141" t="n">
-        <v>27526</v>
+        <v>0</v>
       </c>
       <c r="BT141" t="n">
-        <v>5525</v>
+        <v>0</v>
       </c>
       <c r="BU141" t="n">
-        <v>6290</v>
+        <v>0</v>
       </c>
       <c r="BV141" t="n">
-        <v>34940</v>
+        <v>0</v>
       </c>
       <c r="BW141" t="n">
-        <v>5175</v>
+        <v>0</v>
       </c>
       <c r="BX141" t="n">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="BY141" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BZ141" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="CA141" t="n">
-        <v>3350</v>
+        <v>0</v>
       </c>
       <c r="CB141" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="CC141" t="n">
-        <v>16285</v>
+        <v>0</v>
       </c>
       <c r="CD141" t="n">
-        <v>5908</v>
+        <v>0</v>
       </c>
       <c r="CE141" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="CF141" t="n">
-        <v>21646</v>
+        <v>0</v>
       </c>
       <c r="CG141" t="n">
-        <v>3692</v>
+        <v>0</v>
       </c>
       <c r="CH141" t="n">
-        <v>1665</v>
+        <v>0</v>
       </c>
       <c r="CI141" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="CJ141" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="CK141" t="n">
-        <v>18054</v>
+        <v>70</v>
       </c>
       <c r="CL141" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="CM141" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="CN141" t="n">
-        <v>11123</v>
+        <v>0</v>
       </c>
       <c r="CO141" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="CP141" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="CQ141" t="n">
-        <v>12112</v>
+        <v>0</v>
       </c>
       <c r="CR141" t="n">
-        <v>65996</v>
+        <v>0</v>
       </c>
       <c r="CS141" t="n">
-        <v>2715</v>
+        <v>0</v>
       </c>
       <c r="CT141" t="n">
-        <v>1310</v>
+        <v>0</v>
       </c>
       <c r="CU141" t="n">
-        <v>2736</v>
+        <v>0</v>
       </c>
       <c r="CV141" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="CW141" t="n">
-        <v>8936</v>
+        <v>0</v>
       </c>
       <c r="CX141" t="n">
-        <v>18892</v>
+        <v>0</v>
       </c>
       <c r="CY141" t="n">
-        <v>13884</v>
+        <v>0</v>
       </c>
       <c r="CZ141" t="n">
-        <v>220401</v>
+        <v>0</v>
       </c>
       <c r="DA141" t="n">
-        <v>1125</v>
+        <v>0</v>
       </c>
       <c r="DB141" t="n">
-        <v>1351</v>
+        <v>0</v>
       </c>
       <c r="DC141" t="n">
-        <v>1485</v>
+        <v>0</v>
       </c>
       <c r="DD141" t="n">
         <v>45</v>
       </c>
       <c r="DE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS141" t="n">
+        <v>55</v>
+      </c>
+      <c r="DT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2547</v>
+      </c>
+      <c r="C142" t="n">
+        <v>995</v>
+      </c>
+      <c r="D142" t="n">
+        <v>150</v>
+      </c>
+      <c r="E142" t="n">
+        <v>72213</v>
+      </c>
+      <c r="F142" t="n">
+        <v>500</v>
+      </c>
+      <c r="G142" t="n">
+        <v>400</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2718</v>
+      </c>
+      <c r="I142" t="n">
+        <v>3200</v>
+      </c>
+      <c r="J142" t="n">
+        <v>22373</v>
+      </c>
+      <c r="K142" t="n">
+        <v>17305</v>
+      </c>
+      <c r="L142" t="n">
+        <v>5790</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1742</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3005</v>
+      </c>
+      <c r="O142" t="n">
+        <v>5784</v>
+      </c>
+      <c r="P142" t="n">
+        <v>6845</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>105</v>
+      </c>
+      <c r="R142" t="n">
+        <v>434984</v>
+      </c>
+      <c r="S142" t="n">
+        <v>975</v>
+      </c>
+      <c r="T142" t="n">
+        <v>960</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2174</v>
+      </c>
+      <c r="V142" t="n">
+        <v>14436</v>
+      </c>
+      <c r="W142" t="n">
+        <v>24559</v>
+      </c>
+      <c r="X142" t="n">
+        <v>4820</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>2945</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>485</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>9239</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>210</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>10770</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>545</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>145</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1505</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>615</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>840</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>12358</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>427</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>51403</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>4755</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>3715</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>282</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>2039</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>385</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>280</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>27174</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>565</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>2720</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>7079</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>5655</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>460</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>41302</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>6666</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>3280</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>9887</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>6845</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>435</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>10010</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1190</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>13569</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1035</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>660</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>48116</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1992</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>114410</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>4120</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>7460</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>95601</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>22490</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>13710</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>27526</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>5525</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>6290</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>34940</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>5175</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>696</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>42</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>215</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>3350</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>435</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>16285</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>5908</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>145</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>21646</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>3692</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1665</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>470</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>350</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>18124</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>345</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>220</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>11123</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>140</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>275</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>12112</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>65996</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>2715</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1310</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>2736</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>125</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>8936</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>18892</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>13884</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>220401</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>1125</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>1351</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>1485</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>90</v>
+      </c>
+      <c r="DE142" t="n">
         <v>21081</v>
       </c>
-      <c r="DF141" t="n">
+      <c r="DF142" t="n">
         <v>38189</v>
       </c>
-      <c r="DG141" t="n">
+      <c r="DG142" t="n">
         <v>24118</v>
       </c>
-      <c r="DH141" t="n">
+      <c r="DH142" t="n">
         <v>100763</v>
       </c>
-      <c r="DI141" t="n">
+      <c r="DI142" t="n">
         <v>1240</v>
       </c>
-      <c r="DJ141" t="n">
+      <c r="DJ142" t="n">
         <v>15330</v>
       </c>
-      <c r="DK141" t="n">
+      <c r="DK142" t="n">
         <v>10780</v>
       </c>
-      <c r="DL141" t="n">
+      <c r="DL142" t="n">
         <v>18415</v>
       </c>
-      <c r="DM141" t="n">
+      <c r="DM142" t="n">
         <v>580</v>
       </c>
-      <c r="DN141" t="n">
+      <c r="DN142" t="n">
         <v>3025</v>
       </c>
-      <c r="DO141" t="n">
+      <c r="DO142" t="n">
         <v>7925</v>
       </c>
-      <c r="DP141" t="n">
+      <c r="DP142" t="n">
         <v>58663</v>
       </c>
-      <c r="DQ141" t="n">
+      <c r="DQ142" t="n">
         <v>1450</v>
       </c>
-      <c r="DR141" t="n">
+      <c r="DR142" t="n">
         <v>71697</v>
       </c>
-      <c r="DS141" t="n">
-        <v>4927</v>
-      </c>
-      <c r="DT141" t="n">
+      <c r="DS142" t="n">
+        <v>4982</v>
+      </c>
+      <c r="DT142" t="n">
         <v>27881</v>
       </c>
-      <c r="DU141" t="n">
-        <v>2098683</v>
+      <c r="DU142" t="n">
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>
@@ -61995,7 +62374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70577,62 +70956,123 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>185</v>
+      </c>
+      <c r="E141" t="n">
+        <v>115</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>890</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B142" t="n">
         <v>79117</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C142" t="n">
         <v>17804</v>
       </c>
-      <c r="D141" t="n">
-        <v>62972</v>
-      </c>
-      <c r="E141" t="n">
-        <v>867459</v>
-      </c>
-      <c r="F141" t="n">
+      <c r="D142" t="n">
+        <v>63157</v>
+      </c>
+      <c r="E142" t="n">
+        <v>867574</v>
+      </c>
+      <c r="F142" t="n">
         <v>5937</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G142" t="n">
         <v>34409</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H142" t="n">
         <v>8240</v>
       </c>
-      <c r="I141" t="n">
-        <v>286740</v>
-      </c>
-      <c r="J141" t="n">
+      <c r="I142" t="n">
+        <v>287630</v>
+      </c>
+      <c r="J142" t="n">
         <v>5457</v>
       </c>
-      <c r="K141" t="n">
+      <c r="K142" t="n">
         <v>113789</v>
       </c>
-      <c r="L141" t="n">
+      <c r="L142" t="n">
         <v>33131</v>
       </c>
-      <c r="M141" t="n">
+      <c r="M142" t="n">
         <v>5908</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N142" t="n">
         <v>42</v>
       </c>
-      <c r="O141" t="n">
+      <c r="O142" t="n">
         <v>24816</v>
       </c>
-      <c r="P141" t="n">
+      <c r="P142" t="n">
         <v>426493</v>
       </c>
-      <c r="Q141" t="n">
+      <c r="Q142" t="n">
         <v>36784</v>
       </c>
-      <c r="R141" t="n">
+      <c r="R142" t="n">
         <v>89585</v>
       </c>
-      <c r="S141" t="n">
-        <v>2098683</v>
+      <c r="S142" t="n">
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>
@@ -81936,7 +82376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89252,53 +89692,105 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1190</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B142" t="n">
         <v>402324</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C142" t="n">
         <v>225127</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D142" t="n">
         <v>59172</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E142" t="n">
         <v>14604</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F142" t="n">
         <v>69197</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G142" t="n">
         <v>23490</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H142" t="n">
         <v>6860</v>
       </c>
-      <c r="I141" t="n">
-        <v>760554</v>
-      </c>
-      <c r="J141" t="n">
+      <c r="I142" t="n">
+        <v>761744</v>
+      </c>
+      <c r="J142" t="n">
         <v>220401</v>
       </c>
-      <c r="K141" t="n">
+      <c r="K142" t="n">
         <v>32660</v>
       </c>
-      <c r="L141" t="n">
+      <c r="L142" t="n">
         <v>62307</v>
       </c>
-      <c r="M141" t="n">
+      <c r="M142" t="n">
         <v>100763</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N142" t="n">
         <v>71697</v>
       </c>
-      <c r="O141" t="n">
+      <c r="O142" t="n">
         <v>49527</v>
       </c>
-      <c r="P141" t="n">
-        <v>2098683</v>
+      <c r="P142" t="n">
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>
@@ -97236,7 +97728,7 @@
         <v>190</v>
       </c>
       <c r="T13" t="n">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="U13" t="n">
         <v>220</v>
@@ -97311,7 +97803,7 @@
         <v>280</v>
       </c>
       <c r="AS13" t="n">
-        <v>2250</v>
+        <v>2435</v>
       </c>
       <c r="AT13" t="n">
         <v>565</v>
@@ -97320,7 +97812,7 @@
         <v>360</v>
       </c>
       <c r="AV13" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AW13" t="n">
         <v>355</v>
@@ -97338,7 +97830,7 @@
         <v>335</v>
       </c>
       <c r="BB13" t="n">
-        <v>597</v>
+        <v>722</v>
       </c>
       <c r="BC13" t="n">
         <v>140</v>
@@ -97383,10 +97875,10 @@
         <v>6495</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1730</v>
+        <v>1930</v>
       </c>
       <c r="BR13" t="n">
-        <v>1062</v>
+        <v>1342</v>
       </c>
       <c r="BS13" t="n">
         <v>3832</v>
@@ -97443,7 +97935,7 @@
         <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="CL13" t="n">
         <v>50</v>
@@ -97500,7 +97992,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="DE13" t="n">
         <v>1570</v>
@@ -97545,13 +98037,13 @@
         <v>5915</v>
       </c>
       <c r="DS13" t="n">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="DT13" t="n">
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>179916</v>
+        <v>181106</v>
       </c>
     </row>
     <row r="14">
@@ -97615,7 +98107,7 @@
         <v>975</v>
       </c>
       <c r="T14" t="n">
-        <v>870</v>
+        <v>960</v>
       </c>
       <c r="U14" t="n">
         <v>2174</v>
@@ -97690,7 +98182,7 @@
         <v>280</v>
       </c>
       <c r="AS14" t="n">
-        <v>26989</v>
+        <v>27174</v>
       </c>
       <c r="AT14" t="n">
         <v>565</v>
@@ -97699,7 +98191,7 @@
         <v>2720</v>
       </c>
       <c r="AV14" t="n">
-        <v>6939</v>
+        <v>7079</v>
       </c>
       <c r="AW14" t="n">
         <v>5655</v>
@@ -97717,7 +98209,7 @@
         <v>3280</v>
       </c>
       <c r="BB14" t="n">
-        <v>9762</v>
+        <v>9887</v>
       </c>
       <c r="BC14" t="n">
         <v>6845</v>
@@ -97762,10 +98254,10 @@
         <v>95601</v>
       </c>
       <c r="BQ14" t="n">
-        <v>22290</v>
+        <v>22490</v>
       </c>
       <c r="BR14" t="n">
-        <v>13430</v>
+        <v>13710</v>
       </c>
       <c r="BS14" t="n">
         <v>27526</v>
@@ -97822,7 +98314,7 @@
         <v>350</v>
       </c>
       <c r="CK14" t="n">
-        <v>18054</v>
+        <v>18124</v>
       </c>
       <c r="CL14" t="n">
         <v>345</v>
@@ -97879,7 +98371,7 @@
         <v>1485</v>
       </c>
       <c r="DD14" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="DE14" t="n">
         <v>21081</v>
@@ -97924,13 +98416,13 @@
         <v>71697</v>
       </c>
       <c r="DS14" t="n">
-        <v>4927</v>
+        <v>4982</v>
       </c>
       <c r="DT14" t="n">
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2098683</v>
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>
@@ -98704,10 +99196,10 @@
         <v>2550</v>
       </c>
       <c r="D13" t="n">
-        <v>5660</v>
+        <v>5845</v>
       </c>
       <c r="E13" t="n">
-        <v>75819</v>
+        <v>75934</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -98719,7 +99211,7 @@
         <v>1960</v>
       </c>
       <c r="I13" t="n">
-        <v>21854</v>
+        <v>22744</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
@@ -98749,7 +99241,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>179916</v>
+        <v>181106</v>
       </c>
     </row>
     <row r="14">
@@ -98765,10 +99257,10 @@
         <v>17804</v>
       </c>
       <c r="D14" t="n">
-        <v>62972</v>
+        <v>63157</v>
       </c>
       <c r="E14" t="n">
-        <v>867459</v>
+        <v>867574</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -98780,7 +99272,7 @@
         <v>8240</v>
       </c>
       <c r="I14" t="n">
-        <v>286740</v>
+        <v>287630</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
@@ -98810,7 +99302,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2098683</v>
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>
@@ -99485,7 +99977,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>77753</v>
+        <v>78943</v>
       </c>
       <c r="J13" t="n">
         <v>16330</v>
@@ -99506,7 +99998,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>179916</v>
+        <v>181106</v>
       </c>
     </row>
     <row r="14">
@@ -99537,7 +100029,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>760554</v>
+        <v>761744</v>
       </c>
       <c r="J14" t="n">
         <v>220401</v>
@@ -99558,7 +100050,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2098683</v>
+        <v>2099873</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54067,7 +54067,7 @@
         <v>0</v>
       </c>
       <c r="CZ141" t="n">
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="DA141" t="n">
         <v>0</v>
@@ -54091,7 +54091,7 @@
         <v>0</v>
       </c>
       <c r="DH141" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="DI141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>1190</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="142">
@@ -54446,7 +54446,7 @@
         <v>13884</v>
       </c>
       <c r="CZ142" t="n">
-        <v>220401</v>
+        <v>221426</v>
       </c>
       <c r="DA142" t="n">
         <v>1125</v>
@@ -54470,7 +54470,7 @@
         <v>24118</v>
       </c>
       <c r="DH142" t="n">
-        <v>100763</v>
+        <v>101048</v>
       </c>
       <c r="DI142" t="n">
         <v>1240</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>
@@ -60347,7 +60347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60773,50 +60773,99 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>285</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>16330</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6260</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B10" t="n">
+        <v>17355</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6545</v>
+      </c>
+      <c r="D10" t="n">
         <v>5965</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>4886</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>5115</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>5915</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>2445</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>4555</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>2880</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>1955</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>2690</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>16154</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>27013</v>
       </c>
-      <c r="O9" t="n">
-        <v>102163</v>
+      <c r="O10" t="n">
+        <v>103473</v>
       </c>
     </row>
   </sheetData>
@@ -60830,7 +60879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62238,129 +62287,139 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>220401</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="B142" t="n">
+        <v>221426</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B144" t="n">
-        <v>6885</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B145" t="n">
-        <v>10546</v>
+        <v>6885</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B146" t="n">
-        <v>10537</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B147" t="n">
-        <v>13913</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B148" t="n">
-        <v>16988</v>
+        <v>13913</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B149" t="n">
-        <v>17285</v>
+        <v>16988</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B150" t="n">
-        <v>21884</v>
+        <v>17285</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B151" t="n">
-        <v>25698</v>
+        <v>21884</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B152" t="n">
-        <v>24908</v>
+        <v>25698</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B153" t="n">
-        <v>26942</v>
+        <v>24908</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="n">
-        <v>28485</v>
+        <v>26942</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>28485</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
         <v>2026</v>
       </c>
-      <c r="B155" t="n">
-        <v>16330</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="B156" t="n">
+        <v>17355</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>220401</v>
+      <c r="B157" t="n">
+        <v>221426</v>
       </c>
     </row>
   </sheetData>
@@ -70981,7 +71040,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>890</v>
+        <v>1915</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -71002,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71011,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>1190</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="142">
@@ -71042,7 +71101,7 @@
         <v>8240</v>
       </c>
       <c r="I142" t="n">
-        <v>287630</v>
+        <v>288655</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
@@ -71063,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>426493</v>
+        <v>426778</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71072,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>
@@ -71086,7 +71145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72494,129 +72553,139 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>100763</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="B142" t="n">
+        <v>101048</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B144" t="n">
-        <v>4620</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B145" t="n">
-        <v>9287</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B146" t="n">
-        <v>9052</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B147" t="n">
-        <v>11885</v>
+        <v>9052</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B148" t="n">
-        <v>10945</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B149" t="n">
-        <v>5985</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B150" t="n">
-        <v>7700</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B151" t="n">
-        <v>7774</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B152" t="n">
-        <v>7025</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B153" t="n">
-        <v>9800</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="n">
-        <v>10430</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>10430</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
         <v>2026</v>
       </c>
-      <c r="B155" t="n">
-        <v>6260</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="B156" t="n">
+        <v>6545</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>100763</v>
+      <c r="B157" t="n">
+        <v>101048</v>
       </c>
     </row>
   </sheetData>
@@ -89720,7 +89789,7 @@
         <v>1190</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -89729,7 +89798,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -89738,7 +89807,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>1190</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="142">
@@ -89772,7 +89841,7 @@
         <v>761744</v>
       </c>
       <c r="J142" t="n">
-        <v>220401</v>
+        <v>221426</v>
       </c>
       <c r="K142" t="n">
         <v>32660</v>
@@ -89781,7 +89850,7 @@
         <v>62307</v>
       </c>
       <c r="M142" t="n">
-        <v>100763</v>
+        <v>101048</v>
       </c>
       <c r="N142" t="n">
         <v>71697</v>
@@ -89790,7 +89859,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>
@@ -97980,7 +98049,7 @@
         <v>1030</v>
       </c>
       <c r="CZ13" t="n">
-        <v>16330</v>
+        <v>17355</v>
       </c>
       <c r="DA13" t="n">
         <v>125</v>
@@ -98004,7 +98073,7 @@
         <v>2450</v>
       </c>
       <c r="DH13" t="n">
-        <v>6260</v>
+        <v>6545</v>
       </c>
       <c r="DI13" t="n">
         <v>420</v>
@@ -98043,7 +98112,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>181106</v>
+        <v>182416</v>
       </c>
     </row>
     <row r="14">
@@ -98359,7 +98428,7 @@
         <v>13884</v>
       </c>
       <c r="CZ14" t="n">
-        <v>220401</v>
+        <v>221426</v>
       </c>
       <c r="DA14" t="n">
         <v>1125</v>
@@ -98383,7 +98452,7 @@
         <v>24118</v>
       </c>
       <c r="DH14" t="n">
-        <v>100763</v>
+        <v>101048</v>
       </c>
       <c r="DI14" t="n">
         <v>1240</v>
@@ -98422,7 +98491,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>
@@ -99211,7 +99280,7 @@
         <v>1960</v>
       </c>
       <c r="I13" t="n">
-        <v>22744</v>
+        <v>23769</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
@@ -99232,7 +99301,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>32044</v>
+        <v>32329</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99241,7 +99310,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>181106</v>
+        <v>182416</v>
       </c>
     </row>
     <row r="14">
@@ -99272,7 +99341,7 @@
         <v>8240</v>
       </c>
       <c r="I14" t="n">
-        <v>287630</v>
+        <v>288655</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
@@ -99293,7 +99362,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>426493</v>
+        <v>426778</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99302,7 +99371,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>
@@ -99980,7 +100049,7 @@
         <v>78943</v>
       </c>
       <c r="J13" t="n">
-        <v>16330</v>
+        <v>17355</v>
       </c>
       <c r="K13" t="n">
         <v>2445</v>
@@ -99989,7 +100058,7 @@
         <v>5965</v>
       </c>
       <c r="M13" t="n">
-        <v>6260</v>
+        <v>6545</v>
       </c>
       <c r="N13" t="n">
         <v>5915</v>
@@ -99998,7 +100067,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>181106</v>
+        <v>182416</v>
       </c>
     </row>
     <row r="14">
@@ -100032,7 +100101,7 @@
         <v>761744</v>
       </c>
       <c r="J14" t="n">
-        <v>220401</v>
+        <v>221426</v>
       </c>
       <c r="K14" t="n">
         <v>32660</v>
@@ -100041,7 +100110,7 @@
         <v>62307</v>
       </c>
       <c r="M14" t="n">
-        <v>100763</v>
+        <v>101048</v>
       </c>
       <c r="N14" t="n">
         <v>71697</v>
@@ -100050,7 +100119,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2099873</v>
+        <v>2101183</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53770,7 +53770,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -53785,7 +53785,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53854,7 +53854,7 @@
         <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH141" t="n">
         <v>0</v>
@@ -54115,7 +54115,7 @@
         <v>0</v>
       </c>
       <c r="DP141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DQ141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>2500</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="142">
@@ -54149,7 +54149,7 @@
         <v>150</v>
       </c>
       <c r="E142" t="n">
-        <v>72213</v>
+        <v>72343</v>
       </c>
       <c r="F142" t="n">
         <v>500</v>
@@ -54164,7 +54164,7 @@
         <v>3200</v>
       </c>
       <c r="J142" t="n">
-        <v>22373</v>
+        <v>22473</v>
       </c>
       <c r="K142" t="n">
         <v>17305</v>
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>434984</v>
+        <v>435484</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54233,7 +54233,7 @@
         <v>145</v>
       </c>
       <c r="AG142" t="n">
-        <v>1505</v>
+        <v>1545</v>
       </c>
       <c r="AH142" t="n">
         <v>615</v>
@@ -54494,7 +54494,7 @@
         <v>7925</v>
       </c>
       <c r="DP142" t="n">
-        <v>58663</v>
+        <v>58683</v>
       </c>
       <c r="DQ142" t="n">
         <v>1450</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O9" t="n">
-        <v>1310</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="10">
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>16154</v>
+        <v>16384</v>
       </c>
       <c r="N10" t="n">
-        <v>27013</v>
+        <v>27513</v>
       </c>
       <c r="O10" t="n">
-        <v>103473</v>
+        <v>104203</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>185</v>
       </c>
       <c r="E141" t="n">
-        <v>115</v>
+        <v>635</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>285</v>
+        <v>555</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>2500</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63157</v>
       </c>
       <c r="E142" t="n">
-        <v>867574</v>
+        <v>868094</v>
       </c>
       <c r="F142" t="n">
         <v>5937</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>426778</v>
+        <v>427048</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>
@@ -89765,10 +89765,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -89786,7 +89786,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1190</v>
+        <v>1250</v>
       </c>
       <c r="J141" t="n">
         <v>1025</v>
@@ -89807,7 +89807,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2500</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="142">
@@ -89817,10 +89817,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>402324</v>
+        <v>402824</v>
       </c>
       <c r="C142" t="n">
-        <v>225127</v>
+        <v>225357</v>
       </c>
       <c r="D142" t="n">
         <v>59172</v>
@@ -89838,7 +89838,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>761744</v>
+        <v>761804</v>
       </c>
       <c r="J142" t="n">
         <v>221426</v>
@@ -89859,7 +89859,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>
@@ -89873,7 +89873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91281,129 +91281,139 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>225127</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="B142" t="n">
+        <v>225357</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B144" t="n">
-        <v>6668</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B145" t="n">
-        <v>8792</v>
+        <v>6668</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B146" t="n">
-        <v>15242</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B147" t="n">
-        <v>21112</v>
+        <v>15242</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B148" t="n">
-        <v>21273</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B149" t="n">
-        <v>15805</v>
+        <v>21273</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B150" t="n">
-        <v>18542</v>
+        <v>15805</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B151" t="n">
-        <v>22238</v>
+        <v>18542</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B152" t="n">
-        <v>23439</v>
+        <v>22238</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B153" t="n">
-        <v>27420</v>
+        <v>23439</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="n">
-        <v>28442</v>
+        <v>27420</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>28442</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
         <v>2026</v>
       </c>
-      <c r="B155" t="n">
-        <v>16154</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="B156" t="n">
+        <v>16384</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>225127</v>
+      <c r="B157" t="n">
+        <v>225357</v>
       </c>
     </row>
   </sheetData>
@@ -91417,7 +91427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92825,129 +92835,139 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>402324</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="B142" t="n">
+        <v>402824</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B144" t="n">
-        <v>21287</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B145" t="n">
-        <v>31458</v>
+        <v>21287</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B146" t="n">
-        <v>36331</v>
+        <v>31458</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B147" t="n">
-        <v>41722</v>
+        <v>36331</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B148" t="n">
-        <v>35690</v>
+        <v>41722</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B149" t="n">
-        <v>23272</v>
+        <v>35690</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B150" t="n">
-        <v>26164</v>
+        <v>23272</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B151" t="n">
-        <v>34239</v>
+        <v>26164</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B152" t="n">
-        <v>43523</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B153" t="n">
-        <v>39596</v>
+        <v>43523</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="n">
-        <v>42029</v>
+        <v>39596</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>42029</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
         <v>2026</v>
       </c>
-      <c r="B155" t="n">
-        <v>27013</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="B156" t="n">
+        <v>27513</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>402324</v>
+      <c r="B157" t="n">
+        <v>402824</v>
       </c>
     </row>
   </sheetData>
@@ -97752,7 +97772,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5532</v>
+        <v>5662</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97767,7 +97787,7 @@
         <v>595</v>
       </c>
       <c r="J13" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="K13" t="n">
         <v>1380</v>
@@ -97791,7 +97811,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>29458</v>
+        <v>29958</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97836,7 +97856,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH13" t="n">
         <v>235</v>
@@ -98097,7 +98117,7 @@
         <v>595</v>
       </c>
       <c r="DP13" t="n">
-        <v>5374</v>
+        <v>5394</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
@@ -98112,7 +98132,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>182416</v>
+        <v>183206</v>
       </c>
     </row>
     <row r="14">
@@ -98131,7 +98151,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72213</v>
+        <v>72343</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98146,7 +98166,7 @@
         <v>3200</v>
       </c>
       <c r="J14" t="n">
-        <v>22373</v>
+        <v>22473</v>
       </c>
       <c r="K14" t="n">
         <v>17305</v>
@@ -98170,7 +98190,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>434984</v>
+        <v>435484</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98215,7 +98235,7 @@
         <v>145</v>
       </c>
       <c r="AG14" t="n">
-        <v>1505</v>
+        <v>1545</v>
       </c>
       <c r="AH14" t="n">
         <v>615</v>
@@ -98476,7 +98496,7 @@
         <v>7925</v>
       </c>
       <c r="DP14" t="n">
-        <v>58663</v>
+        <v>58683</v>
       </c>
       <c r="DQ14" t="n">
         <v>1450</v>
@@ -98491,7 +98511,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>
@@ -99268,7 +99288,7 @@
         <v>5845</v>
       </c>
       <c r="E13" t="n">
-        <v>75934</v>
+        <v>76454</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99301,7 +99321,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>32329</v>
+        <v>32599</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99310,7 +99330,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>182416</v>
+        <v>183206</v>
       </c>
     </row>
     <row r="14">
@@ -99329,7 +99349,7 @@
         <v>63157</v>
       </c>
       <c r="E14" t="n">
-        <v>867574</v>
+        <v>868094</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -99362,7 +99382,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>426778</v>
+        <v>427048</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99371,7 +99391,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>
@@ -100025,10 +100045,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>27013</v>
+        <v>27513</v>
       </c>
       <c r="C13" t="n">
-        <v>16154</v>
+        <v>16384</v>
       </c>
       <c r="D13" t="n">
         <v>5115</v>
@@ -100046,7 +100066,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>78943</v>
+        <v>79003</v>
       </c>
       <c r="J13" t="n">
         <v>17355</v>
@@ -100067,7 +100087,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>182416</v>
+        <v>183206</v>
       </c>
     </row>
     <row r="14">
@@ -100077,10 +100097,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>402324</v>
+        <v>402824</v>
       </c>
       <c r="C14" t="n">
-        <v>225127</v>
+        <v>225357</v>
       </c>
       <c r="D14" t="n">
         <v>59172</v>
@@ -100098,7 +100118,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>761744</v>
+        <v>761804</v>
       </c>
       <c r="J14" t="n">
         <v>221426</v>
@@ -100119,7 +100139,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2101183</v>
+        <v>2101973</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53839,7 +53839,7 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -53863,7 +53863,7 @@
         <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AK141" t="n">
         <v>0</v>
@@ -53917,7 +53917,7 @@
         <v>0</v>
       </c>
       <c r="BB141" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="BC141" t="n">
         <v>0</v>
@@ -53968,7 +53968,7 @@
         <v>280</v>
       </c>
       <c r="BS141" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="BT141" t="n">
         <v>0</v>
@@ -53983,7 +53983,7 @@
         <v>0</v>
       </c>
       <c r="BX141" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="BY141" t="n">
         <v>0</v>
@@ -54019,7 +54019,7 @@
         <v>0</v>
       </c>
       <c r="CJ141" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="CK141" t="n">
         <v>70</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>3290</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="142">
@@ -54218,7 +54218,7 @@
         <v>9239</v>
       </c>
       <c r="AB142" t="n">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="AC142" t="n">
         <v>10770</v>
@@ -54242,7 +54242,7 @@
         <v>840</v>
       </c>
       <c r="AJ142" t="n">
-        <v>12358</v>
+        <v>12598</v>
       </c>
       <c r="AK142" t="n">
         <v>427</v>
@@ -54296,7 +54296,7 @@
         <v>3280</v>
       </c>
       <c r="BB142" t="n">
-        <v>9887</v>
+        <v>9952</v>
       </c>
       <c r="BC142" t="n">
         <v>6845</v>
@@ -54347,7 +54347,7 @@
         <v>13710</v>
       </c>
       <c r="BS142" t="n">
-        <v>27526</v>
+        <v>28014</v>
       </c>
       <c r="BT142" t="n">
         <v>5525</v>
@@ -54362,7 +54362,7 @@
         <v>5175</v>
       </c>
       <c r="BX142" t="n">
-        <v>696</v>
+        <v>731</v>
       </c>
       <c r="BY142" t="n">
         <v>42</v>
@@ -54398,7 +54398,7 @@
         <v>470</v>
       </c>
       <c r="CJ142" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="CK142" t="n">
         <v>18124</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>
@@ -71034,19 +71034,19 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1915</v>
+        <v>1980</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>3290</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="142">
@@ -71095,19 +71095,19 @@
         <v>5937</v>
       </c>
       <c r="G142" t="n">
-        <v>34409</v>
+        <v>34479</v>
       </c>
       <c r="H142" t="n">
         <v>8240</v>
       </c>
       <c r="I142" t="n">
-        <v>288655</v>
+        <v>288720</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
       </c>
       <c r="K142" t="n">
-        <v>113789</v>
+        <v>114607</v>
       </c>
       <c r="L142" t="n">
         <v>33131</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>
@@ -89786,7 +89786,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1250</v>
+        <v>2203</v>
       </c>
       <c r="J141" t="n">
         <v>1025</v>
@@ -89807,7 +89807,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>3290</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="142">
@@ -89838,7 +89838,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>761804</v>
+        <v>762757</v>
       </c>
       <c r="J142" t="n">
         <v>221426</v>
@@ -89859,7 +89859,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>
@@ -97841,7 +97841,7 @@
         <v>925</v>
       </c>
       <c r="AB13" t="n">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="AC13" t="n">
         <v>1250</v>
@@ -97865,7 +97865,7 @@
         <v>225</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1064</v>
+        <v>1304</v>
       </c>
       <c r="AK13" t="n">
         <v>55</v>
@@ -97919,7 +97919,7 @@
         <v>335</v>
       </c>
       <c r="BB13" t="n">
-        <v>722</v>
+        <v>787</v>
       </c>
       <c r="BC13" t="n">
         <v>140</v>
@@ -97970,7 +97970,7 @@
         <v>1342</v>
       </c>
       <c r="BS13" t="n">
-        <v>3832</v>
+        <v>4320</v>
       </c>
       <c r="BT13" t="n">
         <v>700</v>
@@ -97985,7 +97985,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="BY13" t="n">
         <v>0</v>
@@ -98021,7 +98021,7 @@
         <v>0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="CK13" t="n">
         <v>510</v>
@@ -98132,7 +98132,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>183206</v>
+        <v>184159</v>
       </c>
     </row>
     <row r="14">
@@ -98220,7 +98220,7 @@
         <v>9239</v>
       </c>
       <c r="AB14" t="n">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="AC14" t="n">
         <v>10770</v>
@@ -98244,7 +98244,7 @@
         <v>840</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12358</v>
+        <v>12598</v>
       </c>
       <c r="AK14" t="n">
         <v>427</v>
@@ -98298,7 +98298,7 @@
         <v>3280</v>
       </c>
       <c r="BB14" t="n">
-        <v>9887</v>
+        <v>9952</v>
       </c>
       <c r="BC14" t="n">
         <v>6845</v>
@@ -98349,7 +98349,7 @@
         <v>13710</v>
       </c>
       <c r="BS14" t="n">
-        <v>27526</v>
+        <v>28014</v>
       </c>
       <c r="BT14" t="n">
         <v>5525</v>
@@ -98364,7 +98364,7 @@
         <v>5175</v>
       </c>
       <c r="BX14" t="n">
-        <v>696</v>
+        <v>731</v>
       </c>
       <c r="BY14" t="n">
         <v>42</v>
@@ -98400,7 +98400,7 @@
         <v>470</v>
       </c>
       <c r="CJ14" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="CK14" t="n">
         <v>18124</v>
@@ -98511,7 +98511,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>
@@ -99294,19 +99294,19 @@
         <v>472</v>
       </c>
       <c r="G13" t="n">
-        <v>3223</v>
+        <v>3293</v>
       </c>
       <c r="H13" t="n">
         <v>1960</v>
       </c>
       <c r="I13" t="n">
-        <v>23769</v>
+        <v>23834</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>11296</v>
+        <v>12114</v>
       </c>
       <c r="L13" t="n">
         <v>2493</v>
@@ -99330,7 +99330,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>183206</v>
+        <v>184159</v>
       </c>
     </row>
     <row r="14">
@@ -99355,19 +99355,19 @@
         <v>5937</v>
       </c>
       <c r="G14" t="n">
-        <v>34409</v>
+        <v>34479</v>
       </c>
       <c r="H14" t="n">
         <v>8240</v>
       </c>
       <c r="I14" t="n">
-        <v>288655</v>
+        <v>288720</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
       </c>
       <c r="K14" t="n">
-        <v>113789</v>
+        <v>114607</v>
       </c>
       <c r="L14" t="n">
         <v>33131</v>
@@ -99391,7 +99391,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>
@@ -100066,7 +100066,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>79003</v>
+        <v>79956</v>
       </c>
       <c r="J13" t="n">
         <v>17355</v>
@@ -100087,7 +100087,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>183206</v>
+        <v>184159</v>
       </c>
     </row>
     <row r="14">
@@ -100118,7 +100118,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>761804</v>
+        <v>762757</v>
       </c>
       <c r="J14" t="n">
         <v>221426</v>
@@ -100139,7 +100139,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2101973</v>
+        <v>2102926</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53863,7 +53863,7 @@
         <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AK141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>4243</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="142">
@@ -54242,7 +54242,7 @@
         <v>840</v>
       </c>
       <c r="AJ142" t="n">
-        <v>12598</v>
+        <v>12605</v>
       </c>
       <c r="AK142" t="n">
         <v>427</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>
@@ -71046,7 +71046,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>4243</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="142">
@@ -71107,7 +71107,7 @@
         <v>5457</v>
       </c>
       <c r="K142" t="n">
-        <v>114607</v>
+        <v>114614</v>
       </c>
       <c r="L142" t="n">
         <v>33131</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>
@@ -89786,7 +89786,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2203</v>
+        <v>2210</v>
       </c>
       <c r="J141" t="n">
         <v>1025</v>
@@ -89807,7 +89807,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>4243</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="142">
@@ -89838,7 +89838,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>762757</v>
+        <v>762764</v>
       </c>
       <c r="J142" t="n">
         <v>221426</v>
@@ -89859,7 +89859,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>
@@ -97865,7 +97865,7 @@
         <v>225</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="AK13" t="n">
         <v>55</v>
@@ -98132,7 +98132,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>184159</v>
+        <v>184166</v>
       </c>
     </row>
     <row r="14">
@@ -98244,7 +98244,7 @@
         <v>840</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12598</v>
+        <v>12605</v>
       </c>
       <c r="AK14" t="n">
         <v>427</v>
@@ -98511,7 +98511,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>
@@ -99306,7 +99306,7 @@
         <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>12114</v>
+        <v>12121</v>
       </c>
       <c r="L13" t="n">
         <v>2493</v>
@@ -99330,7 +99330,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>184159</v>
+        <v>184166</v>
       </c>
     </row>
     <row r="14">
@@ -99367,7 +99367,7 @@
         <v>5457</v>
       </c>
       <c r="K14" t="n">
-        <v>114607</v>
+        <v>114614</v>
       </c>
       <c r="L14" t="n">
         <v>33131</v>
@@ -99391,7 +99391,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>
@@ -100066,7 +100066,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>79956</v>
+        <v>79963</v>
       </c>
       <c r="J13" t="n">
         <v>17355</v>
@@ -100087,7 +100087,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>184159</v>
+        <v>184166</v>
       </c>
     </row>
     <row r="14">
@@ -100118,7 +100118,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>762757</v>
+        <v>762764</v>
       </c>
       <c r="J14" t="n">
         <v>221426</v>
@@ -100139,7 +100139,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2102926</v>
+        <v>2102933</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53791,7 +53791,7 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>500</v>
+        <v>1355</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53824,7 +53824,7 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="X141" t="n">
         <v>0</v>
@@ -53866,10 +53866,10 @@
         <v>247</v>
       </c>
       <c r="AK141" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL141" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM141" t="n">
         <v>0</v>
@@ -54121,7 +54121,7 @@
         <v>0</v>
       </c>
       <c r="DR141" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="DS141" t="n">
         <v>55</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>4250</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="142">
@@ -54170,7 +54170,7 @@
         <v>17305</v>
       </c>
       <c r="L142" t="n">
-        <v>5790</v>
+        <v>6040</v>
       </c>
       <c r="M142" t="n">
         <v>1742</v>
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>435484</v>
+        <v>436339</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54203,7 +54203,7 @@
         <v>14436</v>
       </c>
       <c r="W142" t="n">
-        <v>24559</v>
+        <v>24629</v>
       </c>
       <c r="X142" t="n">
         <v>4820</v>
@@ -54245,10 +54245,10 @@
         <v>12605</v>
       </c>
       <c r="AK142" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AL142" t="n">
-        <v>51403</v>
+        <v>51493</v>
       </c>
       <c r="AM142" t="n">
         <v>4755</v>
@@ -54500,7 +54500,7 @@
         <v>1450</v>
       </c>
       <c r="DR142" t="n">
-        <v>71697</v>
+        <v>72207</v>
       </c>
       <c r="DS142" t="n">
         <v>4982</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>
@@ -60792,10 +60792,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -60813,10 +60813,10 @@
         <v>230</v>
       </c>
       <c r="N9" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
       <c r="O9" t="n">
-        <v>2040</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="10">
@@ -60841,10 +60841,10 @@
         <v>5115</v>
       </c>
       <c r="G10" t="n">
-        <v>5915</v>
+        <v>6425</v>
       </c>
       <c r="H10" t="n">
-        <v>2445</v>
+        <v>2720</v>
       </c>
       <c r="I10" t="n">
         <v>4555</v>
@@ -60862,10 +60862,10 @@
         <v>16384</v>
       </c>
       <c r="N10" t="n">
-        <v>27513</v>
+        <v>28093</v>
       </c>
       <c r="O10" t="n">
-        <v>104203</v>
+        <v>105568</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>185</v>
       </c>
       <c r="E141" t="n">
-        <v>635</v>
+        <v>2460</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>4250</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63157</v>
       </c>
       <c r="E142" t="n">
-        <v>868094</v>
+        <v>869919</v>
       </c>
       <c r="F142" t="n">
         <v>5937</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>
@@ -76801,7 +76801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78169,129 +78169,139 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>71697</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="B138" t="n">
+        <v>72207</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B140" t="n">
-        <v>1540</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B141" t="n">
-        <v>1524</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B142" t="n">
-        <v>1647</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B143" t="n">
-        <v>4030</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B144" t="n">
-        <v>6012</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B145" t="n">
-        <v>4976</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B146" t="n">
-        <v>4864</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B147" t="n">
-        <v>7007</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B148" t="n">
-        <v>8675</v>
+        <v>7007</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B149" t="n">
-        <v>12945</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B150" t="n">
-        <v>12562</v>
+        <v>12945</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B151" t="n">
+        <v>12562</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
         <v>2026</v>
       </c>
-      <c r="B151" t="n">
-        <v>5915</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="B152" t="n">
+        <v>6425</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>71697</v>
+      <c r="B153" t="n">
+        <v>72207</v>
       </c>
     </row>
   </sheetData>
@@ -78305,7 +78315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79113,105 +79123,115 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>32660</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="B82" t="n">
+        <v>32935</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B84" t="n">
-        <v>3555</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B85" t="n">
-        <v>3730</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B86" t="n">
-        <v>2620</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B87" t="n">
-        <v>2735</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B88" t="n">
-        <v>3590</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B89" t="n">
-        <v>4330</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B90" t="n">
-        <v>4975</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B91" t="n">
-        <v>4680</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
         <v>2026</v>
       </c>
-      <c r="B92" t="n">
-        <v>2445</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="B93" t="n">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>32660</v>
+      <c r="B94" t="n">
+        <v>32935</v>
       </c>
     </row>
   </sheetData>
@@ -89765,7 +89785,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
       <c r="C141" t="n">
         <v>230</v>
@@ -89786,13 +89806,13 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2210</v>
+        <v>2670</v>
       </c>
       <c r="J141" t="n">
         <v>1025</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -89801,13 +89821,13 @@
         <v>285</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>4250</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="142">
@@ -89817,7 +89837,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>402824</v>
+        <v>403404</v>
       </c>
       <c r="C142" t="n">
         <v>225357</v>
@@ -89838,13 +89858,13 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>762764</v>
+        <v>763224</v>
       </c>
       <c r="J142" t="n">
         <v>221426</v>
       </c>
       <c r="K142" t="n">
-        <v>32660</v>
+        <v>32935</v>
       </c>
       <c r="L142" t="n">
         <v>62307</v>
@@ -89853,13 +89873,13 @@
         <v>101048</v>
       </c>
       <c r="N142" t="n">
-        <v>71697</v>
+        <v>72207</v>
       </c>
       <c r="O142" t="n">
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>
@@ -92839,7 +92859,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="142">
@@ -92849,7 +92869,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>402824</v>
+        <v>403404</v>
       </c>
     </row>
     <row r="144">
@@ -92957,7 +92977,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>27513</v>
+        <v>28093</v>
       </c>
     </row>
     <row r="157">
@@ -92967,7 +92987,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>402824</v>
+        <v>403404</v>
       </c>
     </row>
   </sheetData>
@@ -97793,7 +97813,7 @@
         <v>1380</v>
       </c>
       <c r="L13" t="n">
-        <v>825</v>
+        <v>1075</v>
       </c>
       <c r="M13" t="n">
         <v>422</v>
@@ -97811,7 +97831,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>29958</v>
+        <v>30813</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97826,7 +97846,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>2570</v>
+        <v>2640</v>
       </c>
       <c r="X13" t="n">
         <v>830</v>
@@ -97868,10 +97888,10 @@
         <v>1311</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="AL13" t="n">
-        <v>2862</v>
+        <v>2952</v>
       </c>
       <c r="AM13" t="n">
         <v>165</v>
@@ -98123,7 +98143,7 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>5915</v>
+        <v>6425</v>
       </c>
       <c r="DS13" t="n">
         <v>330</v>
@@ -98132,7 +98152,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>184166</v>
+        <v>185991</v>
       </c>
     </row>
     <row r="14">
@@ -98172,7 +98192,7 @@
         <v>17305</v>
       </c>
       <c r="L14" t="n">
-        <v>5790</v>
+        <v>6040</v>
       </c>
       <c r="M14" t="n">
         <v>1742</v>
@@ -98190,7 +98210,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>435484</v>
+        <v>436339</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98205,7 +98225,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>24559</v>
+        <v>24629</v>
       </c>
       <c r="X14" t="n">
         <v>4820</v>
@@ -98247,10 +98267,10 @@
         <v>12605</v>
       </c>
       <c r="AK14" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AL14" t="n">
-        <v>51403</v>
+        <v>51493</v>
       </c>
       <c r="AM14" t="n">
         <v>4755</v>
@@ -98502,7 +98522,7 @@
         <v>1450</v>
       </c>
       <c r="DR14" t="n">
-        <v>71697</v>
+        <v>72207</v>
       </c>
       <c r="DS14" t="n">
         <v>4982</v>
@@ -98511,7 +98531,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>
@@ -99288,7 +99308,7 @@
         <v>5845</v>
       </c>
       <c r="E13" t="n">
-        <v>76454</v>
+        <v>78279</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99330,7 +99350,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>184166</v>
+        <v>185991</v>
       </c>
     </row>
     <row r="14">
@@ -99349,7 +99369,7 @@
         <v>63157</v>
       </c>
       <c r="E14" t="n">
-        <v>868094</v>
+        <v>869919</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -99391,7 +99411,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>
@@ -100045,7 +100065,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>27513</v>
+        <v>28093</v>
       </c>
       <c r="C13" t="n">
         <v>16384</v>
@@ -100066,13 +100086,13 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>79963</v>
+        <v>80423</v>
       </c>
       <c r="J13" t="n">
         <v>17355</v>
       </c>
       <c r="K13" t="n">
-        <v>2445</v>
+        <v>2720</v>
       </c>
       <c r="L13" t="n">
         <v>5965</v>
@@ -100081,13 +100101,13 @@
         <v>6545</v>
       </c>
       <c r="N13" t="n">
-        <v>5915</v>
+        <v>6425</v>
       </c>
       <c r="O13" t="n">
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>184166</v>
+        <v>185991</v>
       </c>
     </row>
     <row r="14">
@@ -100097,7 +100117,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>402824</v>
+        <v>403404</v>
       </c>
       <c r="C14" t="n">
         <v>225357</v>
@@ -100118,13 +100138,13 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>762764</v>
+        <v>763224</v>
       </c>
       <c r="J14" t="n">
         <v>221426</v>
       </c>
       <c r="K14" t="n">
-        <v>32660</v>
+        <v>32935</v>
       </c>
       <c r="L14" t="n">
         <v>62307</v>
@@ -100133,13 +100153,13 @@
         <v>101048</v>
       </c>
       <c r="N14" t="n">
-        <v>71697</v>
+        <v>72207</v>
       </c>
       <c r="O14" t="n">
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2102933</v>
+        <v>2104758</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1355</v>
+        <v>2495</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>6075</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="142">
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>436339</v>
+        <v>437479</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>
@@ -60813,10 +60813,10 @@
         <v>230</v>
       </c>
       <c r="N9" t="n">
-        <v>1080</v>
+        <v>2220</v>
       </c>
       <c r="O9" t="n">
-        <v>3405</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="10">
@@ -60862,10 +60862,10 @@
         <v>16384</v>
       </c>
       <c r="N10" t="n">
-        <v>28093</v>
+        <v>29233</v>
       </c>
       <c r="O10" t="n">
-        <v>105568</v>
+        <v>106708</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>185</v>
       </c>
       <c r="E141" t="n">
-        <v>2460</v>
+        <v>3600</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>6075</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63157</v>
       </c>
       <c r="E142" t="n">
-        <v>869919</v>
+        <v>871059</v>
       </c>
       <c r="F142" t="n">
         <v>5937</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>
@@ -89785,7 +89785,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1080</v>
+        <v>2220</v>
       </c>
       <c r="C141" t="n">
         <v>230</v>
@@ -89827,7 +89827,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>6075</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="142">
@@ -89837,7 +89837,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>403404</v>
+        <v>404544</v>
       </c>
       <c r="C142" t="n">
         <v>225357</v>
@@ -89879,7 +89879,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>
@@ -92859,7 +92859,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1080</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="142">
@@ -92869,7 +92869,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>403404</v>
+        <v>404544</v>
       </c>
     </row>
     <row r="144">
@@ -92977,7 +92977,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>28093</v>
+        <v>29233</v>
       </c>
     </row>
     <row r="157">
@@ -92987,7 +92987,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>403404</v>
+        <v>404544</v>
       </c>
     </row>
   </sheetData>
@@ -97831,7 +97831,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>30813</v>
+        <v>31953</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -98152,7 +98152,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>185991</v>
+        <v>187131</v>
       </c>
     </row>
     <row r="14">
@@ -98210,7 +98210,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>436339</v>
+        <v>437479</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98531,7 +98531,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>
@@ -99308,7 +99308,7 @@
         <v>5845</v>
       </c>
       <c r="E13" t="n">
-        <v>78279</v>
+        <v>79419</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99350,7 +99350,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>185991</v>
+        <v>187131</v>
       </c>
     </row>
     <row r="14">
@@ -99369,7 +99369,7 @@
         <v>63157</v>
       </c>
       <c r="E14" t="n">
-        <v>869919</v>
+        <v>871059</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -99411,7 +99411,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>
@@ -100065,7 +100065,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>28093</v>
+        <v>29233</v>
       </c>
       <c r="C13" t="n">
         <v>16384</v>
@@ -100107,7 +100107,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>185991</v>
+        <v>187131</v>
       </c>
     </row>
     <row r="14">
@@ -100117,7 +100117,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>403404</v>
+        <v>404544</v>
       </c>
       <c r="C14" t="n">
         <v>225357</v>
@@ -100159,7 +100159,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2104758</v>
+        <v>2105898</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53959,7 +53959,7 @@
         <v>0</v>
       </c>
       <c r="BP141" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="BQ141" t="n">
         <v>200</v>
@@ -53977,7 +53977,7 @@
         <v>0</v>
       </c>
       <c r="BV141" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>7215</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="142">
@@ -54338,7 +54338,7 @@
         <v>7460</v>
       </c>
       <c r="BP142" t="n">
-        <v>95601</v>
+        <v>95966</v>
       </c>
       <c r="BQ142" t="n">
         <v>22490</v>
@@ -54356,7 +54356,7 @@
         <v>6290</v>
       </c>
       <c r="BV142" t="n">
-        <v>34940</v>
+        <v>35000</v>
       </c>
       <c r="BW142" t="n">
         <v>5175</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>230</v>
+        <v>655</v>
       </c>
       <c r="N9" t="n">
         <v>2220</v>
       </c>
       <c r="O9" t="n">
-        <v>4545</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="10">
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>16384</v>
+        <v>16809</v>
       </c>
       <c r="N10" t="n">
         <v>29233</v>
       </c>
       <c r="O10" t="n">
-        <v>106708</v>
+        <v>107133</v>
       </c>
     </row>
   </sheetData>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>555</v>
+        <v>980</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>7215</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="142">
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>427048</v>
+        <v>427473</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>
@@ -89788,7 +89788,7 @@
         <v>2220</v>
       </c>
       <c r="C141" t="n">
-        <v>230</v>
+        <v>655</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -89827,7 +89827,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>7215</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="142">
@@ -89840,7 +89840,7 @@
         <v>404544</v>
       </c>
       <c r="C142" t="n">
-        <v>225357</v>
+        <v>225782</v>
       </c>
       <c r="D142" t="n">
         <v>59172</v>
@@ -89879,7 +89879,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>
@@ -91305,7 +91305,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>230</v>
+        <v>655</v>
       </c>
     </row>
     <row r="142">
@@ -91315,7 +91315,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>225357</v>
+        <v>225782</v>
       </c>
     </row>
     <row r="144">
@@ -91423,7 +91423,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>16384</v>
+        <v>16809</v>
       </c>
     </row>
     <row r="157">
@@ -91433,7 +91433,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>225357</v>
+        <v>225782</v>
       </c>
     </row>
   </sheetData>
@@ -97981,7 +97981,7 @@
         <v>430</v>
       </c>
       <c r="BP13" t="n">
-        <v>6495</v>
+        <v>6860</v>
       </c>
       <c r="BQ13" t="n">
         <v>1930</v>
@@ -97999,7 +97999,7 @@
         <v>1540</v>
       </c>
       <c r="BV13" t="n">
-        <v>2727</v>
+        <v>2787</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -98152,7 +98152,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>187131</v>
+        <v>187556</v>
       </c>
     </row>
     <row r="14">
@@ -98360,7 +98360,7 @@
         <v>7460</v>
       </c>
       <c r="BP14" t="n">
-        <v>95601</v>
+        <v>95966</v>
       </c>
       <c r="BQ14" t="n">
         <v>22490</v>
@@ -98378,7 +98378,7 @@
         <v>6290</v>
       </c>
       <c r="BV14" t="n">
-        <v>34940</v>
+        <v>35000</v>
       </c>
       <c r="BW14" t="n">
         <v>5175</v>
@@ -98531,7 +98531,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>
@@ -99341,7 +99341,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>32599</v>
+        <v>33024</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99350,7 +99350,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>187131</v>
+        <v>187556</v>
       </c>
     </row>
     <row r="14">
@@ -99402,7 +99402,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>427048</v>
+        <v>427473</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99411,7 +99411,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>
@@ -100068,7 +100068,7 @@
         <v>29233</v>
       </c>
       <c r="C13" t="n">
-        <v>16384</v>
+        <v>16809</v>
       </c>
       <c r="D13" t="n">
         <v>5115</v>
@@ -100107,7 +100107,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>187131</v>
+        <v>187556</v>
       </c>
     </row>
     <row r="14">
@@ -100120,7 +100120,7 @@
         <v>404544</v>
       </c>
       <c r="C14" t="n">
-        <v>225357</v>
+        <v>225782</v>
       </c>
       <c r="D14" t="n">
         <v>59172</v>
@@ -100159,7 +100159,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2105898</v>
+        <v>2106323</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2495</v>
+        <v>2660</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53971,7 +53971,7 @@
         <v>488</v>
       </c>
       <c r="BT141" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BU141" t="n">
         <v>0</v>
@@ -54043,10 +54043,10 @@
         <v>0</v>
       </c>
       <c r="CR141" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="CS141" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="CT141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>7640</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="142">
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>437479</v>
+        <v>437644</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54350,7 +54350,7 @@
         <v>28014</v>
       </c>
       <c r="BT142" t="n">
-        <v>5525</v>
+        <v>5705</v>
       </c>
       <c r="BU142" t="n">
         <v>6290</v>
@@ -54422,10 +54422,10 @@
         <v>12112</v>
       </c>
       <c r="CR142" t="n">
-        <v>65996</v>
+        <v>66191</v>
       </c>
       <c r="CS142" t="n">
-        <v>2715</v>
+        <v>2835</v>
       </c>
       <c r="CT142" t="n">
         <v>1310</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>
@@ -60813,10 +60813,10 @@
         <v>655</v>
       </c>
       <c r="N9" t="n">
-        <v>2220</v>
+        <v>2385</v>
       </c>
       <c r="O9" t="n">
-        <v>4970</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="10">
@@ -60862,10 +60862,10 @@
         <v>16809</v>
       </c>
       <c r="N10" t="n">
-        <v>29233</v>
+        <v>29398</v>
       </c>
       <c r="O10" t="n">
-        <v>107133</v>
+        <v>107298</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>185</v>
       </c>
       <c r="E141" t="n">
-        <v>3600</v>
+        <v>3960</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -71037,7 +71037,7 @@
         <v>70</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I141" t="n">
         <v>1980</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>7640</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63157</v>
       </c>
       <c r="E142" t="n">
-        <v>871059</v>
+        <v>871419</v>
       </c>
       <c r="F142" t="n">
         <v>5937</v>
@@ -71098,7 +71098,7 @@
         <v>34479</v>
       </c>
       <c r="H142" t="n">
-        <v>8240</v>
+        <v>8540</v>
       </c>
       <c r="I142" t="n">
         <v>288720</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>
@@ -89785,7 +89785,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2220</v>
+        <v>2385</v>
       </c>
       <c r="C141" t="n">
         <v>655</v>
@@ -89806,7 +89806,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2670</v>
+        <v>3165</v>
       </c>
       <c r="J141" t="n">
         <v>1025</v>
@@ -89827,7 +89827,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>7640</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="142">
@@ -89837,7 +89837,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404544</v>
+        <v>404709</v>
       </c>
       <c r="C142" t="n">
         <v>225782</v>
@@ -89858,7 +89858,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>763224</v>
+        <v>763719</v>
       </c>
       <c r="J142" t="n">
         <v>221426</v>
@@ -89879,7 +89879,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>
@@ -92859,7 +92859,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2220</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="142">
@@ -92869,7 +92869,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404544</v>
+        <v>404709</v>
       </c>
     </row>
     <row r="144">
@@ -92977,7 +92977,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>29233</v>
+        <v>29398</v>
       </c>
     </row>
     <row r="157">
@@ -92987,7 +92987,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>404544</v>
+        <v>404709</v>
       </c>
     </row>
   </sheetData>
@@ -97831,7 +97831,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>31953</v>
+        <v>32118</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97993,7 +97993,7 @@
         <v>4320</v>
       </c>
       <c r="BT13" t="n">
-        <v>700</v>
+        <v>880</v>
       </c>
       <c r="BU13" t="n">
         <v>1540</v>
@@ -98065,10 +98065,10 @@
         <v>710</v>
       </c>
       <c r="CR13" t="n">
-        <v>5276</v>
+        <v>5471</v>
       </c>
       <c r="CS13" t="n">
-        <v>1260</v>
+        <v>1380</v>
       </c>
       <c r="CT13" t="n">
         <v>125</v>
@@ -98152,7 +98152,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>187556</v>
+        <v>188216</v>
       </c>
     </row>
     <row r="14">
@@ -98210,7 +98210,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>437479</v>
+        <v>437644</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98372,7 +98372,7 @@
         <v>28014</v>
       </c>
       <c r="BT14" t="n">
-        <v>5525</v>
+        <v>5705</v>
       </c>
       <c r="BU14" t="n">
         <v>6290</v>
@@ -98444,10 +98444,10 @@
         <v>12112</v>
       </c>
       <c r="CR14" t="n">
-        <v>65996</v>
+        <v>66191</v>
       </c>
       <c r="CS14" t="n">
-        <v>2715</v>
+        <v>2835</v>
       </c>
       <c r="CT14" t="n">
         <v>1310</v>
@@ -98531,7 +98531,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>
@@ -99308,7 +99308,7 @@
         <v>5845</v>
       </c>
       <c r="E13" t="n">
-        <v>79419</v>
+        <v>79779</v>
       </c>
       <c r="F13" t="n">
         <v>472</v>
@@ -99317,7 +99317,7 @@
         <v>3293</v>
       </c>
       <c r="H13" t="n">
-        <v>1960</v>
+        <v>2260</v>
       </c>
       <c r="I13" t="n">
         <v>23834</v>
@@ -99350,7 +99350,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>187556</v>
+        <v>188216</v>
       </c>
     </row>
     <row r="14">
@@ -99369,7 +99369,7 @@
         <v>63157</v>
       </c>
       <c r="E14" t="n">
-        <v>871059</v>
+        <v>871419</v>
       </c>
       <c r="F14" t="n">
         <v>5937</v>
@@ -99378,7 +99378,7 @@
         <v>34479</v>
       </c>
       <c r="H14" t="n">
-        <v>8240</v>
+        <v>8540</v>
       </c>
       <c r="I14" t="n">
         <v>288720</v>
@@ -99411,7 +99411,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>
@@ -100065,7 +100065,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>29233</v>
+        <v>29398</v>
       </c>
       <c r="C13" t="n">
         <v>16809</v>
@@ -100086,7 +100086,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>80423</v>
+        <v>80918</v>
       </c>
       <c r="J13" t="n">
         <v>17355</v>
@@ -100107,7 +100107,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>187556</v>
+        <v>188216</v>
       </c>
     </row>
     <row r="14">
@@ -100117,7 +100117,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>404544</v>
+        <v>404709</v>
       </c>
       <c r="C14" t="n">
         <v>225782</v>
@@ -100138,7 +100138,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>763224</v>
+        <v>763719</v>
       </c>
       <c r="J14" t="n">
         <v>221426</v>
@@ -100159,7 +100159,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2106323</v>
+        <v>2106983</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53770,7 +53770,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>130</v>
+        <v>507</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2660</v>
+        <v>2715</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53827,7 +53827,7 @@
         <v>70</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
@@ -53836,7 +53836,7 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB141" t="n">
         <v>55</v>
@@ -53902,7 +53902,7 @@
         <v>140</v>
       </c>
       <c r="AW141" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AX141" t="n">
         <v>0</v>
@@ -54064,10 +54064,10 @@
         <v>0</v>
       </c>
       <c r="CY141" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="CZ141" t="n">
-        <v>1025</v>
+        <v>2365</v>
       </c>
       <c r="DA141" t="n">
         <v>0</v>
@@ -54085,13 +54085,13 @@
         <v>0</v>
       </c>
       <c r="DF141" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="DG141" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="DH141" t="n">
-        <v>285</v>
+        <v>655</v>
       </c>
       <c r="DI141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>0</v>
       </c>
       <c r="DU141" t="n">
-        <v>8300</v>
+        <v>11612</v>
       </c>
     </row>
     <row r="142">
@@ -54149,7 +54149,7 @@
         <v>150</v>
       </c>
       <c r="E142" t="n">
-        <v>72343</v>
+        <v>72720</v>
       </c>
       <c r="F142" t="n">
         <v>500</v>
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>437644</v>
+        <v>437699</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54206,7 +54206,7 @@
         <v>24629</v>
       </c>
       <c r="X142" t="n">
-        <v>4820</v>
+        <v>4890</v>
       </c>
       <c r="Y142" t="n">
         <v>2945</v>
@@ -54215,7 +54215,7 @@
         <v>485</v>
       </c>
       <c r="AA142" t="n">
-        <v>9239</v>
+        <v>9319</v>
       </c>
       <c r="AB142" t="n">
         <v>265</v>
@@ -54281,7 +54281,7 @@
         <v>7079</v>
       </c>
       <c r="AW142" t="n">
-        <v>5655</v>
+        <v>5875</v>
       </c>
       <c r="AX142" t="n">
         <v>460</v>
@@ -54443,10 +54443,10 @@
         <v>18892</v>
       </c>
       <c r="CY142" t="n">
-        <v>13884</v>
+        <v>13984</v>
       </c>
       <c r="CZ142" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
       <c r="DA142" t="n">
         <v>1125</v>
@@ -54464,13 +54464,13 @@
         <v>21081</v>
       </c>
       <c r="DF142" t="n">
-        <v>38189</v>
+        <v>38674</v>
       </c>
       <c r="DG142" t="n">
-        <v>24118</v>
+        <v>24333</v>
       </c>
       <c r="DH142" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
       <c r="DI142" t="n">
         <v>1240</v>
@@ -54509,7 +54509,7 @@
         <v>27881</v>
       </c>
       <c r="DU142" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>
@@ -60777,13 +60777,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1025</v>
+        <v>2365</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>655</v>
+        <v>1032</v>
       </c>
       <c r="N9" t="n">
-        <v>2385</v>
+        <v>2440</v>
       </c>
       <c r="O9" t="n">
-        <v>5135</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="10">
@@ -60826,13 +60826,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17355</v>
+        <v>18695</v>
       </c>
       <c r="C10" t="n">
-        <v>6545</v>
+        <v>6915</v>
       </c>
       <c r="D10" t="n">
-        <v>5965</v>
+        <v>6665</v>
       </c>
       <c r="E10" t="n">
         <v>4886</v>
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>16809</v>
+        <v>17186</v>
       </c>
       <c r="N10" t="n">
-        <v>29398</v>
+        <v>29453</v>
       </c>
       <c r="O10" t="n">
-        <v>107298</v>
+        <v>110140</v>
       </c>
     </row>
   </sheetData>
@@ -62291,7 +62291,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1025</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="142">
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
     </row>
     <row r="144">
@@ -62409,7 +62409,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>17355</v>
+        <v>18695</v>
       </c>
     </row>
     <row r="157">
@@ -62419,7 +62419,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
     </row>
   </sheetData>
@@ -71025,13 +71025,13 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>185</v>
+        <v>435</v>
       </c>
       <c r="E141" t="n">
-        <v>3960</v>
+        <v>4015</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="G141" t="n">
         <v>70</v>
@@ -71040,7 +71040,7 @@
         <v>300</v>
       </c>
       <c r="I141" t="n">
-        <v>1980</v>
+        <v>3320</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>980</v>
+        <v>2427</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>8300</v>
+        <v>11612</v>
       </c>
     </row>
     <row r="142">
@@ -71086,13 +71086,13 @@
         <v>17804</v>
       </c>
       <c r="D142" t="n">
-        <v>63157</v>
+        <v>63407</v>
       </c>
       <c r="E142" t="n">
-        <v>871419</v>
+        <v>871474</v>
       </c>
       <c r="F142" t="n">
-        <v>5937</v>
+        <v>6157</v>
       </c>
       <c r="G142" t="n">
         <v>34479</v>
@@ -71101,7 +71101,7 @@
         <v>8540</v>
       </c>
       <c r="I142" t="n">
-        <v>288720</v>
+        <v>290060</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>427473</v>
+        <v>428920</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>89585</v>
       </c>
       <c r="S142" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>
@@ -72557,7 +72557,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>285</v>
+        <v>655</v>
       </c>
     </row>
     <row r="142">
@@ -72567,7 +72567,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
     </row>
     <row r="144">
@@ -72675,7 +72675,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>6545</v>
+        <v>6915</v>
       </c>
     </row>
     <row r="157">
@@ -72685,7 +72685,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
     </row>
   </sheetData>
@@ -72699,7 +72699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73987,129 +73987,139 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>62307</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="B130" t="n">
+        <v>63007</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B132" t="n">
-        <v>337</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B133" t="n">
-        <v>2431</v>
+        <v>337</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B134" t="n">
-        <v>2574</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B135" t="n">
-        <v>2985</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B136" t="n">
-        <v>4530</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B137" t="n">
-        <v>5425</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B138" t="n">
-        <v>6245</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B139" t="n">
-        <v>6030</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B140" t="n">
-        <v>7580</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B141" t="n">
-        <v>8604</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B142" t="n">
-        <v>9601</v>
+        <v>8604</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B143" t="n">
+        <v>9601</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
         <v>2026</v>
       </c>
-      <c r="B143" t="n">
-        <v>5965</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="B144" t="n">
+        <v>6665</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>62307</v>
+      <c r="B145" t="n">
+        <v>63007</v>
       </c>
     </row>
   </sheetData>
@@ -89785,10 +89795,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2385</v>
+        <v>2440</v>
       </c>
       <c r="C141" t="n">
-        <v>655</v>
+        <v>1032</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -89806,19 +89816,19 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>3165</v>
+        <v>3635</v>
       </c>
       <c r="J141" t="n">
-        <v>1025</v>
+        <v>2365</v>
       </c>
       <c r="K141" t="n">
         <v>275</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M141" t="n">
-        <v>285</v>
+        <v>655</v>
       </c>
       <c r="N141" t="n">
         <v>510</v>
@@ -89827,7 +89837,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>8300</v>
+        <v>11612</v>
       </c>
     </row>
     <row r="142">
@@ -89837,10 +89847,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404709</v>
+        <v>404764</v>
       </c>
       <c r="C142" t="n">
-        <v>225782</v>
+        <v>226159</v>
       </c>
       <c r="D142" t="n">
         <v>59172</v>
@@ -89858,19 +89868,19 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>763719</v>
+        <v>764189</v>
       </c>
       <c r="J142" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
       <c r="K142" t="n">
         <v>32935</v>
       </c>
       <c r="L142" t="n">
-        <v>62307</v>
+        <v>63007</v>
       </c>
       <c r="M142" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
       <c r="N142" t="n">
         <v>72207</v>
@@ -89879,7 +89889,7 @@
         <v>49527</v>
       </c>
       <c r="P142" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>
@@ -91305,7 +91315,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>655</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="142">
@@ -91315,7 +91325,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>225782</v>
+        <v>226159</v>
       </c>
     </row>
     <row r="144">
@@ -91423,7 +91433,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>16809</v>
+        <v>17186</v>
       </c>
     </row>
     <row r="157">
@@ -91433,7 +91443,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>225782</v>
+        <v>226159</v>
       </c>
     </row>
   </sheetData>
@@ -92859,7 +92869,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2385</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="142">
@@ -92869,7 +92879,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404709</v>
+        <v>404764</v>
       </c>
     </row>
     <row r="144">
@@ -92977,7 +92987,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>29398</v>
+        <v>29453</v>
       </c>
     </row>
     <row r="157">
@@ -92987,7 +92997,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>404709</v>
+        <v>404764</v>
       </c>
     </row>
   </sheetData>
@@ -97792,7 +97802,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5662</v>
+        <v>6039</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97831,7 +97841,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>32118</v>
+        <v>32173</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97849,7 +97859,7 @@
         <v>2640</v>
       </c>
       <c r="X13" t="n">
-        <v>830</v>
+        <v>900</v>
       </c>
       <c r="Y13" t="n">
         <v>95</v>
@@ -97858,7 +97868,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>925</v>
+        <v>1005</v>
       </c>
       <c r="AB13" t="n">
         <v>265</v>
@@ -97924,7 +97934,7 @@
         <v>580</v>
       </c>
       <c r="AW13" t="n">
-        <v>355</v>
+        <v>575</v>
       </c>
       <c r="AX13" t="n">
         <v>50</v>
@@ -98086,10 +98096,10 @@
         <v>2590</v>
       </c>
       <c r="CY13" t="n">
-        <v>1030</v>
+        <v>1130</v>
       </c>
       <c r="CZ13" t="n">
-        <v>17355</v>
+        <v>18695</v>
       </c>
       <c r="DA13" t="n">
         <v>125</v>
@@ -98107,13 +98117,13 @@
         <v>1570</v>
       </c>
       <c r="DF13" t="n">
-        <v>3515</v>
+        <v>4000</v>
       </c>
       <c r="DG13" t="n">
-        <v>2450</v>
+        <v>2665</v>
       </c>
       <c r="DH13" t="n">
-        <v>6545</v>
+        <v>6915</v>
       </c>
       <c r="DI13" t="n">
         <v>420</v>
@@ -98152,7 +98162,7 @@
         <v>2015</v>
       </c>
       <c r="DU13" t="n">
-        <v>188216</v>
+        <v>191528</v>
       </c>
     </row>
     <row r="14">
@@ -98171,7 +98181,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72343</v>
+        <v>72720</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98210,7 +98220,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>437644</v>
+        <v>437699</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98228,7 +98238,7 @@
         <v>24629</v>
       </c>
       <c r="X14" t="n">
-        <v>4820</v>
+        <v>4890</v>
       </c>
       <c r="Y14" t="n">
         <v>2945</v>
@@ -98237,7 +98247,7 @@
         <v>485</v>
       </c>
       <c r="AA14" t="n">
-        <v>9239</v>
+        <v>9319</v>
       </c>
       <c r="AB14" t="n">
         <v>265</v>
@@ -98303,7 +98313,7 @@
         <v>7079</v>
       </c>
       <c r="AW14" t="n">
-        <v>5655</v>
+        <v>5875</v>
       </c>
       <c r="AX14" t="n">
         <v>460</v>
@@ -98465,10 +98475,10 @@
         <v>18892</v>
       </c>
       <c r="CY14" t="n">
-        <v>13884</v>
+        <v>13984</v>
       </c>
       <c r="CZ14" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
       <c r="DA14" t="n">
         <v>1125</v>
@@ -98486,13 +98496,13 @@
         <v>21081</v>
       </c>
       <c r="DF14" t="n">
-        <v>38189</v>
+        <v>38674</v>
       </c>
       <c r="DG14" t="n">
-        <v>24118</v>
+        <v>24333</v>
       </c>
       <c r="DH14" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
       <c r="DI14" t="n">
         <v>1240</v>
@@ -98531,7 +98541,7 @@
         <v>27881</v>
       </c>
       <c r="DU14" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>
@@ -99305,13 +99315,13 @@
         <v>2550</v>
       </c>
       <c r="D13" t="n">
-        <v>5845</v>
+        <v>6095</v>
       </c>
       <c r="E13" t="n">
-        <v>79779</v>
+        <v>79834</v>
       </c>
       <c r="F13" t="n">
-        <v>472</v>
+        <v>692</v>
       </c>
       <c r="G13" t="n">
         <v>3293</v>
@@ -99320,7 +99330,7 @@
         <v>2260</v>
       </c>
       <c r="I13" t="n">
-        <v>23834</v>
+        <v>25174</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
@@ -99341,7 +99351,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>33024</v>
+        <v>34471</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99350,7 +99360,7 @@
         <v>10252</v>
       </c>
       <c r="S13" t="n">
-        <v>188216</v>
+        <v>191528</v>
       </c>
     </row>
     <row r="14">
@@ -99366,13 +99376,13 @@
         <v>17804</v>
       </c>
       <c r="D14" t="n">
-        <v>63157</v>
+        <v>63407</v>
       </c>
       <c r="E14" t="n">
-        <v>871419</v>
+        <v>871474</v>
       </c>
       <c r="F14" t="n">
-        <v>5937</v>
+        <v>6157</v>
       </c>
       <c r="G14" t="n">
         <v>34479</v>
@@ -99381,7 +99391,7 @@
         <v>8540</v>
       </c>
       <c r="I14" t="n">
-        <v>288720</v>
+        <v>290060</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
@@ -99402,7 +99412,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>427473</v>
+        <v>428920</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99411,7 +99421,7 @@
         <v>89585</v>
       </c>
       <c r="S14" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>
@@ -100065,10 +100075,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>29398</v>
+        <v>29453</v>
       </c>
       <c r="C13" t="n">
-        <v>16809</v>
+        <v>17186</v>
       </c>
       <c r="D13" t="n">
         <v>5115</v>
@@ -100086,19 +100096,19 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>80918</v>
+        <v>81388</v>
       </c>
       <c r="J13" t="n">
-        <v>17355</v>
+        <v>18695</v>
       </c>
       <c r="K13" t="n">
         <v>2720</v>
       </c>
       <c r="L13" t="n">
-        <v>5965</v>
+        <v>6665</v>
       </c>
       <c r="M13" t="n">
-        <v>6545</v>
+        <v>6915</v>
       </c>
       <c r="N13" t="n">
         <v>6425</v>
@@ -100107,7 +100117,7 @@
         <v>4555</v>
       </c>
       <c r="P13" t="n">
-        <v>188216</v>
+        <v>191528</v>
       </c>
     </row>
     <row r="14">
@@ -100117,10 +100127,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>404709</v>
+        <v>404764</v>
       </c>
       <c r="C14" t="n">
-        <v>225782</v>
+        <v>226159</v>
       </c>
       <c r="D14" t="n">
         <v>59172</v>
@@ -100138,19 +100148,19 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>763719</v>
+        <v>764189</v>
       </c>
       <c r="J14" t="n">
-        <v>221426</v>
+        <v>222766</v>
       </c>
       <c r="K14" t="n">
         <v>32935</v>
       </c>
       <c r="L14" t="n">
-        <v>62307</v>
+        <v>63007</v>
       </c>
       <c r="M14" t="n">
-        <v>101048</v>
+        <v>101418</v>
       </c>
       <c r="N14" t="n">
         <v>72207</v>
@@ -100159,7 +100169,7 @@
         <v>49527</v>
       </c>
       <c r="P14" t="n">
-        <v>2106983</v>
+        <v>2110295</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53770,7 +53770,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>507</v>
+        <v>637</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -53788,7 +53788,7 @@
         <v>100</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L141" t="n">
         <v>250</v>
@@ -53908,7 +53908,7 @@
         <v>0</v>
       </c>
       <c r="AY141" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AZ141" t="n">
         <v>0</v>
@@ -53935,10 +53935,10 @@
         <v>0</v>
       </c>
       <c r="BH141" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="BI141" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="BJ141" t="n">
         <v>0</v>
@@ -53968,13 +53968,13 @@
         <v>280</v>
       </c>
       <c r="BS141" t="n">
-        <v>488</v>
+        <v>678</v>
       </c>
       <c r="BT141" t="n">
         <v>180</v>
       </c>
       <c r="BU141" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="BV141" t="n">
         <v>60</v>
@@ -54007,7 +54007,7 @@
         <v>0</v>
       </c>
       <c r="CF141" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="CG141" t="n">
         <v>0</v>
@@ -54103,7 +54103,7 @@
         <v>0</v>
       </c>
       <c r="DL141" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="DM141" t="n">
         <v>0</v>
@@ -54127,10 +54127,10 @@
         <v>55</v>
       </c>
       <c r="DT141" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>11612</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="142">
@@ -54149,7 +54149,7 @@
         <v>150</v>
       </c>
       <c r="E142" t="n">
-        <v>72720</v>
+        <v>72850</v>
       </c>
       <c r="F142" t="n">
         <v>500</v>
@@ -54167,7 +54167,7 @@
         <v>22473</v>
       </c>
       <c r="K142" t="n">
-        <v>17305</v>
+        <v>17405</v>
       </c>
       <c r="L142" t="n">
         <v>6040</v>
@@ -54287,7 +54287,7 @@
         <v>460</v>
       </c>
       <c r="AY142" t="n">
-        <v>41302</v>
+        <v>41367</v>
       </c>
       <c r="AZ142" t="n">
         <v>6666</v>
@@ -54314,10 +54314,10 @@
         <v>1190</v>
       </c>
       <c r="BH142" t="n">
-        <v>13569</v>
+        <v>13909</v>
       </c>
       <c r="BI142" t="n">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="BJ142" t="n">
         <v>660</v>
@@ -54347,13 +54347,13 @@
         <v>13710</v>
       </c>
       <c r="BS142" t="n">
-        <v>28014</v>
+        <v>28204</v>
       </c>
       <c r="BT142" t="n">
         <v>5705</v>
       </c>
       <c r="BU142" t="n">
-        <v>6290</v>
+        <v>6605</v>
       </c>
       <c r="BV142" t="n">
         <v>35000</v>
@@ -54386,7 +54386,7 @@
         <v>145</v>
       </c>
       <c r="CF142" t="n">
-        <v>21646</v>
+        <v>22031</v>
       </c>
       <c r="CG142" t="n">
         <v>3692</v>
@@ -54482,7 +54482,7 @@
         <v>10780</v>
       </c>
       <c r="DL142" t="n">
-        <v>18415</v>
+        <v>18616</v>
       </c>
       <c r="DM142" t="n">
         <v>580</v>
@@ -54506,10 +54506,10 @@
         <v>4982</v>
       </c>
       <c r="DT142" t="n">
-        <v>27881</v>
+        <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>
@@ -60789,7 +60789,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G9" t="n">
         <v>510</v>
@@ -60798,25 +60798,25 @@
         <v>275</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1032</v>
+        <v>1162</v>
       </c>
       <c r="N9" t="n">
         <v>2440</v>
       </c>
       <c r="O9" t="n">
-        <v>7977</v>
+        <v>9517</v>
       </c>
     </row>
     <row r="10">
@@ -60838,7 +60838,7 @@
         <v>4886</v>
       </c>
       <c r="F10" t="n">
-        <v>5115</v>
+        <v>5495</v>
       </c>
       <c r="G10" t="n">
         <v>6425</v>
@@ -60847,25 +60847,25 @@
         <v>2720</v>
       </c>
       <c r="I10" t="n">
-        <v>4555</v>
+        <v>5210</v>
       </c>
       <c r="J10" t="n">
         <v>2880</v>
       </c>
       <c r="K10" t="n">
-        <v>1955</v>
+        <v>2330</v>
       </c>
       <c r="L10" t="n">
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>17186</v>
+        <v>17316</v>
       </c>
       <c r="N10" t="n">
         <v>29453</v>
       </c>
       <c r="O10" t="n">
-        <v>110140</v>
+        <v>111680</v>
       </c>
     </row>
   </sheetData>
@@ -71022,7 +71022,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D141" t="n">
         <v>435</v>
@@ -71046,10 +71046,10 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>825</v>
+        <v>1395</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -71061,16 +71061,16 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2427</v>
+        <v>2557</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="S141" t="n">
-        <v>11612</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="142">
@@ -71083,7 +71083,7 @@
         <v>79117</v>
       </c>
       <c r="C142" t="n">
-        <v>17804</v>
+        <v>18179</v>
       </c>
       <c r="D142" t="n">
         <v>63407</v>
@@ -71107,10 +71107,10 @@
         <v>5457</v>
       </c>
       <c r="K142" t="n">
-        <v>114614</v>
+        <v>115184</v>
       </c>
       <c r="L142" t="n">
-        <v>33131</v>
+        <v>33332</v>
       </c>
       <c r="M142" t="n">
         <v>5908</v>
@@ -71122,16 +71122,16 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>428920</v>
+        <v>429050</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
       </c>
       <c r="R142" t="n">
-        <v>89585</v>
+        <v>90340</v>
       </c>
       <c r="S142" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>
@@ -75537,7 +75537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76675,129 +76675,139 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>59172</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="B115" t="n">
+        <v>59552</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B117" t="n">
-        <v>4297</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B118" t="n">
-        <v>3945</v>
+        <v>4297</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B119" t="n">
-        <v>4200</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B120" t="n">
-        <v>4280</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B121" t="n">
-        <v>6480</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B122" t="n">
-        <v>2685</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B123" t="n">
-        <v>3115</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B124" t="n">
-        <v>4745</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B125" t="n">
-        <v>5860</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B126" t="n">
-        <v>6490</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B127" t="n">
-        <v>7960</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B128" t="n">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
         <v>2026</v>
       </c>
-      <c r="B128" t="n">
-        <v>5115</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="B129" t="n">
+        <v>5495</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>59172</v>
+      <c r="B130" t="n">
+        <v>59552</v>
       </c>
     </row>
   </sheetData>
@@ -79255,7 +79265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B149"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80593,129 +80603,139 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>49527</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="B135" t="n">
+        <v>50182</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B137" t="n">
-        <v>1867</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B138" t="n">
-        <v>2625</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B139" t="n">
-        <v>3270</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B140" t="n">
-        <v>3960</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B141" t="n">
-        <v>4420</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B142" t="n">
-        <v>3140</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B143" t="n">
-        <v>3010</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B144" t="n">
-        <v>3854</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B145" t="n">
-        <v>5282</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B146" t="n">
-        <v>6515</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B147" t="n">
-        <v>7029</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B148" t="n">
+        <v>7029</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
         <v>2026</v>
       </c>
-      <c r="B148" t="n">
-        <v>4555</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="B149" t="n">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>49527</v>
+      <c r="B150" t="n">
+        <v>50182</v>
       </c>
     </row>
   </sheetData>
@@ -81357,7 +81377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82115,113 +82135,123 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>14604</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="B77" t="n">
+        <v>14979</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B79" t="n">
-        <v>1085</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B80" t="n">
-        <v>1525</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B81" t="n">
-        <v>1000</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B82" t="n">
-        <v>730</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B83" t="n">
-        <v>910</v>
+        <v>730</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B84" t="n">
-        <v>635</v>
+        <v>910</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B85" t="n">
-        <v>2487</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B86" t="n">
-        <v>2275</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B87" t="n">
-        <v>2002</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>2026</v>
       </c>
-      <c r="B88" t="n">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="B89" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>14604</v>
+      <c r="B90" t="n">
+        <v>14979</v>
       </c>
     </row>
   </sheetData>
@@ -89798,13 +89828,13 @@
         <v>2440</v>
       </c>
       <c r="C141" t="n">
-        <v>1032</v>
+        <v>1162</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -89816,7 +89846,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>3635</v>
+        <v>4126</v>
       </c>
       <c r="J141" t="n">
         <v>2365</v>
@@ -89834,10 +89864,10 @@
         <v>510</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>11612</v>
+        <v>13643</v>
       </c>
     </row>
     <row r="142">
@@ -89850,13 +89880,13 @@
         <v>404764</v>
       </c>
       <c r="C142" t="n">
-        <v>226159</v>
+        <v>226289</v>
       </c>
       <c r="D142" t="n">
-        <v>59172</v>
+        <v>59552</v>
       </c>
       <c r="E142" t="n">
-        <v>14604</v>
+        <v>14979</v>
       </c>
       <c r="F142" t="n">
         <v>69197</v>
@@ -89868,7 +89898,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>764189</v>
+        <v>764680</v>
       </c>
       <c r="J142" t="n">
         <v>222766</v>
@@ -89886,10 +89916,10 @@
         <v>72207</v>
       </c>
       <c r="O142" t="n">
-        <v>49527</v>
+        <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>
@@ -91315,7 +91345,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1032</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="142">
@@ -91325,7 +91355,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>226159</v>
+        <v>226289</v>
       </c>
     </row>
     <row r="144">
@@ -91433,7 +91463,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>17186</v>
+        <v>17316</v>
       </c>
     </row>
     <row r="157">
@@ -91443,7 +91473,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>226159</v>
+        <v>226289</v>
       </c>
     </row>
   </sheetData>
@@ -97802,7 +97832,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6039</v>
+        <v>6169</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97820,7 +97850,7 @@
         <v>1500</v>
       </c>
       <c r="K13" t="n">
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="L13" t="n">
         <v>1075</v>
@@ -97940,7 +97970,7 @@
         <v>50</v>
       </c>
       <c r="AY13" t="n">
-        <v>2870</v>
+        <v>2935</v>
       </c>
       <c r="AZ13" t="n">
         <v>460</v>
@@ -97967,10 +97997,10 @@
         <v>85</v>
       </c>
       <c r="BH13" t="n">
-        <v>1605</v>
+        <v>1945</v>
       </c>
       <c r="BI13" t="n">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="BJ13" t="n">
         <v>40</v>
@@ -98000,13 +98030,13 @@
         <v>1342</v>
       </c>
       <c r="BS13" t="n">
-        <v>4320</v>
+        <v>4510</v>
       </c>
       <c r="BT13" t="n">
         <v>880</v>
       </c>
       <c r="BU13" t="n">
-        <v>1540</v>
+        <v>1855</v>
       </c>
       <c r="BV13" t="n">
         <v>2787</v>
@@ -98039,7 +98069,7 @@
         <v>30</v>
       </c>
       <c r="CF13" t="n">
-        <v>2540</v>
+        <v>2925</v>
       </c>
       <c r="CG13" t="n">
         <v>517</v>
@@ -98135,7 +98165,7 @@
         <v>640</v>
       </c>
       <c r="DL13" t="n">
-        <v>2102</v>
+        <v>2303</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -98159,10 +98189,10 @@
         <v>330</v>
       </c>
       <c r="DT13" t="n">
-        <v>2015</v>
+        <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>191528</v>
+        <v>193559</v>
       </c>
     </row>
     <row r="14">
@@ -98181,7 +98211,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72720</v>
+        <v>72850</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98199,7 +98229,7 @@
         <v>22473</v>
       </c>
       <c r="K14" t="n">
-        <v>17305</v>
+        <v>17405</v>
       </c>
       <c r="L14" t="n">
         <v>6040</v>
@@ -98319,7 +98349,7 @@
         <v>460</v>
       </c>
       <c r="AY14" t="n">
-        <v>41302</v>
+        <v>41367</v>
       </c>
       <c r="AZ14" t="n">
         <v>6666</v>
@@ -98346,10 +98376,10 @@
         <v>1190</v>
       </c>
       <c r="BH14" t="n">
-        <v>13569</v>
+        <v>13909</v>
       </c>
       <c r="BI14" t="n">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="BJ14" t="n">
         <v>660</v>
@@ -98379,13 +98409,13 @@
         <v>13710</v>
       </c>
       <c r="BS14" t="n">
-        <v>28014</v>
+        <v>28204</v>
       </c>
       <c r="BT14" t="n">
         <v>5705</v>
       </c>
       <c r="BU14" t="n">
-        <v>6290</v>
+        <v>6605</v>
       </c>
       <c r="BV14" t="n">
         <v>35000</v>
@@ -98418,7 +98448,7 @@
         <v>145</v>
       </c>
       <c r="CF14" t="n">
-        <v>21646</v>
+        <v>22031</v>
       </c>
       <c r="CG14" t="n">
         <v>3692</v>
@@ -98514,7 +98544,7 @@
         <v>10780</v>
       </c>
       <c r="DL14" t="n">
-        <v>18415</v>
+        <v>18616</v>
       </c>
       <c r="DM14" t="n">
         <v>580</v>
@@ -98538,10 +98568,10 @@
         <v>4982</v>
       </c>
       <c r="DT14" t="n">
-        <v>27881</v>
+        <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>
@@ -99312,7 +99342,7 @@
         <v>6076</v>
       </c>
       <c r="C13" t="n">
-        <v>2550</v>
+        <v>2925</v>
       </c>
       <c r="D13" t="n">
         <v>6095</v>
@@ -99336,10 +99366,10 @@
         <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>12121</v>
+        <v>12691</v>
       </c>
       <c r="L13" t="n">
-        <v>2493</v>
+        <v>2694</v>
       </c>
       <c r="M13" t="n">
         <v>995</v>
@@ -99351,16 +99381,16 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>34471</v>
+        <v>34601</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
       </c>
       <c r="R13" t="n">
-        <v>10252</v>
+        <v>11007</v>
       </c>
       <c r="S13" t="n">
-        <v>191528</v>
+        <v>193559</v>
       </c>
     </row>
     <row r="14">
@@ -99373,7 +99403,7 @@
         <v>79117</v>
       </c>
       <c r="C14" t="n">
-        <v>17804</v>
+        <v>18179</v>
       </c>
       <c r="D14" t="n">
         <v>63407</v>
@@ -99397,10 +99427,10 @@
         <v>5457</v>
       </c>
       <c r="K14" t="n">
-        <v>114614</v>
+        <v>115184</v>
       </c>
       <c r="L14" t="n">
-        <v>33131</v>
+        <v>33332</v>
       </c>
       <c r="M14" t="n">
         <v>5908</v>
@@ -99412,16 +99442,16 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>428920</v>
+        <v>429050</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
       </c>
       <c r="R14" t="n">
-        <v>89585</v>
+        <v>90340</v>
       </c>
       <c r="S14" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>
@@ -100078,13 +100108,13 @@
         <v>29453</v>
       </c>
       <c r="C13" t="n">
-        <v>17186</v>
+        <v>17316</v>
       </c>
       <c r="D13" t="n">
-        <v>5115</v>
+        <v>5495</v>
       </c>
       <c r="E13" t="n">
-        <v>1955</v>
+        <v>2330</v>
       </c>
       <c r="F13" t="n">
         <v>4886</v>
@@ -100096,7 +100126,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>81388</v>
+        <v>81879</v>
       </c>
       <c r="J13" t="n">
         <v>18695</v>
@@ -100114,10 +100144,10 @@
         <v>6425</v>
       </c>
       <c r="O13" t="n">
-        <v>4555</v>
+        <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>191528</v>
+        <v>193559</v>
       </c>
     </row>
     <row r="14">
@@ -100130,13 +100160,13 @@
         <v>404764</v>
       </c>
       <c r="C14" t="n">
-        <v>226159</v>
+        <v>226289</v>
       </c>
       <c r="D14" t="n">
-        <v>59172</v>
+        <v>59552</v>
       </c>
       <c r="E14" t="n">
-        <v>14604</v>
+        <v>14979</v>
       </c>
       <c r="F14" t="n">
         <v>69197</v>
@@ -100148,7 +100178,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>764189</v>
+        <v>764680</v>
       </c>
       <c r="J14" t="n">
         <v>222766</v>
@@ -100166,10 +100196,10 @@
         <v>72207</v>
       </c>
       <c r="O14" t="n">
-        <v>49527</v>
+        <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2110295</v>
+        <v>2112326</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53824,7 +53824,7 @@
         <v>0</v>
       </c>
       <c r="W141" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="X141" t="n">
         <v>70</v>
@@ -53869,7 +53869,7 @@
         <v>50</v>
       </c>
       <c r="AL141" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="AM141" t="n">
         <v>0</v>
@@ -54043,7 +54043,7 @@
         <v>0</v>
       </c>
       <c r="CR141" t="n">
-        <v>195</v>
+        <v>550</v>
       </c>
       <c r="CS141" t="n">
         <v>120</v>
@@ -54115,7 +54115,7 @@
         <v>0</v>
       </c>
       <c r="DP141" t="n">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="DQ141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>13643</v>
+        <v>14650</v>
       </c>
     </row>
     <row r="142">
@@ -54203,7 +54203,7 @@
         <v>14436</v>
       </c>
       <c r="W142" t="n">
-        <v>24629</v>
+        <v>24789</v>
       </c>
       <c r="X142" t="n">
         <v>4890</v>
@@ -54248,7 +54248,7 @@
         <v>477</v>
       </c>
       <c r="AL142" t="n">
-        <v>51493</v>
+        <v>51568</v>
       </c>
       <c r="AM142" t="n">
         <v>4755</v>
@@ -54422,7 +54422,7 @@
         <v>12112</v>
       </c>
       <c r="CR142" t="n">
-        <v>66191</v>
+        <v>66546</v>
       </c>
       <c r="CS142" t="n">
         <v>2835</v>
@@ -54494,7 +54494,7 @@
         <v>7925</v>
       </c>
       <c r="DP142" t="n">
-        <v>58683</v>
+        <v>59100</v>
       </c>
       <c r="DQ142" t="n">
         <v>1450</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>435</v>
       </c>
       <c r="E141" t="n">
-        <v>4015</v>
+        <v>5022</v>
       </c>
       <c r="F141" t="n">
         <v>220</v>
@@ -71070,7 +71070,7 @@
         <v>755</v>
       </c>
       <c r="S141" t="n">
-        <v>13643</v>
+        <v>14650</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63407</v>
       </c>
       <c r="E142" t="n">
-        <v>871474</v>
+        <v>872481</v>
       </c>
       <c r="F142" t="n">
         <v>6157</v>
@@ -71131,7 +71131,7 @@
         <v>90340</v>
       </c>
       <c r="S142" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>
@@ -89846,7 +89846,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>4126</v>
+        <v>5133</v>
       </c>
       <c r="J141" t="n">
         <v>2365</v>
@@ -89867,7 +89867,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>13643</v>
+        <v>14650</v>
       </c>
     </row>
     <row r="142">
@@ -89898,7 +89898,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>764680</v>
+        <v>765687</v>
       </c>
       <c r="J142" t="n">
         <v>222766</v>
@@ -89919,7 +89919,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>
@@ -97886,7 +97886,7 @@
         <v>111</v>
       </c>
       <c r="W13" t="n">
-        <v>2640</v>
+        <v>2800</v>
       </c>
       <c r="X13" t="n">
         <v>900</v>
@@ -97931,7 +97931,7 @@
         <v>105</v>
       </c>
       <c r="AL13" t="n">
-        <v>2952</v>
+        <v>3027</v>
       </c>
       <c r="AM13" t="n">
         <v>165</v>
@@ -98105,7 +98105,7 @@
         <v>710</v>
       </c>
       <c r="CR13" t="n">
-        <v>5471</v>
+        <v>5826</v>
       </c>
       <c r="CS13" t="n">
         <v>1380</v>
@@ -98177,7 +98177,7 @@
         <v>595</v>
       </c>
       <c r="DP13" t="n">
-        <v>5394</v>
+        <v>5811</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
@@ -98192,7 +98192,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>193559</v>
+        <v>194566</v>
       </c>
     </row>
     <row r="14">
@@ -98265,7 +98265,7 @@
         <v>14436</v>
       </c>
       <c r="W14" t="n">
-        <v>24629</v>
+        <v>24789</v>
       </c>
       <c r="X14" t="n">
         <v>4890</v>
@@ -98310,7 +98310,7 @@
         <v>477</v>
       </c>
       <c r="AL14" t="n">
-        <v>51493</v>
+        <v>51568</v>
       </c>
       <c r="AM14" t="n">
         <v>4755</v>
@@ -98484,7 +98484,7 @@
         <v>12112</v>
       </c>
       <c r="CR14" t="n">
-        <v>66191</v>
+        <v>66546</v>
       </c>
       <c r="CS14" t="n">
         <v>2835</v>
@@ -98556,7 +98556,7 @@
         <v>7925</v>
       </c>
       <c r="DP14" t="n">
-        <v>58683</v>
+        <v>59100</v>
       </c>
       <c r="DQ14" t="n">
         <v>1450</v>
@@ -98571,7 +98571,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>
@@ -99348,7 +99348,7 @@
         <v>6095</v>
       </c>
       <c r="E13" t="n">
-        <v>79834</v>
+        <v>80841</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99390,7 +99390,7 @@
         <v>11007</v>
       </c>
       <c r="S13" t="n">
-        <v>193559</v>
+        <v>194566</v>
       </c>
     </row>
     <row r="14">
@@ -99409,7 +99409,7 @@
         <v>63407</v>
       </c>
       <c r="E14" t="n">
-        <v>871474</v>
+        <v>872481</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -99451,7 +99451,7 @@
         <v>90340</v>
       </c>
       <c r="S14" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>
@@ -100126,7 +100126,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>81879</v>
+        <v>82886</v>
       </c>
       <c r="J13" t="n">
         <v>18695</v>
@@ -100147,7 +100147,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>193559</v>
+        <v>194566</v>
       </c>
     </row>
     <row r="14">
@@ -100178,7 +100178,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>764680</v>
+        <v>765687</v>
       </c>
       <c r="J14" t="n">
         <v>222766</v>
@@ -100199,7 +100199,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2112326</v>
+        <v>2113333</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53770,7 +53770,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>637</v>
+        <v>727</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -53788,7 +53788,7 @@
         <v>100</v>
       </c>
       <c r="K141" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="L141" t="n">
         <v>250</v>
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2715</v>
+        <v>2768</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53944,7 +53944,7 @@
         <v>0</v>
       </c>
       <c r="BK141" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="BL141" t="n">
         <v>0</v>
@@ -54082,7 +54082,7 @@
         <v>45</v>
       </c>
       <c r="DE141" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="DF141" t="n">
         <v>485</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>14650</v>
+        <v>15753</v>
       </c>
     </row>
     <row r="142">
@@ -54149,7 +54149,7 @@
         <v>150</v>
       </c>
       <c r="E142" t="n">
-        <v>72850</v>
+        <v>72940</v>
       </c>
       <c r="F142" t="n">
         <v>500</v>
@@ -54167,7 +54167,7 @@
         <v>22473</v>
       </c>
       <c r="K142" t="n">
-        <v>17405</v>
+        <v>17625</v>
       </c>
       <c r="L142" t="n">
         <v>6040</v>
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>437699</v>
+        <v>437752</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54323,7 +54323,7 @@
         <v>660</v>
       </c>
       <c r="BK142" t="n">
-        <v>48116</v>
+        <v>48586</v>
       </c>
       <c r="BL142" t="n">
         <v>1992</v>
@@ -54461,7 +54461,7 @@
         <v>90</v>
       </c>
       <c r="DE142" t="n">
-        <v>21081</v>
+        <v>21351</v>
       </c>
       <c r="DF142" t="n">
         <v>38674</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>
@@ -60786,7 +60786,7 @@
         <v>700</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="F9" t="n">
         <v>380</v>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1162</v>
+        <v>1252</v>
       </c>
       <c r="N9" t="n">
-        <v>2440</v>
+        <v>2493</v>
       </c>
       <c r="O9" t="n">
-        <v>9517</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="10">
@@ -60835,7 +60835,7 @@
         <v>6665</v>
       </c>
       <c r="E10" t="n">
-        <v>4886</v>
+        <v>5626</v>
       </c>
       <c r="F10" t="n">
         <v>5495</v>
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>17316</v>
+        <v>17406</v>
       </c>
       <c r="N10" t="n">
-        <v>29453</v>
+        <v>29506</v>
       </c>
       <c r="O10" t="n">
-        <v>111680</v>
+        <v>112563</v>
       </c>
     </row>
   </sheetData>
@@ -71019,7 +71019,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="C141" t="n">
         <v>375</v>
@@ -71028,7 +71028,7 @@
         <v>435</v>
       </c>
       <c r="E141" t="n">
-        <v>5022</v>
+        <v>5075</v>
       </c>
       <c r="F141" t="n">
         <v>220</v>
@@ -71061,16 +71061,16 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2557</v>
+        <v>2647</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>755</v>
+        <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>14650</v>
+        <v>15753</v>
       </c>
     </row>
     <row r="142">
@@ -71080,7 +71080,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>79117</v>
+        <v>79857</v>
       </c>
       <c r="C142" t="n">
         <v>18179</v>
@@ -71089,7 +71089,7 @@
         <v>63407</v>
       </c>
       <c r="E142" t="n">
-        <v>872481</v>
+        <v>872534</v>
       </c>
       <c r="F142" t="n">
         <v>6157</v>
@@ -71122,16 +71122,16 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>429050</v>
+        <v>429140</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
       </c>
       <c r="R142" t="n">
-        <v>90340</v>
+        <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>
@@ -74133,7 +74133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75401,129 +75401,139 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>69197</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="B128" t="n">
+        <v>69937</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B130" t="n">
-        <v>1095</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B131" t="n">
-        <v>2905</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B132" t="n">
-        <v>3064</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B133" t="n">
-        <v>5885</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B134" t="n">
-        <v>6805</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B135" t="n">
-        <v>6325</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B136" t="n">
-        <v>4515</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B137" t="n">
-        <v>7158</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B138" t="n">
-        <v>7879</v>
+        <v>7158</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B139" t="n">
-        <v>9963</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B140" t="n">
-        <v>8717</v>
+        <v>9963</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B141" t="n">
+        <v>8717</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
         <v>2026</v>
       </c>
-      <c r="B141" t="n">
-        <v>4886</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="B142" t="n">
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>69197</v>
+      <c r="B143" t="n">
+        <v>69937</v>
       </c>
     </row>
   </sheetData>
@@ -89825,10 +89835,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2440</v>
+        <v>2493</v>
       </c>
       <c r="C141" t="n">
-        <v>1162</v>
+        <v>1252</v>
       </c>
       <c r="D141" t="n">
         <v>380</v>
@@ -89837,7 +89847,7 @@
         <v>375</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -89846,7 +89856,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>5133</v>
+        <v>5353</v>
       </c>
       <c r="J141" t="n">
         <v>2365</v>
@@ -89867,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>14650</v>
+        <v>15753</v>
       </c>
     </row>
     <row r="142">
@@ -89877,10 +89887,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404764</v>
+        <v>404817</v>
       </c>
       <c r="C142" t="n">
-        <v>226289</v>
+        <v>226379</v>
       </c>
       <c r="D142" t="n">
         <v>59552</v>
@@ -89889,7 +89899,7 @@
         <v>14979</v>
       </c>
       <c r="F142" t="n">
-        <v>69197</v>
+        <v>69937</v>
       </c>
       <c r="G142" t="n">
         <v>23490</v>
@@ -89898,7 +89908,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>765687</v>
+        <v>765907</v>
       </c>
       <c r="J142" t="n">
         <v>222766</v>
@@ -89919,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>
@@ -91345,7 +91355,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1162</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="142">
@@ -91355,7 +91365,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>226289</v>
+        <v>226379</v>
       </c>
     </row>
     <row r="144">
@@ -91463,7 +91473,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>17316</v>
+        <v>17406</v>
       </c>
     </row>
     <row r="157">
@@ -91473,7 +91483,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>226289</v>
+        <v>226379</v>
       </c>
     </row>
   </sheetData>
@@ -92899,7 +92909,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2440</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="142">
@@ -92909,7 +92919,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404764</v>
+        <v>404817</v>
       </c>
     </row>
     <row r="144">
@@ -93017,7 +93027,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>29453</v>
+        <v>29506</v>
       </c>
     </row>
     <row r="157">
@@ -93027,7 +93037,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>404764</v>
+        <v>404817</v>
       </c>
     </row>
   </sheetData>
@@ -97832,7 +97842,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6169</v>
+        <v>6259</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -97850,7 +97860,7 @@
         <v>1500</v>
       </c>
       <c r="K13" t="n">
-        <v>1480</v>
+        <v>1700</v>
       </c>
       <c r="L13" t="n">
         <v>1075</v>
@@ -97871,7 +97881,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>32173</v>
+        <v>32226</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -98006,7 +98016,7 @@
         <v>40</v>
       </c>
       <c r="BK13" t="n">
-        <v>3316</v>
+        <v>3786</v>
       </c>
       <c r="BL13" t="n">
         <v>0</v>
@@ -98144,7 +98154,7 @@
         <v>90</v>
       </c>
       <c r="DE13" t="n">
-        <v>1570</v>
+        <v>1840</v>
       </c>
       <c r="DF13" t="n">
         <v>4000</v>
@@ -98192,7 +98202,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>194566</v>
+        <v>195669</v>
       </c>
     </row>
     <row r="14">
@@ -98211,7 +98221,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72850</v>
+        <v>72940</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98229,7 +98239,7 @@
         <v>22473</v>
       </c>
       <c r="K14" t="n">
-        <v>17405</v>
+        <v>17625</v>
       </c>
       <c r="L14" t="n">
         <v>6040</v>
@@ -98250,7 +98260,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>437699</v>
+        <v>437752</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98385,7 +98395,7 @@
         <v>660</v>
       </c>
       <c r="BK14" t="n">
-        <v>48116</v>
+        <v>48586</v>
       </c>
       <c r="BL14" t="n">
         <v>1992</v>
@@ -98523,7 +98533,7 @@
         <v>90</v>
       </c>
       <c r="DE14" t="n">
-        <v>21081</v>
+        <v>21351</v>
       </c>
       <c r="DF14" t="n">
         <v>38674</v>
@@ -98571,7 +98581,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>
@@ -99339,7 +99349,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>6076</v>
+        <v>6816</v>
       </c>
       <c r="C13" t="n">
         <v>2925</v>
@@ -99348,7 +99358,7 @@
         <v>6095</v>
       </c>
       <c r="E13" t="n">
-        <v>80841</v>
+        <v>80894</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99381,16 +99391,16 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>34601</v>
+        <v>34691</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
       </c>
       <c r="R13" t="n">
-        <v>11007</v>
+        <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>194566</v>
+        <v>195669</v>
       </c>
     </row>
     <row r="14">
@@ -99400,7 +99410,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79117</v>
+        <v>79857</v>
       </c>
       <c r="C14" t="n">
         <v>18179</v>
@@ -99409,7 +99419,7 @@
         <v>63407</v>
       </c>
       <c r="E14" t="n">
-        <v>872481</v>
+        <v>872534</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -99442,16 +99452,16 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>429050</v>
+        <v>429140</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
       </c>
       <c r="R14" t="n">
-        <v>90340</v>
+        <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>
@@ -100105,10 +100115,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>29453</v>
+        <v>29506</v>
       </c>
       <c r="C13" t="n">
-        <v>17316</v>
+        <v>17406</v>
       </c>
       <c r="D13" t="n">
         <v>5495</v>
@@ -100117,7 +100127,7 @@
         <v>2330</v>
       </c>
       <c r="F13" t="n">
-        <v>4886</v>
+        <v>5626</v>
       </c>
       <c r="G13" t="n">
         <v>2880</v>
@@ -100126,7 +100136,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>82886</v>
+        <v>83106</v>
       </c>
       <c r="J13" t="n">
         <v>18695</v>
@@ -100147,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>194566</v>
+        <v>195669</v>
       </c>
     </row>
     <row r="14">
@@ -100157,10 +100167,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>404764</v>
+        <v>404817</v>
       </c>
       <c r="C14" t="n">
-        <v>226289</v>
+        <v>226379</v>
       </c>
       <c r="D14" t="n">
         <v>59552</v>
@@ -100169,7 +100179,7 @@
         <v>14979</v>
       </c>
       <c r="F14" t="n">
-        <v>69197</v>
+        <v>69937</v>
       </c>
       <c r="G14" t="n">
         <v>23490</v>
@@ -100178,7 +100188,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>765687</v>
+        <v>765907</v>
       </c>
       <c r="J14" t="n">
         <v>222766</v>
@@ -100199,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2113333</v>
+        <v>2114436</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53785,7 +53785,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="K141" t="n">
         <v>320</v>
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2768</v>
+        <v>3913</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -54091,7 +54091,7 @@
         <v>215</v>
       </c>
       <c r="DH141" t="n">
-        <v>655</v>
+        <v>730</v>
       </c>
       <c r="DI141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>15753</v>
+        <v>17113</v>
       </c>
     </row>
     <row r="142">
@@ -54164,7 +54164,7 @@
         <v>3200</v>
       </c>
       <c r="J142" t="n">
-        <v>22473</v>
+        <v>22613</v>
       </c>
       <c r="K142" t="n">
         <v>17625</v>
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>437752</v>
+        <v>438897</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54470,7 +54470,7 @@
         <v>24333</v>
       </c>
       <c r="DH142" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
       <c r="DI142" t="n">
         <v>1240</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>
@@ -60780,7 +60780,7 @@
         <v>2365</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>730</v>
       </c>
       <c r="D9" t="n">
         <v>700</v>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1252</v>
+        <v>1392</v>
       </c>
       <c r="N9" t="n">
-        <v>2493</v>
+        <v>3638</v>
       </c>
       <c r="O9" t="n">
-        <v>10400</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="10">
@@ -60829,7 +60829,7 @@
         <v>18695</v>
       </c>
       <c r="C10" t="n">
-        <v>6915</v>
+        <v>6990</v>
       </c>
       <c r="D10" t="n">
         <v>6665</v>
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>17406</v>
+        <v>17546</v>
       </c>
       <c r="N10" t="n">
-        <v>29506</v>
+        <v>30651</v>
       </c>
       <c r="O10" t="n">
-        <v>112563</v>
+        <v>113923</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>435</v>
       </c>
       <c r="E141" t="n">
-        <v>5075</v>
+        <v>6220</v>
       </c>
       <c r="F141" t="n">
         <v>220</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2647</v>
+        <v>2862</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>15753</v>
+        <v>17113</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63407</v>
       </c>
       <c r="E142" t="n">
-        <v>872534</v>
+        <v>873679</v>
       </c>
       <c r="F142" t="n">
         <v>6157</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>429140</v>
+        <v>429355</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>
@@ -72557,7 +72557,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>655</v>
+        <v>730</v>
       </c>
     </row>
     <row r="142">
@@ -72567,7 +72567,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
     </row>
     <row r="144">
@@ -72675,7 +72675,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>6915</v>
+        <v>6990</v>
       </c>
     </row>
     <row r="157">
@@ -72685,7 +72685,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
     </row>
   </sheetData>
@@ -89835,10 +89835,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2493</v>
+        <v>3638</v>
       </c>
       <c r="C141" t="n">
-        <v>1252</v>
+        <v>1392</v>
       </c>
       <c r="D141" t="n">
         <v>380</v>
@@ -89868,7 +89868,7 @@
         <v>700</v>
       </c>
       <c r="M141" t="n">
-        <v>655</v>
+        <v>730</v>
       </c>
       <c r="N141" t="n">
         <v>510</v>
@@ -89877,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>15753</v>
+        <v>17113</v>
       </c>
     </row>
     <row r="142">
@@ -89887,10 +89887,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404817</v>
+        <v>405962</v>
       </c>
       <c r="C142" t="n">
-        <v>226379</v>
+        <v>226519</v>
       </c>
       <c r="D142" t="n">
         <v>59552</v>
@@ -89920,7 +89920,7 @@
         <v>63007</v>
       </c>
       <c r="M142" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
       <c r="N142" t="n">
         <v>72207</v>
@@ -89929,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>
@@ -91355,7 +91355,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1252</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="142">
@@ -91365,7 +91365,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>226379</v>
+        <v>226519</v>
       </c>
     </row>
     <row r="144">
@@ -91473,7 +91473,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>17406</v>
+        <v>17546</v>
       </c>
     </row>
     <row r="157">
@@ -91483,7 +91483,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>226379</v>
+        <v>226519</v>
       </c>
     </row>
   </sheetData>
@@ -92909,7 +92909,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2493</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="142">
@@ -92919,7 +92919,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>404817</v>
+        <v>405962</v>
       </c>
     </row>
     <row r="144">
@@ -93027,7 +93027,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>29506</v>
+        <v>30651</v>
       </c>
     </row>
     <row r="157">
@@ -93037,7 +93037,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>404817</v>
+        <v>405962</v>
       </c>
     </row>
   </sheetData>
@@ -97857,7 +97857,7 @@
         <v>595</v>
       </c>
       <c r="J13" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="K13" t="n">
         <v>1700</v>
@@ -97881,7 +97881,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>32226</v>
+        <v>33371</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -98163,7 +98163,7 @@
         <v>2665</v>
       </c>
       <c r="DH13" t="n">
-        <v>6915</v>
+        <v>6990</v>
       </c>
       <c r="DI13" t="n">
         <v>420</v>
@@ -98202,7 +98202,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>195669</v>
+        <v>197029</v>
       </c>
     </row>
     <row r="14">
@@ -98236,7 +98236,7 @@
         <v>3200</v>
       </c>
       <c r="J14" t="n">
-        <v>22473</v>
+        <v>22613</v>
       </c>
       <c r="K14" t="n">
         <v>17625</v>
@@ -98260,7 +98260,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>437752</v>
+        <v>438897</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98542,7 +98542,7 @@
         <v>24333</v>
       </c>
       <c r="DH14" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
       <c r="DI14" t="n">
         <v>1240</v>
@@ -98581,7 +98581,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>
@@ -99358,7 +99358,7 @@
         <v>6095</v>
       </c>
       <c r="E13" t="n">
-        <v>80894</v>
+        <v>82039</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99391,7 +99391,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>34691</v>
+        <v>34906</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99400,7 +99400,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>195669</v>
+        <v>197029</v>
       </c>
     </row>
     <row r="14">
@@ -99419,7 +99419,7 @@
         <v>63407</v>
       </c>
       <c r="E14" t="n">
-        <v>872534</v>
+        <v>873679</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -99452,7 +99452,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>429140</v>
+        <v>429355</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99461,7 +99461,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>
@@ -100115,10 +100115,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>29506</v>
+        <v>30651</v>
       </c>
       <c r="C13" t="n">
-        <v>17406</v>
+        <v>17546</v>
       </c>
       <c r="D13" t="n">
         <v>5495</v>
@@ -100148,7 +100148,7 @@
         <v>6665</v>
       </c>
       <c r="M13" t="n">
-        <v>6915</v>
+        <v>6990</v>
       </c>
       <c r="N13" t="n">
         <v>6425</v>
@@ -100157,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>195669</v>
+        <v>197029</v>
       </c>
     </row>
     <row r="14">
@@ -100167,10 +100167,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>404817</v>
+        <v>405962</v>
       </c>
       <c r="C14" t="n">
-        <v>226379</v>
+        <v>226519</v>
       </c>
       <c r="D14" t="n">
         <v>59552</v>
@@ -100200,7 +100200,7 @@
         <v>63007</v>
       </c>
       <c r="M14" t="n">
-        <v>101418</v>
+        <v>101493</v>
       </c>
       <c r="N14" t="n">
         <v>72207</v>
@@ -100209,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2114436</v>
+        <v>2115796</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53785,7 +53785,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="K141" t="n">
         <v>320</v>
@@ -53884,13 +53884,13 @@
         <v>0</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AR141" t="n">
         <v>0</v>
       </c>
       <c r="AS141" t="n">
-        <v>185</v>
+        <v>560</v>
       </c>
       <c r="AT141" t="n">
         <v>0</v>
@@ -53959,13 +53959,13 @@
         <v>0</v>
       </c>
       <c r="BP141" t="n">
-        <v>365</v>
+        <v>1045</v>
       </c>
       <c r="BQ141" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="BR141" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="BS141" t="n">
         <v>678</v>
@@ -53977,7 +53977,7 @@
         <v>315</v>
       </c>
       <c r="BV141" t="n">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="BW141" t="n">
         <v>0</v>
@@ -54124,13 +54124,13 @@
         <v>510</v>
       </c>
       <c r="DS141" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="DT141" t="n">
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>17113</v>
+        <v>18643</v>
       </c>
     </row>
     <row r="142">
@@ -54164,7 +54164,7 @@
         <v>3200</v>
       </c>
       <c r="J142" t="n">
-        <v>22613</v>
+        <v>22638</v>
       </c>
       <c r="K142" t="n">
         <v>17625</v>
@@ -54263,13 +54263,13 @@
         <v>2039</v>
       </c>
       <c r="AQ142" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="AR142" t="n">
         <v>280</v>
       </c>
       <c r="AS142" t="n">
-        <v>27174</v>
+        <v>27549</v>
       </c>
       <c r="AT142" t="n">
         <v>565</v>
@@ -54338,13 +54338,13 @@
         <v>7460</v>
       </c>
       <c r="BP142" t="n">
-        <v>95966</v>
+        <v>96646</v>
       </c>
       <c r="BQ142" t="n">
-        <v>22490</v>
+        <v>22615</v>
       </c>
       <c r="BR142" t="n">
-        <v>13710</v>
+        <v>13790</v>
       </c>
       <c r="BS142" t="n">
         <v>28204</v>
@@ -54356,7 +54356,7 @@
         <v>6605</v>
       </c>
       <c r="BV142" t="n">
-        <v>35000</v>
+        <v>35165</v>
       </c>
       <c r="BW142" t="n">
         <v>5175</v>
@@ -54503,13 +54503,13 @@
         <v>72207</v>
       </c>
       <c r="DS142" t="n">
-        <v>4982</v>
+        <v>5007</v>
       </c>
       <c r="DT142" t="n">
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>
@@ -60810,13 +60810,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1392</v>
+        <v>2262</v>
       </c>
       <c r="N9" t="n">
         <v>3638</v>
       </c>
       <c r="O9" t="n">
-        <v>11760</v>
+        <v>12630</v>
       </c>
     </row>
     <row r="10">
@@ -60859,13 +60859,13 @@
         <v>2690</v>
       </c>
       <c r="M10" t="n">
-        <v>17546</v>
+        <v>18416</v>
       </c>
       <c r="N10" t="n">
         <v>30651</v>
       </c>
       <c r="O10" t="n">
-        <v>113923</v>
+        <v>114793</v>
       </c>
     </row>
   </sheetData>
@@ -71025,7 +71025,7 @@
         <v>375</v>
       </c>
       <c r="D141" t="n">
-        <v>435</v>
+        <v>865</v>
       </c>
       <c r="E141" t="n">
         <v>6220</v>
@@ -71040,7 +71040,7 @@
         <v>300</v>
       </c>
       <c r="I141" t="n">
-        <v>3320</v>
+        <v>3550</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>2862</v>
+        <v>3732</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>17113</v>
+        <v>18643</v>
       </c>
     </row>
     <row r="142">
@@ -71086,7 +71086,7 @@
         <v>18179</v>
       </c>
       <c r="D142" t="n">
-        <v>63407</v>
+        <v>63837</v>
       </c>
       <c r="E142" t="n">
         <v>873679</v>
@@ -71101,7 +71101,7 @@
         <v>8540</v>
       </c>
       <c r="I142" t="n">
-        <v>290060</v>
+        <v>290290</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>429355</v>
+        <v>430225</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>
@@ -89838,7 +89838,7 @@
         <v>3638</v>
       </c>
       <c r="C141" t="n">
-        <v>1392</v>
+        <v>2262</v>
       </c>
       <c r="D141" t="n">
         <v>380</v>
@@ -89856,7 +89856,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>5353</v>
+        <v>6013</v>
       </c>
       <c r="J141" t="n">
         <v>2365</v>
@@ -89877,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>17113</v>
+        <v>18643</v>
       </c>
     </row>
     <row r="142">
@@ -89890,7 +89890,7 @@
         <v>405962</v>
       </c>
       <c r="C142" t="n">
-        <v>226519</v>
+        <v>227389</v>
       </c>
       <c r="D142" t="n">
         <v>59552</v>
@@ -89908,7 +89908,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>765907</v>
+        <v>766567</v>
       </c>
       <c r="J142" t="n">
         <v>222766</v>
@@ -89929,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>
@@ -91355,7 +91355,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1392</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="142">
@@ -91365,7 +91365,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>226519</v>
+        <v>227389</v>
       </c>
     </row>
     <row r="144">
@@ -91473,7 +91473,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>17546</v>
+        <v>18416</v>
       </c>
     </row>
     <row r="157">
@@ -91483,7 +91483,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>226519</v>
+        <v>227389</v>
       </c>
     </row>
   </sheetData>
@@ -97857,7 +97857,7 @@
         <v>595</v>
       </c>
       <c r="J13" t="n">
-        <v>1640</v>
+        <v>1665</v>
       </c>
       <c r="K13" t="n">
         <v>1700</v>
@@ -97956,13 +97956,13 @@
         <v>170</v>
       </c>
       <c r="AQ13" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="AR13" t="n">
         <v>280</v>
       </c>
       <c r="AS13" t="n">
-        <v>2435</v>
+        <v>2810</v>
       </c>
       <c r="AT13" t="n">
         <v>565</v>
@@ -98031,13 +98031,13 @@
         <v>430</v>
       </c>
       <c r="BP13" t="n">
-        <v>6860</v>
+        <v>7540</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1930</v>
+        <v>2055</v>
       </c>
       <c r="BR13" t="n">
-        <v>1342</v>
+        <v>1422</v>
       </c>
       <c r="BS13" t="n">
         <v>4510</v>
@@ -98049,7 +98049,7 @@
         <v>1855</v>
       </c>
       <c r="BV13" t="n">
-        <v>2787</v>
+        <v>2952</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -98196,13 +98196,13 @@
         <v>6425</v>
       </c>
       <c r="DS13" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="DT13" t="n">
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>197029</v>
+        <v>198559</v>
       </c>
     </row>
     <row r="14">
@@ -98236,7 +98236,7 @@
         <v>3200</v>
       </c>
       <c r="J14" t="n">
-        <v>22613</v>
+        <v>22638</v>
       </c>
       <c r="K14" t="n">
         <v>17625</v>
@@ -98335,13 +98335,13 @@
         <v>2039</v>
       </c>
       <c r="AQ14" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="AR14" t="n">
         <v>280</v>
       </c>
       <c r="AS14" t="n">
-        <v>27174</v>
+        <v>27549</v>
       </c>
       <c r="AT14" t="n">
         <v>565</v>
@@ -98410,13 +98410,13 @@
         <v>7460</v>
       </c>
       <c r="BP14" t="n">
-        <v>95966</v>
+        <v>96646</v>
       </c>
       <c r="BQ14" t="n">
-        <v>22490</v>
+        <v>22615</v>
       </c>
       <c r="BR14" t="n">
-        <v>13710</v>
+        <v>13790</v>
       </c>
       <c r="BS14" t="n">
         <v>28204</v>
@@ -98428,7 +98428,7 @@
         <v>6605</v>
       </c>
       <c r="BV14" t="n">
-        <v>35000</v>
+        <v>35165</v>
       </c>
       <c r="BW14" t="n">
         <v>5175</v>
@@ -98575,13 +98575,13 @@
         <v>72207</v>
       </c>
       <c r="DS14" t="n">
-        <v>4982</v>
+        <v>5007</v>
       </c>
       <c r="DT14" t="n">
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>
@@ -99355,7 +99355,7 @@
         <v>2925</v>
       </c>
       <c r="D13" t="n">
-        <v>6095</v>
+        <v>6525</v>
       </c>
       <c r="E13" t="n">
         <v>82039</v>
@@ -99370,7 +99370,7 @@
         <v>2260</v>
       </c>
       <c r="I13" t="n">
-        <v>25174</v>
+        <v>25404</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
@@ -99391,7 +99391,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>34906</v>
+        <v>35776</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99400,7 +99400,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>197029</v>
+        <v>198559</v>
       </c>
     </row>
     <row r="14">
@@ -99416,7 +99416,7 @@
         <v>18179</v>
       </c>
       <c r="D14" t="n">
-        <v>63407</v>
+        <v>63837</v>
       </c>
       <c r="E14" t="n">
         <v>873679</v>
@@ -99431,7 +99431,7 @@
         <v>8540</v>
       </c>
       <c r="I14" t="n">
-        <v>290060</v>
+        <v>290290</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
@@ -99452,7 +99452,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>429355</v>
+        <v>430225</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99461,7 +99461,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>
@@ -100118,7 +100118,7 @@
         <v>30651</v>
       </c>
       <c r="C13" t="n">
-        <v>17546</v>
+        <v>18416</v>
       </c>
       <c r="D13" t="n">
         <v>5495</v>
@@ -100136,7 +100136,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>83106</v>
+        <v>83766</v>
       </c>
       <c r="J13" t="n">
         <v>18695</v>
@@ -100157,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>197029</v>
+        <v>198559</v>
       </c>
     </row>
     <row r="14">
@@ -100170,7 +100170,7 @@
         <v>405962</v>
       </c>
       <c r="C14" t="n">
-        <v>226519</v>
+        <v>227389</v>
       </c>
       <c r="D14" t="n">
         <v>59552</v>
@@ -100188,7 +100188,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>765907</v>
+        <v>766567</v>
       </c>
       <c r="J14" t="n">
         <v>222766</v>
@@ -100209,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2115796</v>
+        <v>2117326</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53809,7 +53809,7 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3913</v>
+        <v>4142</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -53893,10 +53893,10 @@
         <v>560</v>
       </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AU141" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AV141" t="n">
         <v>140</v>
@@ -53998,7 +53998,7 @@
         <v>0</v>
       </c>
       <c r="CC141" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="CD141" t="n">
         <v>0</v>
@@ -54022,7 +54022,7 @@
         <v>70</v>
       </c>
       <c r="CK141" t="n">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="CL141" t="n">
         <v>0</v>
@@ -54040,10 +54040,10 @@
         <v>0</v>
       </c>
       <c r="CQ141" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CR141" t="n">
-        <v>550</v>
+        <v>716</v>
       </c>
       <c r="CS141" t="n">
         <v>120</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>18643</v>
+        <v>19383</v>
       </c>
     </row>
     <row r="142">
@@ -54188,7 +54188,7 @@
         <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>438897</v>
+        <v>439126</v>
       </c>
       <c r="S142" t="n">
         <v>975</v>
@@ -54272,10 +54272,10 @@
         <v>27549</v>
       </c>
       <c r="AT142" t="n">
-        <v>565</v>
+        <v>665</v>
       </c>
       <c r="AU142" t="n">
-        <v>2720</v>
+        <v>2750</v>
       </c>
       <c r="AV142" t="n">
         <v>7079</v>
@@ -54377,7 +54377,7 @@
         <v>435</v>
       </c>
       <c r="CC142" t="n">
-        <v>16285</v>
+        <v>16350</v>
       </c>
       <c r="CD142" t="n">
         <v>5908</v>
@@ -54401,7 +54401,7 @@
         <v>420</v>
       </c>
       <c r="CK142" t="n">
-        <v>18124</v>
+        <v>18219</v>
       </c>
       <c r="CL142" t="n">
         <v>345</v>
@@ -54419,10 +54419,10 @@
         <v>275</v>
       </c>
       <c r="CQ142" t="n">
-        <v>12112</v>
+        <v>12167</v>
       </c>
       <c r="CR142" t="n">
-        <v>66546</v>
+        <v>66712</v>
       </c>
       <c r="CS142" t="n">
         <v>2835</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>
@@ -60813,10 +60813,10 @@
         <v>2262</v>
       </c>
       <c r="N9" t="n">
-        <v>3638</v>
+        <v>3867</v>
       </c>
       <c r="O9" t="n">
-        <v>12630</v>
+        <v>12859</v>
       </c>
     </row>
     <row r="10">
@@ -60862,10 +60862,10 @@
         <v>18416</v>
       </c>
       <c r="N10" t="n">
-        <v>30651</v>
+        <v>30880</v>
       </c>
       <c r="O10" t="n">
-        <v>114793</v>
+        <v>115022</v>
       </c>
     </row>
   </sheetData>
@@ -71028,7 +71028,7 @@
         <v>865</v>
       </c>
       <c r="E141" t="n">
-        <v>6220</v>
+        <v>6895</v>
       </c>
       <c r="F141" t="n">
         <v>220</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>3732</v>
+        <v>3797</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>18643</v>
+        <v>19383</v>
       </c>
     </row>
     <row r="142">
@@ -71089,7 +71089,7 @@
         <v>63837</v>
       </c>
       <c r="E142" t="n">
-        <v>873679</v>
+        <v>874354</v>
       </c>
       <c r="F142" t="n">
         <v>6157</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>430225</v>
+        <v>430290</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>
@@ -89835,7 +89835,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3638</v>
+        <v>3867</v>
       </c>
       <c r="C141" t="n">
         <v>2262</v>
@@ -89856,7 +89856,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>6013</v>
+        <v>6524</v>
       </c>
       <c r="J141" t="n">
         <v>2365</v>
@@ -89877,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>18643</v>
+        <v>19383</v>
       </c>
     </row>
     <row r="142">
@@ -89887,7 +89887,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>405962</v>
+        <v>406191</v>
       </c>
       <c r="C142" t="n">
         <v>227389</v>
@@ -89908,7 +89908,7 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>766567</v>
+        <v>767078</v>
       </c>
       <c r="J142" t="n">
         <v>222766</v>
@@ -89929,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>
@@ -92909,7 +92909,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3638</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="142">
@@ -92919,7 +92919,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>405962</v>
+        <v>406191</v>
       </c>
     </row>
     <row r="144">
@@ -93027,7 +93027,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>30651</v>
+        <v>30880</v>
       </c>
     </row>
     <row r="157">
@@ -93037,7 +93037,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>405962</v>
+        <v>406191</v>
       </c>
     </row>
   </sheetData>
@@ -97881,7 +97881,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>33371</v>
+        <v>33600</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97965,10 +97965,10 @@
         <v>2810</v>
       </c>
       <c r="AT13" t="n">
-        <v>565</v>
+        <v>665</v>
       </c>
       <c r="AU13" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AV13" t="n">
         <v>580</v>
@@ -98070,7 +98070,7 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>2555</v>
+        <v>2620</v>
       </c>
       <c r="CD13" t="n">
         <v>995</v>
@@ -98094,7 +98094,7 @@
         <v>70</v>
       </c>
       <c r="CK13" t="n">
-        <v>510</v>
+        <v>605</v>
       </c>
       <c r="CL13" t="n">
         <v>50</v>
@@ -98112,10 +98112,10 @@
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>710</v>
+        <v>765</v>
       </c>
       <c r="CR13" t="n">
-        <v>5826</v>
+        <v>5992</v>
       </c>
       <c r="CS13" t="n">
         <v>1380</v>
@@ -98202,7 +98202,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>198559</v>
+        <v>199299</v>
       </c>
     </row>
     <row r="14">
@@ -98260,7 +98260,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>438897</v>
+        <v>439126</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98344,10 +98344,10 @@
         <v>27549</v>
       </c>
       <c r="AT14" t="n">
-        <v>565</v>
+        <v>665</v>
       </c>
       <c r="AU14" t="n">
-        <v>2720</v>
+        <v>2750</v>
       </c>
       <c r="AV14" t="n">
         <v>7079</v>
@@ -98449,7 +98449,7 @@
         <v>435</v>
       </c>
       <c r="CC14" t="n">
-        <v>16285</v>
+        <v>16350</v>
       </c>
       <c r="CD14" t="n">
         <v>5908</v>
@@ -98473,7 +98473,7 @@
         <v>420</v>
       </c>
       <c r="CK14" t="n">
-        <v>18124</v>
+        <v>18219</v>
       </c>
       <c r="CL14" t="n">
         <v>345</v>
@@ -98491,10 +98491,10 @@
         <v>275</v>
       </c>
       <c r="CQ14" t="n">
-        <v>12112</v>
+        <v>12167</v>
       </c>
       <c r="CR14" t="n">
-        <v>66546</v>
+        <v>66712</v>
       </c>
       <c r="CS14" t="n">
         <v>2835</v>
@@ -98581,7 +98581,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>
@@ -99358,7 +99358,7 @@
         <v>6525</v>
       </c>
       <c r="E13" t="n">
-        <v>82039</v>
+        <v>82714</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99391,7 +99391,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>35776</v>
+        <v>35841</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99400,7 +99400,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>198559</v>
+        <v>199299</v>
       </c>
     </row>
     <row r="14">
@@ -99419,7 +99419,7 @@
         <v>63837</v>
       </c>
       <c r="E14" t="n">
-        <v>873679</v>
+        <v>874354</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -99452,7 +99452,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>430225</v>
+        <v>430290</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99461,7 +99461,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>
@@ -100115,7 +100115,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>30651</v>
+        <v>30880</v>
       </c>
       <c r="C13" t="n">
         <v>18416</v>
@@ -100136,7 +100136,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>83766</v>
+        <v>84277</v>
       </c>
       <c r="J13" t="n">
         <v>18695</v>
@@ -100157,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>198559</v>
+        <v>199299</v>
       </c>
     </row>
     <row r="14">
@@ -100167,7 +100167,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>405962</v>
+        <v>406191</v>
       </c>
       <c r="C14" t="n">
         <v>227389</v>
@@ -100188,7 +100188,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>766567</v>
+        <v>767078</v>
       </c>
       <c r="J14" t="n">
         <v>222766</v>
@@ -100209,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2117326</v>
+        <v>2118066</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54067,7 +54067,7 @@
         <v>100</v>
       </c>
       <c r="CZ141" t="n">
-        <v>2365</v>
+        <v>2585</v>
       </c>
       <c r="DA141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>19383</v>
+        <v>19603</v>
       </c>
     </row>
     <row r="142">
@@ -54446,7 +54446,7 @@
         <v>13984</v>
       </c>
       <c r="CZ142" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
       <c r="DA142" t="n">
         <v>1125</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>
@@ -60777,7 +60777,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2365</v>
+        <v>2585</v>
       </c>
       <c r="C9" t="n">
         <v>730</v>
@@ -60816,7 +60816,7 @@
         <v>3867</v>
       </c>
       <c r="O9" t="n">
-        <v>12859</v>
+        <v>13079</v>
       </c>
     </row>
     <row r="10">
@@ -60826,7 +60826,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18695</v>
+        <v>18915</v>
       </c>
       <c r="C10" t="n">
         <v>6990</v>
@@ -60865,7 +60865,7 @@
         <v>30880</v>
       </c>
       <c r="O10" t="n">
-        <v>115022</v>
+        <v>115242</v>
       </c>
     </row>
   </sheetData>
@@ -62291,7 +62291,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2365</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="142">
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
     </row>
     <row r="144">
@@ -62409,7 +62409,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>18695</v>
+        <v>18915</v>
       </c>
     </row>
     <row r="157">
@@ -62419,7 +62419,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
     </row>
   </sheetData>
@@ -71040,7 +71040,7 @@
         <v>300</v>
       </c>
       <c r="I141" t="n">
-        <v>3550</v>
+        <v>3770</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>19383</v>
+        <v>19603</v>
       </c>
     </row>
     <row r="142">
@@ -71101,7 +71101,7 @@
         <v>8540</v>
       </c>
       <c r="I142" t="n">
-        <v>290290</v>
+        <v>290510</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
@@ -71131,7 +71131,7 @@
         <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>
@@ -89859,7 +89859,7 @@
         <v>6524</v>
       </c>
       <c r="J141" t="n">
-        <v>2365</v>
+        <v>2585</v>
       </c>
       <c r="K141" t="n">
         <v>275</v>
@@ -89877,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>19383</v>
+        <v>19603</v>
       </c>
     </row>
     <row r="142">
@@ -89911,7 +89911,7 @@
         <v>767078</v>
       </c>
       <c r="J142" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
       <c r="K142" t="n">
         <v>32935</v>
@@ -89929,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>
@@ -98139,7 +98139,7 @@
         <v>1130</v>
       </c>
       <c r="CZ13" t="n">
-        <v>18695</v>
+        <v>18915</v>
       </c>
       <c r="DA13" t="n">
         <v>125</v>
@@ -98202,7 +98202,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>199299</v>
+        <v>199519</v>
       </c>
     </row>
     <row r="14">
@@ -98518,7 +98518,7 @@
         <v>13984</v>
       </c>
       <c r="CZ14" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
       <c r="DA14" t="n">
         <v>1125</v>
@@ -98581,7 +98581,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>
@@ -99370,7 +99370,7 @@
         <v>2260</v>
       </c>
       <c r="I13" t="n">
-        <v>25404</v>
+        <v>25624</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
@@ -99400,7 +99400,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>199299</v>
+        <v>199519</v>
       </c>
     </row>
     <row r="14">
@@ -99431,7 +99431,7 @@
         <v>8540</v>
       </c>
       <c r="I14" t="n">
-        <v>290290</v>
+        <v>290510</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
@@ -99461,7 +99461,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>
@@ -100139,7 +100139,7 @@
         <v>84277</v>
       </c>
       <c r="J13" t="n">
-        <v>18695</v>
+        <v>18915</v>
       </c>
       <c r="K13" t="n">
         <v>2720</v>
@@ -100157,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>199299</v>
+        <v>199519</v>
       </c>
     </row>
     <row r="14">
@@ -100191,7 +100191,7 @@
         <v>767078</v>
       </c>
       <c r="J14" t="n">
-        <v>222766</v>
+        <v>222986</v>
       </c>
       <c r="K14" t="n">
         <v>32935</v>
@@ -100209,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2118066</v>
+        <v>2118286</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -53761,7 +53761,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -53857,10 +53857,10 @@
         <v>40</v>
       </c>
       <c r="AH141" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI141" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ141" t="n">
         <v>247</v>
@@ -53908,7 +53908,7 @@
         <v>0</v>
       </c>
       <c r="AY141" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AZ141" t="n">
         <v>0</v>
@@ -53956,7 +53956,7 @@
         <v>0</v>
       </c>
       <c r="BO141" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="BP141" t="n">
         <v>1045</v>
@@ -53968,7 +53968,7 @@
         <v>360</v>
       </c>
       <c r="BS141" t="n">
-        <v>678</v>
+        <v>848</v>
       </c>
       <c r="BT141" t="n">
         <v>180</v>
@@ -54067,7 +54067,7 @@
         <v>100</v>
       </c>
       <c r="CZ141" t="n">
-        <v>2585</v>
+        <v>3385</v>
       </c>
       <c r="DA141" t="n">
         <v>0</v>
@@ -54091,7 +54091,7 @@
         <v>215</v>
       </c>
       <c r="DH141" t="n">
-        <v>730</v>
+        <v>1045</v>
       </c>
       <c r="DI141" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>270</v>
       </c>
       <c r="DU141" t="n">
-        <v>19603</v>
+        <v>21423</v>
       </c>
     </row>
     <row r="142">
@@ -54140,7 +54140,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2547</v>
+        <v>2692</v>
       </c>
       <c r="C142" t="n">
         <v>995</v>
@@ -54236,10 +54236,10 @@
         <v>1545</v>
       </c>
       <c r="AH142" t="n">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="AI142" t="n">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="AJ142" t="n">
         <v>12605</v>
@@ -54287,7 +54287,7 @@
         <v>460</v>
       </c>
       <c r="AY142" t="n">
-        <v>41367</v>
+        <v>41592</v>
       </c>
       <c r="AZ142" t="n">
         <v>6666</v>
@@ -54335,7 +54335,7 @@
         <v>4120</v>
       </c>
       <c r="BO142" t="n">
-        <v>7460</v>
+        <v>7565</v>
       </c>
       <c r="BP142" t="n">
         <v>96646</v>
@@ -54347,7 +54347,7 @@
         <v>13790</v>
       </c>
       <c r="BS142" t="n">
-        <v>28204</v>
+        <v>28374</v>
       </c>
       <c r="BT142" t="n">
         <v>5705</v>
@@ -54446,7 +54446,7 @@
         <v>13984</v>
       </c>
       <c r="CZ142" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
       <c r="DA142" t="n">
         <v>1125</v>
@@ -54470,7 +54470,7 @@
         <v>24333</v>
       </c>
       <c r="DH142" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
       <c r="DI142" t="n">
         <v>1240</v>
@@ -54509,7 +54509,7 @@
         <v>28151</v>
       </c>
       <c r="DU142" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>
@@ -60777,10 +60777,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2585</v>
+        <v>3385</v>
       </c>
       <c r="C9" t="n">
-        <v>730</v>
+        <v>1045</v>
       </c>
       <c r="D9" t="n">
         <v>700</v>
@@ -60789,7 +60789,7 @@
         <v>740</v>
       </c>
       <c r="F9" t="n">
-        <v>380</v>
+        <v>710</v>
       </c>
       <c r="G9" t="n">
         <v>510</v>
@@ -60816,7 +60816,7 @@
         <v>3867</v>
       </c>
       <c r="O9" t="n">
-        <v>13079</v>
+        <v>14524</v>
       </c>
     </row>
     <row r="10">
@@ -60826,10 +60826,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18915</v>
+        <v>19715</v>
       </c>
       <c r="C10" t="n">
-        <v>6990</v>
+        <v>7305</v>
       </c>
       <c r="D10" t="n">
         <v>6665</v>
@@ -60838,7 +60838,7 @@
         <v>5626</v>
       </c>
       <c r="F10" t="n">
-        <v>5495</v>
+        <v>5825</v>
       </c>
       <c r="G10" t="n">
         <v>6425</v>
@@ -60865,7 +60865,7 @@
         <v>30880</v>
       </c>
       <c r="O10" t="n">
-        <v>115242</v>
+        <v>116687</v>
       </c>
     </row>
   </sheetData>
@@ -62291,7 +62291,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2585</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="142">
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
     </row>
     <row r="144">
@@ -62409,7 +62409,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>18915</v>
+        <v>19715</v>
       </c>
     </row>
     <row r="157">
@@ -62419,7 +62419,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
     </row>
   </sheetData>
@@ -71040,13 +71040,13 @@
         <v>300</v>
       </c>
       <c r="I141" t="n">
-        <v>3770</v>
+        <v>4630</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1395</v>
+        <v>2040</v>
       </c>
       <c r="L141" t="n">
         <v>201</v>
@@ -71061,7 +71061,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>3797</v>
+        <v>4112</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -71070,7 +71070,7 @@
         <v>975</v>
       </c>
       <c r="S141" t="n">
-        <v>19603</v>
+        <v>21423</v>
       </c>
     </row>
     <row r="142">
@@ -71101,13 +71101,13 @@
         <v>8540</v>
       </c>
       <c r="I142" t="n">
-        <v>290510</v>
+        <v>291370</v>
       </c>
       <c r="J142" t="n">
         <v>5457</v>
       </c>
       <c r="K142" t="n">
-        <v>115184</v>
+        <v>115829</v>
       </c>
       <c r="L142" t="n">
         <v>33332</v>
@@ -71122,7 +71122,7 @@
         <v>24816</v>
       </c>
       <c r="P142" t="n">
-        <v>430290</v>
+        <v>430605</v>
       </c>
       <c r="Q142" t="n">
         <v>36784</v>
@@ -71131,7 +71131,7 @@
         <v>90560</v>
       </c>
       <c r="S142" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>
@@ -72557,7 +72557,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>730</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="142">
@@ -72567,7 +72567,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
     </row>
     <row r="144">
@@ -72675,7 +72675,7 @@
         <v>2026</v>
       </c>
       <c r="B156" t="n">
-        <v>6990</v>
+        <v>7305</v>
       </c>
     </row>
     <row r="157">
@@ -72685,7 +72685,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
     </row>
   </sheetData>
@@ -76689,7 +76689,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>380</v>
+        <v>710</v>
       </c>
     </row>
     <row r="115">
@@ -76699,7 +76699,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>59552</v>
+        <v>59882</v>
       </c>
     </row>
     <row r="117">
@@ -76807,7 +76807,7 @@
         <v>2026</v>
       </c>
       <c r="B129" t="n">
-        <v>5495</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="130">
@@ -76817,7 +76817,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>59552</v>
+        <v>59882</v>
       </c>
     </row>
   </sheetData>
@@ -89841,7 +89841,7 @@
         <v>2262</v>
       </c>
       <c r="D141" t="n">
-        <v>380</v>
+        <v>710</v>
       </c>
       <c r="E141" t="n">
         <v>375</v>
@@ -89856,10 +89856,10 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>6524</v>
+        <v>6899</v>
       </c>
       <c r="J141" t="n">
-        <v>2585</v>
+        <v>3385</v>
       </c>
       <c r="K141" t="n">
         <v>275</v>
@@ -89868,7 +89868,7 @@
         <v>700</v>
       </c>
       <c r="M141" t="n">
-        <v>730</v>
+        <v>1045</v>
       </c>
       <c r="N141" t="n">
         <v>510</v>
@@ -89877,7 +89877,7 @@
         <v>655</v>
       </c>
       <c r="P141" t="n">
-        <v>19603</v>
+        <v>21423</v>
       </c>
     </row>
     <row r="142">
@@ -89893,7 +89893,7 @@
         <v>227389</v>
       </c>
       <c r="D142" t="n">
-        <v>59552</v>
+        <v>59882</v>
       </c>
       <c r="E142" t="n">
         <v>14979</v>
@@ -89908,10 +89908,10 @@
         <v>6860</v>
       </c>
       <c r="I142" t="n">
-        <v>767078</v>
+        <v>767453</v>
       </c>
       <c r="J142" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
       <c r="K142" t="n">
         <v>32935</v>
@@ -89920,7 +89920,7 @@
         <v>63007</v>
       </c>
       <c r="M142" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
       <c r="N142" t="n">
         <v>72207</v>
@@ -89929,7 +89929,7 @@
         <v>50182</v>
       </c>
       <c r="P142" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>
@@ -97833,7 +97833,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>345</v>
+        <v>490</v>
       </c>
       <c r="C13" t="n">
         <v>60</v>
@@ -97929,10 +97929,10 @@
         <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="AI13" t="n">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="AJ13" t="n">
         <v>1311</v>
@@ -97980,7 +97980,7 @@
         <v>50</v>
       </c>
       <c r="AY13" t="n">
-        <v>2935</v>
+        <v>3160</v>
       </c>
       <c r="AZ13" t="n">
         <v>460</v>
@@ -98028,7 +98028,7 @@
         <v>275</v>
       </c>
       <c r="BO13" t="n">
-        <v>430</v>
+        <v>535</v>
       </c>
       <c r="BP13" t="n">
         <v>7540</v>
@@ -98040,7 +98040,7 @@
         <v>1422</v>
       </c>
       <c r="BS13" t="n">
-        <v>4510</v>
+        <v>4680</v>
       </c>
       <c r="BT13" t="n">
         <v>880</v>
@@ -98139,7 +98139,7 @@
         <v>1130</v>
       </c>
       <c r="CZ13" t="n">
-        <v>18915</v>
+        <v>19715</v>
       </c>
       <c r="DA13" t="n">
         <v>125</v>
@@ -98163,7 +98163,7 @@
         <v>2665</v>
       </c>
       <c r="DH13" t="n">
-        <v>6990</v>
+        <v>7305</v>
       </c>
       <c r="DI13" t="n">
         <v>420</v>
@@ -98202,7 +98202,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>199519</v>
+        <v>201339</v>
       </c>
     </row>
     <row r="14">
@@ -98212,7 +98212,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2547</v>
+        <v>2692</v>
       </c>
       <c r="C14" t="n">
         <v>995</v>
@@ -98308,10 +98308,10 @@
         <v>1545</v>
       </c>
       <c r="AH14" t="n">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="AI14" t="n">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="AJ14" t="n">
         <v>12605</v>
@@ -98359,7 +98359,7 @@
         <v>460</v>
       </c>
       <c r="AY14" t="n">
-        <v>41367</v>
+        <v>41592</v>
       </c>
       <c r="AZ14" t="n">
         <v>6666</v>
@@ -98407,7 +98407,7 @@
         <v>4120</v>
       </c>
       <c r="BO14" t="n">
-        <v>7460</v>
+        <v>7565</v>
       </c>
       <c r="BP14" t="n">
         <v>96646</v>
@@ -98419,7 +98419,7 @@
         <v>13790</v>
       </c>
       <c r="BS14" t="n">
-        <v>28204</v>
+        <v>28374</v>
       </c>
       <c r="BT14" t="n">
         <v>5705</v>
@@ -98518,7 +98518,7 @@
         <v>13984</v>
       </c>
       <c r="CZ14" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
       <c r="DA14" t="n">
         <v>1125</v>
@@ -98542,7 +98542,7 @@
         <v>24333</v>
       </c>
       <c r="DH14" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
       <c r="DI14" t="n">
         <v>1240</v>
@@ -98581,7 +98581,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>
@@ -99370,13 +99370,13 @@
         <v>2260</v>
       </c>
       <c r="I13" t="n">
-        <v>25624</v>
+        <v>26484</v>
       </c>
       <c r="J13" t="n">
         <v>1432</v>
       </c>
       <c r="K13" t="n">
-        <v>12691</v>
+        <v>13336</v>
       </c>
       <c r="L13" t="n">
         <v>2694</v>
@@ -99391,7 +99391,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>35841</v>
+        <v>36156</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99400,7 +99400,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>199519</v>
+        <v>201339</v>
       </c>
     </row>
     <row r="14">
@@ -99431,13 +99431,13 @@
         <v>8540</v>
       </c>
       <c r="I14" t="n">
-        <v>290510</v>
+        <v>291370</v>
       </c>
       <c r="J14" t="n">
         <v>5457</v>
       </c>
       <c r="K14" t="n">
-        <v>115184</v>
+        <v>115829</v>
       </c>
       <c r="L14" t="n">
         <v>33332</v>
@@ -99452,7 +99452,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>430290</v>
+        <v>430605</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99461,7 +99461,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>
@@ -100121,7 +100121,7 @@
         <v>18416</v>
       </c>
       <c r="D13" t="n">
-        <v>5495</v>
+        <v>5825</v>
       </c>
       <c r="E13" t="n">
         <v>2330</v>
@@ -100136,10 +100136,10 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>84277</v>
+        <v>84652</v>
       </c>
       <c r="J13" t="n">
-        <v>18915</v>
+        <v>19715</v>
       </c>
       <c r="K13" t="n">
         <v>2720</v>
@@ -100148,7 +100148,7 @@
         <v>6665</v>
       </c>
       <c r="M13" t="n">
-        <v>6990</v>
+        <v>7305</v>
       </c>
       <c r="N13" t="n">
         <v>6425</v>
@@ -100157,7 +100157,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>199519</v>
+        <v>201339</v>
       </c>
     </row>
     <row r="14">
@@ -100173,7 +100173,7 @@
         <v>227389</v>
       </c>
       <c r="D14" t="n">
-        <v>59552</v>
+        <v>59882</v>
       </c>
       <c r="E14" t="n">
         <v>14979</v>
@@ -100188,10 +100188,10 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>767078</v>
+        <v>767453</v>
       </c>
       <c r="J14" t="n">
-        <v>222986</v>
+        <v>223786</v>
       </c>
       <c r="K14" t="n">
         <v>32935</v>
@@ -100200,7 +100200,7 @@
         <v>63007</v>
       </c>
       <c r="M14" t="n">
-        <v>101493</v>
+        <v>101808</v>
       </c>
       <c r="N14" t="n">
         <v>72207</v>
@@ -100209,7 +100209,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2118286</v>
+        <v>2120106</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU142"/>
+  <dimension ref="A1:DU143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54136,380 +54136,759 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>70</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>440</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>134</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>140</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>120</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>435</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>80</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="n">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B143" t="n">
         <v>2692</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C143" t="n">
         <v>995</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D143" t="n">
         <v>150</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E143" t="n">
         <v>72940</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F143" t="n">
         <v>500</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G143" t="n">
         <v>400</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H143" t="n">
         <v>2718</v>
       </c>
-      <c r="I142" t="n">
+      <c r="I143" t="n">
         <v>3200</v>
       </c>
-      <c r="J142" t="n">
+      <c r="J143" t="n">
         <v>22638</v>
       </c>
-      <c r="K142" t="n">
+      <c r="K143" t="n">
         <v>17625</v>
       </c>
-      <c r="L142" t="n">
+      <c r="L143" t="n">
         <v>6040</v>
       </c>
-      <c r="M142" t="n">
+      <c r="M143" t="n">
         <v>1742</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N143" t="n">
         <v>3005</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O143" t="n">
         <v>5784</v>
       </c>
-      <c r="P142" t="n">
+      <c r="P143" t="n">
         <v>6845</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="Q143" t="n">
         <v>105</v>
       </c>
-      <c r="R142" t="n">
-        <v>439126</v>
-      </c>
-      <c r="S142" t="n">
+      <c r="R143" t="n">
+        <v>439196</v>
+      </c>
+      <c r="S143" t="n">
         <v>975</v>
       </c>
-      <c r="T142" t="n">
+      <c r="T143" t="n">
         <v>960</v>
       </c>
-      <c r="U142" t="n">
+      <c r="U143" t="n">
         <v>2174</v>
       </c>
-      <c r="V142" t="n">
+      <c r="V143" t="n">
         <v>14436</v>
       </c>
-      <c r="W142" t="n">
+      <c r="W143" t="n">
         <v>24789</v>
       </c>
-      <c r="X142" t="n">
+      <c r="X143" t="n">
         <v>4890</v>
       </c>
-      <c r="Y142" t="n">
+      <c r="Y143" t="n">
         <v>2945</v>
       </c>
-      <c r="Z142" t="n">
+      <c r="Z143" t="n">
         <v>485</v>
       </c>
-      <c r="AA142" t="n">
+      <c r="AA143" t="n">
         <v>9319</v>
       </c>
-      <c r="AB142" t="n">
+      <c r="AB143" t="n">
         <v>265</v>
       </c>
-      <c r="AC142" t="n">
+      <c r="AC143" t="n">
         <v>10770</v>
       </c>
-      <c r="AD142" t="n">
+      <c r="AD143" t="n">
         <v>10</v>
       </c>
-      <c r="AE142" t="n">
+      <c r="AE143" t="n">
         <v>545</v>
       </c>
-      <c r="AF142" t="n">
+      <c r="AF143" t="n">
         <v>145</v>
       </c>
-      <c r="AG142" t="n">
+      <c r="AG143" t="n">
         <v>1545</v>
       </c>
-      <c r="AH142" t="n">
+      <c r="AH143" t="n">
         <v>645</v>
       </c>
-      <c r="AI142" t="n">
+      <c r="AI143" t="n">
         <v>870</v>
       </c>
-      <c r="AJ142" t="n">
+      <c r="AJ143" t="n">
         <v>12605</v>
       </c>
-      <c r="AK142" t="n">
+      <c r="AK143" t="n">
         <v>477</v>
       </c>
-      <c r="AL142" t="n">
-        <v>51568</v>
-      </c>
-      <c r="AM142" t="n">
+      <c r="AL143" t="n">
+        <v>52008</v>
+      </c>
+      <c r="AM143" t="n">
         <v>4755</v>
       </c>
-      <c r="AN142" t="n">
+      <c r="AN143" t="n">
         <v>3715</v>
       </c>
-      <c r="AO142" t="n">
+      <c r="AO143" t="n">
         <v>282</v>
       </c>
-      <c r="AP142" t="n">
+      <c r="AP143" t="n">
         <v>2039</v>
       </c>
-      <c r="AQ142" t="n">
+      <c r="AQ143" t="n">
         <v>440</v>
       </c>
-      <c r="AR142" t="n">
+      <c r="AR143" t="n">
         <v>280</v>
       </c>
-      <c r="AS142" t="n">
+      <c r="AS143" t="n">
         <v>27549</v>
       </c>
-      <c r="AT142" t="n">
+      <c r="AT143" t="n">
         <v>665</v>
       </c>
-      <c r="AU142" t="n">
+      <c r="AU143" t="n">
         <v>2750</v>
       </c>
-      <c r="AV142" t="n">
+      <c r="AV143" t="n">
         <v>7079</v>
       </c>
-      <c r="AW142" t="n">
+      <c r="AW143" t="n">
         <v>5875</v>
       </c>
-      <c r="AX142" t="n">
+      <c r="AX143" t="n">
         <v>460</v>
       </c>
-      <c r="AY142" t="n">
+      <c r="AY143" t="n">
         <v>41592</v>
       </c>
-      <c r="AZ142" t="n">
+      <c r="AZ143" t="n">
         <v>6666</v>
       </c>
-      <c r="BA142" t="n">
+      <c r="BA143" t="n">
         <v>3280</v>
       </c>
-      <c r="BB142" t="n">
+      <c r="BB143" t="n">
         <v>9952</v>
       </c>
-      <c r="BC142" t="n">
+      <c r="BC143" t="n">
         <v>6845</v>
       </c>
-      <c r="BD142" t="n">
+      <c r="BD143" t="n">
         <v>50</v>
       </c>
-      <c r="BE142" t="n">
+      <c r="BE143" t="n">
         <v>435</v>
       </c>
-      <c r="BF142" t="n">
+      <c r="BF143" t="n">
         <v>10010</v>
       </c>
-      <c r="BG142" t="n">
+      <c r="BG143" t="n">
         <v>1190</v>
       </c>
-      <c r="BH142" t="n">
+      <c r="BH143" t="n">
         <v>13909</v>
       </c>
-      <c r="BI142" t="n">
+      <c r="BI143" t="n">
         <v>1070</v>
       </c>
-      <c r="BJ142" t="n">
+      <c r="BJ143" t="n">
         <v>660</v>
       </c>
-      <c r="BK142" t="n">
+      <c r="BK143" t="n">
         <v>48586</v>
       </c>
-      <c r="BL142" t="n">
+      <c r="BL143" t="n">
         <v>1992</v>
       </c>
-      <c r="BM142" t="n">
+      <c r="BM143" t="n">
         <v>114410</v>
       </c>
-      <c r="BN142" t="n">
+      <c r="BN143" t="n">
         <v>4120</v>
       </c>
-      <c r="BO142" t="n">
+      <c r="BO143" t="n">
         <v>7565</v>
       </c>
-      <c r="BP142" t="n">
+      <c r="BP143" t="n">
         <v>96646</v>
       </c>
-      <c r="BQ142" t="n">
+      <c r="BQ143" t="n">
         <v>22615</v>
       </c>
-      <c r="BR142" t="n">
+      <c r="BR143" t="n">
         <v>13790</v>
       </c>
-      <c r="BS142" t="n">
+      <c r="BS143" t="n">
         <v>28374</v>
       </c>
-      <c r="BT142" t="n">
-        <v>5705</v>
-      </c>
-      <c r="BU142" t="n">
+      <c r="BT143" t="n">
+        <v>5775</v>
+      </c>
+      <c r="BU143" t="n">
         <v>6605</v>
       </c>
-      <c r="BV142" t="n">
+      <c r="BV143" t="n">
         <v>35165</v>
       </c>
-      <c r="BW142" t="n">
+      <c r="BW143" t="n">
         <v>5175</v>
       </c>
-      <c r="BX142" t="n">
+      <c r="BX143" t="n">
         <v>731</v>
       </c>
-      <c r="BY142" t="n">
+      <c r="BY143" t="n">
         <v>42</v>
       </c>
-      <c r="BZ142" t="n">
+      <c r="BZ143" t="n">
         <v>215</v>
       </c>
-      <c r="CA142" t="n">
+      <c r="CA143" t="n">
         <v>3350</v>
       </c>
-      <c r="CB142" t="n">
+      <c r="CB143" t="n">
         <v>435</v>
       </c>
-      <c r="CC142" t="n">
+      <c r="CC143" t="n">
         <v>16350</v>
       </c>
-      <c r="CD142" t="n">
-        <v>5908</v>
-      </c>
-      <c r="CE142" t="n">
+      <c r="CD143" t="n">
+        <v>6042</v>
+      </c>
+      <c r="CE143" t="n">
         <v>145</v>
       </c>
-      <c r="CF142" t="n">
+      <c r="CF143" t="n">
         <v>22031</v>
       </c>
-      <c r="CG142" t="n">
+      <c r="CG143" t="n">
         <v>3692</v>
       </c>
-      <c r="CH142" t="n">
+      <c r="CH143" t="n">
         <v>1665</v>
       </c>
-      <c r="CI142" t="n">
+      <c r="CI143" t="n">
         <v>470</v>
       </c>
-      <c r="CJ142" t="n">
+      <c r="CJ143" t="n">
         <v>420</v>
       </c>
-      <c r="CK142" t="n">
+      <c r="CK143" t="n">
         <v>18219</v>
       </c>
-      <c r="CL142" t="n">
+      <c r="CL143" t="n">
         <v>345</v>
       </c>
-      <c r="CM142" t="n">
+      <c r="CM143" t="n">
         <v>220</v>
       </c>
-      <c r="CN142" t="n">
+      <c r="CN143" t="n">
         <v>11123</v>
       </c>
-      <c r="CO142" t="n">
+      <c r="CO143" t="n">
         <v>140</v>
       </c>
-      <c r="CP142" t="n">
+      <c r="CP143" t="n">
         <v>275</v>
       </c>
-      <c r="CQ142" t="n">
+      <c r="CQ143" t="n">
         <v>12167</v>
       </c>
-      <c r="CR142" t="n">
-        <v>66712</v>
-      </c>
-      <c r="CS142" t="n">
-        <v>2835</v>
-      </c>
-      <c r="CT142" t="n">
+      <c r="CR143" t="n">
+        <v>66852</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>2955</v>
+      </c>
+      <c r="CT143" t="n">
         <v>1310</v>
       </c>
-      <c r="CU142" t="n">
+      <c r="CU143" t="n">
         <v>2736</v>
       </c>
-      <c r="CV142" t="n">
+      <c r="CV143" t="n">
         <v>125</v>
       </c>
-      <c r="CW142" t="n">
+      <c r="CW143" t="n">
         <v>8936</v>
       </c>
-      <c r="CX142" t="n">
-        <v>18892</v>
-      </c>
-      <c r="CY142" t="n">
+      <c r="CX143" t="n">
+        <v>19327</v>
+      </c>
+      <c r="CY143" t="n">
         <v>13984</v>
       </c>
-      <c r="CZ142" t="n">
+      <c r="CZ143" t="n">
         <v>223786</v>
       </c>
-      <c r="DA142" t="n">
+      <c r="DA143" t="n">
         <v>1125</v>
       </c>
-      <c r="DB142" t="n">
+      <c r="DB143" t="n">
         <v>1351</v>
       </c>
-      <c r="DC142" t="n">
+      <c r="DC143" t="n">
         <v>1485</v>
       </c>
-      <c r="DD142" t="n">
+      <c r="DD143" t="n">
         <v>90</v>
       </c>
-      <c r="DE142" t="n">
+      <c r="DE143" t="n">
         <v>21351</v>
       </c>
-      <c r="DF142" t="n">
+      <c r="DF143" t="n">
         <v>38674</v>
       </c>
-      <c r="DG142" t="n">
+      <c r="DG143" t="n">
         <v>24333</v>
       </c>
-      <c r="DH142" t="n">
-        <v>101808</v>
-      </c>
-      <c r="DI142" t="n">
+      <c r="DH143" t="n">
+        <v>101888</v>
+      </c>
+      <c r="DI143" t="n">
         <v>1240</v>
       </c>
-      <c r="DJ142" t="n">
+      <c r="DJ143" t="n">
         <v>15330</v>
       </c>
-      <c r="DK142" t="n">
+      <c r="DK143" t="n">
         <v>10780</v>
       </c>
-      <c r="DL142" t="n">
+      <c r="DL143" t="n">
         <v>18616</v>
       </c>
-      <c r="DM142" t="n">
+      <c r="DM143" t="n">
         <v>580</v>
       </c>
-      <c r="DN142" t="n">
+      <c r="DN143" t="n">
         <v>3025</v>
       </c>
-      <c r="DO142" t="n">
+      <c r="DO143" t="n">
         <v>7925</v>
       </c>
-      <c r="DP142" t="n">
+      <c r="DP143" t="n">
         <v>59100</v>
       </c>
-      <c r="DQ142" t="n">
+      <c r="DQ143" t="n">
         <v>1450</v>
       </c>
-      <c r="DR142" t="n">
+      <c r="DR143" t="n">
         <v>72207</v>
       </c>
-      <c r="DS142" t="n">
+      <c r="DS143" t="n">
         <v>5007</v>
       </c>
-      <c r="DT142" t="n">
+      <c r="DT143" t="n">
         <v>28151</v>
       </c>
-      <c r="DU142" t="n">
-        <v>2120106</v>
+      <c r="DU143" t="n">
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>
@@ -60347,7 +60726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60822,50 +61201,99 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>70</v>
+      </c>
+      <c r="O10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>19715</v>
       </c>
-      <c r="C10" t="n">
-        <v>7305</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C11" t="n">
+        <v>7385</v>
+      </c>
+      <c r="D11" t="n">
         <v>6665</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>5626</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>5825</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>6425</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>2720</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>5210</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2880</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>2330</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>2690</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>18416</v>
       </c>
-      <c r="N10" t="n">
-        <v>30880</v>
-      </c>
-      <c r="O10" t="n">
-        <v>116687</v>
+      <c r="N11" t="n">
+        <v>30950</v>
+      </c>
+      <c r="O11" t="n">
+        <v>116837</v>
       </c>
     </row>
   </sheetData>
@@ -62433,7 +62861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:S143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71076,62 +71504,123 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>650</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>435</v>
+      </c>
+      <c r="H142" t="n">
+        <v>190</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>134</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B143" t="n">
         <v>79857</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C143" t="n">
         <v>18179</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D143" t="n">
         <v>63837</v>
       </c>
-      <c r="E142" t="n">
-        <v>874354</v>
-      </c>
-      <c r="F142" t="n">
+      <c r="E143" t="n">
+        <v>875004</v>
+      </c>
+      <c r="F143" t="n">
         <v>6157</v>
       </c>
-      <c r="G142" t="n">
-        <v>34479</v>
-      </c>
-      <c r="H142" t="n">
-        <v>8540</v>
-      </c>
-      <c r="I142" t="n">
+      <c r="G143" t="n">
+        <v>34914</v>
+      </c>
+      <c r="H143" t="n">
+        <v>8730</v>
+      </c>
+      <c r="I143" t="n">
         <v>291370</v>
       </c>
-      <c r="J142" t="n">
+      <c r="J143" t="n">
         <v>5457</v>
       </c>
-      <c r="K142" t="n">
+      <c r="K143" t="n">
         <v>115829</v>
       </c>
-      <c r="L142" t="n">
+      <c r="L143" t="n">
         <v>33332</v>
       </c>
-      <c r="M142" t="n">
-        <v>5908</v>
-      </c>
-      <c r="N142" t="n">
+      <c r="M143" t="n">
+        <v>6042</v>
+      </c>
+      <c r="N143" t="n">
         <v>42</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O143" t="n">
         <v>24816</v>
       </c>
-      <c r="P142" t="n">
-        <v>430605</v>
-      </c>
-      <c r="Q142" t="n">
+      <c r="P143" t="n">
+        <v>430685</v>
+      </c>
+      <c r="Q143" t="n">
         <v>36784</v>
       </c>
-      <c r="R142" t="n">
+      <c r="R143" t="n">
         <v>90560</v>
       </c>
-      <c r="S142" t="n">
-        <v>2120106</v>
+      <c r="S143" t="n">
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>
@@ -71145,7 +71634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72563,129 +73052,139 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>101808</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="B143" t="n">
+        <v>101888</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B145" t="n">
-        <v>4620</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B146" t="n">
-        <v>9287</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B147" t="n">
-        <v>9052</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B148" t="n">
-        <v>11885</v>
+        <v>9052</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B149" t="n">
-        <v>10945</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B150" t="n">
-        <v>5985</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B151" t="n">
-        <v>7700</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B152" t="n">
-        <v>7774</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B153" t="n">
-        <v>7025</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B154" t="n">
-        <v>9800</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="n">
-        <v>10430</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B156" t="n">
+        <v>10430</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
         <v>2026</v>
       </c>
-      <c r="B156" t="n">
-        <v>7305</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="B157" t="n">
+        <v>7385</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>101808</v>
+      <c r="B158" t="n">
+        <v>101888</v>
       </c>
     </row>
   </sheetData>
@@ -82515,7 +83014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89883,53 +90382,105 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>70</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1339</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>80</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>406191</v>
-      </c>
-      <c r="C142" t="n">
+      <c r="B143" t="n">
+        <v>406261</v>
+      </c>
+      <c r="C143" t="n">
         <v>227389</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D143" t="n">
         <v>59882</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E143" t="n">
         <v>14979</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F143" t="n">
         <v>69937</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G143" t="n">
         <v>23490</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H143" t="n">
         <v>6860</v>
       </c>
-      <c r="I142" t="n">
-        <v>767453</v>
-      </c>
-      <c r="J142" t="n">
+      <c r="I143" t="n">
+        <v>768792</v>
+      </c>
+      <c r="J143" t="n">
         <v>223786</v>
       </c>
-      <c r="K142" t="n">
+      <c r="K143" t="n">
         <v>32935</v>
       </c>
-      <c r="L142" t="n">
+      <c r="L143" t="n">
         <v>63007</v>
       </c>
-      <c r="M142" t="n">
-        <v>101808</v>
-      </c>
-      <c r="N142" t="n">
+      <c r="M143" t="n">
+        <v>101888</v>
+      </c>
+      <c r="N143" t="n">
         <v>72207</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O143" t="n">
         <v>50182</v>
       </c>
-      <c r="P142" t="n">
-        <v>2120106</v>
+      <c r="P143" t="n">
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>
@@ -91497,7 +92048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92915,129 +93466,139 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>406191</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="B143" t="n">
+        <v>406261</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B145" t="n">
-        <v>21287</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B146" t="n">
-        <v>31458</v>
+        <v>21287</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B147" t="n">
-        <v>36331</v>
+        <v>31458</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B148" t="n">
-        <v>41722</v>
+        <v>36331</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B149" t="n">
-        <v>35690</v>
+        <v>41722</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B150" t="n">
-        <v>23272</v>
+        <v>35690</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B151" t="n">
-        <v>26164</v>
+        <v>23272</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B152" t="n">
-        <v>34239</v>
+        <v>26164</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B153" t="n">
-        <v>43523</v>
+        <v>34239</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B154" t="n">
-        <v>39596</v>
+        <v>43523</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="n">
-        <v>42029</v>
+        <v>39596</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B156" t="n">
+        <v>42029</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
         <v>2026</v>
       </c>
-      <c r="B156" t="n">
-        <v>30880</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="B157" t="n">
+        <v>30950</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>406191</v>
+      <c r="B158" t="n">
+        <v>406261</v>
       </c>
     </row>
   </sheetData>
@@ -97881,7 +98442,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>33600</v>
+        <v>33670</v>
       </c>
       <c r="S13" t="n">
         <v>190</v>
@@ -97941,7 +98502,7 @@
         <v>105</v>
       </c>
       <c r="AL13" t="n">
-        <v>3027</v>
+        <v>3467</v>
       </c>
       <c r="AM13" t="n">
         <v>165</v>
@@ -98043,7 +98604,7 @@
         <v>4680</v>
       </c>
       <c r="BT13" t="n">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="BU13" t="n">
         <v>1855</v>
@@ -98073,7 +98634,7 @@
         <v>2620</v>
       </c>
       <c r="CD13" t="n">
-        <v>995</v>
+        <v>1129</v>
       </c>
       <c r="CE13" t="n">
         <v>30</v>
@@ -98115,10 +98676,10 @@
         <v>765</v>
       </c>
       <c r="CR13" t="n">
-        <v>5992</v>
+        <v>6132</v>
       </c>
       <c r="CS13" t="n">
-        <v>1380</v>
+        <v>1500</v>
       </c>
       <c r="CT13" t="n">
         <v>125</v>
@@ -98133,7 +98694,7 @@
         <v>190</v>
       </c>
       <c r="CX13" t="n">
-        <v>2590</v>
+        <v>3025</v>
       </c>
       <c r="CY13" t="n">
         <v>1130</v>
@@ -98163,7 +98724,7 @@
         <v>2665</v>
       </c>
       <c r="DH13" t="n">
-        <v>7305</v>
+        <v>7385</v>
       </c>
       <c r="DI13" t="n">
         <v>420</v>
@@ -98202,7 +98763,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>201339</v>
+        <v>202828</v>
       </c>
     </row>
     <row r="14">
@@ -98260,7 +98821,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>439126</v>
+        <v>439196</v>
       </c>
       <c r="S14" t="n">
         <v>975</v>
@@ -98320,7 +98881,7 @@
         <v>477</v>
       </c>
       <c r="AL14" t="n">
-        <v>51568</v>
+        <v>52008</v>
       </c>
       <c r="AM14" t="n">
         <v>4755</v>
@@ -98422,7 +98983,7 @@
         <v>28374</v>
       </c>
       <c r="BT14" t="n">
-        <v>5705</v>
+        <v>5775</v>
       </c>
       <c r="BU14" t="n">
         <v>6605</v>
@@ -98452,7 +99013,7 @@
         <v>16350</v>
       </c>
       <c r="CD14" t="n">
-        <v>5908</v>
+        <v>6042</v>
       </c>
       <c r="CE14" t="n">
         <v>145</v>
@@ -98494,10 +99055,10 @@
         <v>12167</v>
       </c>
       <c r="CR14" t="n">
-        <v>66712</v>
+        <v>66852</v>
       </c>
       <c r="CS14" t="n">
-        <v>2835</v>
+        <v>2955</v>
       </c>
       <c r="CT14" t="n">
         <v>1310</v>
@@ -98512,7 +99073,7 @@
         <v>8936</v>
       </c>
       <c r="CX14" t="n">
-        <v>18892</v>
+        <v>19327</v>
       </c>
       <c r="CY14" t="n">
         <v>13984</v>
@@ -98542,7 +99103,7 @@
         <v>24333</v>
       </c>
       <c r="DH14" t="n">
-        <v>101808</v>
+        <v>101888</v>
       </c>
       <c r="DI14" t="n">
         <v>1240</v>
@@ -98581,7 +99142,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2120106</v>
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>
@@ -99358,16 +99919,16 @@
         <v>6525</v>
       </c>
       <c r="E13" t="n">
-        <v>82714</v>
+        <v>83364</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
       </c>
       <c r="G13" t="n">
-        <v>3293</v>
+        <v>3728</v>
       </c>
       <c r="H13" t="n">
-        <v>2260</v>
+        <v>2450</v>
       </c>
       <c r="I13" t="n">
         <v>26484</v>
@@ -99382,7 +99943,7 @@
         <v>2694</v>
       </c>
       <c r="M13" t="n">
-        <v>995</v>
+        <v>1129</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -99391,7 +99952,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>36156</v>
+        <v>36236</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99400,7 +99961,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>201339</v>
+        <v>202828</v>
       </c>
     </row>
     <row r="14">
@@ -99419,16 +99980,16 @@
         <v>63837</v>
       </c>
       <c r="E14" t="n">
-        <v>874354</v>
+        <v>875004</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
       </c>
       <c r="G14" t="n">
-        <v>34479</v>
+        <v>34914</v>
       </c>
       <c r="H14" t="n">
-        <v>8540</v>
+        <v>8730</v>
       </c>
       <c r="I14" t="n">
         <v>291370</v>
@@ -99443,7 +100004,7 @@
         <v>33332</v>
       </c>
       <c r="M14" t="n">
-        <v>5908</v>
+        <v>6042</v>
       </c>
       <c r="N14" t="n">
         <v>42</v>
@@ -99452,7 +100013,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>430605</v>
+        <v>430685</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -99461,7 +100022,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2120106</v>
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>
@@ -100115,7 +100676,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>30880</v>
+        <v>30950</v>
       </c>
       <c r="C13" t="n">
         <v>18416</v>
@@ -100136,7 +100697,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>84652</v>
+        <v>85991</v>
       </c>
       <c r="J13" t="n">
         <v>19715</v>
@@ -100148,7 +100709,7 @@
         <v>6665</v>
       </c>
       <c r="M13" t="n">
-        <v>7305</v>
+        <v>7385</v>
       </c>
       <c r="N13" t="n">
         <v>6425</v>
@@ -100157,7 +100718,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>201339</v>
+        <v>202828</v>
       </c>
     </row>
     <row r="14">
@@ -100167,7 +100728,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>406191</v>
+        <v>406261</v>
       </c>
       <c r="C14" t="n">
         <v>227389</v>
@@ -100188,7 +100749,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>767453</v>
+        <v>768792</v>
       </c>
       <c r="J14" t="n">
         <v>223786</v>
@@ -100200,7 +100761,7 @@
         <v>63007</v>
       </c>
       <c r="M14" t="n">
-        <v>101808</v>
+        <v>101888</v>
       </c>
       <c r="N14" t="n">
         <v>72207</v>
@@ -100209,7 +100770,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2120106</v>
+        <v>2121595</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -11361,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1995</v>
+        <v>1920</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2373</v>
+        <v>2263</v>
       </c>
       <c r="S30" t="n">
         <v>100</v>
@@ -11806,7 +11806,7 @@
         <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -12119,7 +12119,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2757</v>
+        <v>2587</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -12498,7 +12498,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3291</v>
+        <v>3191</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -12564,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -12877,7 +12877,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3525</v>
+        <v>3425</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -12943,7 +12943,7 @@
         <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -13256,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2497</v>
+        <v>2422</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -13322,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -14393,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1747</v>
+        <v>1647</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -15151,7 +15151,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4030</v>
+        <v>3980</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -15530,7 +15530,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3105</v>
+        <v>3100</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -15596,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4170</v>
+        <v>4140</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -16733,7 +16733,7 @@
         <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -54188,10 +54188,10 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T142" t="n">
         <v>0</v>
@@ -54206,7 +54206,7 @@
         <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
@@ -54227,7 +54227,7 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF142" t="n">
         <v>0</v>
@@ -54254,7 +54254,7 @@
         <v>0</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
@@ -54443,7 +54443,7 @@
         <v>435</v>
       </c>
       <c r="CY142" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CZ142" t="n">
         <v>0</v>
@@ -54509,7 +54509,7 @@
         <v>0</v>
       </c>
       <c r="DU142" t="n">
-        <v>1489</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="143">
@@ -54567,10 +54567,10 @@
         <v>105</v>
       </c>
       <c r="R143" t="n">
-        <v>439196</v>
+        <v>438411</v>
       </c>
       <c r="S143" t="n">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="T143" t="n">
         <v>960</v>
@@ -54585,7 +54585,7 @@
         <v>24789</v>
       </c>
       <c r="X143" t="n">
-        <v>4890</v>
+        <v>5020</v>
       </c>
       <c r="Y143" t="n">
         <v>2945</v>
@@ -54606,7 +54606,7 @@
         <v>10</v>
       </c>
       <c r="AE143" t="n">
-        <v>545</v>
+        <v>595</v>
       </c>
       <c r="AF143" t="n">
         <v>145</v>
@@ -54633,7 +54633,7 @@
         <v>4755</v>
       </c>
       <c r="AN143" t="n">
-        <v>3715</v>
+        <v>4665</v>
       </c>
       <c r="AO143" t="n">
         <v>282</v>
@@ -54822,7 +54822,7 @@
         <v>19327</v>
       </c>
       <c r="CY143" t="n">
-        <v>13984</v>
+        <v>14109</v>
       </c>
       <c r="CZ143" t="n">
         <v>223786</v>
@@ -54888,7 +54888,7 @@
         <v>28151</v>
       </c>
       <c r="DU143" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -55074,10 +55074,10 @@
         <v>195</v>
       </c>
       <c r="N3" t="n">
-        <v>3205</v>
+        <v>3155</v>
       </c>
       <c r="O3" t="n">
-        <v>9080</v>
+        <v>9030</v>
       </c>
     </row>
     <row r="4">
@@ -55123,10 +55123,10 @@
         <v>2710</v>
       </c>
       <c r="N4" t="n">
-        <v>3045</v>
+        <v>3040</v>
       </c>
       <c r="O4" t="n">
-        <v>10650</v>
+        <v>10645</v>
       </c>
     </row>
     <row r="5">
@@ -55270,10 +55270,10 @@
         <v>2110</v>
       </c>
       <c r="N7" t="n">
-        <v>4115</v>
+        <v>4085</v>
       </c>
       <c r="O7" t="n">
-        <v>8980</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="8">
@@ -55613,10 +55613,10 @@
         <v>21112</v>
       </c>
       <c r="N14" t="n">
-        <v>41722</v>
+        <v>41637</v>
       </c>
       <c r="O14" t="n">
-        <v>117702</v>
+        <v>117617</v>
       </c>
     </row>
   </sheetData>
@@ -61241,10 +61241,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -61290,10 +61290,10 @@
         <v>18416</v>
       </c>
       <c r="N11" t="n">
-        <v>30950</v>
+        <v>30980</v>
       </c>
       <c r="O11" t="n">
-        <v>116837</v>
+        <v>116867</v>
       </c>
     </row>
   </sheetData>
@@ -64624,7 +64624,7 @@
         <v>123</v>
       </c>
       <c r="E29" t="n">
-        <v>2575</v>
+        <v>2500</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -64639,7 +64639,7 @@
         <v>1578</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -64685,7 +64685,7 @@
         <v>328</v>
       </c>
       <c r="E30" t="n">
-        <v>4197</v>
+        <v>4087</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -64700,7 +64700,7 @@
         <v>885</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
         <v>270</v>
@@ -64746,7 +64746,7 @@
         <v>328</v>
       </c>
       <c r="E31" t="n">
-        <v>4142</v>
+        <v>3972</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -64761,7 +64761,7 @@
         <v>1325</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K31" t="n">
         <v>340</v>
@@ -64807,7 +64807,7 @@
         <v>158</v>
       </c>
       <c r="E32" t="n">
-        <v>4961</v>
+        <v>4861</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -64822,7 +64822,7 @@
         <v>565</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
         <v>1280</v>
@@ -64868,7 +64868,7 @@
         <v>236</v>
       </c>
       <c r="E33" t="n">
-        <v>4760</v>
+        <v>4660</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -64883,7 +64883,7 @@
         <v>1630</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
         <v>325</v>
@@ -64929,7 +64929,7 @@
         <v>225</v>
       </c>
       <c r="E34" t="n">
-        <v>3782</v>
+        <v>3707</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -64944,7 +64944,7 @@
         <v>1585</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
         <v>720</v>
@@ -65112,7 +65112,7 @@
         <v>202</v>
       </c>
       <c r="E37" t="n">
-        <v>2387</v>
+        <v>2287</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -65127,7 +65127,7 @@
         <v>695</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
         <v>815</v>
@@ -65234,7 +65234,7 @@
         <v>147</v>
       </c>
       <c r="E39" t="n">
-        <v>5270</v>
+        <v>5220</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -65249,7 +65249,7 @@
         <v>1120</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
         <v>960</v>
@@ -65295,7 +65295,7 @@
         <v>360</v>
       </c>
       <c r="E40" t="n">
-        <v>4850</v>
+        <v>4845</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -65310,7 +65310,7 @@
         <v>1500</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
         <v>975</v>
@@ -65478,7 +65478,7 @@
         <v>325</v>
       </c>
       <c r="E43" t="n">
-        <v>6430</v>
+        <v>6400</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -65493,7 +65493,7 @@
         <v>1205</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K43" t="n">
         <v>550</v>
@@ -71514,10 +71514,10 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="E142" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -71532,7 +71532,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -71559,7 +71559,7 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>1489</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="143">
@@ -71575,10 +71575,10 @@
         <v>18179</v>
       </c>
       <c r="D143" t="n">
-        <v>63837</v>
+        <v>64162</v>
       </c>
       <c r="E143" t="n">
-        <v>875004</v>
+        <v>874219</v>
       </c>
       <c r="F143" t="n">
         <v>6157</v>
@@ -71593,7 +71593,7 @@
         <v>291370</v>
       </c>
       <c r="J143" t="n">
-        <v>5457</v>
+        <v>6407</v>
       </c>
       <c r="K143" t="n">
         <v>115829</v>
@@ -71620,7 +71620,7 @@
         <v>90560</v>
       </c>
       <c r="S143" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -84510,7 +84510,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1995</v>
+        <v>1920</v>
       </c>
       <c r="C29" t="n">
         <v>1519</v>
@@ -84531,7 +84531,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1648</v>
+        <v>1723</v>
       </c>
       <c r="J29" t="n">
         <v>1203</v>
@@ -84562,7 +84562,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2373</v>
+        <v>2263</v>
       </c>
       <c r="C30" t="n">
         <v>1320</v>
@@ -84583,7 +84583,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2988</v>
+        <v>3098</v>
       </c>
       <c r="J30" t="n">
         <v>715</v>
@@ -84614,7 +84614,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2757</v>
+        <v>2587</v>
       </c>
       <c r="C31" t="n">
         <v>798</v>
@@ -84635,7 +84635,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4400</v>
+        <v>4570</v>
       </c>
       <c r="J31" t="n">
         <v>770</v>
@@ -84666,7 +84666,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3291</v>
+        <v>3191</v>
       </c>
       <c r="C32" t="n">
         <v>1635</v>
@@ -84687,7 +84687,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2973</v>
+        <v>3073</v>
       </c>
       <c r="J32" t="n">
         <v>565</v>
@@ -84718,7 +84718,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3525</v>
+        <v>3425</v>
       </c>
       <c r="C33" t="n">
         <v>1370</v>
@@ -84739,7 +84739,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2606</v>
+        <v>2706</v>
       </c>
       <c r="J33" t="n">
         <v>1135</v>
@@ -84770,7 +84770,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2497</v>
+        <v>2422</v>
       </c>
       <c r="C34" t="n">
         <v>2235</v>
@@ -84791,7 +84791,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3125</v>
+        <v>3200</v>
       </c>
       <c r="J34" t="n">
         <v>1230</v>
@@ -84926,7 +84926,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1747</v>
+        <v>1647</v>
       </c>
       <c r="C37" t="n">
         <v>1280</v>
@@ -84947,7 +84947,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1787</v>
+        <v>1887</v>
       </c>
       <c r="J37" t="n">
         <v>455</v>
@@ -85030,7 +85030,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3205</v>
+        <v>3155</v>
       </c>
       <c r="C39" t="n">
         <v>195</v>
@@ -85051,7 +85051,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2297</v>
+        <v>2347</v>
       </c>
       <c r="J39" t="n">
         <v>1070</v>
@@ -85082,7 +85082,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3045</v>
+        <v>3040</v>
       </c>
       <c r="C40" t="n">
         <v>2710</v>
@@ -85103,7 +85103,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3105</v>
+        <v>3110</v>
       </c>
       <c r="J40" t="n">
         <v>1165</v>
@@ -85238,7 +85238,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4115</v>
+        <v>4085</v>
       </c>
       <c r="C43" t="n">
         <v>2110</v>
@@ -85259,7 +85259,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3630</v>
+        <v>3660</v>
       </c>
       <c r="J43" t="n">
         <v>975</v>
@@ -90386,7 +90386,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -90407,7 +90407,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1339</v>
+        <v>1799</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -90428,7 +90428,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>1489</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="143">
@@ -90438,7 +90438,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>406261</v>
+        <v>405476</v>
       </c>
       <c r="C143" t="n">
         <v>227389</v>
@@ -90459,7 +90459,7 @@
         <v>6860</v>
       </c>
       <c r="I143" t="n">
-        <v>768792</v>
+        <v>770067</v>
       </c>
       <c r="J143" t="n">
         <v>223786</v>
@@ -90480,7 +90480,7 @@
         <v>50182</v>
       </c>
       <c r="P143" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -92340,7 +92340,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1995</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="30">
@@ -92350,7 +92350,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2373</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="31">
@@ -92360,7 +92360,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2757</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="32">
@@ -92370,7 +92370,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3291</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="33">
@@ -92380,7 +92380,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3525</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="34">
@@ -92390,7 +92390,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2497</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="35">
@@ -92420,7 +92420,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1747</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="38">
@@ -92440,7 +92440,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3205</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="40">
@@ -92450,7 +92450,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3045</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="41">
@@ -92480,7 +92480,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4115</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="44">
@@ -93470,7 +93470,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143">
@@ -93480,7 +93480,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>406261</v>
+        <v>405476</v>
       </c>
     </row>
     <row r="145">
@@ -93516,7 +93516,7 @@
         <v>2017</v>
       </c>
       <c r="B148" t="n">
-        <v>36331</v>
+        <v>35601</v>
       </c>
     </row>
     <row r="149">
@@ -93524,7 +93524,7 @@
         <v>2018</v>
       </c>
       <c r="B149" t="n">
-        <v>41722</v>
+        <v>41637</v>
       </c>
     </row>
     <row r="150">
@@ -93588,7 +93588,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>30950</v>
+        <v>30980</v>
       </c>
     </row>
     <row r="158">
@@ -93598,7 +93598,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>406261</v>
+        <v>405476</v>
       </c>
     </row>
   </sheetData>
@@ -95049,7 +95049,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>36331</v>
+        <v>35601</v>
       </c>
       <c r="S4" t="n">
         <v>140</v>
@@ -95115,7 +95115,7 @@
         <v>125</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -95426,7 +95426,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>45277</v>
+        <v>45192</v>
       </c>
       <c r="S5" t="n">
         <v>175</v>
@@ -95492,7 +95492,7 @@
         <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -98442,10 +98442,10 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>33670</v>
+        <v>33700</v>
       </c>
       <c r="S13" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="T13" t="n">
         <v>590</v>
@@ -98460,7 +98460,7 @@
         <v>2800</v>
       </c>
       <c r="X13" t="n">
-        <v>900</v>
+        <v>1030</v>
       </c>
       <c r="Y13" t="n">
         <v>95</v>
@@ -98481,7 +98481,7 @@
         <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -98508,7 +98508,7 @@
         <v>165</v>
       </c>
       <c r="AN13" t="n">
-        <v>1010</v>
+        <v>1145</v>
       </c>
       <c r="AO13" t="n">
         <v>117</v>
@@ -98697,7 +98697,7 @@
         <v>3025</v>
       </c>
       <c r="CY13" t="n">
-        <v>1130</v>
+        <v>1255</v>
       </c>
       <c r="CZ13" t="n">
         <v>19715</v>
@@ -98763,7 +98763,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>202828</v>
+        <v>203318</v>
       </c>
     </row>
     <row r="14">
@@ -98821,10 +98821,10 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>439196</v>
+        <v>438411</v>
       </c>
       <c r="S14" t="n">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="T14" t="n">
         <v>960</v>
@@ -98839,7 +98839,7 @@
         <v>24789</v>
       </c>
       <c r="X14" t="n">
-        <v>4890</v>
+        <v>5020</v>
       </c>
       <c r="Y14" t="n">
         <v>2945</v>
@@ -98860,7 +98860,7 @@
         <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>545</v>
+        <v>595</v>
       </c>
       <c r="AF14" t="n">
         <v>145</v>
@@ -98887,7 +98887,7 @@
         <v>4755</v>
       </c>
       <c r="AN14" t="n">
-        <v>3715</v>
+        <v>4665</v>
       </c>
       <c r="AO14" t="n">
         <v>282</v>
@@ -99076,7 +99076,7 @@
         <v>19327</v>
       </c>
       <c r="CY14" t="n">
-        <v>13984</v>
+        <v>14109</v>
       </c>
       <c r="CZ14" t="n">
         <v>223786</v>
@@ -99142,7 +99142,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -99388,7 +99388,7 @@
         <v>2157</v>
       </c>
       <c r="E4" t="n">
-        <v>48458</v>
+        <v>47728</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -99403,7 +99403,7 @@
         <v>13812</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="K4" t="n">
         <v>7433</v>
@@ -99447,7 +99447,7 @@
         <v>4090</v>
       </c>
       <c r="E5" t="n">
-        <v>71667</v>
+        <v>71582</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -99462,7 +99462,7 @@
         <v>17216</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K5" t="n">
         <v>7945</v>
@@ -99916,10 +99916,10 @@
         <v>2925</v>
       </c>
       <c r="D13" t="n">
-        <v>6525</v>
+        <v>6850</v>
       </c>
       <c r="E13" t="n">
-        <v>83364</v>
+        <v>83394</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99934,7 +99934,7 @@
         <v>26484</v>
       </c>
       <c r="J13" t="n">
-        <v>1432</v>
+        <v>1567</v>
       </c>
       <c r="K13" t="n">
         <v>13336</v>
@@ -99961,7 +99961,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>202828</v>
+        <v>203318</v>
       </c>
     </row>
     <row r="14">
@@ -99977,10 +99977,10 @@
         <v>18179</v>
       </c>
       <c r="D14" t="n">
-        <v>63837</v>
+        <v>64162</v>
       </c>
       <c r="E14" t="n">
-        <v>875004</v>
+        <v>874219</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -99995,7 +99995,7 @@
         <v>291370</v>
       </c>
       <c r="J14" t="n">
-        <v>5457</v>
+        <v>6407</v>
       </c>
       <c r="K14" t="n">
         <v>115829</v>
@@ -100022,7 +100022,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -100226,7 +100226,7 @@
         <v>2017</v>
       </c>
       <c r="B4" t="n">
-        <v>36331</v>
+        <v>35601</v>
       </c>
       <c r="C4" t="n">
         <v>15242</v>
@@ -100247,7 +100247,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>28867</v>
+        <v>29597</v>
       </c>
       <c r="J4" t="n">
         <v>10537</v>
@@ -100276,7 +100276,7 @@
         <v>2018</v>
       </c>
       <c r="B5" t="n">
-        <v>41722</v>
+        <v>41637</v>
       </c>
       <c r="C5" t="n">
         <v>21112</v>
@@ -100297,7 +100297,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>43631</v>
+        <v>43716</v>
       </c>
       <c r="J5" t="n">
         <v>13913</v>
@@ -100676,7 +100676,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>30950</v>
+        <v>30980</v>
       </c>
       <c r="C13" t="n">
         <v>18416</v>
@@ -100697,7 +100697,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>85991</v>
+        <v>86451</v>
       </c>
       <c r="J13" t="n">
         <v>19715</v>
@@ -100718,7 +100718,7 @@
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>202828</v>
+        <v>203318</v>
       </c>
     </row>
     <row r="14">
@@ -100728,7 +100728,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>406261</v>
+        <v>405476</v>
       </c>
       <c r="C14" t="n">
         <v>227389</v>
@@ -100749,7 +100749,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>768792</v>
+        <v>770067</v>
       </c>
       <c r="J14" t="n">
         <v>223786</v>
@@ -100770,7 +100770,7 @@
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2121595</v>
+        <v>2122085</v>
       </c>
     </row>
   </sheetData>
@@ -102510,10 +102510,10 @@
         <v>1519</v>
       </c>
       <c r="N5" t="n">
-        <v>1995</v>
+        <v>1920</v>
       </c>
       <c r="O5" t="n">
-        <v>5852</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="6">
@@ -102559,10 +102559,10 @@
         <v>1320</v>
       </c>
       <c r="N6" t="n">
-        <v>2373</v>
+        <v>2263</v>
       </c>
       <c r="O6" t="n">
-        <v>6540</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="7">
@@ -102608,10 +102608,10 @@
         <v>798</v>
       </c>
       <c r="N7" t="n">
-        <v>2757</v>
+        <v>2587</v>
       </c>
       <c r="O7" t="n">
-        <v>6230</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="8">
@@ -102657,10 +102657,10 @@
         <v>1635</v>
       </c>
       <c r="N8" t="n">
-        <v>3291</v>
+        <v>3191</v>
       </c>
       <c r="O8" t="n">
-        <v>7901</v>
+        <v>7801</v>
       </c>
     </row>
     <row r="9">
@@ -102706,10 +102706,10 @@
         <v>1370</v>
       </c>
       <c r="N9" t="n">
-        <v>3525</v>
+        <v>3425</v>
       </c>
       <c r="O9" t="n">
-        <v>8060</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="10">
@@ -102755,10 +102755,10 @@
         <v>2235</v>
       </c>
       <c r="N10" t="n">
-        <v>2497</v>
+        <v>2422</v>
       </c>
       <c r="O10" t="n">
-        <v>9331</v>
+        <v>9256</v>
       </c>
     </row>
     <row r="11">
@@ -102902,10 +102902,10 @@
         <v>1280</v>
       </c>
       <c r="N13" t="n">
-        <v>1747</v>
+        <v>1647</v>
       </c>
       <c r="O13" t="n">
-        <v>4997</v>
+        <v>4897</v>
       </c>
     </row>
     <row r="14">
@@ -102951,10 +102951,10 @@
         <v>15242</v>
       </c>
       <c r="N14" t="n">
-        <v>36331</v>
+        <v>35601</v>
       </c>
       <c r="O14" t="n">
-        <v>87102</v>
+        <v>86372</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54188,7 +54188,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>100</v>
+        <v>885</v>
       </c>
       <c r="S142" t="n">
         <v>20</v>
@@ -54338,7 +54338,7 @@
         <v>0</v>
       </c>
       <c r="BP142" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BQ142" t="n">
         <v>0</v>
@@ -54500,7 +54500,7 @@
         <v>0</v>
       </c>
       <c r="DR142" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="DS142" t="n">
         <v>0</v>
@@ -54509,7 +54509,7 @@
         <v>0</v>
       </c>
       <c r="DU142" t="n">
-        <v>1979</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="143">
@@ -54567,7 +54567,7 @@
         <v>105</v>
       </c>
       <c r="R143" t="n">
-        <v>438411</v>
+        <v>439196</v>
       </c>
       <c r="S143" t="n">
         <v>995</v>
@@ -54717,7 +54717,7 @@
         <v>7565</v>
       </c>
       <c r="BP143" t="n">
-        <v>96646</v>
+        <v>96701</v>
       </c>
       <c r="BQ143" t="n">
         <v>22615</v>
@@ -54879,7 +54879,7 @@
         <v>1450</v>
       </c>
       <c r="DR143" t="n">
-        <v>72207</v>
+        <v>72682</v>
       </c>
       <c r="DS143" t="n">
         <v>5007</v>
@@ -54888,7 +54888,7 @@
         <v>28151</v>
       </c>
       <c r="DU143" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>
@@ -61220,10 +61220,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -61238,13 +61238,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N10" t="n">
-        <v>100</v>
+        <v>875</v>
       </c>
       <c r="O10" t="n">
-        <v>180</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="11">
@@ -61269,10 +61269,10 @@
         <v>5825</v>
       </c>
       <c r="G11" t="n">
-        <v>6425</v>
+        <v>6900</v>
       </c>
       <c r="H11" t="n">
-        <v>2720</v>
+        <v>2730</v>
       </c>
       <c r="I11" t="n">
         <v>5210</v>
@@ -61287,13 +61287,13 @@
         <v>2690</v>
       </c>
       <c r="M11" t="n">
-        <v>18416</v>
+        <v>18471</v>
       </c>
       <c r="N11" t="n">
-        <v>30980</v>
+        <v>31755</v>
       </c>
       <c r="O11" t="n">
-        <v>116867</v>
+        <v>118182</v>
       </c>
     </row>
   </sheetData>
@@ -71517,7 +71517,7 @@
         <v>325</v>
       </c>
       <c r="E142" t="n">
-        <v>680</v>
+        <v>1940</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -71550,7 +71550,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -71559,7 +71559,7 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>1979</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="143">
@@ -71578,7 +71578,7 @@
         <v>64162</v>
       </c>
       <c r="E143" t="n">
-        <v>874219</v>
+        <v>875479</v>
       </c>
       <c r="F143" t="n">
         <v>6157</v>
@@ -71611,7 +71611,7 @@
         <v>24816</v>
       </c>
       <c r="P143" t="n">
-        <v>430685</v>
+        <v>430740</v>
       </c>
       <c r="Q143" t="n">
         <v>36784</v>
@@ -71620,7 +71620,7 @@
         <v>90560</v>
       </c>
       <c r="S143" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>
@@ -77330,7 +77330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B153"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78708,129 +78708,139 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>72207</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="B139" t="n">
+        <v>72682</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B141" t="n">
-        <v>1540</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B142" t="n">
-        <v>1524</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B143" t="n">
-        <v>1647</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B144" t="n">
-        <v>4030</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B145" t="n">
-        <v>6012</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B146" t="n">
-        <v>4976</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B147" t="n">
-        <v>4864</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B148" t="n">
-        <v>7007</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B149" t="n">
-        <v>8675</v>
+        <v>7007</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B150" t="n">
-        <v>12945</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="n">
-        <v>12562</v>
+        <v>12945</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B152" t="n">
+        <v>12562</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
         <v>2026</v>
       </c>
-      <c r="B152" t="n">
-        <v>6425</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="B153" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>72207</v>
+      <c r="B154" t="n">
+        <v>72682</v>
       </c>
     </row>
   </sheetData>
@@ -78844,7 +78854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79662,105 +79672,115 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>32935</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="B83" t="n">
+        <v>32945</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B85" t="n">
-        <v>3555</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B86" t="n">
-        <v>3730</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B87" t="n">
-        <v>2620</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B88" t="n">
-        <v>2735</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B89" t="n">
-        <v>3590</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B90" t="n">
-        <v>4330</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B91" t="n">
-        <v>4975</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B92" t="n">
-        <v>4680</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
         <v>2026</v>
       </c>
-      <c r="B93" t="n">
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="B94" t="n">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>32935</v>
+      <c r="B95" t="n">
+        <v>32945</v>
       </c>
     </row>
   </sheetData>
@@ -90386,10 +90406,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>100</v>
+        <v>875</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -90413,7 +90433,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -90422,13 +90442,13 @@
         <v>80</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>1979</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="143">
@@ -90438,10 +90458,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>405476</v>
+        <v>406251</v>
       </c>
       <c r="C143" t="n">
-        <v>227389</v>
+        <v>227444</v>
       </c>
       <c r="D143" t="n">
         <v>59882</v>
@@ -90465,7 +90485,7 @@
         <v>223786</v>
       </c>
       <c r="K143" t="n">
-        <v>32935</v>
+        <v>32945</v>
       </c>
       <c r="L143" t="n">
         <v>63007</v>
@@ -90474,13 +90494,13 @@
         <v>101888</v>
       </c>
       <c r="N143" t="n">
-        <v>72207</v>
+        <v>72682</v>
       </c>
       <c r="O143" t="n">
         <v>50182</v>
       </c>
       <c r="P143" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>
@@ -90494,7 +90514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91912,129 +91932,139 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>227389</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="B143" t="n">
+        <v>227444</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B145" t="n">
-        <v>6668</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B146" t="n">
-        <v>8792</v>
+        <v>6668</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B147" t="n">
-        <v>15242</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B148" t="n">
-        <v>21112</v>
+        <v>15242</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B149" t="n">
-        <v>21273</v>
+        <v>21112</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B150" t="n">
-        <v>15805</v>
+        <v>21273</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B151" t="n">
-        <v>18542</v>
+        <v>15805</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B152" t="n">
-        <v>22238</v>
+        <v>18542</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B153" t="n">
-        <v>23439</v>
+        <v>22238</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B154" t="n">
-        <v>27420</v>
+        <v>23439</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="n">
-        <v>28442</v>
+        <v>27420</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B156" t="n">
+        <v>28442</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
         <v>2026</v>
       </c>
-      <c r="B156" t="n">
-        <v>18416</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="B157" t="n">
+        <v>18471</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>227389</v>
+      <c r="B158" t="n">
+        <v>227444</v>
       </c>
     </row>
   </sheetData>
@@ -93470,7 +93500,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>100</v>
+        <v>875</v>
       </c>
     </row>
     <row r="143">
@@ -93480,7 +93510,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>405476</v>
+        <v>406251</v>
       </c>
     </row>
     <row r="145">
@@ -93588,7 +93618,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>30980</v>
+        <v>31755</v>
       </c>
     </row>
     <row r="158">
@@ -93598,7 +93628,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>405476</v>
+        <v>406251</v>
       </c>
     </row>
   </sheetData>
@@ -98442,7 +98472,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>33700</v>
+        <v>34485</v>
       </c>
       <c r="S13" t="n">
         <v>210</v>
@@ -98592,7 +98622,7 @@
         <v>535</v>
       </c>
       <c r="BP13" t="n">
-        <v>7540</v>
+        <v>7595</v>
       </c>
       <c r="BQ13" t="n">
         <v>2055</v>
@@ -98754,7 +98784,7 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>6425</v>
+        <v>6900</v>
       </c>
       <c r="DS13" t="n">
         <v>355</v>
@@ -98763,7 +98793,7 @@
         <v>2285</v>
       </c>
       <c r="DU13" t="n">
-        <v>203318</v>
+        <v>204633</v>
       </c>
     </row>
     <row r="14">
@@ -98821,7 +98851,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>438411</v>
+        <v>439196</v>
       </c>
       <c r="S14" t="n">
         <v>995</v>
@@ -98971,7 +99001,7 @@
         <v>7565</v>
       </c>
       <c r="BP14" t="n">
-        <v>96646</v>
+        <v>96701</v>
       </c>
       <c r="BQ14" t="n">
         <v>22615</v>
@@ -99133,7 +99163,7 @@
         <v>1450</v>
       </c>
       <c r="DR14" t="n">
-        <v>72207</v>
+        <v>72682</v>
       </c>
       <c r="DS14" t="n">
         <v>5007</v>
@@ -99142,7 +99172,7 @@
         <v>28151</v>
       </c>
       <c r="DU14" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>
@@ -99919,7 +99949,7 @@
         <v>6850</v>
       </c>
       <c r="E13" t="n">
-        <v>83394</v>
+        <v>84654</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -99952,7 +99982,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>36236</v>
+        <v>36291</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -99961,7 +99991,7 @@
         <v>11227</v>
       </c>
       <c r="S13" t="n">
-        <v>203318</v>
+        <v>204633</v>
       </c>
     </row>
     <row r="14">
@@ -99980,7 +100010,7 @@
         <v>64162</v>
       </c>
       <c r="E14" t="n">
-        <v>874219</v>
+        <v>875479</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -100013,7 +100043,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>430685</v>
+        <v>430740</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -100022,7 +100052,7 @@
         <v>90560</v>
       </c>
       <c r="S14" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>
@@ -100676,10 +100706,10 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>30980</v>
+        <v>31755</v>
       </c>
       <c r="C13" t="n">
-        <v>18416</v>
+        <v>18471</v>
       </c>
       <c r="D13" t="n">
         <v>5825</v>
@@ -100703,7 +100733,7 @@
         <v>19715</v>
       </c>
       <c r="K13" t="n">
-        <v>2720</v>
+        <v>2730</v>
       </c>
       <c r="L13" t="n">
         <v>6665</v>
@@ -100712,13 +100742,13 @@
         <v>7385</v>
       </c>
       <c r="N13" t="n">
-        <v>6425</v>
+        <v>6900</v>
       </c>
       <c r="O13" t="n">
         <v>5210</v>
       </c>
       <c r="P13" t="n">
-        <v>203318</v>
+        <v>204633</v>
       </c>
     </row>
     <row r="14">
@@ -100728,10 +100758,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>405476</v>
+        <v>406251</v>
       </c>
       <c r="C14" t="n">
-        <v>227389</v>
+        <v>227444</v>
       </c>
       <c r="D14" t="n">
         <v>59882</v>
@@ -100755,7 +100785,7 @@
         <v>223786</v>
       </c>
       <c r="K14" t="n">
-        <v>32935</v>
+        <v>32945</v>
       </c>
       <c r="L14" t="n">
         <v>63007</v>
@@ -100764,13 +100794,13 @@
         <v>101888</v>
       </c>
       <c r="N14" t="n">
-        <v>72207</v>
+        <v>72682</v>
       </c>
       <c r="O14" t="n">
         <v>50182</v>
       </c>
       <c r="P14" t="n">
-        <v>2122085</v>
+        <v>2123400</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54149,7 +54149,7 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -54167,7 +54167,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -54386,13 +54386,13 @@
         <v>0</v>
       </c>
       <c r="CF142" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="CG142" t="n">
         <v>0</v>
       </c>
       <c r="CH142" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CI142" t="n">
         <v>0</v>
@@ -54491,7 +54491,7 @@
         <v>0</v>
       </c>
       <c r="DO142" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="DP142" t="n">
         <v>0</v>
@@ -54506,10 +54506,10 @@
         <v>0</v>
       </c>
       <c r="DT142" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>3294</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="143">
@@ -54528,7 +54528,7 @@
         <v>150</v>
       </c>
       <c r="E143" t="n">
-        <v>72940</v>
+        <v>73080</v>
       </c>
       <c r="F143" t="n">
         <v>500</v>
@@ -54546,7 +54546,7 @@
         <v>22638</v>
       </c>
       <c r="K143" t="n">
-        <v>17625</v>
+        <v>17770</v>
       </c>
       <c r="L143" t="n">
         <v>6040</v>
@@ -54765,13 +54765,13 @@
         <v>145</v>
       </c>
       <c r="CF143" t="n">
-        <v>22031</v>
+        <v>22331</v>
       </c>
       <c r="CG143" t="n">
         <v>3692</v>
       </c>
       <c r="CH143" t="n">
-        <v>1665</v>
+        <v>1690</v>
       </c>
       <c r="CI143" t="n">
         <v>470</v>
@@ -54870,7 +54870,7 @@
         <v>3025</v>
       </c>
       <c r="DO143" t="n">
-        <v>7925</v>
+        <v>8085</v>
       </c>
       <c r="DP143" t="n">
         <v>59100</v>
@@ -54885,10 +54885,10 @@
         <v>5007</v>
       </c>
       <c r="DT143" t="n">
-        <v>28151</v>
+        <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>
@@ -61226,7 +61226,7 @@
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -61238,13 +61238,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="N10" t="n">
         <v>875</v>
       </c>
       <c r="O10" t="n">
-        <v>1495</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="11">
@@ -61275,7 +61275,7 @@
         <v>2730</v>
       </c>
       <c r="I11" t="n">
-        <v>5210</v>
+        <v>5960</v>
       </c>
       <c r="J11" t="n">
         <v>2880</v>
@@ -61287,13 +61287,13 @@
         <v>2690</v>
       </c>
       <c r="M11" t="n">
-        <v>18471</v>
+        <v>18611</v>
       </c>
       <c r="N11" t="n">
         <v>31755</v>
       </c>
       <c r="O11" t="n">
-        <v>118182</v>
+        <v>119072</v>
       </c>
     </row>
   </sheetData>
@@ -71550,16 +71550,16 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>135</v>
+        <v>435</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="S142" t="n">
-        <v>3294</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="143">
@@ -71611,16 +71611,16 @@
         <v>24816</v>
       </c>
       <c r="P143" t="n">
-        <v>430740</v>
+        <v>431040</v>
       </c>
       <c r="Q143" t="n">
         <v>36784</v>
       </c>
       <c r="R143" t="n">
-        <v>90560</v>
+        <v>91480</v>
       </c>
       <c r="S143" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>
@@ -79794,7 +79794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81142,129 +81142,139 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>50182</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="B136" t="n">
+        <v>50932</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B138" t="n">
-        <v>1867</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B139" t="n">
-        <v>2625</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B140" t="n">
-        <v>3270</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B141" t="n">
-        <v>3960</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B142" t="n">
-        <v>4420</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B143" t="n">
-        <v>3140</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B144" t="n">
-        <v>3010</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B145" t="n">
-        <v>3854</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B146" t="n">
-        <v>5282</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B147" t="n">
-        <v>6515</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="n">
-        <v>7029</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="n">
+        <v>7029</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
         <v>2026</v>
       </c>
-      <c r="B149" t="n">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="B150" t="n">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>50182</v>
+      <c r="B151" t="n">
+        <v>50932</v>
       </c>
     </row>
   </sheetData>
@@ -90409,7 +90419,7 @@
         <v>875</v>
       </c>
       <c r="C142" t="n">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -90427,7 +90437,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1799</v>
+        <v>2129</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -90445,10 +90455,10 @@
         <v>475</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="P142" t="n">
-        <v>3294</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="143">
@@ -90461,7 +90471,7 @@
         <v>406251</v>
       </c>
       <c r="C143" t="n">
-        <v>227444</v>
+        <v>227584</v>
       </c>
       <c r="D143" t="n">
         <v>59882</v>
@@ -90479,7 +90489,7 @@
         <v>6860</v>
       </c>
       <c r="I143" t="n">
-        <v>770067</v>
+        <v>770397</v>
       </c>
       <c r="J143" t="n">
         <v>223786</v>
@@ -90497,10 +90507,10 @@
         <v>72682</v>
       </c>
       <c r="O143" t="n">
-        <v>50182</v>
+        <v>50932</v>
       </c>
       <c r="P143" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>
@@ -91936,7 +91946,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>55</v>
+        <v>195</v>
       </c>
     </row>
     <row r="143">
@@ -91946,7 +91956,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>227444</v>
+        <v>227584</v>
       </c>
     </row>
     <row r="145">
@@ -92054,7 +92064,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>18471</v>
+        <v>18611</v>
       </c>
     </row>
     <row r="158">
@@ -92064,7 +92074,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>227444</v>
+        <v>227584</v>
       </c>
     </row>
   </sheetData>
@@ -98433,7 +98443,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6259</v>
+        <v>6399</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -98451,7 +98461,7 @@
         <v>1665</v>
       </c>
       <c r="K13" t="n">
-        <v>1700</v>
+        <v>1845</v>
       </c>
       <c r="L13" t="n">
         <v>1075</v>
@@ -98670,13 +98680,13 @@
         <v>30</v>
       </c>
       <c r="CF13" t="n">
-        <v>2925</v>
+        <v>3225</v>
       </c>
       <c r="CG13" t="n">
         <v>517</v>
       </c>
       <c r="CH13" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -98775,7 +98785,7 @@
         <v>380</v>
       </c>
       <c r="DO13" t="n">
-        <v>595</v>
+        <v>755</v>
       </c>
       <c r="DP13" t="n">
         <v>5811</v>
@@ -98790,10 +98800,10 @@
         <v>355</v>
       </c>
       <c r="DT13" t="n">
-        <v>2285</v>
+        <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>204633</v>
+        <v>205853</v>
       </c>
     </row>
     <row r="14">
@@ -98812,7 +98822,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>72940</v>
+        <v>73080</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -98830,7 +98840,7 @@
         <v>22638</v>
       </c>
       <c r="K14" t="n">
-        <v>17625</v>
+        <v>17770</v>
       </c>
       <c r="L14" t="n">
         <v>6040</v>
@@ -99049,13 +99059,13 @@
         <v>145</v>
       </c>
       <c r="CF14" t="n">
-        <v>22031</v>
+        <v>22331</v>
       </c>
       <c r="CG14" t="n">
         <v>3692</v>
       </c>
       <c r="CH14" t="n">
-        <v>1665</v>
+        <v>1690</v>
       </c>
       <c r="CI14" t="n">
         <v>470</v>
@@ -99154,7 +99164,7 @@
         <v>3025</v>
       </c>
       <c r="DO14" t="n">
-        <v>7925</v>
+        <v>8085</v>
       </c>
       <c r="DP14" t="n">
         <v>59100</v>
@@ -99169,10 +99179,10 @@
         <v>5007</v>
       </c>
       <c r="DT14" t="n">
-        <v>28151</v>
+        <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>
@@ -99982,16 +99992,16 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>36291</v>
+        <v>36591</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
       </c>
       <c r="R13" t="n">
-        <v>11227</v>
+        <v>12147</v>
       </c>
       <c r="S13" t="n">
-        <v>204633</v>
+        <v>205853</v>
       </c>
     </row>
     <row r="14">
@@ -100043,16 +100053,16 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>430740</v>
+        <v>431040</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
       </c>
       <c r="R14" t="n">
-        <v>90560</v>
+        <v>91480</v>
       </c>
       <c r="S14" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>
@@ -100709,7 +100719,7 @@
         <v>31755</v>
       </c>
       <c r="C13" t="n">
-        <v>18471</v>
+        <v>18611</v>
       </c>
       <c r="D13" t="n">
         <v>5825</v>
@@ -100727,7 +100737,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>86451</v>
+        <v>86781</v>
       </c>
       <c r="J13" t="n">
         <v>19715</v>
@@ -100745,10 +100755,10 @@
         <v>6900</v>
       </c>
       <c r="O13" t="n">
-        <v>5210</v>
+        <v>5960</v>
       </c>
       <c r="P13" t="n">
-        <v>204633</v>
+        <v>205853</v>
       </c>
     </row>
     <row r="14">
@@ -100761,7 +100771,7 @@
         <v>406251</v>
       </c>
       <c r="C14" t="n">
-        <v>227444</v>
+        <v>227584</v>
       </c>
       <c r="D14" t="n">
         <v>59882</v>
@@ -100779,7 +100789,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>770067</v>
+        <v>770397</v>
       </c>
       <c r="J14" t="n">
         <v>223786</v>
@@ -100797,10 +100807,10 @@
         <v>72682</v>
       </c>
       <c r="O14" t="n">
-        <v>50182</v>
+        <v>50932</v>
       </c>
       <c r="P14" t="n">
-        <v>2123400</v>
+        <v>2124620</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54182,7 +54182,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -54464,10 +54464,10 @@
         <v>0</v>
       </c>
       <c r="DF142" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="DG142" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="DH142" t="n">
         <v>80</v>
@@ -54509,7 +54509,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>4514</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="143">
@@ -54561,7 +54561,7 @@
         <v>5784</v>
       </c>
       <c r="P143" t="n">
-        <v>6845</v>
+        <v>6990</v>
       </c>
       <c r="Q143" t="n">
         <v>105</v>
@@ -54843,10 +54843,10 @@
         <v>21351</v>
       </c>
       <c r="DF143" t="n">
-        <v>38674</v>
+        <v>39089</v>
       </c>
       <c r="DG143" t="n">
-        <v>24333</v>
+        <v>24443</v>
       </c>
       <c r="DH143" t="n">
         <v>101888</v>
@@ -54888,7 +54888,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>
@@ -61211,7 +61211,7 @@
         <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -61244,7 +61244,7 @@
         <v>875</v>
       </c>
       <c r="O10" t="n">
-        <v>2385</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="11">
@@ -61260,7 +61260,7 @@
         <v>7385</v>
       </c>
       <c r="D11" t="n">
-        <v>6665</v>
+        <v>7190</v>
       </c>
       <c r="E11" t="n">
         <v>5626</v>
@@ -61293,7 +61293,7 @@
         <v>31755</v>
       </c>
       <c r="O11" t="n">
-        <v>119072</v>
+        <v>119597</v>
       </c>
     </row>
   </sheetData>
@@ -71508,7 +71508,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -71550,7 +71550,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>435</v>
+        <v>960</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -71559,7 +71559,7 @@
         <v>920</v>
       </c>
       <c r="S142" t="n">
-        <v>4514</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="143">
@@ -71569,7 +71569,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>79857</v>
+        <v>80002</v>
       </c>
       <c r="C143" t="n">
         <v>18179</v>
@@ -71611,7 +71611,7 @@
         <v>24816</v>
       </c>
       <c r="P143" t="n">
-        <v>431040</v>
+        <v>431565</v>
       </c>
       <c r="Q143" t="n">
         <v>36784</v>
@@ -71620,7 +71620,7 @@
         <v>91480</v>
       </c>
       <c r="S143" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>
@@ -73198,7 +73198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74496,129 +74496,139 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>63007</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="B131" t="n">
+        <v>63532</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B133" t="n">
-        <v>337</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B134" t="n">
-        <v>2431</v>
+        <v>337</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B135" t="n">
-        <v>2574</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B136" t="n">
-        <v>2985</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B137" t="n">
-        <v>4530</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B138" t="n">
-        <v>5425</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B139" t="n">
-        <v>6245</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B140" t="n">
-        <v>6030</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B141" t="n">
-        <v>7580</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B142" t="n">
-        <v>8604</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B143" t="n">
-        <v>9601</v>
+        <v>8604</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B144" t="n">
+        <v>9601</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
         <v>2026</v>
       </c>
-      <c r="B144" t="n">
-        <v>6665</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="B145" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B145" t="n">
-        <v>63007</v>
+      <c r="B146" t="n">
+        <v>63532</v>
       </c>
     </row>
   </sheetData>
@@ -90437,7 +90447,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>2129</v>
+        <v>2274</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -90446,7 +90456,7 @@
         <v>10</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="M142" t="n">
         <v>80</v>
@@ -90458,7 +90468,7 @@
         <v>750</v>
       </c>
       <c r="P142" t="n">
-        <v>4514</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="143">
@@ -90489,7 +90499,7 @@
         <v>6860</v>
       </c>
       <c r="I143" t="n">
-        <v>770397</v>
+        <v>770542</v>
       </c>
       <c r="J143" t="n">
         <v>223786</v>
@@ -90498,7 +90508,7 @@
         <v>32945</v>
       </c>
       <c r="L143" t="n">
-        <v>63007</v>
+        <v>63532</v>
       </c>
       <c r="M143" t="n">
         <v>101888</v>
@@ -90510,7 +90520,7 @@
         <v>50932</v>
       </c>
       <c r="P143" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>
@@ -98476,7 +98486,7 @@
         <v>70</v>
       </c>
       <c r="P13" t="n">
-        <v>810</v>
+        <v>955</v>
       </c>
       <c r="Q13" t="n">
         <v>105</v>
@@ -98758,10 +98768,10 @@
         <v>1840</v>
       </c>
       <c r="DF13" t="n">
-        <v>4000</v>
+        <v>4415</v>
       </c>
       <c r="DG13" t="n">
-        <v>2665</v>
+        <v>2775</v>
       </c>
       <c r="DH13" t="n">
         <v>7385</v>
@@ -98803,7 +98813,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>205853</v>
+        <v>206523</v>
       </c>
     </row>
     <row r="14">
@@ -98855,7 +98865,7 @@
         <v>5784</v>
       </c>
       <c r="P14" t="n">
-        <v>6845</v>
+        <v>6990</v>
       </c>
       <c r="Q14" t="n">
         <v>105</v>
@@ -99137,10 +99147,10 @@
         <v>21351</v>
       </c>
       <c r="DF14" t="n">
-        <v>38674</v>
+        <v>39089</v>
       </c>
       <c r="DG14" t="n">
-        <v>24333</v>
+        <v>24443</v>
       </c>
       <c r="DH14" t="n">
         <v>101888</v>
@@ -99182,7 +99192,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>
@@ -99950,7 +99960,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>6816</v>
+        <v>6961</v>
       </c>
       <c r="C13" t="n">
         <v>2925</v>
@@ -99992,7 +100002,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>36591</v>
+        <v>37116</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -100001,7 +100011,7 @@
         <v>12147</v>
       </c>
       <c r="S13" t="n">
-        <v>205853</v>
+        <v>206523</v>
       </c>
     </row>
     <row r="14">
@@ -100011,7 +100021,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79857</v>
+        <v>80002</v>
       </c>
       <c r="C14" t="n">
         <v>18179</v>
@@ -100053,7 +100063,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>431040</v>
+        <v>431565</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -100062,7 +100072,7 @@
         <v>91480</v>
       </c>
       <c r="S14" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>
@@ -100737,7 +100747,7 @@
         <v>2690</v>
       </c>
       <c r="I13" t="n">
-        <v>86781</v>
+        <v>86926</v>
       </c>
       <c r="J13" t="n">
         <v>19715</v>
@@ -100746,7 +100756,7 @@
         <v>2730</v>
       </c>
       <c r="L13" t="n">
-        <v>6665</v>
+        <v>7190</v>
       </c>
       <c r="M13" t="n">
         <v>7385</v>
@@ -100758,7 +100768,7 @@
         <v>5960</v>
       </c>
       <c r="P13" t="n">
-        <v>205853</v>
+        <v>206523</v>
       </c>
     </row>
     <row r="14">
@@ -100789,7 +100799,7 @@
         <v>6860</v>
       </c>
       <c r="I14" t="n">
-        <v>770397</v>
+        <v>770542</v>
       </c>
       <c r="J14" t="n">
         <v>223786</v>
@@ -100798,7 +100808,7 @@
         <v>32945</v>
       </c>
       <c r="L14" t="n">
-        <v>63007</v>
+        <v>63532</v>
       </c>
       <c r="M14" t="n">
         <v>101888</v>
@@ -100810,7 +100820,7 @@
         <v>50932</v>
       </c>
       <c r="P14" t="n">
-        <v>2124620</v>
+        <v>2125290</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54188,7 +54188,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>885</v>
+        <v>1800</v>
       </c>
       <c r="S142" t="n">
         <v>20</v>
@@ -54509,7 +54509,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>5184</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="143">
@@ -54567,7 +54567,7 @@
         <v>105</v>
       </c>
       <c r="R143" t="n">
-        <v>439196</v>
+        <v>440111</v>
       </c>
       <c r="S143" t="n">
         <v>995</v>
@@ -54888,7 +54888,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>
@@ -61241,10 +61241,10 @@
         <v>195</v>
       </c>
       <c r="N10" t="n">
-        <v>875</v>
+        <v>1790</v>
       </c>
       <c r="O10" t="n">
-        <v>2910</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="11">
@@ -61290,10 +61290,10 @@
         <v>18611</v>
       </c>
       <c r="N11" t="n">
-        <v>31755</v>
+        <v>32670</v>
       </c>
       <c r="O11" t="n">
-        <v>119597</v>
+        <v>120512</v>
       </c>
     </row>
   </sheetData>
@@ -71517,7 +71517,7 @@
         <v>325</v>
       </c>
       <c r="E142" t="n">
-        <v>1940</v>
+        <v>2855</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -71559,7 +71559,7 @@
         <v>920</v>
       </c>
       <c r="S142" t="n">
-        <v>5184</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="143">
@@ -71578,7 +71578,7 @@
         <v>64162</v>
       </c>
       <c r="E143" t="n">
-        <v>875479</v>
+        <v>876394</v>
       </c>
       <c r="F143" t="n">
         <v>6157</v>
@@ -71620,7 +71620,7 @@
         <v>91480</v>
       </c>
       <c r="S143" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>
@@ -90426,7 +90426,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>875</v>
+        <v>1790</v>
       </c>
       <c r="C142" t="n">
         <v>195</v>
@@ -90468,7 +90468,7 @@
         <v>750</v>
       </c>
       <c r="P142" t="n">
-        <v>5184</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="143">
@@ -90478,7 +90478,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>406251</v>
+        <v>407166</v>
       </c>
       <c r="C143" t="n">
         <v>227584</v>
@@ -90520,7 +90520,7 @@
         <v>50932</v>
       </c>
       <c r="P143" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>
@@ -93520,7 +93520,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>875</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="143">
@@ -93530,7 +93530,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>406251</v>
+        <v>407166</v>
       </c>
     </row>
     <row r="145">
@@ -93638,7 +93638,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>31755</v>
+        <v>32670</v>
       </c>
     </row>
     <row r="158">
@@ -93648,7 +93648,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>406251</v>
+        <v>407166</v>
       </c>
     </row>
   </sheetData>
@@ -98492,7 +98492,7 @@
         <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>34485</v>
+        <v>35400</v>
       </c>
       <c r="S13" t="n">
         <v>210</v>
@@ -98813,7 +98813,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>206523</v>
+        <v>207438</v>
       </c>
     </row>
     <row r="14">
@@ -98871,7 +98871,7 @@
         <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>439196</v>
+        <v>440111</v>
       </c>
       <c r="S14" t="n">
         <v>995</v>
@@ -99192,7 +99192,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>
@@ -99969,7 +99969,7 @@
         <v>6850</v>
       </c>
       <c r="E13" t="n">
-        <v>84654</v>
+        <v>85569</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -100011,7 +100011,7 @@
         <v>12147</v>
       </c>
       <c r="S13" t="n">
-        <v>206523</v>
+        <v>207438</v>
       </c>
     </row>
     <row r="14">
@@ -100030,7 +100030,7 @@
         <v>64162</v>
       </c>
       <c r="E14" t="n">
-        <v>875479</v>
+        <v>876394</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -100072,7 +100072,7 @@
         <v>91480</v>
       </c>
       <c r="S14" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>
@@ -100726,7 +100726,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="n">
-        <v>31755</v>
+        <v>32670</v>
       </c>
       <c r="C13" t="n">
         <v>18611</v>
@@ -100768,7 +100768,7 @@
         <v>5960</v>
       </c>
       <c r="P13" t="n">
-        <v>206523</v>
+        <v>207438</v>
       </c>
     </row>
     <row r="14">
@@ -100778,7 +100778,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>406251</v>
+        <v>407166</v>
       </c>
       <c r="C14" t="n">
         <v>227584</v>
@@ -100820,7 +100820,7 @@
         <v>50932</v>
       </c>
       <c r="P14" t="n">
-        <v>2125290</v>
+        <v>2126205</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54150,7 +54150,7 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>140</v>
+        <v>711</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -54261,7 +54261,7 @@
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AQ142" t="n">
         <v>0</v>
@@ -54339,7 +54339,7 @@
         <v>0</v>
       </c>
       <c r="BP142" t="n">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="BQ142" t="n">
         <v>0</v>
@@ -54510,7 +54510,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>6099</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="143">
@@ -54529,7 +54529,7 @@
         <v>150</v>
       </c>
       <c r="E143" t="n">
-        <v>73080</v>
+        <v>73651</v>
       </c>
       <c r="F143" t="n">
         <v>500</v>
@@ -54640,7 +54640,7 @@
         <v>282</v>
       </c>
       <c r="AP143" t="n">
-        <v>2039</v>
+        <v>2074</v>
       </c>
       <c r="AQ143" t="n">
         <v>440</v>
@@ -54718,7 +54718,7 @@
         <v>7565</v>
       </c>
       <c r="BP143" t="n">
-        <v>96701</v>
+        <v>96956</v>
       </c>
       <c r="BQ143" t="n">
         <v>22615</v>
@@ -54889,7 +54889,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2126205</v>
+        <v>2127066</v>
       </c>
     </row>
   </sheetData>
@@ -61596,7 +61596,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>1056</v>
       </c>
       <c r="F10" t="n">
         <v>915</v>
@@ -61629,7 +61629,7 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5329</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="11">
@@ -61648,7 +61648,7 @@
         <v>27100</v>
       </c>
       <c r="E11" t="n">
-        <v>18791</v>
+        <v>19652</v>
       </c>
       <c r="F11" t="n">
         <v>17223</v>
@@ -61681,7 +61681,7 @@
         <v>2730</v>
       </c>
       <c r="P11" t="n">
-        <v>192830</v>
+        <v>193691</v>
       </c>
     </row>
   </sheetData>
@@ -71948,7 +71948,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>960</v>
+        <v>1821</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -71957,7 +71957,7 @@
         <v>920</v>
       </c>
       <c r="S142" t="n">
-        <v>6099</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="143">
@@ -72009,7 +72009,7 @@
         <v>24816</v>
       </c>
       <c r="P143" t="n">
-        <v>431565</v>
+        <v>432426</v>
       </c>
       <c r="Q143" t="n">
         <v>36784</v>
@@ -72018,7 +72018,7 @@
         <v>91480</v>
       </c>
       <c r="S143" t="n">
-        <v>2126205</v>
+        <v>2127066</v>
       </c>
     </row>
   </sheetData>
@@ -76332,7 +76332,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>195</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="143">
@@ -76342,7 +76342,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>229773</v>
+        <v>230634</v>
       </c>
     </row>
     <row r="145">
@@ -76450,7 +76450,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>18791</v>
+        <v>19652</v>
       </c>
     </row>
     <row r="158">
@@ -76460,7 +76460,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>229773</v>
+        <v>230634</v>
       </c>
     </row>
   </sheetData>
@@ -94302,7 +94302,7 @@
         <v>1940</v>
       </c>
       <c r="C142" t="n">
-        <v>195</v>
+        <v>1056</v>
       </c>
       <c r="D142" t="n">
         <v>920</v>
@@ -94344,7 +94344,7 @@
         <v>80</v>
       </c>
       <c r="Q142" t="n">
-        <v>6109</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="143">
@@ -94357,7 +94357,7 @@
         <v>506963</v>
       </c>
       <c r="C143" t="n">
-        <v>229773</v>
+        <v>230634</v>
       </c>
       <c r="D143" t="n">
         <v>94155</v>
@@ -94399,7 +94399,7 @@
         <v>325674</v>
       </c>
       <c r="Q143" t="n">
-        <v>2159150</v>
+        <v>2160011</v>
       </c>
     </row>
   </sheetData>
@@ -102376,7 +102376,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6399</v>
+        <v>6970</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -102487,7 +102487,7 @@
         <v>117</v>
       </c>
       <c r="AP13" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="AQ13" t="n">
         <v>90</v>
@@ -102565,7 +102565,7 @@
         <v>535</v>
       </c>
       <c r="BP13" t="n">
-        <v>7595</v>
+        <v>7850</v>
       </c>
       <c r="BQ13" t="n">
         <v>2055</v>
@@ -102736,7 +102736,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>207438</v>
+        <v>208299</v>
       </c>
     </row>
     <row r="14">
@@ -102755,7 +102755,7 @@
         <v>150</v>
       </c>
       <c r="E14" t="n">
-        <v>73080</v>
+        <v>73651</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -102866,7 +102866,7 @@
         <v>282</v>
       </c>
       <c r="AP14" t="n">
-        <v>2039</v>
+        <v>2074</v>
       </c>
       <c r="AQ14" t="n">
         <v>440</v>
@@ -102944,7 +102944,7 @@
         <v>7565</v>
       </c>
       <c r="BP14" t="n">
-        <v>96701</v>
+        <v>96956</v>
       </c>
       <c r="BQ14" t="n">
         <v>22615</v>
@@ -103115,7 +103115,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2126205</v>
+        <v>2127066</v>
       </c>
     </row>
   </sheetData>
@@ -103925,7 +103925,7 @@
         <v>410</v>
       </c>
       <c r="P13" t="n">
-        <v>37116</v>
+        <v>37977</v>
       </c>
       <c r="Q13" t="n">
         <v>3380</v>
@@ -103934,7 +103934,7 @@
         <v>12147</v>
       </c>
       <c r="S13" t="n">
-        <v>207438</v>
+        <v>208299</v>
       </c>
     </row>
     <row r="14">
@@ -103986,7 +103986,7 @@
         <v>24816</v>
       </c>
       <c r="P14" t="n">
-        <v>431565</v>
+        <v>432426</v>
       </c>
       <c r="Q14" t="n">
         <v>36784</v>
@@ -103995,7 +103995,7 @@
         <v>91480</v>
       </c>
       <c r="S14" t="n">
-        <v>2126205</v>
+        <v>2127066</v>
       </c>
     </row>
   </sheetData>
@@ -104690,7 +104690,7 @@
         <v>41532</v>
       </c>
       <c r="C13" t="n">
-        <v>18791</v>
+        <v>19652</v>
       </c>
       <c r="D13" t="n">
         <v>10965</v>
@@ -104732,7 +104732,7 @@
         <v>27100</v>
       </c>
       <c r="Q13" t="n">
-        <v>210168</v>
+        <v>211029</v>
       </c>
     </row>
     <row r="14">
@@ -104745,7 +104745,7 @@
         <v>506963</v>
       </c>
       <c r="C14" t="n">
-        <v>229773</v>
+        <v>230634</v>
       </c>
       <c r="D14" t="n">
         <v>94155</v>
@@ -104787,7 +104787,7 @@
         <v>325674</v>
       </c>
       <c r="Q14" t="n">
-        <v>2159150</v>
+        <v>2160011</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -54144,7 +54144,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -54162,13 +54162,13 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -54315,10 +54315,10 @@
         <v>0</v>
       </c>
       <c r="BH142" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BI142" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BJ142" t="n">
         <v>0</v>
@@ -54372,7 +54372,7 @@
         <v>0</v>
       </c>
       <c r="CA142" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="CB142" t="n">
         <v>0</v>
@@ -54432,7 +54432,7 @@
         <v>0</v>
       </c>
       <c r="CU142" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CV142" t="n">
         <v>0</v>
@@ -54450,7 +54450,7 @@
         <v>0</v>
       </c>
       <c r="DA142" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="DB142" t="n">
         <v>0</v>
@@ -54483,7 +54483,7 @@
         <v>0</v>
       </c>
       <c r="DL142" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="DM142" t="n">
         <v>0</v>
@@ -54510,7 +54510,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>6960</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="143">
@@ -54523,7 +54523,7 @@
         <v>2692</v>
       </c>
       <c r="C143" t="n">
-        <v>995</v>
+        <v>1055</v>
       </c>
       <c r="D143" t="n">
         <v>150</v>
@@ -54541,13 +54541,13 @@
         <v>2718</v>
       </c>
       <c r="I143" t="n">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="J143" t="n">
         <v>22638</v>
       </c>
       <c r="K143" t="n">
-        <v>17770</v>
+        <v>17850</v>
       </c>
       <c r="L143" t="n">
         <v>6040</v>
@@ -54694,10 +54694,10 @@
         <v>1190</v>
       </c>
       <c r="BH143" t="n">
-        <v>13909</v>
+        <v>14144</v>
       </c>
       <c r="BI143" t="n">
-        <v>1070</v>
+        <v>1095</v>
       </c>
       <c r="BJ143" t="n">
         <v>660</v>
@@ -54751,7 +54751,7 @@
         <v>215</v>
       </c>
       <c r="CA143" t="n">
-        <v>3350</v>
+        <v>3445</v>
       </c>
       <c r="CB143" t="n">
         <v>435</v>
@@ -54811,7 +54811,7 @@
         <v>1310</v>
       </c>
       <c r="CU143" t="n">
-        <v>2736</v>
+        <v>2776</v>
       </c>
       <c r="CV143" t="n">
         <v>125</v>
@@ -54829,7 +54829,7 @@
         <v>223786</v>
       </c>
       <c r="DA143" t="n">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="DB143" t="n">
         <v>1351</v>
@@ -54862,7 +54862,7 @@
         <v>10780</v>
       </c>
       <c r="DL143" t="n">
-        <v>18616</v>
+        <v>18825</v>
       </c>
       <c r="DM143" t="n">
         <v>580</v>
@@ -54889,7 +54889,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2127066</v>
+        <v>2128005</v>
       </c>
     </row>
   </sheetData>
@@ -61602,7 +61602,7 @@
         <v>915</v>
       </c>
       <c r="G10" t="n">
-        <v>920</v>
+        <v>1209</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -61623,13 +61623,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>6190</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="11">
@@ -61654,7 +61654,7 @@
         <v>17223</v>
       </c>
       <c r="G11" t="n">
-        <v>10965</v>
+        <v>11254</v>
       </c>
       <c r="H11" t="n">
         <v>9059</v>
@@ -61675,13 +61675,13 @@
         <v>5825</v>
       </c>
       <c r="N11" t="n">
-        <v>3120</v>
+        <v>3575</v>
       </c>
       <c r="O11" t="n">
         <v>2730</v>
       </c>
       <c r="P11" t="n">
-        <v>193691</v>
+        <v>194435</v>
       </c>
     </row>
   </sheetData>
@@ -71909,7 +71909,7 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="D142" t="n">
         <v>325</v>
@@ -71936,7 +71936,7 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="M142" t="n">
         <v>134</v>
@@ -71945,19 +71945,19 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P142" t="n">
         <v>1821</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="R142" t="n">
-        <v>920</v>
+        <v>1040</v>
       </c>
       <c r="S142" t="n">
-        <v>6960</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="143">
@@ -71970,7 +71970,7 @@
         <v>80002</v>
       </c>
       <c r="C143" t="n">
-        <v>18179</v>
+        <v>18589</v>
       </c>
       <c r="D143" t="n">
         <v>64162</v>
@@ -71997,7 +71997,7 @@
         <v>115829</v>
       </c>
       <c r="L143" t="n">
-        <v>33332</v>
+        <v>33541</v>
       </c>
       <c r="M143" t="n">
         <v>6042</v>
@@ -72006,19 +72006,19 @@
         <v>42</v>
       </c>
       <c r="O143" t="n">
-        <v>24816</v>
+        <v>24911</v>
       </c>
       <c r="P143" t="n">
         <v>432426</v>
       </c>
       <c r="Q143" t="n">
-        <v>36784</v>
+        <v>36889</v>
       </c>
       <c r="R143" t="n">
-        <v>91480</v>
+        <v>91600</v>
       </c>
       <c r="S143" t="n">
-        <v>2127066</v>
+        <v>2128005</v>
       </c>
     </row>
   </sheetData>
@@ -79420,7 +79420,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>920</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="139">
@@ -79430,7 +79430,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>94155</v>
+        <v>94444</v>
       </c>
     </row>
     <row r="141">
@@ -79538,7 +79538,7 @@
         <v>2026</v>
       </c>
       <c r="B153" t="n">
-        <v>10965</v>
+        <v>11254</v>
       </c>
     </row>
     <row r="154">
@@ -79548,7 +79548,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>94155</v>
+        <v>94444</v>
       </c>
     </row>
   </sheetData>
@@ -94305,7 +94305,7 @@
         <v>1056</v>
       </c>
       <c r="D142" t="n">
-        <v>920</v>
+        <v>1209</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -94314,7 +94314,7 @@
         <v>324</v>
       </c>
       <c r="G142" t="n">
-        <v>780</v>
+        <v>975</v>
       </c>
       <c r="H142" t="n">
         <v>915</v>
@@ -94329,7 +94329,7 @@
         <v>145</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -94344,7 +94344,7 @@
         <v>80</v>
       </c>
       <c r="Q142" t="n">
-        <v>6970</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="143">
@@ -94360,7 +94360,7 @@
         <v>230634</v>
       </c>
       <c r="D143" t="n">
-        <v>94155</v>
+        <v>94444</v>
       </c>
       <c r="E143" t="n">
         <v>59882</v>
@@ -94369,7 +94369,7 @@
         <v>166576</v>
       </c>
       <c r="G143" t="n">
-        <v>171472</v>
+        <v>171667</v>
       </c>
       <c r="H143" t="n">
         <v>205766</v>
@@ -94384,7 +94384,7 @@
         <v>94683</v>
       </c>
       <c r="L143" t="n">
-        <v>25088</v>
+        <v>25543</v>
       </c>
       <c r="M143" t="n">
         <v>42955</v>
@@ -94399,7 +94399,7 @@
         <v>325674</v>
       </c>
       <c r="Q143" t="n">
-        <v>2160011</v>
+        <v>2160950</v>
       </c>
     </row>
   </sheetData>
@@ -95697,7 +95697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96525,113 +96525,123 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>25088</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="B84" t="n">
+        <v>25543</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Gallons</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B86" t="n">
-        <v>1085</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B87" t="n">
-        <v>1525</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B88" t="n">
-        <v>1000</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B89" t="n">
-        <v>730</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B90" t="n">
-        <v>1010</v>
+        <v>730</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B91" t="n">
-        <v>1615</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B92" t="n">
-        <v>4432</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B93" t="n">
-        <v>6194</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B94" t="n">
-        <v>4377</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
         <v>2026</v>
       </c>
-      <c r="B95" t="n">
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="B96" t="n">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>25088</v>
+      <c r="B97" t="n">
+        <v>25543</v>
       </c>
     </row>
   </sheetData>
@@ -102370,7 +102380,7 @@
         <v>490</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -102388,13 +102398,13 @@
         <v>150</v>
       </c>
       <c r="I13" t="n">
-        <v>595</v>
+        <v>745</v>
       </c>
       <c r="J13" t="n">
         <v>1665</v>
       </c>
       <c r="K13" t="n">
-        <v>1845</v>
+        <v>1925</v>
       </c>
       <c r="L13" t="n">
         <v>1075</v>
@@ -102541,10 +102551,10 @@
         <v>85</v>
       </c>
       <c r="BH13" t="n">
-        <v>1945</v>
+        <v>2180</v>
       </c>
       <c r="BI13" t="n">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="BJ13" t="n">
         <v>40</v>
@@ -102598,7 +102608,7 @@
         <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
@@ -102658,7 +102668,7 @@
         <v>125</v>
       </c>
       <c r="CU13" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="CV13" t="n">
         <v>125</v>
@@ -102676,7 +102686,7 @@
         <v>19715</v>
       </c>
       <c r="DA13" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="DB13" t="n">
         <v>153</v>
@@ -102709,7 +102719,7 @@
         <v>640</v>
       </c>
       <c r="DL13" t="n">
-        <v>2303</v>
+        <v>2512</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -102736,7 +102746,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>208299</v>
+        <v>209238</v>
       </c>
     </row>
     <row r="14">
@@ -102749,7 +102759,7 @@
         <v>2692</v>
       </c>
       <c r="C14" t="n">
-        <v>995</v>
+        <v>1055</v>
       </c>
       <c r="D14" t="n">
         <v>150</v>
@@ -102767,13 +102777,13 @@
         <v>2718</v>
       </c>
       <c r="I14" t="n">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="J14" t="n">
         <v>22638</v>
       </c>
       <c r="K14" t="n">
-        <v>17770</v>
+        <v>17850</v>
       </c>
       <c r="L14" t="n">
         <v>6040</v>
@@ -102920,10 +102930,10 @@
         <v>1190</v>
       </c>
       <c r="BH14" t="n">
-        <v>13909</v>
+        <v>14144</v>
       </c>
       <c r="BI14" t="n">
-        <v>1070</v>
+        <v>1095</v>
       </c>
       <c r="BJ14" t="n">
         <v>660</v>
@@ -102977,7 +102987,7 @@
         <v>215</v>
       </c>
       <c r="CA14" t="n">
-        <v>3350</v>
+        <v>3445</v>
       </c>
       <c r="CB14" t="n">
         <v>435</v>
@@ -103037,7 +103047,7 @@
         <v>1310</v>
       </c>
       <c r="CU14" t="n">
-        <v>2736</v>
+        <v>2776</v>
       </c>
       <c r="CV14" t="n">
         <v>125</v>
@@ -103055,7 +103065,7 @@
         <v>223786</v>
       </c>
       <c r="DA14" t="n">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="DB14" t="n">
         <v>1351</v>
@@ -103088,7 +103098,7 @@
         <v>10780</v>
       </c>
       <c r="DL14" t="n">
-        <v>18616</v>
+        <v>18825</v>
       </c>
       <c r="DM14" t="n">
         <v>580</v>
@@ -103115,7 +103125,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2127066</v>
+        <v>2128005</v>
       </c>
     </row>
   </sheetData>
@@ -103886,7 +103896,7 @@
         <v>6961</v>
       </c>
       <c r="C13" t="n">
-        <v>2925</v>
+        <v>3335</v>
       </c>
       <c r="D13" t="n">
         <v>6850</v>
@@ -103913,7 +103923,7 @@
         <v>13336</v>
       </c>
       <c r="L13" t="n">
-        <v>2694</v>
+        <v>2903</v>
       </c>
       <c r="M13" t="n">
         <v>1129</v>
@@ -103922,19 +103932,19 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>410</v>
+        <v>505</v>
       </c>
       <c r="P13" t="n">
         <v>37977</v>
       </c>
       <c r="Q13" t="n">
-        <v>3380</v>
+        <v>3485</v>
       </c>
       <c r="R13" t="n">
-        <v>12147</v>
+        <v>12267</v>
       </c>
       <c r="S13" t="n">
-        <v>208299</v>
+        <v>209238</v>
       </c>
     </row>
     <row r="14">
@@ -103947,7 +103957,7 @@
         <v>80002</v>
       </c>
       <c r="C14" t="n">
-        <v>18179</v>
+        <v>18589</v>
       </c>
       <c r="D14" t="n">
         <v>64162</v>
@@ -103974,7 +103984,7 @@
         <v>115829</v>
       </c>
       <c r="L14" t="n">
-        <v>33332</v>
+        <v>33541</v>
       </c>
       <c r="M14" t="n">
         <v>6042</v>
@@ -103983,19 +103993,19 @@
         <v>42</v>
       </c>
       <c r="O14" t="n">
-        <v>24816</v>
+        <v>24911</v>
       </c>
       <c r="P14" t="n">
         <v>432426</v>
       </c>
       <c r="Q14" t="n">
-        <v>36784</v>
+        <v>36889</v>
       </c>
       <c r="R14" t="n">
-        <v>91480</v>
+        <v>91600</v>
       </c>
       <c r="S14" t="n">
-        <v>2127066</v>
+        <v>2128005</v>
       </c>
     </row>
   </sheetData>
@@ -104693,7 +104703,7 @@
         <v>19652</v>
       </c>
       <c r="D13" t="n">
-        <v>10965</v>
+        <v>11254</v>
       </c>
       <c r="E13" t="n">
         <v>5825</v>
@@ -104702,7 +104712,7 @@
         <v>28499</v>
       </c>
       <c r="G13" t="n">
-        <v>17338</v>
+        <v>17533</v>
       </c>
       <c r="H13" t="n">
         <v>17223</v>
@@ -104717,7 +104727,7 @@
         <v>8621</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>3575</v>
       </c>
       <c r="M13" t="n">
         <v>6055</v>
@@ -104732,7 +104742,7 @@
         <v>27100</v>
       </c>
       <c r="Q13" t="n">
-        <v>211029</v>
+        <v>211968</v>
       </c>
     </row>
     <row r="14">
@@ -104748,7 +104758,7 @@
         <v>230634</v>
       </c>
       <c r="D14" t="n">
-        <v>94155</v>
+        <v>94444</v>
       </c>
       <c r="E14" t="n">
         <v>59882</v>
@@ -104757,7 +104767,7 @@
         <v>166576</v>
       </c>
       <c r="G14" t="n">
-        <v>171472</v>
+        <v>171667</v>
       </c>
       <c r="H14" t="n">
         <v>205766</v>
@@ -104772,7 +104782,7 @@
         <v>94683</v>
       </c>
       <c r="L14" t="n">
-        <v>25088</v>
+        <v>25543</v>
       </c>
       <c r="M14" t="n">
         <v>42955</v>
@@ -104787,7 +104797,7 @@
         <v>325674</v>
       </c>
       <c r="Q14" t="n">
-        <v>2160011</v>
+        <v>2160950</v>
       </c>
     </row>
   </sheetData>

--- a/oil_collection_report.xlsx
+++ b/oil_collection_report.xlsx
@@ -48561,10 +48561,10 @@
         <v>326</v>
       </c>
       <c r="AK127" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
@@ -49319,10 +49319,10 @@
         <v>279</v>
       </c>
       <c r="AK129" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL129" t="n">
-        <v>1401</v>
+        <v>1501</v>
       </c>
       <c r="AM129" t="n">
         <v>145</v>
@@ -49698,10 +49698,10 @@
         <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>1100</v>
+        <v>1185</v>
       </c>
       <c r="AM130" t="n">
         <v>0</v>
@@ -50077,10 +50077,10 @@
         <v>294</v>
       </c>
       <c r="AK131" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AL131" t="n">
-        <v>1306</v>
+        <v>1396</v>
       </c>
       <c r="AM131" t="n">
         <v>110</v>
@@ -53488,10 +53488,10 @@
         <v>0</v>
       </c>
       <c r="AK140" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL140" t="n">
-        <v>746</v>
+        <v>801</v>
       </c>
       <c r="AM140" t="n">
         <v>0</v>
@@ -53867,10 +53867,10 @@
         <v>247</v>
       </c>
       <c r="AK141" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL141" t="n">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="AM141" t="n">
         <v>0</v>
@@ -54249,7 +54249,7 @@
         <v>0</v>
       </c>
       <c r="AL142" t="n">
-        <v>440</v>
+        <v>1735</v>
       </c>
       <c r="AM142" t="n">
         <v>0</v>
@@ -54501,7 +54501,7 @@
         <v>0</v>
       </c>
       <c r="DR142" t="n">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="DS142" t="n">
         <v>0</v>
@@ -54510,7 +54510,7 @@
         <v>450</v>
       </c>
       <c r="DU142" t="n">
-        <v>7899</v>
+        <v>9239</v>
       </c>
     </row>
     <row r="143">
@@ -54625,10 +54625,10 @@
         <v>12605</v>
       </c>
       <c r="AK143" t="n">
-        <v>477</v>
+        <v>62</v>
       </c>
       <c r="AL143" t="n">
-        <v>52008</v>
+        <v>53718</v>
       </c>
       <c r="AM143" t="n">
         <v>4755</v>
@@ -54880,7 +54880,7 @@
         <v>1450</v>
       </c>
       <c r="DR143" t="n">
-        <v>72682</v>
+        <v>72727</v>
       </c>
       <c r="DS143" t="n">
         <v>5007</v>
@@ -54889,7 +54889,7 @@
         <v>28601</v>
       </c>
       <c r="DU143" t="n">
-        <v>2128005</v>
+        <v>2129345</v>
       </c>
     </row>
   </sheetData>
@@ -61599,7 +61599,7 @@
         <v>1056</v>
       </c>
       <c r="F10" t="n">
-        <v>915</v>
+        <v>2255</v>
       </c>
       <c r="G10" t="n">
         <v>1209</v>
@@ -61629,7 +61629,7 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>6934</v>
+        <v>8274</v>
       </c>
     </row>
     <row r="11">
@@ -61651,7 +61651,7 @@
         <v>19652</v>
       </c>
       <c r="F11" t="n">
-        <v>17223</v>
+        <v>18563</v>
       </c>
       <c r="G11" t="n">
         <v>11254</v>
@@ -61681,7 +61681,7 @@
         <v>2730</v>
       </c>
       <c r="P11" t="n">
-        <v>194435</v>
+        <v>195775</v>
       </c>
     </row>
   </sheetData>
@@ -71915,7 +71915,7 @@
         <v>325</v>
       </c>
       <c r="E142" t="n">
-        <v>2855</v>
+        <v>4195</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -71957,7 +71957,7 @@
         <v>1040</v>
       </c>
       <c r="S142" t="n">
-        <v>7899</v>
+        <v>9239</v>
       </c>
     </row>
     <row r="143">
@@ -71976,7 +71976,7 @@
         <v>64162</v>
       </c>
       <c r="E143" t="n">
-        <v>876394</v>
+        <v>877734</v>
       </c>
       <c r="F143" t="n">
         <v>6157</v>
@@ -72018,7 +72018,7 @@
         <v>91600</v>
       </c>
       <c r="S143" t="n">
-        <v>2128005</v>
+        <v>2129345</v>
       </c>
     </row>
   </sheetData>
@@ -77896,7 +77896,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>915</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="143">
@@ -77906,7 +77906,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>205766</v>
+        <v>207106</v>
       </c>
     </row>
     <row r="145">
@@ -78014,7 +78014,7 @@
         <v>2026</v>
       </c>
       <c r="B157" t="n">
-        <v>17223</v>
+        <v>18563</v>
       </c>
     </row>
     <row r="158">
@@ -78024,7 +78024,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>205766</v>
+        <v>207106</v>
       </c>
     </row>
   </sheetData>
@@ -94317,7 +94317,7 @@
         <v>975</v>
       </c>
       <c r="H142" t="n">
-        <v>915</v>
+        <v>2255</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -94344,7 +94344,7 @@
         <v>80</v>
       </c>
       <c r="Q142" t="n">
-        <v>7909</v>
+        <v>9249</v>
       </c>
     </row>
     <row r="143">
@@ -94372,7 +94372,7 @@
         <v>171667</v>
       </c>
       <c r="H143" t="n">
-        <v>205766</v>
+        <v>207106</v>
       </c>
       <c r="I143" t="n">
         <v>93618</v>
@@ -94399,7 +94399,7 @@
         <v>325674</v>
       </c>
       <c r="Q143" t="n">
-        <v>2160950</v>
+        <v>2162290</v>
       </c>
     </row>
   </sheetData>
@@ -102105,10 +102105,10 @@
         <v>1909</v>
       </c>
       <c r="AK12" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>7970</v>
+        <v>8280</v>
       </c>
       <c r="AM12" t="n">
         <v>400</v>
@@ -102482,10 +102482,10 @@
         <v>1311</v>
       </c>
       <c r="AK13" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>3467</v>
+        <v>4867</v>
       </c>
       <c r="AM13" t="n">
         <v>165</v>
@@ -102737,7 +102737,7 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>6900</v>
+        <v>6945</v>
       </c>
       <c r="DS13" t="n">
         <v>355</v>
@@ -102746,7 +102746,7 @@
         <v>2735</v>
       </c>
       <c r="DU13" t="n">
-        <v>209238</v>
+        <v>210578</v>
       </c>
     </row>
     <row r="14">
@@ -102861,10 +102861,10 @@
         <v>12605</v>
       </c>
       <c r="AK14" t="n">
-        <v>477</v>
+        <v>62</v>
       </c>
       <c r="AL14" t="n">
-        <v>52008</v>
+        <v>53718</v>
       </c>
       <c r="AM14" t="n">
         <v>4755</v>
@@ -103116,7 +103116,7 @@
         <v>1450</v>
       </c>
       <c r="DR14" t="n">
-        <v>72682</v>
+        <v>72727</v>
       </c>
       <c r="DS14" t="n">
         <v>5007</v>
@@ -103125,7 +103125,7 @@
         <v>28601</v>
       </c>
       <c r="DU14" t="n">
-        <v>2128005</v>
+        <v>2129345</v>
       </c>
     </row>
   </sheetData>
@@ -103902,7 +103902,7 @@
         <v>6850</v>
       </c>
       <c r="E13" t="n">
-        <v>85569</v>
+        <v>86909</v>
       </c>
       <c r="F13" t="n">
         <v>692</v>
@@ -103944,7 +103944,7 @@
         <v>12267</v>
       </c>
       <c r="S13" t="n">
-        <v>209238</v>
+        <v>210578</v>
       </c>
     </row>
     <row r="14">
@@ -103963,7 +103963,7 @@
         <v>64162</v>
       </c>
       <c r="E14" t="n">
-        <v>876394</v>
+        <v>877734</v>
       </c>
       <c r="F14" t="n">
         <v>6157</v>
@@ -104005,7 +104005,7 @@
         <v>91600</v>
       </c>
       <c r="S14" t="n">
-        <v>2128005</v>
+        <v>2129345</v>
       </c>
     </row>
   </sheetData>
@@ -104715,7 +104715,7 @@
         <v>17533</v>
       </c>
       <c r="H13" t="n">
-        <v>17223</v>
+        <v>18563</v>
       </c>
       <c r="I13" t="n">
         <v>9059</v>
@@ -104742,7 +104742,7 @@
         <v>27100</v>
       </c>
       <c r="Q13" t="n">
-        <v>211968</v>
+        <v>213308</v>
       </c>
     </row>
     <row r="14">
@@ -104770,7 +104770,7 @@
         <v>171667</v>
       </c>
       <c r="H14" t="n">
-        <v>205766</v>
+        <v>207106</v>
       </c>
       <c r="I14" t="n">
         <v>93618</v>
@@ -104797,7 +104797,7 @@
         <v>325674</v>
       </c>
       <c r="Q14" t="n">
-        <v>2160950</v>
+        <v>2162290</v>
       </c>
     </row>
   </sheetData>
